--- a/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4D240F5E-32DA-450F-9510-FE32B2915D81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8D4DC223-DFBF-418F-BB57-15A1955C50CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="907" uniqueCount="180">
   <si>
     <t>PSET_PN</t>
   </si>
@@ -277,262 +277,307 @@
     <t>POL</t>
   </si>
   <si>
-    <t>w112614319-400_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w112614319-400_POL</t>
+    <t>Gdynia_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Gdynia_POL</t>
   </si>
   <si>
     <t>en_gas_ccgt,en_gas_turbine,en_chp_gas_cc_ext,en_gas_ccs,en_coal_subcritical,en_coal_supercritical,en_coal_ultrasupercritical,en_coal_igcc,en_nuclear,en_nuclear_smr,en_biomass,en_chp_biomass_chips_ext,en_hop_gas_boiler,en_hop_biomass_chips,en_hop_electric_boiler,en_hp_air_10mw,en_chp_gas_cc_ext_ccs</t>
   </si>
   <si>
-    <t>w40946790-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w40946790-220_POL</t>
-  </si>
-  <si>
-    <t>w171917072-400_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w171917072-400_POL</t>
-  </si>
-  <si>
-    <t>PL15-400_POL</t>
-  </si>
-  <si>
-    <t>at grid node - PL15-400_POL</t>
-  </si>
-  <si>
-    <t>w87667718-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w87667718-220_POL</t>
-  </si>
-  <si>
-    <t>w199098053-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w199098053-220_POL</t>
-  </si>
-  <si>
-    <t>w44389929-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w44389929-220_POL</t>
-  </si>
-  <si>
-    <t>w121656686-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w121656686-220_POL</t>
-  </si>
-  <si>
-    <t>w245964556-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w245964556-220_POL</t>
-  </si>
-  <si>
-    <t>w183945016-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w183945016-220_POL</t>
-  </si>
-  <si>
-    <t>w39428977-400_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w39428977-400_POL</t>
-  </si>
-  <si>
-    <t>PL18-400_POL</t>
-  </si>
-  <si>
-    <t>at grid node - PL18-400_POL</t>
-  </si>
-  <si>
-    <t>w46092396-400_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w46092396-400_POL</t>
-  </si>
-  <si>
-    <t>w180535363-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w180535363-220_POL</t>
-  </si>
-  <si>
-    <t>w88544449-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w88544449-220_POL</t>
-  </si>
-  <si>
-    <t>w170316833-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w170316833-220_POL</t>
-  </si>
-  <si>
-    <t>w215282393-400_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w215282393-400_POL</t>
-  </si>
-  <si>
-    <t>w658600169-400_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w658600169-400_POL</t>
-  </si>
-  <si>
-    <t>w165763717-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w165763717-220_POL</t>
-  </si>
-  <si>
-    <t>w198635989-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w198635989-220_POL</t>
-  </si>
-  <si>
-    <t>PL46-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - PL46-220_POL</t>
-  </si>
-  <si>
-    <t>PL7-400_POL</t>
-  </si>
-  <si>
-    <t>at grid node - PL7-400_POL</t>
-  </si>
-  <si>
-    <t>PL36-400_POL</t>
-  </si>
-  <si>
-    <t>at grid node - PL36-400_POL</t>
-  </si>
-  <si>
-    <t>w158232924-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w158232924-220_POL</t>
-  </si>
-  <si>
-    <t>w170259740-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w170259740-220_POL</t>
-  </si>
-  <si>
-    <t>w216060722-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w216060722-220_POL</t>
-  </si>
-  <si>
-    <t>w293489607-400_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w293489607-400_POL</t>
-  </si>
-  <si>
-    <t>w255277953-400_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w255277953-400_POL</t>
-  </si>
-  <si>
-    <t>w111615226-380_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w111615226-380_POL</t>
+    <t>Katowice_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Katowice_POL</t>
+  </si>
+  <si>
+    <t>Radomsko_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Radomsko_POL</t>
+  </si>
+  <si>
+    <t>Poznan_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Poznan_POL</t>
+  </si>
+  <si>
+    <t>Krakow_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Krakow_POL</t>
+  </si>
+  <si>
+    <t>Mielec_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Mielec_POL</t>
+  </si>
+  <si>
+    <t>Lomza_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Lomza_POL</t>
+  </si>
+  <si>
+    <t>Wloclawek_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Wloclawek_POL</t>
+  </si>
+  <si>
+    <t>Konin_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Konin_POL</t>
+  </si>
+  <si>
+    <t>Sosnowiec_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Sosnowiec_POL</t>
+  </si>
+  <si>
+    <t>Bydgoszcz_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Bydgoszcz_POL</t>
+  </si>
+  <si>
+    <t>Szczecin_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Szczecin_POL</t>
+  </si>
+  <si>
+    <t>Gdansk_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Gdansk_POL</t>
+  </si>
+  <si>
+    <t>GorzowWielkopolski_POL</t>
+  </si>
+  <si>
+    <t>at grid node - GorzowWielkopolski_POL</t>
+  </si>
+  <si>
+    <t>Grudziadz_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Grudziadz_POL</t>
+  </si>
+  <si>
+    <t>Lubin_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Lubin_POL</t>
+  </si>
+  <si>
+    <t>Olesnica_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Olesnica_POL</t>
+  </si>
+  <si>
+    <t>Pulawy_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Pulawy_POL</t>
+  </si>
+  <si>
+    <t>PiotrkowTrybunalsk_POL</t>
+  </si>
+  <si>
+    <t>at grid node - PiotrkowTrybunalsk_POL</t>
+  </si>
+  <si>
+    <t>Rzeszow_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Rzeszow_POL</t>
+  </si>
+  <si>
+    <t>Plock_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Plock_POL</t>
+  </si>
+  <si>
+    <t>Police_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Police_POL</t>
+  </si>
+  <si>
+    <t>Debica_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Debica_POL</t>
+  </si>
+  <si>
+    <t>Wroclaw_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Wroclaw_POL</t>
+  </si>
+  <si>
+    <t>Warsaw_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Warsaw_POL</t>
+  </si>
+  <si>
+    <t>Kwidzyn_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Kwidzyn_POL</t>
+  </si>
+  <si>
+    <t>ZielonaGora_POL</t>
+  </si>
+  <si>
+    <t>at grid node - ZielonaGora_POL</t>
+  </si>
+  <si>
+    <t>Bialystok_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Bialystok_POL</t>
+  </si>
+  <si>
+    <t>BielskoBiala_POL</t>
+  </si>
+  <si>
+    <t>at grid node - BielskoBiala_POL</t>
+  </si>
+  <si>
+    <t>Czestochowa_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Czestochowa_POL</t>
+  </si>
+  <si>
+    <t>Gliwice_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Gliwice_POL</t>
+  </si>
+  <si>
+    <t>Opole_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Opole_POL</t>
+  </si>
+  <si>
+    <t>Boleslawiec_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Boleslawiec_POL</t>
   </si>
   <si>
     <t>EN_STG8hbNREL,EN_STG4hbNREL</t>
   </si>
   <si>
-    <t>w255314292_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w255314292_POL</t>
-  </si>
-  <si>
-    <t>w178838661-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w178838661-220_POL</t>
-  </si>
-  <si>
-    <t>w336990960-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w336990960-220_POL</t>
-  </si>
-  <si>
-    <t>w191038569-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w191038569-220_POL</t>
-  </si>
-  <si>
-    <t>w166838338-400_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w166838338-400_POL</t>
+    <t>Ustka_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Ustka_POL</t>
+  </si>
+  <si>
+    <t>Koszalin_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Koszalin_POL</t>
+  </si>
+  <si>
+    <t>KedzierzynKozle_POL</t>
+  </si>
+  <si>
+    <t>at grid node - KedzierzynKozle_POL</t>
+  </si>
+  <si>
+    <t>Swidnica_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Swidnica_POL</t>
+  </si>
+  <si>
+    <t>Tarnow_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Tarnow_POL</t>
+  </si>
+  <si>
+    <t>Krosno_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Krosno_POL</t>
   </si>
   <si>
     <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
   </si>
   <si>
-    <t>w101915790-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w101915790-220_POL</t>
-  </si>
-  <si>
-    <t>w303870256-400_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w303870256-400_POL</t>
-  </si>
-  <si>
-    <t>w254235846-400_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w254235846-400_POL</t>
-  </si>
-  <si>
-    <t>w199098050-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w199098050-220_POL</t>
-  </si>
-  <si>
-    <t>w173613665-220_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w173613665-220_POL</t>
-  </si>
-  <si>
-    <t>w194903381-400_POL</t>
-  </si>
-  <si>
-    <t>at grid node - w194903381-400_POL</t>
-  </si>
-  <si>
-    <t>PL34-400_POL</t>
-  </si>
-  <si>
-    <t>at grid node - PL34-400_POL</t>
+    <t>Legnica_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Legnica_POL</t>
+  </si>
+  <si>
+    <t>Chelm_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Chelm_POL</t>
+  </si>
+  <si>
+    <t>OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>at grid node - OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>Grajewo_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Grajewo_POL</t>
+  </si>
+  <si>
+    <t>Slupsk_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Slupsk_POL</t>
+  </si>
+  <si>
+    <t>Elk_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Elk_POL</t>
+  </si>
+  <si>
+    <t>Kielce_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Kielce_POL</t>
+  </si>
+  <si>
+    <t>Zamosc_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Zamosc_POL</t>
+  </si>
+  <si>
+    <t>Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Olsztyn_POL</t>
   </si>
   <si>
     <t>h_demand</t>
+  </si>
+  <si>
+    <t>en_hop_gas_boiler,en_hop_biomass_chips,en_hop_electric_boiler,en_hp_air_10mw</t>
   </si>
 </sst>
 </file>
@@ -860,15 +905,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{268E9BAB-B98F-4B82-9042-51EABC9ED525}">
-  <dimension ref="B3:T51"/>
+  <dimension ref="B3:Y58"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="3" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
         <v>21</v>
       </c>
@@ -876,7 +921,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="5" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
         <v>44</v>
       </c>
@@ -884,7 +929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="2:20" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
         <v>70</v>
       </c>
@@ -897,8 +942,11 @@
       <c r="Q9" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="10" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="V9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
         <v>32</v>
       </c>
@@ -947,8 +995,20 @@
       <c r="T10" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="11" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="V10" t="s">
+        <v>32</v>
+      </c>
+      <c r="W10" t="s">
+        <v>71</v>
+      </c>
+      <c r="X10" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
         <v>78</v>
       </c>
@@ -965,40 +1025,52 @@
         <v>78</v>
       </c>
       <c r="H11" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="I11" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="J11" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="L11" t="s">
         <v>78</v>
       </c>
       <c r="M11" t="s">
-        <v>94</v>
+        <v>130</v>
       </c>
       <c r="N11" t="s">
-        <v>95</v>
+        <v>131</v>
       </c>
       <c r="O11" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="Q11" t="s">
         <v>78</v>
       </c>
       <c r="R11" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="S11" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="T11" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="12" spans="2:20" x14ac:dyDescent="0.45">
+        <v>178</v>
+      </c>
+      <c r="V11" t="s">
+        <v>78</v>
+      </c>
+      <c r="W11" t="s">
+        <v>92</v>
+      </c>
+      <c r="X11" t="s">
+        <v>93</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="12" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
         <v>78</v>
       </c>
@@ -1015,40 +1087,52 @@
         <v>78</v>
       </c>
       <c r="H12" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="I12" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="J12" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="L12" t="s">
         <v>78</v>
       </c>
       <c r="M12" t="s">
-        <v>108</v>
+        <v>144</v>
       </c>
       <c r="N12" t="s">
-        <v>109</v>
+        <v>145</v>
       </c>
       <c r="O12" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="Q12" t="s">
         <v>78</v>
       </c>
       <c r="R12" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="S12" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="T12" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="13" spans="2:20" x14ac:dyDescent="0.45">
+        <v>178</v>
+      </c>
+      <c r="V12" t="s">
+        <v>78</v>
+      </c>
+      <c r="W12" t="s">
+        <v>130</v>
+      </c>
+      <c r="X12" t="s">
+        <v>131</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="13" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
         <v>78</v>
       </c>
@@ -1065,40 +1149,52 @@
         <v>78</v>
       </c>
       <c r="H13" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="I13" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="J13" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="L13" t="s">
         <v>78</v>
       </c>
       <c r="M13" t="s">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="N13" t="s">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="O13" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="Q13" t="s">
         <v>78</v>
       </c>
       <c r="R13" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="S13" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="T13" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="14" spans="2:20" x14ac:dyDescent="0.45">
+        <v>178</v>
+      </c>
+      <c r="V13" t="s">
+        <v>78</v>
+      </c>
+      <c r="W13" t="s">
+        <v>122</v>
+      </c>
+      <c r="X13" t="s">
+        <v>123</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="14" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
         <v>78</v>
       </c>
@@ -1121,34 +1217,46 @@
         <v>91</v>
       </c>
       <c r="J14" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="L14" t="s">
         <v>78</v>
       </c>
       <c r="M14" t="s">
-        <v>104</v>
+        <v>155</v>
       </c>
       <c r="N14" t="s">
-        <v>105</v>
+        <v>156</v>
       </c>
       <c r="O14" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="Q14" t="s">
         <v>78</v>
       </c>
       <c r="R14" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="S14" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="T14" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="15" spans="2:20" x14ac:dyDescent="0.45">
+        <v>178</v>
+      </c>
+      <c r="V14" t="s">
+        <v>78</v>
+      </c>
+      <c r="W14" t="s">
+        <v>134</v>
+      </c>
+      <c r="X14" t="s">
+        <v>135</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="15" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
         <v>78</v>
       </c>
@@ -1171,19 +1279,19 @@
         <v>80</v>
       </c>
       <c r="J15" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="L15" t="s">
         <v>78</v>
       </c>
       <c r="M15" t="s">
+        <v>142</v>
+      </c>
+      <c r="N15" t="s">
         <v>143</v>
       </c>
-      <c r="N15" t="s">
-        <v>144</v>
-      </c>
       <c r="O15" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="Q15" t="s">
         <v>78</v>
@@ -1195,10 +1303,22 @@
         <v>83</v>
       </c>
       <c r="T15" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="16" spans="2:20" x14ac:dyDescent="0.45">
+        <v>178</v>
+      </c>
+      <c r="V15" t="s">
+        <v>78</v>
+      </c>
+      <c r="W15" t="s">
+        <v>82</v>
+      </c>
+      <c r="X15" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="16" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
         <v>78</v>
       </c>
@@ -1221,19 +1341,19 @@
         <v>83</v>
       </c>
       <c r="J16" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="L16" t="s">
         <v>78</v>
       </c>
       <c r="M16" t="s">
-        <v>112</v>
+        <v>147</v>
       </c>
       <c r="N16" t="s">
-        <v>113</v>
+        <v>148</v>
       </c>
       <c r="O16" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="Q16" t="s">
         <v>78</v>
@@ -1245,10 +1365,22 @@
         <v>91</v>
       </c>
       <c r="T16" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="17" spans="2:20" x14ac:dyDescent="0.45">
+        <v>178</v>
+      </c>
+      <c r="V16" t="s">
+        <v>78</v>
+      </c>
+      <c r="W16" t="s">
+        <v>90</v>
+      </c>
+      <c r="X16" t="s">
+        <v>91</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="17" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
         <v>78</v>
       </c>
@@ -1271,34 +1403,46 @@
         <v>85</v>
       </c>
       <c r="J17" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="L17" t="s">
         <v>78</v>
       </c>
       <c r="M17" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="N17" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="O17" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="Q17" t="s">
         <v>78</v>
       </c>
       <c r="R17" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="S17" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="T17" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="18" spans="2:20" x14ac:dyDescent="0.45">
+        <v>178</v>
+      </c>
+      <c r="V17" t="s">
+        <v>78</v>
+      </c>
+      <c r="W17" t="s">
+        <v>104</v>
+      </c>
+      <c r="X17" t="s">
+        <v>105</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="18" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
         <v>78</v>
       </c>
@@ -1321,34 +1465,46 @@
         <v>87</v>
       </c>
       <c r="J18" t="s">
+        <v>146</v>
+      </c>
+      <c r="L18" t="s">
+        <v>78</v>
+      </c>
+      <c r="M18" t="s">
+        <v>108</v>
+      </c>
+      <c r="N18" t="s">
+        <v>109</v>
+      </c>
+      <c r="O18" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>78</v>
+      </c>
+      <c r="R18" t="s">
         <v>138</v>
       </c>
-      <c r="L18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M18" t="s">
-        <v>100</v>
-      </c>
-      <c r="N18" t="s">
-        <v>101</v>
-      </c>
-      <c r="O18" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>78</v>
-      </c>
-      <c r="R18" t="s">
-        <v>79</v>
-      </c>
       <c r="S18" t="s">
-        <v>80</v>
+        <v>139</v>
       </c>
       <c r="T18" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="19" spans="2:20" x14ac:dyDescent="0.45">
+        <v>178</v>
+      </c>
+      <c r="V18" t="s">
+        <v>78</v>
+      </c>
+      <c r="W18" t="s">
+        <v>138</v>
+      </c>
+      <c r="X18" t="s">
+        <v>139</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="19" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B19" t="s">
         <v>78</v>
       </c>
@@ -1371,34 +1527,46 @@
         <v>89</v>
       </c>
       <c r="J19" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="L19" t="s">
         <v>78</v>
       </c>
       <c r="M19" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="N19" t="s">
-        <v>80</v>
+        <v>105</v>
       </c>
       <c r="O19" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="Q19" t="s">
         <v>78</v>
       </c>
       <c r="R19" t="s">
-        <v>130</v>
+        <v>96</v>
       </c>
       <c r="S19" t="s">
-        <v>131</v>
+        <v>97</v>
       </c>
       <c r="T19" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="20" spans="2:20" x14ac:dyDescent="0.45">
+        <v>178</v>
+      </c>
+      <c r="V19" t="s">
+        <v>78</v>
+      </c>
+      <c r="W19" t="s">
+        <v>96</v>
+      </c>
+      <c r="X19" t="s">
+        <v>97</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="20" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B20" t="s">
         <v>78</v>
       </c>
@@ -1421,34 +1589,46 @@
         <v>93</v>
       </c>
       <c r="J20" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="L20" t="s">
         <v>78</v>
       </c>
       <c r="M20" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="N20" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="O20" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="Q20" t="s">
         <v>78</v>
       </c>
       <c r="R20" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="S20" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="T20" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="21" spans="2:20" x14ac:dyDescent="0.45">
+        <v>178</v>
+      </c>
+      <c r="V20" t="s">
+        <v>78</v>
+      </c>
+      <c r="W20" t="s">
+        <v>98</v>
+      </c>
+      <c r="X20" t="s">
+        <v>99</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="21" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B21" t="s">
         <v>78</v>
       </c>
@@ -1471,34 +1651,46 @@
         <v>95</v>
       </c>
       <c r="J21" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="L21" t="s">
         <v>78</v>
       </c>
       <c r="M21" t="s">
-        <v>152</v>
+        <v>98</v>
       </c>
       <c r="N21" t="s">
-        <v>153</v>
+        <v>99</v>
       </c>
       <c r="O21" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="Q21" t="s">
         <v>78</v>
       </c>
       <c r="R21" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="S21" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="T21" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="22" spans="2:20" x14ac:dyDescent="0.45">
+        <v>178</v>
+      </c>
+      <c r="V21" t="s">
+        <v>78</v>
+      </c>
+      <c r="W21" t="s">
+        <v>100</v>
+      </c>
+      <c r="X21" t="s">
+        <v>101</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="22" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
         <v>78</v>
       </c>
@@ -1515,40 +1707,52 @@
         <v>78</v>
       </c>
       <c r="H22" t="s">
-        <v>96</v>
+        <v>138</v>
       </c>
       <c r="I22" t="s">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="J22" t="s">
+        <v>146</v>
+      </c>
+      <c r="L22" t="s">
+        <v>78</v>
+      </c>
+      <c r="M22" t="s">
         <v>138</v>
       </c>
-      <c r="L22" t="s">
-        <v>78</v>
-      </c>
-      <c r="M22" t="s">
-        <v>96</v>
-      </c>
       <c r="N22" t="s">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="O22" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="Q22" t="s">
         <v>78</v>
       </c>
       <c r="R22" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="S22" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="T22" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="23" spans="2:20" x14ac:dyDescent="0.45">
+        <v>178</v>
+      </c>
+      <c r="V22" t="s">
+        <v>78</v>
+      </c>
+      <c r="W22" t="s">
+        <v>102</v>
+      </c>
+      <c r="X22" t="s">
+        <v>103</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="23" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B23" t="s">
         <v>78</v>
       </c>
@@ -1565,40 +1769,52 @@
         <v>78</v>
       </c>
       <c r="H23" t="s">
-        <v>130</v>
+        <v>96</v>
       </c>
       <c r="I23" t="s">
-        <v>131</v>
+        <v>97</v>
       </c>
       <c r="J23" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="L23" t="s">
         <v>78</v>
       </c>
       <c r="M23" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="N23" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="O23" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="Q23" t="s">
         <v>78</v>
       </c>
       <c r="R23" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="S23" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="T23" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="24" spans="2:20" x14ac:dyDescent="0.45">
+        <v>178</v>
+      </c>
+      <c r="V23" t="s">
+        <v>78</v>
+      </c>
+      <c r="W23" t="s">
+        <v>106</v>
+      </c>
+      <c r="X23" t="s">
+        <v>107</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="24" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
         <v>78</v>
       </c>
@@ -1621,34 +1837,46 @@
         <v>99</v>
       </c>
       <c r="J24" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="L24" t="s">
         <v>78</v>
       </c>
       <c r="M24" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="N24" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="O24" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="Q24" t="s">
         <v>78</v>
       </c>
       <c r="R24" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="S24" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="T24" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="25" spans="2:20" x14ac:dyDescent="0.45">
+        <v>178</v>
+      </c>
+      <c r="V24" t="s">
+        <v>78</v>
+      </c>
+      <c r="W24" t="s">
+        <v>110</v>
+      </c>
+      <c r="X24" t="s">
+        <v>111</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="25" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B25" t="s">
         <v>78</v>
       </c>
@@ -1671,34 +1899,46 @@
         <v>101</v>
       </c>
       <c r="J25" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="L25" t="s">
         <v>78</v>
       </c>
       <c r="M25" t="s">
-        <v>156</v>
+        <v>86</v>
       </c>
       <c r="N25" t="s">
-        <v>157</v>
+        <v>87</v>
       </c>
       <c r="O25" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="Q25" t="s">
         <v>78</v>
       </c>
       <c r="R25" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="S25" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="T25" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="26" spans="2:20" x14ac:dyDescent="0.45">
+        <v>178</v>
+      </c>
+      <c r="V25" t="s">
+        <v>78</v>
+      </c>
+      <c r="W25" t="s">
+        <v>112</v>
+      </c>
+      <c r="X25" t="s">
+        <v>113</v>
+      </c>
+      <c r="Y25" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="26" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B26" t="s">
         <v>78</v>
       </c>
@@ -1721,19 +1961,19 @@
         <v>103</v>
       </c>
       <c r="J26" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="L26" t="s">
         <v>78</v>
       </c>
       <c r="M26" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="N26" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="O26" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="Q26" t="s">
         <v>78</v>
@@ -1745,10 +1985,22 @@
         <v>89</v>
       </c>
       <c r="T26" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="27" spans="2:20" x14ac:dyDescent="0.45">
+        <v>178</v>
+      </c>
+      <c r="V26" t="s">
+        <v>78</v>
+      </c>
+      <c r="W26" t="s">
+        <v>88</v>
+      </c>
+      <c r="X26" t="s">
+        <v>89</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="27" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B27" t="s">
         <v>78</v>
       </c>
@@ -1771,34 +2023,46 @@
         <v>105</v>
       </c>
       <c r="J27" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="L27" t="s">
         <v>78</v>
       </c>
       <c r="M27" t="s">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="N27" t="s">
-        <v>140</v>
+        <v>165</v>
       </c>
       <c r="O27" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="Q27" t="s">
         <v>78</v>
       </c>
       <c r="R27" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="S27" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="T27" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="28" spans="2:20" x14ac:dyDescent="0.45">
+        <v>178</v>
+      </c>
+      <c r="V27" t="s">
+        <v>78</v>
+      </c>
+      <c r="W27" t="s">
+        <v>116</v>
+      </c>
+      <c r="X27" t="s">
+        <v>117</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="28" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B28" t="s">
         <v>78</v>
       </c>
@@ -1821,34 +2085,46 @@
         <v>107</v>
       </c>
       <c r="J28" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="L28" t="s">
         <v>78</v>
       </c>
       <c r="M28" t="s">
-        <v>86</v>
+        <v>166</v>
       </c>
       <c r="N28" t="s">
-        <v>87</v>
+        <v>167</v>
       </c>
       <c r="O28" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="Q28" t="s">
         <v>78</v>
       </c>
       <c r="R28" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="S28" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="T28" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="29" spans="2:20" x14ac:dyDescent="0.45">
+        <v>178</v>
+      </c>
+      <c r="V28" t="s">
+        <v>78</v>
+      </c>
+      <c r="W28" t="s">
+        <v>118</v>
+      </c>
+      <c r="X28" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y28" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="29" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B29" t="s">
         <v>78</v>
       </c>
@@ -1871,34 +2147,46 @@
         <v>109</v>
       </c>
       <c r="J29" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="L29" t="s">
         <v>78</v>
       </c>
       <c r="M29" t="s">
-        <v>141</v>
+        <v>82</v>
       </c>
       <c r="N29" t="s">
-        <v>142</v>
+        <v>83</v>
       </c>
       <c r="O29" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="Q29" t="s">
         <v>78</v>
       </c>
       <c r="R29" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="S29" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="T29" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="30" spans="2:20" x14ac:dyDescent="0.45">
+        <v>178</v>
+      </c>
+      <c r="V29" t="s">
+        <v>78</v>
+      </c>
+      <c r="W29" t="s">
+        <v>120</v>
+      </c>
+      <c r="X29" t="s">
+        <v>121</v>
+      </c>
+      <c r="Y29" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="30" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B30" t="s">
         <v>78</v>
       </c>
@@ -1921,34 +2209,46 @@
         <v>111</v>
       </c>
       <c r="J30" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="L30" t="s">
         <v>78</v>
       </c>
       <c r="M30" t="s">
-        <v>145</v>
+        <v>94</v>
       </c>
       <c r="N30" t="s">
-        <v>146</v>
+        <v>95</v>
       </c>
       <c r="O30" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="Q30" t="s">
         <v>78</v>
       </c>
       <c r="R30" t="s">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="S30" t="s">
-        <v>119</v>
+        <v>87</v>
       </c>
       <c r="T30" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="31" spans="2:20" x14ac:dyDescent="0.45">
+        <v>178</v>
+      </c>
+      <c r="V30" t="s">
+        <v>78</v>
+      </c>
+      <c r="W30" t="s">
+        <v>86</v>
+      </c>
+      <c r="X30" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="31" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B31" t="s">
         <v>78</v>
       </c>
@@ -1971,34 +2271,46 @@
         <v>113</v>
       </c>
       <c r="J31" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="L31" t="s">
         <v>78</v>
       </c>
       <c r="M31" t="s">
-        <v>134</v>
+        <v>168</v>
       </c>
       <c r="N31" t="s">
-        <v>135</v>
+        <v>169</v>
       </c>
       <c r="O31" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="Q31" t="s">
         <v>78</v>
       </c>
       <c r="R31" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="S31" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="T31" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="32" spans="2:20" x14ac:dyDescent="0.45">
+        <v>178</v>
+      </c>
+      <c r="V31" t="s">
+        <v>78</v>
+      </c>
+      <c r="W31" t="s">
+        <v>124</v>
+      </c>
+      <c r="X31" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y31" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="32" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B32" t="s">
         <v>78</v>
       </c>
@@ -2021,34 +2333,46 @@
         <v>115</v>
       </c>
       <c r="J32" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="L32" t="s">
         <v>78</v>
       </c>
       <c r="M32" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="N32" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="O32" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="Q32" t="s">
         <v>78</v>
       </c>
       <c r="R32" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="S32" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="T32" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.45">
+        <v>178</v>
+      </c>
+      <c r="V32" t="s">
+        <v>78</v>
+      </c>
+      <c r="W32" t="s">
+        <v>126</v>
+      </c>
+      <c r="X32" t="s">
+        <v>127</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B33" t="s">
         <v>78</v>
       </c>
@@ -2065,40 +2389,52 @@
         <v>78</v>
       </c>
       <c r="H33" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="I33" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="J33" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="L33" t="s">
         <v>78</v>
       </c>
       <c r="M33" t="s">
-        <v>124</v>
+        <v>79</v>
       </c>
       <c r="N33" t="s">
-        <v>125</v>
+        <v>80</v>
       </c>
       <c r="O33" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="Q33" t="s">
         <v>78</v>
       </c>
       <c r="R33" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="S33" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="T33" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.45">
+        <v>178</v>
+      </c>
+      <c r="V33" t="s">
+        <v>78</v>
+      </c>
+      <c r="W33" t="s">
+        <v>114</v>
+      </c>
+      <c r="X33" t="s">
+        <v>115</v>
+      </c>
+      <c r="Y33" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B34" t="s">
         <v>78</v>
       </c>
@@ -2115,40 +2451,52 @@
         <v>78</v>
       </c>
       <c r="H34" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I34" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J34" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="L34" t="s">
         <v>78</v>
       </c>
       <c r="M34" t="s">
-        <v>118</v>
+        <v>153</v>
       </c>
       <c r="N34" t="s">
-        <v>119</v>
+        <v>154</v>
       </c>
       <c r="O34" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="Q34" t="s">
         <v>78</v>
       </c>
       <c r="R34" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="S34" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="T34" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.45">
+        <v>178</v>
+      </c>
+      <c r="V34" t="s">
+        <v>78</v>
+      </c>
+      <c r="W34" t="s">
+        <v>128</v>
+      </c>
+      <c r="X34" t="s">
+        <v>129</v>
+      </c>
+      <c r="Y34" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B35" t="s">
         <v>78</v>
       </c>
@@ -2165,40 +2513,52 @@
         <v>78</v>
       </c>
       <c r="H35" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="I35" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="J35" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="L35" t="s">
         <v>78</v>
       </c>
       <c r="M35" t="s">
-        <v>98</v>
+        <v>170</v>
       </c>
       <c r="N35" t="s">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="O35" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="Q35" t="s">
         <v>78</v>
       </c>
       <c r="R35" t="s">
-        <v>132</v>
+        <v>94</v>
       </c>
       <c r="S35" t="s">
-        <v>133</v>
+        <v>95</v>
       </c>
       <c r="T35" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="36" spans="2:20" x14ac:dyDescent="0.45">
+        <v>178</v>
+      </c>
+      <c r="V35" t="s">
+        <v>78</v>
+      </c>
+      <c r="W35" t="s">
+        <v>94</v>
+      </c>
+      <c r="X35" t="s">
+        <v>95</v>
+      </c>
+      <c r="Y35" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="36" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B36" t="s">
         <v>78</v>
       </c>
@@ -2215,40 +2575,52 @@
         <v>78</v>
       </c>
       <c r="H36" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="I36" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="J36" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="L36" t="s">
         <v>78</v>
       </c>
       <c r="M36" t="s">
-        <v>116</v>
+        <v>88</v>
       </c>
       <c r="N36" t="s">
-        <v>117</v>
+        <v>89</v>
       </c>
       <c r="O36" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="Q36" t="s">
         <v>78</v>
       </c>
       <c r="R36" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="S36" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="T36" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.45">
+        <v>178</v>
+      </c>
+      <c r="V36" t="s">
+        <v>78</v>
+      </c>
+      <c r="W36" t="s">
+        <v>132</v>
+      </c>
+      <c r="X36" t="s">
+        <v>133</v>
+      </c>
+      <c r="Y36" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B37" t="s">
         <v>78</v>
       </c>
@@ -2265,28 +2637,52 @@
         <v>78</v>
       </c>
       <c r="H37" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="I37" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="J37" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="L37" t="s">
         <v>78</v>
       </c>
       <c r="M37" t="s">
-        <v>84</v>
+        <v>172</v>
       </c>
       <c r="N37" t="s">
-        <v>85</v>
+        <v>173</v>
       </c>
       <c r="O37" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.45">
+        <v>159</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>78</v>
+      </c>
+      <c r="R37" t="s">
+        <v>136</v>
+      </c>
+      <c r="S37" t="s">
+        <v>137</v>
+      </c>
+      <c r="T37" t="s">
+        <v>178</v>
+      </c>
+      <c r="V37" t="s">
+        <v>78</v>
+      </c>
+      <c r="W37" t="s">
+        <v>136</v>
+      </c>
+      <c r="X37" t="s">
+        <v>137</v>
+      </c>
+      <c r="Y37" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="38" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B38" t="s">
         <v>78</v>
       </c>
@@ -2303,28 +2699,52 @@
         <v>78</v>
       </c>
       <c r="H38" t="s">
+        <v>128</v>
+      </c>
+      <c r="I38" t="s">
+        <v>129</v>
+      </c>
+      <c r="J38" t="s">
+        <v>146</v>
+      </c>
+      <c r="L38" t="s">
+        <v>78</v>
+      </c>
+      <c r="M38" t="s">
+        <v>134</v>
+      </c>
+      <c r="N38" t="s">
+        <v>135</v>
+      </c>
+      <c r="O38" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>78</v>
+      </c>
+      <c r="R38" t="s">
+        <v>140</v>
+      </c>
+      <c r="S38" t="s">
         <v>141</v>
       </c>
-      <c r="I38" t="s">
-        <v>142</v>
-      </c>
-      <c r="J38" t="s">
-        <v>138</v>
-      </c>
-      <c r="L38" t="s">
-        <v>78</v>
-      </c>
-      <c r="M38" t="s">
-        <v>132</v>
-      </c>
-      <c r="N38" t="s">
-        <v>133</v>
-      </c>
-      <c r="O38" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.45">
+      <c r="T38" t="s">
+        <v>178</v>
+      </c>
+      <c r="V38" t="s">
+        <v>78</v>
+      </c>
+      <c r="W38" t="s">
+        <v>140</v>
+      </c>
+      <c r="X38" t="s">
+        <v>141</v>
+      </c>
+      <c r="Y38" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B39" t="s">
         <v>78</v>
       </c>
@@ -2341,253 +2761,483 @@
         <v>78</v>
       </c>
       <c r="H39" t="s">
+        <v>132</v>
+      </c>
+      <c r="I39" t="s">
+        <v>133</v>
+      </c>
+      <c r="J39" t="s">
+        <v>146</v>
+      </c>
+      <c r="L39" t="s">
+        <v>78</v>
+      </c>
+      <c r="M39" t="s">
+        <v>110</v>
+      </c>
+      <c r="N39" t="s">
+        <v>111</v>
+      </c>
+      <c r="O39" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>78</v>
+      </c>
+      <c r="R39" t="s">
+        <v>144</v>
+      </c>
+      <c r="S39" t="s">
+        <v>145</v>
+      </c>
+      <c r="T39" t="s">
+        <v>178</v>
+      </c>
+      <c r="V39" t="s">
+        <v>78</v>
+      </c>
+      <c r="W39" t="s">
+        <v>144</v>
+      </c>
+      <c r="X39" t="s">
+        <v>145</v>
+      </c>
+      <c r="Y39" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.45">
+      <c r="B40" t="s">
+        <v>78</v>
+      </c>
+      <c r="C40" t="s">
+        <v>138</v>
+      </c>
+      <c r="D40" t="s">
+        <v>139</v>
+      </c>
+      <c r="E40" t="s">
+        <v>81</v>
+      </c>
+      <c r="G40" t="s">
+        <v>78</v>
+      </c>
+      <c r="H40" t="s">
+        <v>147</v>
+      </c>
+      <c r="I40" t="s">
+        <v>148</v>
+      </c>
+      <c r="J40" t="s">
+        <v>146</v>
+      </c>
+      <c r="L40" t="s">
+        <v>78</v>
+      </c>
+      <c r="M40" t="s">
+        <v>100</v>
+      </c>
+      <c r="N40" t="s">
+        <v>101</v>
+      </c>
+      <c r="O40" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.45">
+      <c r="B41" t="s">
+        <v>78</v>
+      </c>
+      <c r="C41" t="s">
+        <v>140</v>
+      </c>
+      <c r="D41" t="s">
+        <v>141</v>
+      </c>
+      <c r="E41" t="s">
+        <v>81</v>
+      </c>
+      <c r="G41" t="s">
+        <v>78</v>
+      </c>
+      <c r="H41" t="s">
+        <v>149</v>
+      </c>
+      <c r="I41" t="s">
+        <v>150</v>
+      </c>
+      <c r="J41" t="s">
+        <v>146</v>
+      </c>
+      <c r="L41" t="s">
+        <v>78</v>
+      </c>
+      <c r="M41" t="s">
+        <v>92</v>
+      </c>
+      <c r="N41" t="s">
+        <v>93</v>
+      </c>
+      <c r="O41" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.45">
+      <c r="B42" t="s">
+        <v>78</v>
+      </c>
+      <c r="C42" t="s">
+        <v>142</v>
+      </c>
+      <c r="D42" t="s">
         <v>143</v>
       </c>
-      <c r="I39" t="s">
+      <c r="E42" t="s">
+        <v>81</v>
+      </c>
+      <c r="G42" t="s">
+        <v>78</v>
+      </c>
+      <c r="H42" t="s">
+        <v>151</v>
+      </c>
+      <c r="I42" t="s">
+        <v>152</v>
+      </c>
+      <c r="J42" t="s">
+        <v>146</v>
+      </c>
+      <c r="L42" t="s">
+        <v>78</v>
+      </c>
+      <c r="M42" t="s">
+        <v>136</v>
+      </c>
+      <c r="N42" t="s">
+        <v>137</v>
+      </c>
+      <c r="O42" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.45">
+      <c r="B43" t="s">
+        <v>78</v>
+      </c>
+      <c r="C43" t="s">
         <v>144</v>
       </c>
-      <c r="J39" t="s">
-        <v>138</v>
-      </c>
-      <c r="L39" t="s">
-        <v>78</v>
-      </c>
-      <c r="M39" t="s">
-        <v>82</v>
-      </c>
-      <c r="N39" t="s">
-        <v>83</v>
-      </c>
-      <c r="O39" t="s">
+      <c r="D43" t="s">
+        <v>145</v>
+      </c>
+      <c r="E43" t="s">
+        <v>81</v>
+      </c>
+      <c r="G43" t="s">
+        <v>78</v>
+      </c>
+      <c r="H43" t="s">
+        <v>136</v>
+      </c>
+      <c r="I43" t="s">
+        <v>137</v>
+      </c>
+      <c r="J43" t="s">
+        <v>146</v>
+      </c>
+      <c r="L43" t="s">
+        <v>78</v>
+      </c>
+      <c r="M43" t="s">
+        <v>174</v>
+      </c>
+      <c r="N43" t="s">
+        <v>175</v>
+      </c>
+      <c r="O43" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.45">
+      <c r="G44" t="s">
+        <v>78</v>
+      </c>
+      <c r="H44" t="s">
+        <v>140</v>
+      </c>
+      <c r="I44" t="s">
+        <v>141</v>
+      </c>
+      <c r="J44" t="s">
+        <v>146</v>
+      </c>
+      <c r="L44" t="s">
+        <v>78</v>
+      </c>
+      <c r="M44" t="s">
+        <v>176</v>
+      </c>
+      <c r="N44" t="s">
+        <v>177</v>
+      </c>
+      <c r="O44" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.45">
+      <c r="G45" t="s">
+        <v>78</v>
+      </c>
+      <c r="H45" t="s">
+        <v>142</v>
+      </c>
+      <c r="I45" t="s">
+        <v>143</v>
+      </c>
+      <c r="J45" t="s">
+        <v>146</v>
+      </c>
+      <c r="L45" t="s">
+        <v>78</v>
+      </c>
+      <c r="M45" t="s">
+        <v>120</v>
+      </c>
+      <c r="N45" t="s">
+        <v>121</v>
+      </c>
+      <c r="O45" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.45">
+      <c r="G46" t="s">
+        <v>78</v>
+      </c>
+      <c r="H46" t="s">
+        <v>144</v>
+      </c>
+      <c r="I46" t="s">
+        <v>145</v>
+      </c>
+      <c r="J46" t="s">
+        <v>146</v>
+      </c>
+      <c r="L46" t="s">
+        <v>78</v>
+      </c>
+      <c r="M46" t="s">
+        <v>114</v>
+      </c>
+      <c r="N46" t="s">
+        <v>115</v>
+      </c>
+      <c r="O46" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.45">
+      <c r="G47" t="s">
+        <v>78</v>
+      </c>
+      <c r="H47" t="s">
+        <v>153</v>
+      </c>
+      <c r="I47" t="s">
+        <v>154</v>
+      </c>
+      <c r="J47" t="s">
+        <v>146</v>
+      </c>
+      <c r="L47" t="s">
+        <v>78</v>
+      </c>
+      <c r="M47" t="s">
+        <v>106</v>
+      </c>
+      <c r="N47" t="s">
+        <v>107</v>
+      </c>
+      <c r="O47" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.45">
+      <c r="G48" t="s">
+        <v>78</v>
+      </c>
+      <c r="H48" t="s">
+        <v>155</v>
+      </c>
+      <c r="I48" t="s">
+        <v>156</v>
+      </c>
+      <c r="J48" t="s">
+        <v>146</v>
+      </c>
+      <c r="L48" t="s">
+        <v>78</v>
+      </c>
+      <c r="M48" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="G40" t="s">
-        <v>78</v>
-      </c>
-      <c r="H40" t="s">
-        <v>132</v>
-      </c>
-      <c r="I40" t="s">
-        <v>133</v>
-      </c>
-      <c r="J40" t="s">
-        <v>138</v>
-      </c>
-      <c r="L40" t="s">
-        <v>78</v>
-      </c>
-      <c r="M40" t="s">
-        <v>136</v>
-      </c>
-      <c r="N40" t="s">
-        <v>137</v>
-      </c>
-      <c r="O40" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="G41" t="s">
-        <v>78</v>
-      </c>
-      <c r="H41" t="s">
-        <v>134</v>
-      </c>
-      <c r="I41" t="s">
-        <v>135</v>
-      </c>
-      <c r="J41" t="s">
-        <v>138</v>
-      </c>
-      <c r="L41" t="s">
-        <v>78</v>
-      </c>
-      <c r="M41" t="s">
-        <v>147</v>
-      </c>
-      <c r="N41" t="s">
-        <v>148</v>
-      </c>
-      <c r="O41" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="G42" t="s">
-        <v>78</v>
-      </c>
-      <c r="H42" t="s">
-        <v>136</v>
-      </c>
-      <c r="I42" t="s">
-        <v>137</v>
-      </c>
-      <c r="J42" t="s">
-        <v>138</v>
-      </c>
-      <c r="L42" t="s">
-        <v>78</v>
-      </c>
-      <c r="M42" t="s">
-        <v>88</v>
-      </c>
-      <c r="N42" t="s">
-        <v>89</v>
-      </c>
-      <c r="O42" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="G43" t="s">
-        <v>78</v>
-      </c>
-      <c r="H43" t="s">
-        <v>145</v>
-      </c>
-      <c r="I43" t="s">
+      <c r="N48" t="s">
+        <v>150</v>
+      </c>
+      <c r="O48" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="49" spans="7:15" x14ac:dyDescent="0.45">
+      <c r="G49" t="s">
+        <v>78</v>
+      </c>
+      <c r="H49" t="s">
+        <v>157</v>
+      </c>
+      <c r="I49" t="s">
+        <v>158</v>
+      </c>
+      <c r="J49" t="s">
         <v>146</v>
       </c>
-      <c r="J43" t="s">
-        <v>138</v>
-      </c>
-      <c r="L43" t="s">
-        <v>78</v>
-      </c>
-      <c r="M43" t="s">
+      <c r="L49" t="s">
+        <v>78</v>
+      </c>
+      <c r="M49" t="s">
+        <v>128</v>
+      </c>
+      <c r="N49" t="s">
+        <v>129</v>
+      </c>
+      <c r="O49" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="50" spans="7:15" x14ac:dyDescent="0.45">
+      <c r="L50" t="s">
+        <v>78</v>
+      </c>
+      <c r="M50" t="s">
         <v>90</v>
       </c>
-      <c r="N43" t="s">
+      <c r="N50" t="s">
         <v>91</v>
       </c>
-      <c r="O43" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="G44" t="s">
-        <v>78</v>
-      </c>
-      <c r="H44" t="s">
-        <v>147</v>
-      </c>
-      <c r="I44" t="s">
-        <v>148</v>
-      </c>
-      <c r="J44" t="s">
-        <v>138</v>
-      </c>
-      <c r="L44" t="s">
-        <v>78</v>
-      </c>
-      <c r="M44" t="s">
+      <c r="O50" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="51" spans="7:15" x14ac:dyDescent="0.45">
+      <c r="L51" t="s">
+        <v>78</v>
+      </c>
+      <c r="M51" t="s">
+        <v>126</v>
+      </c>
+      <c r="N51" t="s">
+        <v>127</v>
+      </c>
+      <c r="O51" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="52" spans="7:15" x14ac:dyDescent="0.45">
+      <c r="L52" t="s">
+        <v>78</v>
+      </c>
+      <c r="M52" t="s">
+        <v>157</v>
+      </c>
+      <c r="N52" t="s">
         <v>158</v>
       </c>
-      <c r="N44" t="s">
-        <v>159</v>
-      </c>
-      <c r="O44" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="L45" t="s">
-        <v>78</v>
-      </c>
-      <c r="M45" t="s">
-        <v>160</v>
-      </c>
-      <c r="N45" t="s">
-        <v>161</v>
-      </c>
-      <c r="O45" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="L46" t="s">
-        <v>78</v>
-      </c>
-      <c r="M46" t="s">
-        <v>106</v>
-      </c>
-      <c r="N46" t="s">
-        <v>107</v>
-      </c>
-      <c r="O46" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="L47" t="s">
-        <v>78</v>
-      </c>
-      <c r="M47" t="s">
-        <v>126</v>
-      </c>
-      <c r="N47" t="s">
-        <v>127</v>
-      </c>
-      <c r="O47" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.45">
-      <c r="L48" t="s">
-        <v>78</v>
-      </c>
-      <c r="M48" t="s">
-        <v>162</v>
-      </c>
-      <c r="N48" t="s">
-        <v>163</v>
-      </c>
-      <c r="O48" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="49" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L49" t="s">
-        <v>78</v>
-      </c>
-      <c r="M49" t="s">
-        <v>130</v>
-      </c>
-      <c r="N49" t="s">
-        <v>131</v>
-      </c>
-      <c r="O49" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="50" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L50" t="s">
-        <v>78</v>
-      </c>
-      <c r="M50" t="s">
-        <v>128</v>
-      </c>
-      <c r="N50" t="s">
-        <v>129</v>
-      </c>
-      <c r="O50" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="51" spans="12:15" x14ac:dyDescent="0.45">
-      <c r="L51" t="s">
-        <v>78</v>
-      </c>
-      <c r="M51" t="s">
-        <v>102</v>
-      </c>
-      <c r="N51" t="s">
-        <v>103</v>
-      </c>
-      <c r="O51" t="s">
-        <v>149</v>
+      <c r="O52" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="53" spans="7:15" x14ac:dyDescent="0.45">
+      <c r="L53" t="s">
+        <v>78</v>
+      </c>
+      <c r="M53" t="s">
+        <v>118</v>
+      </c>
+      <c r="N53" t="s">
+        <v>119</v>
+      </c>
+      <c r="O53" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="54" spans="7:15" x14ac:dyDescent="0.45">
+      <c r="L54" t="s">
+        <v>78</v>
+      </c>
+      <c r="M54" t="s">
+        <v>151</v>
+      </c>
+      <c r="N54" t="s">
+        <v>152</v>
+      </c>
+      <c r="O54" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="55" spans="7:15" x14ac:dyDescent="0.45">
+      <c r="L55" t="s">
+        <v>78</v>
+      </c>
+      <c r="M55" t="s">
+        <v>116</v>
+      </c>
+      <c r="N55" t="s">
+        <v>117</v>
+      </c>
+      <c r="O55" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="56" spans="7:15" x14ac:dyDescent="0.45">
+      <c r="L56" t="s">
+        <v>78</v>
+      </c>
+      <c r="M56" t="s">
+        <v>140</v>
+      </c>
+      <c r="N56" t="s">
+        <v>141</v>
+      </c>
+      <c r="O56" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="57" spans="7:15" x14ac:dyDescent="0.45">
+      <c r="L57" t="s">
+        <v>78</v>
+      </c>
+      <c r="M57" t="s">
+        <v>124</v>
+      </c>
+      <c r="N57" t="s">
+        <v>125</v>
+      </c>
+      <c r="O57" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="58" spans="7:15" x14ac:dyDescent="0.45">
+      <c r="L58" t="s">
+        <v>78</v>
+      </c>
+      <c r="M58" t="s">
+        <v>84</v>
+      </c>
+      <c r="N58" t="s">
+        <v>85</v>
+      </c>
+      <c r="O58" t="s">
+        <v>159</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8D4DC223-DFBF-418F-BB57-15A1955C50CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8873F433-9A24-495E-8F5D-F078005F8347}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AVA" sheetId="6" r:id="rId1"/>
@@ -520,58 +520,58 @@
     <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
   </si>
   <si>
+    <t>Slupsk_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Slupsk_POL</t>
+  </si>
+  <si>
+    <t>Grajewo_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Grajewo_POL</t>
+  </si>
+  <si>
+    <t>OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>at grid node - OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>Chelm_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Chelm_POL</t>
+  </si>
+  <si>
+    <t>Zamosc_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Zamosc_POL</t>
+  </si>
+  <si>
+    <t>Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Olsztyn_POL</t>
+  </si>
+  <si>
     <t>Legnica_POL</t>
   </si>
   <si>
     <t>at grid node - Legnica_POL</t>
   </si>
   <si>
-    <t>Chelm_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Chelm_POL</t>
-  </si>
-  <si>
-    <t>OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>at grid node - OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>Grajewo_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Grajewo_POL</t>
-  </si>
-  <si>
-    <t>Slupsk_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Slupsk_POL</t>
+    <t>Kielce_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Kielce_POL</t>
   </si>
   <si>
     <t>Elk_POL</t>
   </si>
   <si>
     <t>at grid node - Elk_POL</t>
-  </si>
-  <si>
-    <t>Kielce_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Kielce_POL</t>
-  </si>
-  <si>
-    <t>Zamosc_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Zamosc_POL</t>
-  </si>
-  <si>
-    <t>Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Olsztyn_POL</t>
   </si>
   <si>
     <t>h_demand</t>
@@ -1037,10 +1037,10 @@
         <v>78</v>
       </c>
       <c r="M11" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="N11" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="O11" t="s">
         <v>159</v>
@@ -1099,10 +1099,10 @@
         <v>78</v>
       </c>
       <c r="M12" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="N12" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="O12" t="s">
         <v>159</v>
@@ -1161,10 +1161,10 @@
         <v>78</v>
       </c>
       <c r="M13" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="N13" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="O13" t="s">
         <v>159</v>
@@ -1223,10 +1223,10 @@
         <v>78</v>
       </c>
       <c r="M14" t="s">
-        <v>155</v>
+        <v>116</v>
       </c>
       <c r="N14" t="s">
-        <v>156</v>
+        <v>117</v>
       </c>
       <c r="O14" t="s">
         <v>159</v>
@@ -1285,10 +1285,10 @@
         <v>78</v>
       </c>
       <c r="M15" t="s">
-        <v>142</v>
+        <v>110</v>
       </c>
       <c r="N15" t="s">
-        <v>143</v>
+        <v>111</v>
       </c>
       <c r="O15" t="s">
         <v>159</v>
@@ -1347,10 +1347,10 @@
         <v>78</v>
       </c>
       <c r="M16" t="s">
-        <v>147</v>
+        <v>130</v>
       </c>
       <c r="N16" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="O16" t="s">
         <v>159</v>
@@ -1409,10 +1409,10 @@
         <v>78</v>
       </c>
       <c r="M17" t="s">
-        <v>102</v>
+        <v>140</v>
       </c>
       <c r="N17" t="s">
-        <v>103</v>
+        <v>141</v>
       </c>
       <c r="O17" t="s">
         <v>159</v>
@@ -1471,10 +1471,10 @@
         <v>78</v>
       </c>
       <c r="M18" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="N18" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="O18" t="s">
         <v>159</v>
@@ -1595,10 +1595,10 @@
         <v>78</v>
       </c>
       <c r="M20" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="N20" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O20" t="s">
         <v>159</v>
@@ -1657,10 +1657,10 @@
         <v>78</v>
       </c>
       <c r="M21" t="s">
-        <v>98</v>
+        <v>155</v>
       </c>
       <c r="N21" t="s">
-        <v>99</v>
+        <v>156</v>
       </c>
       <c r="O21" t="s">
         <v>159</v>
@@ -1719,10 +1719,10 @@
         <v>78</v>
       </c>
       <c r="M22" t="s">
-        <v>138</v>
+        <v>108</v>
       </c>
       <c r="N22" t="s">
-        <v>139</v>
+        <v>109</v>
       </c>
       <c r="O22" t="s">
         <v>159</v>
@@ -1781,10 +1781,10 @@
         <v>78</v>
       </c>
       <c r="M23" t="s">
-        <v>162</v>
+        <v>124</v>
       </c>
       <c r="N23" t="s">
-        <v>163</v>
+        <v>125</v>
       </c>
       <c r="O23" t="s">
         <v>159</v>
@@ -1843,10 +1843,10 @@
         <v>78</v>
       </c>
       <c r="M24" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="N24" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="O24" t="s">
         <v>159</v>
@@ -1905,10 +1905,10 @@
         <v>78</v>
       </c>
       <c r="M25" t="s">
-        <v>86</v>
+        <v>144</v>
       </c>
       <c r="N25" t="s">
-        <v>87</v>
+        <v>145</v>
       </c>
       <c r="O25" t="s">
         <v>159</v>
@@ -1967,10 +1967,10 @@
         <v>78</v>
       </c>
       <c r="M26" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="N26" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="O26" t="s">
         <v>159</v>
@@ -2029,10 +2029,10 @@
         <v>78</v>
       </c>
       <c r="M27" t="s">
-        <v>164</v>
+        <v>134</v>
       </c>
       <c r="N27" t="s">
-        <v>165</v>
+        <v>135</v>
       </c>
       <c r="O27" t="s">
         <v>159</v>
@@ -2091,10 +2091,10 @@
         <v>78</v>
       </c>
       <c r="M28" t="s">
-        <v>166</v>
+        <v>136</v>
       </c>
       <c r="N28" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="O28" t="s">
         <v>159</v>
@@ -2153,10 +2153,10 @@
         <v>78</v>
       </c>
       <c r="M29" t="s">
-        <v>82</v>
+        <v>164</v>
       </c>
       <c r="N29" t="s">
-        <v>83</v>
+        <v>165</v>
       </c>
       <c r="O29" t="s">
         <v>159</v>
@@ -2215,10 +2215,10 @@
         <v>78</v>
       </c>
       <c r="M30" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="N30" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="O30" t="s">
         <v>159</v>
@@ -2277,10 +2277,10 @@
         <v>78</v>
       </c>
       <c r="M31" t="s">
-        <v>168</v>
+        <v>96</v>
       </c>
       <c r="N31" t="s">
-        <v>169</v>
+        <v>97</v>
       </c>
       <c r="O31" t="s">
         <v>159</v>
@@ -2339,10 +2339,10 @@
         <v>78</v>
       </c>
       <c r="M32" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="N32" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="O32" t="s">
         <v>159</v>
@@ -2401,10 +2401,10 @@
         <v>78</v>
       </c>
       <c r="M33" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="N33" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="O33" t="s">
         <v>159</v>
@@ -2463,10 +2463,10 @@
         <v>78</v>
       </c>
       <c r="M34" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="N34" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="O34" t="s">
         <v>159</v>
@@ -2525,10 +2525,10 @@
         <v>78</v>
       </c>
       <c r="M35" t="s">
-        <v>170</v>
+        <v>86</v>
       </c>
       <c r="N35" t="s">
-        <v>171</v>
+        <v>87</v>
       </c>
       <c r="O35" t="s">
         <v>159</v>
@@ -2587,10 +2587,10 @@
         <v>78</v>
       </c>
       <c r="M36" t="s">
-        <v>88</v>
+        <v>168</v>
       </c>
       <c r="N36" t="s">
-        <v>89</v>
+        <v>169</v>
       </c>
       <c r="O36" t="s">
         <v>159</v>
@@ -2649,10 +2649,10 @@
         <v>78</v>
       </c>
       <c r="M37" t="s">
-        <v>172</v>
+        <v>112</v>
       </c>
       <c r="N37" t="s">
-        <v>173</v>
+        <v>113</v>
       </c>
       <c r="O37" t="s">
         <v>159</v>
@@ -2711,10 +2711,10 @@
         <v>78</v>
       </c>
       <c r="M38" t="s">
-        <v>134</v>
+        <v>170</v>
       </c>
       <c r="N38" t="s">
-        <v>135</v>
+        <v>171</v>
       </c>
       <c r="O38" t="s">
         <v>159</v>
@@ -2773,10 +2773,10 @@
         <v>78</v>
       </c>
       <c r="M39" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="N39" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="O39" t="s">
         <v>159</v>
@@ -2835,10 +2835,10 @@
         <v>78</v>
       </c>
       <c r="M40" t="s">
-        <v>100</v>
+        <v>138</v>
       </c>
       <c r="N40" t="s">
-        <v>101</v>
+        <v>139</v>
       </c>
       <c r="O40" t="s">
         <v>159</v>
@@ -2873,10 +2873,10 @@
         <v>78</v>
       </c>
       <c r="M41" t="s">
-        <v>92</v>
+        <v>172</v>
       </c>
       <c r="N41" t="s">
-        <v>93</v>
+        <v>173</v>
       </c>
       <c r="O41" t="s">
         <v>159</v>
@@ -2911,10 +2911,10 @@
         <v>78</v>
       </c>
       <c r="M42" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="N42" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="O42" t="s">
         <v>159</v>
@@ -2949,10 +2949,10 @@
         <v>78</v>
       </c>
       <c r="M43" t="s">
-        <v>174</v>
+        <v>149</v>
       </c>
       <c r="N43" t="s">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="O43" t="s">
         <v>159</v>
@@ -2975,10 +2975,10 @@
         <v>78</v>
       </c>
       <c r="M44" t="s">
-        <v>176</v>
+        <v>79</v>
       </c>
       <c r="N44" t="s">
-        <v>177</v>
+        <v>80</v>
       </c>
       <c r="O44" t="s">
         <v>159</v>
@@ -3001,10 +3001,10 @@
         <v>78</v>
       </c>
       <c r="M45" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="N45" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="O45" t="s">
         <v>159</v>
@@ -3027,10 +3027,10 @@
         <v>78</v>
       </c>
       <c r="M46" t="s">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="N46" t="s">
-        <v>115</v>
+        <v>85</v>
       </c>
       <c r="O46" t="s">
         <v>159</v>
@@ -3053,10 +3053,10 @@
         <v>78</v>
       </c>
       <c r="M47" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="N47" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="O47" t="s">
         <v>159</v>
@@ -3079,10 +3079,10 @@
         <v>78</v>
       </c>
       <c r="M48" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="N48" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="O48" t="s">
         <v>159</v>
@@ -3105,10 +3105,10 @@
         <v>78</v>
       </c>
       <c r="M49" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="N49" t="s">
-        <v>129</v>
+        <v>99</v>
       </c>
       <c r="O49" t="s">
         <v>159</v>
@@ -3119,10 +3119,10 @@
         <v>78</v>
       </c>
       <c r="M50" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="N50" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="O50" t="s">
         <v>159</v>
@@ -3133,10 +3133,10 @@
         <v>78</v>
       </c>
       <c r="M51" t="s">
-        <v>126</v>
+        <v>153</v>
       </c>
       <c r="N51" t="s">
-        <v>127</v>
+        <v>154</v>
       </c>
       <c r="O51" t="s">
         <v>159</v>
@@ -3147,10 +3147,10 @@
         <v>78</v>
       </c>
       <c r="M52" t="s">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="N52" t="s">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="O52" t="s">
         <v>159</v>
@@ -3161,10 +3161,10 @@
         <v>78</v>
       </c>
       <c r="M53" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="N53" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="O53" t="s">
         <v>159</v>
@@ -3175,10 +3175,10 @@
         <v>78</v>
       </c>
       <c r="M54" t="s">
-        <v>151</v>
+        <v>176</v>
       </c>
       <c r="N54" t="s">
-        <v>152</v>
+        <v>177</v>
       </c>
       <c r="O54" t="s">
         <v>159</v>
@@ -3189,10 +3189,10 @@
         <v>78</v>
       </c>
       <c r="M55" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N55" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="O55" t="s">
         <v>159</v>
@@ -3203,10 +3203,10 @@
         <v>78</v>
       </c>
       <c r="M56" t="s">
-        <v>140</v>
+        <v>92</v>
       </c>
       <c r="N56" t="s">
-        <v>141</v>
+        <v>93</v>
       </c>
       <c r="O56" t="s">
         <v>159</v>
@@ -3217,10 +3217,10 @@
         <v>78</v>
       </c>
       <c r="M57" t="s">
-        <v>124</v>
+        <v>147</v>
       </c>
       <c r="N57" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="O57" t="s">
         <v>159</v>
@@ -3231,10 +3231,10 @@
         <v>78</v>
       </c>
       <c r="M58" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="N58" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="O58" t="s">
         <v>159</v>

--- a/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8873F433-9A24-495E-8F5D-F078005F8347}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B2514B2-19B7-43DD-95D7-0A61AF97ABB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -520,6 +520,48 @@
     <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
   </si>
   <si>
+    <t>Chelm_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Chelm_POL</t>
+  </si>
+  <si>
+    <t>Kielce_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Kielce_POL</t>
+  </si>
+  <si>
+    <t>OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>at grid node - OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>Zamosc_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Zamosc_POL</t>
+  </si>
+  <si>
+    <t>Elk_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Elk_POL</t>
+  </si>
+  <si>
+    <t>Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>Legnica_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Legnica_POL</t>
+  </si>
+  <si>
     <t>Slupsk_POL</t>
   </si>
   <si>
@@ -530,48 +572,6 @@
   </si>
   <si>
     <t>at grid node - Grajewo_POL</t>
-  </si>
-  <si>
-    <t>OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>at grid node - OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>Chelm_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Chelm_POL</t>
-  </si>
-  <si>
-    <t>Zamosc_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Zamosc_POL</t>
-  </si>
-  <si>
-    <t>Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>Legnica_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Legnica_POL</t>
-  </si>
-  <si>
-    <t>Kielce_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Kielce_POL</t>
-  </si>
-  <si>
-    <t>Elk_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Elk_POL</t>
   </si>
   <si>
     <t>h_demand</t>
@@ -1037,10 +1037,10 @@
         <v>78</v>
       </c>
       <c r="M11" t="s">
-        <v>151</v>
+        <v>98</v>
       </c>
       <c r="N11" t="s">
-        <v>152</v>
+        <v>99</v>
       </c>
       <c r="O11" t="s">
         <v>159</v>
@@ -1161,10 +1161,10 @@
         <v>78</v>
       </c>
       <c r="M13" t="s">
-        <v>142</v>
+        <v>106</v>
       </c>
       <c r="N13" t="s">
-        <v>143</v>
+        <v>107</v>
       </c>
       <c r="O13" t="s">
         <v>159</v>
@@ -1223,10 +1223,10 @@
         <v>78</v>
       </c>
       <c r="M14" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="N14" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="O14" t="s">
         <v>159</v>
@@ -1285,10 +1285,10 @@
         <v>78</v>
       </c>
       <c r="M15" t="s">
-        <v>110</v>
+        <v>162</v>
       </c>
       <c r="N15" t="s">
-        <v>111</v>
+        <v>163</v>
       </c>
       <c r="O15" t="s">
         <v>159</v>
@@ -1347,10 +1347,10 @@
         <v>78</v>
       </c>
       <c r="M16" t="s">
-        <v>130</v>
+        <v>157</v>
       </c>
       <c r="N16" t="s">
-        <v>131</v>
+        <v>158</v>
       </c>
       <c r="O16" t="s">
         <v>159</v>
@@ -1409,10 +1409,10 @@
         <v>78</v>
       </c>
       <c r="M17" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="N17" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="O17" t="s">
         <v>159</v>
@@ -1471,10 +1471,10 @@
         <v>78</v>
       </c>
       <c r="M18" t="s">
-        <v>120</v>
+        <v>164</v>
       </c>
       <c r="N18" t="s">
-        <v>121</v>
+        <v>165</v>
       </c>
       <c r="O18" t="s">
         <v>159</v>
@@ -1533,10 +1533,10 @@
         <v>78</v>
       </c>
       <c r="M19" t="s">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="N19" t="s">
-        <v>105</v>
+        <v>131</v>
       </c>
       <c r="O19" t="s">
         <v>159</v>
@@ -1595,10 +1595,10 @@
         <v>78</v>
       </c>
       <c r="M20" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
       <c r="N20" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="O20" t="s">
         <v>159</v>
@@ -1657,10 +1657,10 @@
         <v>78</v>
       </c>
       <c r="M21" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="N21" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="O21" t="s">
         <v>159</v>
@@ -1719,10 +1719,10 @@
         <v>78</v>
       </c>
       <c r="M22" t="s">
-        <v>108</v>
+        <v>147</v>
       </c>
       <c r="N22" t="s">
-        <v>109</v>
+        <v>148</v>
       </c>
       <c r="O22" t="s">
         <v>159</v>
@@ -1781,10 +1781,10 @@
         <v>78</v>
       </c>
       <c r="M23" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="N23" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="O23" t="s">
         <v>159</v>
@@ -1843,10 +1843,10 @@
         <v>78</v>
       </c>
       <c r="M24" t="s">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="N24" t="s">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="O24" t="s">
         <v>159</v>
@@ -1905,10 +1905,10 @@
         <v>78</v>
       </c>
       <c r="M25" t="s">
-        <v>144</v>
+        <v>114</v>
       </c>
       <c r="N25" t="s">
-        <v>145</v>
+        <v>115</v>
       </c>
       <c r="O25" t="s">
         <v>159</v>
@@ -1967,10 +1967,10 @@
         <v>78</v>
       </c>
       <c r="M26" t="s">
-        <v>128</v>
+        <v>82</v>
       </c>
       <c r="N26" t="s">
-        <v>129</v>
+        <v>83</v>
       </c>
       <c r="O26" t="s">
         <v>159</v>
@@ -2029,10 +2029,10 @@
         <v>78</v>
       </c>
       <c r="M27" t="s">
-        <v>134</v>
+        <v>90</v>
       </c>
       <c r="N27" t="s">
-        <v>135</v>
+        <v>91</v>
       </c>
       <c r="O27" t="s">
         <v>159</v>
@@ -2091,10 +2091,10 @@
         <v>78</v>
       </c>
       <c r="M28" t="s">
-        <v>136</v>
+        <v>166</v>
       </c>
       <c r="N28" t="s">
-        <v>137</v>
+        <v>167</v>
       </c>
       <c r="O28" t="s">
         <v>159</v>
@@ -2153,10 +2153,10 @@
         <v>78</v>
       </c>
       <c r="M29" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="N29" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="O29" t="s">
         <v>159</v>
@@ -2215,10 +2215,10 @@
         <v>78</v>
       </c>
       <c r="M30" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="N30" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="O30" t="s">
         <v>159</v>
@@ -2277,10 +2277,10 @@
         <v>78</v>
       </c>
       <c r="M31" t="s">
-        <v>96</v>
+        <v>155</v>
       </c>
       <c r="N31" t="s">
-        <v>97</v>
+        <v>156</v>
       </c>
       <c r="O31" t="s">
         <v>159</v>
@@ -2339,10 +2339,10 @@
         <v>78</v>
       </c>
       <c r="M32" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="N32" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="O32" t="s">
         <v>159</v>
@@ -2401,10 +2401,10 @@
         <v>78</v>
       </c>
       <c r="M33" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="N33" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="O33" t="s">
         <v>159</v>
@@ -2463,10 +2463,10 @@
         <v>78</v>
       </c>
       <c r="M34" t="s">
-        <v>166</v>
+        <v>144</v>
       </c>
       <c r="N34" t="s">
-        <v>167</v>
+        <v>145</v>
       </c>
       <c r="O34" t="s">
         <v>159</v>
@@ -2525,10 +2525,10 @@
         <v>78</v>
       </c>
       <c r="M35" t="s">
-        <v>86</v>
+        <v>170</v>
       </c>
       <c r="N35" t="s">
-        <v>87</v>
+        <v>171</v>
       </c>
       <c r="O35" t="s">
         <v>159</v>
@@ -2587,10 +2587,10 @@
         <v>78</v>
       </c>
       <c r="M36" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="N36" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="O36" t="s">
         <v>159</v>
@@ -2649,10 +2649,10 @@
         <v>78</v>
       </c>
       <c r="M37" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="N37" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="O37" t="s">
         <v>159</v>
@@ -2711,10 +2711,10 @@
         <v>78</v>
       </c>
       <c r="M38" t="s">
-        <v>170</v>
+        <v>149</v>
       </c>
       <c r="N38" t="s">
-        <v>171</v>
+        <v>150</v>
       </c>
       <c r="O38" t="s">
         <v>159</v>
@@ -2835,10 +2835,10 @@
         <v>78</v>
       </c>
       <c r="M40" t="s">
-        <v>138</v>
+        <v>172</v>
       </c>
       <c r="N40" t="s">
-        <v>139</v>
+        <v>173</v>
       </c>
       <c r="O40" t="s">
         <v>159</v>
@@ -2873,10 +2873,10 @@
         <v>78</v>
       </c>
       <c r="M41" t="s">
-        <v>172</v>
+        <v>126</v>
       </c>
       <c r="N41" t="s">
-        <v>173</v>
+        <v>127</v>
       </c>
       <c r="O41" t="s">
         <v>159</v>
@@ -2911,10 +2911,10 @@
         <v>78</v>
       </c>
       <c r="M42" t="s">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="N42" t="s">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="O42" t="s">
         <v>159</v>
@@ -2949,10 +2949,10 @@
         <v>78</v>
       </c>
       <c r="M43" t="s">
-        <v>149</v>
+        <v>110</v>
       </c>
       <c r="N43" t="s">
-        <v>150</v>
+        <v>111</v>
       </c>
       <c r="O43" t="s">
         <v>159</v>
@@ -2975,10 +2975,10 @@
         <v>78</v>
       </c>
       <c r="M44" t="s">
-        <v>79</v>
+        <v>128</v>
       </c>
       <c r="N44" t="s">
-        <v>80</v>
+        <v>129</v>
       </c>
       <c r="O44" t="s">
         <v>159</v>
@@ -3001,10 +3001,10 @@
         <v>78</v>
       </c>
       <c r="M45" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="N45" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="O45" t="s">
         <v>159</v>
@@ -3027,10 +3027,10 @@
         <v>78</v>
       </c>
       <c r="M46" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="N46" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="O46" t="s">
         <v>159</v>
@@ -3053,10 +3053,10 @@
         <v>78</v>
       </c>
       <c r="M47" t="s">
-        <v>114</v>
+        <v>88</v>
       </c>
       <c r="N47" t="s">
-        <v>115</v>
+        <v>89</v>
       </c>
       <c r="O47" t="s">
         <v>159</v>
@@ -3079,10 +3079,10 @@
         <v>78</v>
       </c>
       <c r="M48" t="s">
-        <v>157</v>
+        <v>102</v>
       </c>
       <c r="N48" t="s">
-        <v>158</v>
+        <v>103</v>
       </c>
       <c r="O48" t="s">
         <v>159</v>
@@ -3105,10 +3105,10 @@
         <v>78</v>
       </c>
       <c r="M49" t="s">
-        <v>98</v>
+        <v>134</v>
       </c>
       <c r="N49" t="s">
-        <v>99</v>
+        <v>135</v>
       </c>
       <c r="O49" t="s">
         <v>159</v>
@@ -3119,10 +3119,10 @@
         <v>78</v>
       </c>
       <c r="M50" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="N50" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="O50" t="s">
         <v>159</v>
@@ -3133,10 +3133,10 @@
         <v>78</v>
       </c>
       <c r="M51" t="s">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="N51" t="s">
-        <v>154</v>
+        <v>175</v>
       </c>
       <c r="O51" t="s">
         <v>159</v>
@@ -3147,10 +3147,10 @@
         <v>78</v>
       </c>
       <c r="M52" t="s">
-        <v>174</v>
+        <v>108</v>
       </c>
       <c r="N52" t="s">
-        <v>175</v>
+        <v>109</v>
       </c>
       <c r="O52" t="s">
         <v>159</v>
@@ -3161,10 +3161,10 @@
         <v>78</v>
       </c>
       <c r="M53" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="N53" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="O53" t="s">
         <v>159</v>
@@ -3175,10 +3175,10 @@
         <v>78</v>
       </c>
       <c r="M54" t="s">
-        <v>176</v>
+        <v>112</v>
       </c>
       <c r="N54" t="s">
-        <v>177</v>
+        <v>113</v>
       </c>
       <c r="O54" t="s">
         <v>159</v>
@@ -3189,10 +3189,10 @@
         <v>78</v>
       </c>
       <c r="M55" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="N55" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="O55" t="s">
         <v>159</v>
@@ -3203,10 +3203,10 @@
         <v>78</v>
       </c>
       <c r="M56" t="s">
-        <v>92</v>
+        <v>118</v>
       </c>
       <c r="N56" t="s">
-        <v>93</v>
+        <v>119</v>
       </c>
       <c r="O56" t="s">
         <v>159</v>
@@ -3217,10 +3217,10 @@
         <v>78</v>
       </c>
       <c r="M57" t="s">
-        <v>147</v>
+        <v>176</v>
       </c>
       <c r="N57" t="s">
-        <v>148</v>
+        <v>177</v>
       </c>
       <c r="O57" t="s">
         <v>159</v>
@@ -3231,10 +3231,10 @@
         <v>78</v>
       </c>
       <c r="M58" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="N58" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="O58" t="s">
         <v>159</v>

--- a/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B2514B2-19B7-43DD-95D7-0A61AF97ABB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AA4BBA7-38A6-42D6-98CF-A09AD8BF74F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -526,52 +526,52 @@
     <t>at grid node - Chelm_POL</t>
   </si>
   <si>
+    <t>Slupsk_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Slupsk_POL</t>
+  </si>
+  <si>
     <t>Kielce_POL</t>
   </si>
   <si>
     <t>at grid node - Kielce_POL</t>
   </si>
   <si>
+    <t>Zamosc_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Zamosc_POL</t>
+  </si>
+  <si>
+    <t>Grajewo_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Grajewo_POL</t>
+  </si>
+  <si>
+    <t>Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Olsztyn_POL</t>
+  </si>
+  <si>
     <t>OstrowiecSwietokrz_POL</t>
   </si>
   <si>
     <t>at grid node - OstrowiecSwietokrz_POL</t>
   </si>
   <si>
-    <t>Zamosc_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Zamosc_POL</t>
-  </si>
-  <si>
     <t>Elk_POL</t>
   </si>
   <si>
     <t>at grid node - Elk_POL</t>
   </si>
   <si>
-    <t>Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Olsztyn_POL</t>
-  </si>
-  <si>
     <t>Legnica_POL</t>
   </si>
   <si>
     <t>at grid node - Legnica_POL</t>
-  </si>
-  <si>
-    <t>Slupsk_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Slupsk_POL</t>
-  </si>
-  <si>
-    <t>Grajewo_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Grajewo_POL</t>
   </si>
   <si>
     <t>h_demand</t>
@@ -1037,10 +1037,10 @@
         <v>78</v>
       </c>
       <c r="M11" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="N11" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="O11" t="s">
         <v>159</v>
@@ -1099,10 +1099,10 @@
         <v>78</v>
       </c>
       <c r="M12" t="s">
-        <v>160</v>
+        <v>108</v>
       </c>
       <c r="N12" t="s">
-        <v>161</v>
+        <v>109</v>
       </c>
       <c r="O12" t="s">
         <v>159</v>
@@ -1161,10 +1161,10 @@
         <v>78</v>
       </c>
       <c r="M13" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="N13" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="O13" t="s">
         <v>159</v>
@@ -1223,10 +1223,10 @@
         <v>78</v>
       </c>
       <c r="M14" t="s">
-        <v>104</v>
+        <v>160</v>
       </c>
       <c r="N14" t="s">
-        <v>105</v>
+        <v>161</v>
       </c>
       <c r="O14" t="s">
         <v>159</v>
@@ -1285,10 +1285,10 @@
         <v>78</v>
       </c>
       <c r="M15" t="s">
-        <v>162</v>
+        <v>122</v>
       </c>
       <c r="N15" t="s">
-        <v>163</v>
+        <v>123</v>
       </c>
       <c r="O15" t="s">
         <v>159</v>
@@ -1347,10 +1347,10 @@
         <v>78</v>
       </c>
       <c r="M16" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="N16" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="O16" t="s">
         <v>159</v>
@@ -1409,10 +1409,10 @@
         <v>78</v>
       </c>
       <c r="M17" t="s">
-        <v>151</v>
+        <v>90</v>
       </c>
       <c r="N17" t="s">
-        <v>152</v>
+        <v>91</v>
       </c>
       <c r="O17" t="s">
         <v>159</v>
@@ -1471,10 +1471,10 @@
         <v>78</v>
       </c>
       <c r="M18" t="s">
-        <v>164</v>
+        <v>112</v>
       </c>
       <c r="N18" t="s">
-        <v>165</v>
+        <v>113</v>
       </c>
       <c r="O18" t="s">
         <v>159</v>
@@ -1533,10 +1533,10 @@
         <v>78</v>
       </c>
       <c r="M19" t="s">
-        <v>130</v>
+        <v>94</v>
       </c>
       <c r="N19" t="s">
-        <v>131</v>
+        <v>95</v>
       </c>
       <c r="O19" t="s">
         <v>159</v>
@@ -1595,10 +1595,10 @@
         <v>78</v>
       </c>
       <c r="M20" t="s">
-        <v>153</v>
+        <v>110</v>
       </c>
       <c r="N20" t="s">
-        <v>154</v>
+        <v>111</v>
       </c>
       <c r="O20" t="s">
         <v>159</v>
@@ -1657,10 +1657,10 @@
         <v>78</v>
       </c>
       <c r="M21" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="N21" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="O21" t="s">
         <v>159</v>
@@ -1719,10 +1719,10 @@
         <v>78</v>
       </c>
       <c r="M22" t="s">
-        <v>147</v>
+        <v>100</v>
       </c>
       <c r="N22" t="s">
-        <v>148</v>
+        <v>101</v>
       </c>
       <c r="O22" t="s">
         <v>159</v>
@@ -1781,10 +1781,10 @@
         <v>78</v>
       </c>
       <c r="M23" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="N23" t="s">
-        <v>123</v>
+        <v>99</v>
       </c>
       <c r="O23" t="s">
         <v>159</v>
@@ -1843,10 +1843,10 @@
         <v>78</v>
       </c>
       <c r="M24" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="N24" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="O24" t="s">
         <v>159</v>
@@ -1905,10 +1905,10 @@
         <v>78</v>
       </c>
       <c r="M25" t="s">
-        <v>114</v>
+        <v>136</v>
       </c>
       <c r="N25" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
       <c r="O25" t="s">
         <v>159</v>
@@ -1967,10 +1967,10 @@
         <v>78</v>
       </c>
       <c r="M26" t="s">
-        <v>82</v>
+        <v>132</v>
       </c>
       <c r="N26" t="s">
-        <v>83</v>
+        <v>133</v>
       </c>
       <c r="O26" t="s">
         <v>159</v>
@@ -2029,10 +2029,10 @@
         <v>78</v>
       </c>
       <c r="M27" t="s">
-        <v>90</v>
+        <v>151</v>
       </c>
       <c r="N27" t="s">
-        <v>91</v>
+        <v>152</v>
       </c>
       <c r="O27" t="s">
         <v>159</v>
@@ -2091,10 +2091,10 @@
         <v>78</v>
       </c>
       <c r="M28" t="s">
-        <v>166</v>
+        <v>104</v>
       </c>
       <c r="N28" t="s">
-        <v>167</v>
+        <v>105</v>
       </c>
       <c r="O28" t="s">
         <v>159</v>
@@ -2153,10 +2153,10 @@
         <v>78</v>
       </c>
       <c r="M29" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="N29" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="O29" t="s">
         <v>159</v>
@@ -2215,10 +2215,10 @@
         <v>78</v>
       </c>
       <c r="M30" t="s">
-        <v>124</v>
+        <v>82</v>
       </c>
       <c r="N30" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="O30" t="s">
         <v>159</v>
@@ -2277,10 +2277,10 @@
         <v>78</v>
       </c>
       <c r="M31" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="N31" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="O31" t="s">
         <v>159</v>
@@ -2339,10 +2339,10 @@
         <v>78</v>
       </c>
       <c r="M32" t="s">
-        <v>92</v>
+        <v>166</v>
       </c>
       <c r="N32" t="s">
-        <v>93</v>
+        <v>167</v>
       </c>
       <c r="O32" t="s">
         <v>159</v>
@@ -2401,10 +2401,10 @@
         <v>78</v>
       </c>
       <c r="M33" t="s">
-        <v>94</v>
+        <v>168</v>
       </c>
       <c r="N33" t="s">
-        <v>95</v>
+        <v>169</v>
       </c>
       <c r="O33" t="s">
         <v>159</v>
@@ -2463,10 +2463,10 @@
         <v>78</v>
       </c>
       <c r="M34" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="N34" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="O34" t="s">
         <v>159</v>
@@ -2525,10 +2525,10 @@
         <v>78</v>
       </c>
       <c r="M35" t="s">
-        <v>170</v>
+        <v>126</v>
       </c>
       <c r="N35" t="s">
-        <v>171</v>
+        <v>127</v>
       </c>
       <c r="O35" t="s">
         <v>159</v>
@@ -2587,10 +2587,10 @@
         <v>78</v>
       </c>
       <c r="M36" t="s">
-        <v>138</v>
+        <v>155</v>
       </c>
       <c r="N36" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="O36" t="s">
         <v>159</v>
@@ -2649,10 +2649,10 @@
         <v>78</v>
       </c>
       <c r="M37" t="s">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="N37" t="s">
-        <v>121</v>
+        <v>103</v>
       </c>
       <c r="O37" t="s">
         <v>159</v>
@@ -2711,10 +2711,10 @@
         <v>78</v>
       </c>
       <c r="M38" t="s">
-        <v>149</v>
+        <v>170</v>
       </c>
       <c r="N38" t="s">
-        <v>150</v>
+        <v>171</v>
       </c>
       <c r="O38" t="s">
         <v>159</v>
@@ -2773,10 +2773,10 @@
         <v>78</v>
       </c>
       <c r="M39" t="s">
-        <v>100</v>
+        <v>147</v>
       </c>
       <c r="N39" t="s">
-        <v>101</v>
+        <v>148</v>
       </c>
       <c r="O39" t="s">
         <v>159</v>
@@ -2835,10 +2835,10 @@
         <v>78</v>
       </c>
       <c r="M40" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
       <c r="N40" t="s">
-        <v>173</v>
+        <v>150</v>
       </c>
       <c r="O40" t="s">
         <v>159</v>
@@ -2873,10 +2873,10 @@
         <v>78</v>
       </c>
       <c r="M41" t="s">
-        <v>126</v>
+        <v>172</v>
       </c>
       <c r="N41" t="s">
-        <v>127</v>
+        <v>173</v>
       </c>
       <c r="O41" t="s">
         <v>159</v>
@@ -2911,10 +2911,10 @@
         <v>78</v>
       </c>
       <c r="M42" t="s">
-        <v>96</v>
+        <v>174</v>
       </c>
       <c r="N42" t="s">
-        <v>97</v>
+        <v>175</v>
       </c>
       <c r="O42" t="s">
         <v>159</v>
@@ -2949,10 +2949,10 @@
         <v>78</v>
       </c>
       <c r="M43" t="s">
-        <v>110</v>
+        <v>153</v>
       </c>
       <c r="N43" t="s">
-        <v>111</v>
+        <v>154</v>
       </c>
       <c r="O43" t="s">
         <v>159</v>
@@ -2975,10 +2975,10 @@
         <v>78</v>
       </c>
       <c r="M44" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="N44" t="s">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="O44" t="s">
         <v>159</v>
@@ -3001,10 +3001,10 @@
         <v>78</v>
       </c>
       <c r="M45" t="s">
-        <v>142</v>
+        <v>88</v>
       </c>
       <c r="N45" t="s">
-        <v>143</v>
+        <v>89</v>
       </c>
       <c r="O45" t="s">
         <v>159</v>
@@ -3027,10 +3027,10 @@
         <v>78</v>
       </c>
       <c r="M46" t="s">
-        <v>86</v>
+        <v>116</v>
       </c>
       <c r="N46" t="s">
-        <v>87</v>
+        <v>117</v>
       </c>
       <c r="O46" t="s">
         <v>159</v>
@@ -3053,10 +3053,10 @@
         <v>78</v>
       </c>
       <c r="M47" t="s">
-        <v>88</v>
+        <v>142</v>
       </c>
       <c r="N47" t="s">
-        <v>89</v>
+        <v>143</v>
       </c>
       <c r="O47" t="s">
         <v>159</v>
@@ -3079,10 +3079,10 @@
         <v>78</v>
       </c>
       <c r="M48" t="s">
-        <v>102</v>
+        <v>138</v>
       </c>
       <c r="N48" t="s">
-        <v>103</v>
+        <v>139</v>
       </c>
       <c r="O48" t="s">
         <v>159</v>
@@ -3105,10 +3105,10 @@
         <v>78</v>
       </c>
       <c r="M49" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="N49" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="O49" t="s">
         <v>159</v>
@@ -3119,10 +3119,10 @@
         <v>78</v>
       </c>
       <c r="M50" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="N50" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="O50" t="s">
         <v>159</v>
@@ -3133,10 +3133,10 @@
         <v>78</v>
       </c>
       <c r="M51" t="s">
-        <v>174</v>
+        <v>124</v>
       </c>
       <c r="N51" t="s">
-        <v>175</v>
+        <v>125</v>
       </c>
       <c r="O51" t="s">
         <v>159</v>
@@ -3147,10 +3147,10 @@
         <v>78</v>
       </c>
       <c r="M52" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="N52" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="O52" t="s">
         <v>159</v>
@@ -3161,10 +3161,10 @@
         <v>78</v>
       </c>
       <c r="M53" t="s">
-        <v>140</v>
+        <v>176</v>
       </c>
       <c r="N53" t="s">
-        <v>141</v>
+        <v>177</v>
       </c>
       <c r="O53" t="s">
         <v>159</v>
@@ -3175,10 +3175,10 @@
         <v>78</v>
       </c>
       <c r="M54" t="s">
-        <v>112</v>
+        <v>84</v>
       </c>
       <c r="N54" t="s">
-        <v>113</v>
+        <v>85</v>
       </c>
       <c r="O54" t="s">
         <v>159</v>
@@ -3189,10 +3189,10 @@
         <v>78</v>
       </c>
       <c r="M55" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N55" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="O55" t="s">
         <v>159</v>
@@ -3203,10 +3203,10 @@
         <v>78</v>
       </c>
       <c r="M56" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="N56" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="O56" t="s">
         <v>159</v>
@@ -3217,10 +3217,10 @@
         <v>78</v>
       </c>
       <c r="M57" t="s">
-        <v>176</v>
+        <v>92</v>
       </c>
       <c r="N57" t="s">
-        <v>177</v>
+        <v>93</v>
       </c>
       <c r="O57" t="s">
         <v>159</v>
@@ -3231,10 +3231,10 @@
         <v>78</v>
       </c>
       <c r="M58" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="N58" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="O58" t="s">
         <v>159</v>

--- a/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AA4BBA7-38A6-42D6-98CF-A09AD8BF74F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89FF4A87-F3D0-4023-9AA0-C687AC31BD25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -517,61 +517,61 @@
     <t>at grid node - Krosno_POL</t>
   </si>
   <si>
+    <t>Legnica_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Legnica_POL</t>
+  </si>
+  <si>
     <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
   </si>
   <si>
+    <t>Slupsk_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Slupsk_POL</t>
+  </si>
+  <si>
+    <t>Kielce_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Kielce_POL</t>
+  </si>
+  <si>
+    <t>Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>Zamosc_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Zamosc_POL</t>
+  </si>
+  <si>
+    <t>OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>at grid node - OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>Grajewo_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Grajewo_POL</t>
+  </si>
+  <si>
+    <t>Elk_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Elk_POL</t>
+  </si>
+  <si>
     <t>Chelm_POL</t>
   </si>
   <si>
     <t>at grid node - Chelm_POL</t>
-  </si>
-  <si>
-    <t>Slupsk_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Slupsk_POL</t>
-  </si>
-  <si>
-    <t>Kielce_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Kielce_POL</t>
-  </si>
-  <si>
-    <t>Zamosc_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Zamosc_POL</t>
-  </si>
-  <si>
-    <t>Grajewo_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Grajewo_POL</t>
-  </si>
-  <si>
-    <t>Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>at grid node - OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>Elk_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Elk_POL</t>
-  </si>
-  <si>
-    <t>Legnica_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Legnica_POL</t>
   </si>
   <si>
     <t>h_demand</t>
@@ -1037,13 +1037,13 @@
         <v>78</v>
       </c>
       <c r="M11" t="s">
-        <v>96</v>
+        <v>159</v>
       </c>
       <c r="N11" t="s">
-        <v>97</v>
+        <v>160</v>
       </c>
       <c r="O11" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q11" t="s">
         <v>78</v>
@@ -1099,13 +1099,13 @@
         <v>78</v>
       </c>
       <c r="M12" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="N12" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="O12" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q12" t="s">
         <v>78</v>
@@ -1161,13 +1161,13 @@
         <v>78</v>
       </c>
       <c r="M13" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="N13" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="O13" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q13" t="s">
         <v>78</v>
@@ -1223,13 +1223,13 @@
         <v>78</v>
       </c>
       <c r="M14" t="s">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="N14" t="s">
-        <v>161</v>
+        <v>131</v>
       </c>
       <c r="O14" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q14" t="s">
         <v>78</v>
@@ -1285,13 +1285,13 @@
         <v>78</v>
       </c>
       <c r="M15" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="N15" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="O15" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q15" t="s">
         <v>78</v>
@@ -1347,13 +1347,13 @@
         <v>78</v>
       </c>
       <c r="M16" t="s">
-        <v>162</v>
+        <v>104</v>
       </c>
       <c r="N16" t="s">
-        <v>163</v>
+        <v>105</v>
       </c>
       <c r="O16" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q16" t="s">
         <v>78</v>
@@ -1409,13 +1409,13 @@
         <v>78</v>
       </c>
       <c r="M17" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="N17" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="O17" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q17" t="s">
         <v>78</v>
@@ -1471,13 +1471,13 @@
         <v>78</v>
       </c>
       <c r="M18" t="s">
-        <v>112</v>
+        <v>162</v>
       </c>
       <c r="N18" t="s">
-        <v>113</v>
+        <v>163</v>
       </c>
       <c r="O18" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q18" t="s">
         <v>78</v>
@@ -1533,13 +1533,13 @@
         <v>78</v>
       </c>
       <c r="M19" t="s">
-        <v>94</v>
+        <v>132</v>
       </c>
       <c r="N19" t="s">
-        <v>95</v>
+        <v>133</v>
       </c>
       <c r="O19" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q19" t="s">
         <v>78</v>
@@ -1595,13 +1595,13 @@
         <v>78</v>
       </c>
       <c r="M20" t="s">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="N20" t="s">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="O20" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q20" t="s">
         <v>78</v>
@@ -1663,7 +1663,7 @@
         <v>165</v>
       </c>
       <c r="O21" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q21" t="s">
         <v>78</v>
@@ -1719,13 +1719,13 @@
         <v>78</v>
       </c>
       <c r="M22" t="s">
-        <v>100</v>
+        <v>128</v>
       </c>
       <c r="N22" t="s">
-        <v>101</v>
+        <v>129</v>
       </c>
       <c r="O22" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q22" t="s">
         <v>78</v>
@@ -1781,13 +1781,13 @@
         <v>78</v>
       </c>
       <c r="M23" t="s">
-        <v>98</v>
+        <v>153</v>
       </c>
       <c r="N23" t="s">
-        <v>99</v>
+        <v>154</v>
       </c>
       <c r="O23" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q23" t="s">
         <v>78</v>
@@ -1849,7 +1849,7 @@
         <v>135</v>
       </c>
       <c r="O24" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q24" t="s">
         <v>78</v>
@@ -1905,13 +1905,13 @@
         <v>78</v>
       </c>
       <c r="M25" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="N25" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="O25" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q25" t="s">
         <v>78</v>
@@ -1967,13 +1967,13 @@
         <v>78</v>
       </c>
       <c r="M26" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="N26" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="O26" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q26" t="s">
         <v>78</v>
@@ -2029,13 +2029,13 @@
         <v>78</v>
       </c>
       <c r="M27" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="N27" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="O27" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q27" t="s">
         <v>78</v>
@@ -2091,13 +2091,13 @@
         <v>78</v>
       </c>
       <c r="M28" t="s">
-        <v>104</v>
+        <v>168</v>
       </c>
       <c r="N28" t="s">
-        <v>105</v>
+        <v>169</v>
       </c>
       <c r="O28" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q28" t="s">
         <v>78</v>
@@ -2153,13 +2153,13 @@
         <v>78</v>
       </c>
       <c r="M29" t="s">
-        <v>157</v>
+        <v>138</v>
       </c>
       <c r="N29" t="s">
-        <v>158</v>
+        <v>139</v>
       </c>
       <c r="O29" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q29" t="s">
         <v>78</v>
@@ -2215,13 +2215,13 @@
         <v>78</v>
       </c>
       <c r="M30" t="s">
-        <v>82</v>
+        <v>114</v>
       </c>
       <c r="N30" t="s">
-        <v>83</v>
+        <v>115</v>
       </c>
       <c r="O30" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q30" t="s">
         <v>78</v>
@@ -2277,13 +2277,13 @@
         <v>78</v>
       </c>
       <c r="M31" t="s">
-        <v>144</v>
+        <v>170</v>
       </c>
       <c r="N31" t="s">
-        <v>145</v>
+        <v>171</v>
       </c>
       <c r="O31" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q31" t="s">
         <v>78</v>
@@ -2339,13 +2339,13 @@
         <v>78</v>
       </c>
       <c r="M32" t="s">
-        <v>166</v>
+        <v>88</v>
       </c>
       <c r="N32" t="s">
-        <v>167</v>
+        <v>89</v>
       </c>
       <c r="O32" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q32" t="s">
         <v>78</v>
@@ -2401,13 +2401,13 @@
         <v>78</v>
       </c>
       <c r="M33" t="s">
-        <v>168</v>
+        <v>92</v>
       </c>
       <c r="N33" t="s">
-        <v>169</v>
+        <v>93</v>
       </c>
       <c r="O33" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q33" t="s">
         <v>78</v>
@@ -2463,13 +2463,13 @@
         <v>78</v>
       </c>
       <c r="M34" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="N34" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="O34" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q34" t="s">
         <v>78</v>
@@ -2531,7 +2531,7 @@
         <v>127</v>
       </c>
       <c r="O35" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q35" t="s">
         <v>78</v>
@@ -2587,13 +2587,13 @@
         <v>78</v>
       </c>
       <c r="M36" t="s">
-        <v>155</v>
+        <v>100</v>
       </c>
       <c r="N36" t="s">
-        <v>156</v>
+        <v>101</v>
       </c>
       <c r="O36" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q36" t="s">
         <v>78</v>
@@ -2649,13 +2649,13 @@
         <v>78</v>
       </c>
       <c r="M37" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="N37" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="O37" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q37" t="s">
         <v>78</v>
@@ -2711,13 +2711,13 @@
         <v>78</v>
       </c>
       <c r="M38" t="s">
-        <v>170</v>
+        <v>82</v>
       </c>
       <c r="N38" t="s">
-        <v>171</v>
+        <v>83</v>
       </c>
       <c r="O38" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q38" t="s">
         <v>78</v>
@@ -2773,13 +2773,13 @@
         <v>78</v>
       </c>
       <c r="M39" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="N39" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="O39" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="Q39" t="s">
         <v>78</v>
@@ -2835,13 +2835,13 @@
         <v>78</v>
       </c>
       <c r="M40" t="s">
-        <v>149</v>
+        <v>94</v>
       </c>
       <c r="N40" t="s">
-        <v>150</v>
+        <v>95</v>
       </c>
       <c r="O40" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="41" spans="2:25" x14ac:dyDescent="0.45">
@@ -2873,13 +2873,13 @@
         <v>78</v>
       </c>
       <c r="M41" t="s">
-        <v>172</v>
+        <v>108</v>
       </c>
       <c r="N41" t="s">
-        <v>173</v>
+        <v>109</v>
       </c>
       <c r="O41" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="42" spans="2:25" x14ac:dyDescent="0.45">
@@ -2911,13 +2911,13 @@
         <v>78</v>
       </c>
       <c r="M42" t="s">
-        <v>174</v>
+        <v>147</v>
       </c>
       <c r="N42" t="s">
-        <v>175</v>
+        <v>148</v>
       </c>
       <c r="O42" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="43" spans="2:25" x14ac:dyDescent="0.45">
@@ -2949,13 +2949,13 @@
         <v>78</v>
       </c>
       <c r="M43" t="s">
-        <v>153</v>
+        <v>86</v>
       </c>
       <c r="N43" t="s">
-        <v>154</v>
+        <v>87</v>
       </c>
       <c r="O43" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="44" spans="2:25" x14ac:dyDescent="0.45">
@@ -2975,13 +2975,13 @@
         <v>78</v>
       </c>
       <c r="M44" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="N44" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="O44" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.45">
@@ -3001,13 +3001,13 @@
         <v>78</v>
       </c>
       <c r="M45" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="N45" t="s">
-        <v>89</v>
+        <v>156</v>
       </c>
       <c r="O45" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="46" spans="2:25" x14ac:dyDescent="0.45">
@@ -3027,13 +3027,13 @@
         <v>78</v>
       </c>
       <c r="M46" t="s">
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="N46" t="s">
-        <v>117</v>
+        <v>143</v>
       </c>
       <c r="O46" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="47" spans="2:25" x14ac:dyDescent="0.45">
@@ -3053,13 +3053,13 @@
         <v>78</v>
       </c>
       <c r="M47" t="s">
-        <v>142</v>
+        <v>84</v>
       </c>
       <c r="N47" t="s">
-        <v>143</v>
+        <v>85</v>
       </c>
       <c r="O47" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="48" spans="2:25" x14ac:dyDescent="0.45">
@@ -3079,13 +3079,13 @@
         <v>78</v>
       </c>
       <c r="M48" t="s">
-        <v>138</v>
+        <v>151</v>
       </c>
       <c r="N48" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="O48" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="49" spans="7:15" x14ac:dyDescent="0.45">
@@ -3105,13 +3105,13 @@
         <v>78</v>
       </c>
       <c r="M49" t="s">
-        <v>140</v>
+        <v>172</v>
       </c>
       <c r="N49" t="s">
-        <v>141</v>
+        <v>173</v>
       </c>
       <c r="O49" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="50" spans="7:15" x14ac:dyDescent="0.45">
@@ -3119,13 +3119,13 @@
         <v>78</v>
       </c>
       <c r="M50" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="N50" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="O50" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="51" spans="7:15" x14ac:dyDescent="0.45">
@@ -3133,13 +3133,13 @@
         <v>78</v>
       </c>
       <c r="M51" t="s">
-        <v>124</v>
+        <v>90</v>
       </c>
       <c r="N51" t="s">
-        <v>125</v>
+        <v>91</v>
       </c>
       <c r="O51" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="52" spans="7:15" x14ac:dyDescent="0.45">
@@ -3147,13 +3147,13 @@
         <v>78</v>
       </c>
       <c r="M52" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="N52" t="s">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="O52" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="53" spans="7:15" x14ac:dyDescent="0.45">
@@ -3161,13 +3161,13 @@
         <v>78</v>
       </c>
       <c r="M53" t="s">
-        <v>176</v>
+        <v>144</v>
       </c>
       <c r="N53" t="s">
-        <v>177</v>
+        <v>145</v>
       </c>
       <c r="O53" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="54" spans="7:15" x14ac:dyDescent="0.45">
@@ -3175,13 +3175,13 @@
         <v>78</v>
       </c>
       <c r="M54" t="s">
-        <v>84</v>
+        <v>174</v>
       </c>
       <c r="N54" t="s">
-        <v>85</v>
+        <v>175</v>
       </c>
       <c r="O54" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="55" spans="7:15" x14ac:dyDescent="0.45">
@@ -3189,13 +3189,13 @@
         <v>78</v>
       </c>
       <c r="M55" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="N55" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="O55" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="56" spans="7:15" x14ac:dyDescent="0.45">
@@ -3203,13 +3203,13 @@
         <v>78</v>
       </c>
       <c r="M56" t="s">
-        <v>130</v>
+        <v>157</v>
       </c>
       <c r="N56" t="s">
-        <v>131</v>
+        <v>158</v>
       </c>
       <c r="O56" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="57" spans="7:15" x14ac:dyDescent="0.45">
@@ -3217,13 +3217,13 @@
         <v>78</v>
       </c>
       <c r="M57" t="s">
-        <v>92</v>
+        <v>176</v>
       </c>
       <c r="N57" t="s">
-        <v>93</v>
+        <v>177</v>
       </c>
       <c r="O57" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="58" spans="7:15" x14ac:dyDescent="0.45">
@@ -3231,13 +3231,13 @@
         <v>78</v>
       </c>
       <c r="M58" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="N58" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="O58" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89FF4A87-F3D0-4023-9AA0-C687AC31BD25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE9739FA-4879-4444-9AA7-40B4C1ADA106}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -517,61 +517,61 @@
     <t>at grid node - Krosno_POL</t>
   </si>
   <si>
+    <t>Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
+  </si>
+  <si>
+    <t>OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>at grid node - OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>Elk_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Elk_POL</t>
+  </si>
+  <si>
+    <t>Chelm_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Chelm_POL</t>
+  </si>
+  <si>
+    <t>Grajewo_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Grajewo_POL</t>
+  </si>
+  <si>
+    <t>Kielce_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Kielce_POL</t>
+  </si>
+  <si>
+    <t>Slupsk_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Slupsk_POL</t>
+  </si>
+  <si>
     <t>Legnica_POL</t>
   </si>
   <si>
     <t>at grid node - Legnica_POL</t>
   </si>
   <si>
-    <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
-  </si>
-  <si>
-    <t>Slupsk_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Slupsk_POL</t>
-  </si>
-  <si>
-    <t>Kielce_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Kielce_POL</t>
-  </si>
-  <si>
-    <t>Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Olsztyn_POL</t>
-  </si>
-  <si>
     <t>Zamosc_POL</t>
   </si>
   <si>
     <t>at grid node - Zamosc_POL</t>
-  </si>
-  <si>
-    <t>OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>at grid node - OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>Grajewo_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Grajewo_POL</t>
-  </si>
-  <si>
-    <t>Elk_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Elk_POL</t>
-  </si>
-  <si>
-    <t>Chelm_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Chelm_POL</t>
   </si>
   <si>
     <t>h_demand</t>
@@ -1099,10 +1099,10 @@
         <v>78</v>
       </c>
       <c r="M12" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="N12" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="O12" t="s">
         <v>161</v>
@@ -1161,10 +1161,10 @@
         <v>78</v>
       </c>
       <c r="M13" t="s">
-        <v>118</v>
+        <v>79</v>
       </c>
       <c r="N13" t="s">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="O13" t="s">
         <v>161</v>
@@ -1223,10 +1223,10 @@
         <v>78</v>
       </c>
       <c r="M14" t="s">
-        <v>130</v>
+        <v>155</v>
       </c>
       <c r="N14" t="s">
-        <v>131</v>
+        <v>156</v>
       </c>
       <c r="O14" t="s">
         <v>161</v>
@@ -1285,10 +1285,10 @@
         <v>78</v>
       </c>
       <c r="M15" t="s">
-        <v>140</v>
+        <v>94</v>
       </c>
       <c r="N15" t="s">
-        <v>141</v>
+        <v>95</v>
       </c>
       <c r="O15" t="s">
         <v>161</v>
@@ -1347,10 +1347,10 @@
         <v>78</v>
       </c>
       <c r="M16" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="N16" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="O16" t="s">
         <v>161</v>
@@ -1409,10 +1409,10 @@
         <v>78</v>
       </c>
       <c r="M17" t="s">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="N17" t="s">
-        <v>103</v>
+        <v>127</v>
       </c>
       <c r="O17" t="s">
         <v>161</v>
@@ -1471,10 +1471,10 @@
         <v>78</v>
       </c>
       <c r="M18" t="s">
-        <v>162</v>
+        <v>112</v>
       </c>
       <c r="N18" t="s">
-        <v>163</v>
+        <v>113</v>
       </c>
       <c r="O18" t="s">
         <v>161</v>
@@ -1533,10 +1533,10 @@
         <v>78</v>
       </c>
       <c r="M19" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="N19" t="s">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="O19" t="s">
         <v>161</v>
@@ -1595,10 +1595,10 @@
         <v>78</v>
       </c>
       <c r="M20" t="s">
-        <v>79</v>
+        <v>140</v>
       </c>
       <c r="N20" t="s">
-        <v>80</v>
+        <v>141</v>
       </c>
       <c r="O20" t="s">
         <v>161</v>
@@ -1657,10 +1657,10 @@
         <v>78</v>
       </c>
       <c r="M21" t="s">
-        <v>164</v>
+        <v>92</v>
       </c>
       <c r="N21" t="s">
-        <v>165</v>
+        <v>93</v>
       </c>
       <c r="O21" t="s">
         <v>161</v>
@@ -1719,10 +1719,10 @@
         <v>78</v>
       </c>
       <c r="M22" t="s">
-        <v>128</v>
+        <v>157</v>
       </c>
       <c r="N22" t="s">
-        <v>129</v>
+        <v>158</v>
       </c>
       <c r="O22" t="s">
         <v>161</v>
@@ -1781,10 +1781,10 @@
         <v>78</v>
       </c>
       <c r="M23" t="s">
-        <v>153</v>
+        <v>82</v>
       </c>
       <c r="N23" t="s">
-        <v>154</v>
+        <v>83</v>
       </c>
       <c r="O23" t="s">
         <v>161</v>
@@ -1843,10 +1843,10 @@
         <v>78</v>
       </c>
       <c r="M24" t="s">
-        <v>134</v>
+        <v>88</v>
       </c>
       <c r="N24" t="s">
-        <v>135</v>
+        <v>89</v>
       </c>
       <c r="O24" t="s">
         <v>161</v>
@@ -1905,10 +1905,10 @@
         <v>78</v>
       </c>
       <c r="M25" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="N25" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="O25" t="s">
         <v>161</v>
@@ -1967,10 +1967,10 @@
         <v>78</v>
       </c>
       <c r="M26" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="N26" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="O26" t="s">
         <v>161</v>
@@ -2029,10 +2029,10 @@
         <v>78</v>
       </c>
       <c r="M27" t="s">
-        <v>166</v>
+        <v>116</v>
       </c>
       <c r="N27" t="s">
-        <v>167</v>
+        <v>117</v>
       </c>
       <c r="O27" t="s">
         <v>161</v>
@@ -2091,10 +2091,10 @@
         <v>78</v>
       </c>
       <c r="M28" t="s">
-        <v>168</v>
+        <v>108</v>
       </c>
       <c r="N28" t="s">
-        <v>169</v>
+        <v>109</v>
       </c>
       <c r="O28" t="s">
         <v>161</v>
@@ -2153,10 +2153,10 @@
         <v>78</v>
       </c>
       <c r="M29" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="N29" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="O29" t="s">
         <v>161</v>
@@ -2215,10 +2215,10 @@
         <v>78</v>
       </c>
       <c r="M30" t="s">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="N30" t="s">
-        <v>115</v>
+        <v>85</v>
       </c>
       <c r="O30" t="s">
         <v>161</v>
@@ -2277,10 +2277,10 @@
         <v>78</v>
       </c>
       <c r="M31" t="s">
-        <v>170</v>
+        <v>114</v>
       </c>
       <c r="N31" t="s">
-        <v>171</v>
+        <v>115</v>
       </c>
       <c r="O31" t="s">
         <v>161</v>
@@ -2339,10 +2339,10 @@
         <v>78</v>
       </c>
       <c r="M32" t="s">
-        <v>88</v>
+        <v>164</v>
       </c>
       <c r="N32" t="s">
-        <v>89</v>
+        <v>165</v>
       </c>
       <c r="O32" t="s">
         <v>161</v>
@@ -2401,10 +2401,10 @@
         <v>78</v>
       </c>
       <c r="M33" t="s">
-        <v>92</v>
+        <v>128</v>
       </c>
       <c r="N33" t="s">
-        <v>93</v>
+        <v>129</v>
       </c>
       <c r="O33" t="s">
         <v>161</v>
@@ -2463,10 +2463,10 @@
         <v>78</v>
       </c>
       <c r="M34" t="s">
-        <v>110</v>
+        <v>151</v>
       </c>
       <c r="N34" t="s">
-        <v>111</v>
+        <v>152</v>
       </c>
       <c r="O34" t="s">
         <v>161</v>
@@ -2525,10 +2525,10 @@
         <v>78</v>
       </c>
       <c r="M35" t="s">
-        <v>126</v>
+        <v>166</v>
       </c>
       <c r="N35" t="s">
-        <v>127</v>
+        <v>167</v>
       </c>
       <c r="O35" t="s">
         <v>161</v>
@@ -2587,10 +2587,10 @@
         <v>78</v>
       </c>
       <c r="M36" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="N36" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="O36" t="s">
         <v>161</v>
@@ -2649,10 +2649,10 @@
         <v>78</v>
       </c>
       <c r="M37" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="N37" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="O37" t="s">
         <v>161</v>
@@ -2711,10 +2711,10 @@
         <v>78</v>
       </c>
       <c r="M38" t="s">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="N38" t="s">
-        <v>83</v>
+        <v>123</v>
       </c>
       <c r="O38" t="s">
         <v>161</v>
@@ -2773,10 +2773,10 @@
         <v>78</v>
       </c>
       <c r="M39" t="s">
-        <v>136</v>
+        <v>168</v>
       </c>
       <c r="N39" t="s">
-        <v>137</v>
+        <v>169</v>
       </c>
       <c r="O39" t="s">
         <v>161</v>
@@ -2835,10 +2835,10 @@
         <v>78</v>
       </c>
       <c r="M40" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="N40" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="O40" t="s">
         <v>161</v>
@@ -2873,10 +2873,10 @@
         <v>78</v>
       </c>
       <c r="M41" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="N41" t="s">
-        <v>109</v>
+        <v>131</v>
       </c>
       <c r="O41" t="s">
         <v>161</v>
@@ -2911,10 +2911,10 @@
         <v>78</v>
       </c>
       <c r="M42" t="s">
-        <v>147</v>
+        <v>86</v>
       </c>
       <c r="N42" t="s">
-        <v>148</v>
+        <v>87</v>
       </c>
       <c r="O42" t="s">
         <v>161</v>
@@ -2949,10 +2949,10 @@
         <v>78</v>
       </c>
       <c r="M43" t="s">
-        <v>86</v>
+        <v>124</v>
       </c>
       <c r="N43" t="s">
-        <v>87</v>
+        <v>125</v>
       </c>
       <c r="O43" t="s">
         <v>161</v>
@@ -2975,10 +2975,10 @@
         <v>78</v>
       </c>
       <c r="M44" t="s">
-        <v>124</v>
+        <v>147</v>
       </c>
       <c r="N44" t="s">
-        <v>125</v>
+        <v>148</v>
       </c>
       <c r="O44" t="s">
         <v>161</v>
@@ -3001,10 +3001,10 @@
         <v>78</v>
       </c>
       <c r="M45" t="s">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="N45" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="O45" t="s">
         <v>161</v>
@@ -3027,10 +3027,10 @@
         <v>78</v>
       </c>
       <c r="M46" t="s">
-        <v>142</v>
+        <v>170</v>
       </c>
       <c r="N46" t="s">
-        <v>143</v>
+        <v>171</v>
       </c>
       <c r="O46" t="s">
         <v>161</v>
@@ -3053,10 +3053,10 @@
         <v>78</v>
       </c>
       <c r="M47" t="s">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="N47" t="s">
-        <v>85</v>
+        <v>143</v>
       </c>
       <c r="O47" t="s">
         <v>161</v>
@@ -3079,10 +3079,10 @@
         <v>78</v>
       </c>
       <c r="M48" t="s">
-        <v>151</v>
+        <v>102</v>
       </c>
       <c r="N48" t="s">
-        <v>152</v>
+        <v>103</v>
       </c>
       <c r="O48" t="s">
         <v>161</v>
@@ -3105,10 +3105,10 @@
         <v>78</v>
       </c>
       <c r="M49" t="s">
-        <v>172</v>
+        <v>90</v>
       </c>
       <c r="N49" t="s">
-        <v>173</v>
+        <v>91</v>
       </c>
       <c r="O49" t="s">
         <v>161</v>
@@ -3119,10 +3119,10 @@
         <v>78</v>
       </c>
       <c r="M50" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="N50" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="O50" t="s">
         <v>161</v>
@@ -3133,10 +3133,10 @@
         <v>78</v>
       </c>
       <c r="M51" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="N51" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="O51" t="s">
         <v>161</v>
@@ -3147,10 +3147,10 @@
         <v>78</v>
       </c>
       <c r="M52" t="s">
-        <v>106</v>
+        <v>172</v>
       </c>
       <c r="N52" t="s">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="O52" t="s">
         <v>161</v>
@@ -3161,10 +3161,10 @@
         <v>78</v>
       </c>
       <c r="M53" t="s">
-        <v>144</v>
+        <v>174</v>
       </c>
       <c r="N53" t="s">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="O53" t="s">
         <v>161</v>
@@ -3175,10 +3175,10 @@
         <v>78</v>
       </c>
       <c r="M54" t="s">
-        <v>174</v>
+        <v>100</v>
       </c>
       <c r="N54" t="s">
-        <v>175</v>
+        <v>101</v>
       </c>
       <c r="O54" t="s">
         <v>161</v>
@@ -3189,10 +3189,10 @@
         <v>78</v>
       </c>
       <c r="M55" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="N55" t="s">
-        <v>117</v>
+        <v>139</v>
       </c>
       <c r="O55" t="s">
         <v>161</v>
@@ -3203,10 +3203,10 @@
         <v>78</v>
       </c>
       <c r="M56" t="s">
-        <v>157</v>
+        <v>176</v>
       </c>
       <c r="N56" t="s">
-        <v>158</v>
+        <v>177</v>
       </c>
       <c r="O56" t="s">
         <v>161</v>
@@ -3217,10 +3217,10 @@
         <v>78</v>
       </c>
       <c r="M57" t="s">
-        <v>176</v>
+        <v>153</v>
       </c>
       <c r="N57" t="s">
-        <v>177</v>
+        <v>154</v>
       </c>
       <c r="O57" t="s">
         <v>161</v>
@@ -3231,10 +3231,10 @@
         <v>78</v>
       </c>
       <c r="M58" t="s">
-        <v>98</v>
+        <v>149</v>
       </c>
       <c r="N58" t="s">
-        <v>99</v>
+        <v>150</v>
       </c>
       <c r="O58" t="s">
         <v>161</v>

--- a/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE9739FA-4879-4444-9AA7-40B4C1ADA106}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57E899C8-3175-4337-AFC4-0DAA2E4B99E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -229,9 +229,6 @@
     <t>other_indexes</t>
   </si>
   <si>
-    <t>flo_emis</t>
-  </si>
-  <si>
     <t>gas</t>
   </si>
   <si>
@@ -578,6 +575,9 @@
   </si>
   <si>
     <t>en_hop_gas_boiler,en_hop_biomass_chips,en_hop_electric_boiler,en_hp_air_10mw</t>
+  </si>
+  <si>
+    <t>*flo_emis</t>
   </si>
 </sst>
 </file>
@@ -931,19 +931,19 @@
     </row>
     <row r="9" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="V9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="2:25" x14ac:dyDescent="0.45">
@@ -951,10 +951,10 @@
         <v>32</v>
       </c>
       <c r="C10" t="s">
+        <v>70</v>
+      </c>
+      <c r="D10" t="s">
         <v>71</v>
-      </c>
-      <c r="D10" t="s">
-        <v>72</v>
       </c>
       <c r="E10" t="s">
         <v>21</v>
@@ -963,10 +963,10 @@
         <v>32</v>
       </c>
       <c r="H10" t="s">
+        <v>70</v>
+      </c>
+      <c r="I10" t="s">
         <v>71</v>
-      </c>
-      <c r="I10" t="s">
-        <v>72</v>
       </c>
       <c r="J10" t="s">
         <v>21</v>
@@ -975,10 +975,10 @@
         <v>32</v>
       </c>
       <c r="M10" t="s">
+        <v>70</v>
+      </c>
+      <c r="N10" t="s">
         <v>71</v>
-      </c>
-      <c r="N10" t="s">
-        <v>72</v>
       </c>
       <c r="O10" t="s">
         <v>21</v>
@@ -987,10 +987,10 @@
         <v>32</v>
       </c>
       <c r="R10" t="s">
+        <v>70</v>
+      </c>
+      <c r="S10" t="s">
         <v>71</v>
-      </c>
-      <c r="S10" t="s">
-        <v>72</v>
       </c>
       <c r="T10" t="s">
         <v>21</v>
@@ -999,10 +999,10 @@
         <v>32</v>
       </c>
       <c r="W10" t="s">
+        <v>70</v>
+      </c>
+      <c r="X10" t="s">
         <v>71</v>
-      </c>
-      <c r="X10" t="s">
-        <v>72</v>
       </c>
       <c r="Y10" t="s">
         <v>21</v>
@@ -1010,2234 +1010,2234 @@
     </row>
     <row r="11" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
+        <v>77</v>
+      </c>
+      <c r="C11" t="s">
         <v>78</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>79</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>80</v>
       </c>
-      <c r="E11" t="s">
-        <v>81</v>
-      </c>
       <c r="G11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H11" t="s">
+        <v>129</v>
+      </c>
+      <c r="I11" t="s">
         <v>130</v>
       </c>
-      <c r="I11" t="s">
-        <v>131</v>
-      </c>
       <c r="J11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M11" t="s">
+        <v>158</v>
+      </c>
+      <c r="N11" t="s">
         <v>159</v>
       </c>
-      <c r="N11" t="s">
-        <v>160</v>
-      </c>
       <c r="O11" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R11" t="s">
+        <v>91</v>
+      </c>
+      <c r="S11" t="s">
         <v>92</v>
       </c>
-      <c r="S11" t="s">
-        <v>93</v>
-      </c>
       <c r="T11" t="s">
+        <v>177</v>
+      </c>
+      <c r="V11" t="s">
+        <v>77</v>
+      </c>
+      <c r="W11" t="s">
+        <v>91</v>
+      </c>
+      <c r="X11" t="s">
+        <v>92</v>
+      </c>
+      <c r="Y11" t="s">
         <v>178</v>
-      </c>
-      <c r="V11" t="s">
-        <v>78</v>
-      </c>
-      <c r="W11" t="s">
-        <v>92</v>
-      </c>
-      <c r="X11" t="s">
-        <v>93</v>
-      </c>
-      <c r="Y11" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="12" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C12" t="s">
+        <v>81</v>
+      </c>
+      <c r="D12" t="s">
         <v>82</v>
       </c>
-      <c r="D12" t="s">
-        <v>83</v>
-      </c>
       <c r="E12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H12" t="s">
+        <v>121</v>
+      </c>
+      <c r="I12" t="s">
         <v>122</v>
       </c>
-      <c r="I12" t="s">
-        <v>123</v>
-      </c>
       <c r="J12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M12" t="s">
+        <v>135</v>
+      </c>
+      <c r="N12" t="s">
         <v>136</v>
       </c>
-      <c r="N12" t="s">
-        <v>137</v>
-      </c>
       <c r="O12" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R12" t="s">
+        <v>129</v>
+      </c>
+      <c r="S12" t="s">
         <v>130</v>
       </c>
-      <c r="S12" t="s">
-        <v>131</v>
-      </c>
       <c r="T12" t="s">
+        <v>177</v>
+      </c>
+      <c r="V12" t="s">
+        <v>77</v>
+      </c>
+      <c r="W12" t="s">
+        <v>129</v>
+      </c>
+      <c r="X12" t="s">
+        <v>130</v>
+      </c>
+      <c r="Y12" t="s">
         <v>178</v>
-      </c>
-      <c r="V12" t="s">
-        <v>78</v>
-      </c>
-      <c r="W12" t="s">
-        <v>130</v>
-      </c>
-      <c r="X12" t="s">
-        <v>131</v>
-      </c>
-      <c r="Y12" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="13" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C13" t="s">
+        <v>83</v>
+      </c>
+      <c r="D13" t="s">
+        <v>84</v>
+      </c>
+      <c r="E13" t="s">
+        <v>80</v>
+      </c>
+      <c r="G13" t="s">
+        <v>77</v>
+      </c>
+      <c r="H13" t="s">
+        <v>133</v>
+      </c>
+      <c r="I13" t="s">
+        <v>134</v>
+      </c>
+      <c r="J13" t="s">
+        <v>145</v>
+      </c>
+      <c r="L13" t="s">
+        <v>77</v>
+      </c>
+      <c r="M13" t="s">
         <v>78</v>
       </c>
-      <c r="C13" t="s">
-        <v>84</v>
-      </c>
-      <c r="D13" t="s">
-        <v>85</v>
-      </c>
-      <c r="E13" t="s">
-        <v>81</v>
-      </c>
-      <c r="G13" t="s">
-        <v>78</v>
-      </c>
-      <c r="H13" t="s">
-        <v>134</v>
-      </c>
-      <c r="I13" t="s">
-        <v>135</v>
-      </c>
-      <c r="J13" t="s">
-        <v>146</v>
-      </c>
-      <c r="L13" t="s">
-        <v>78</v>
-      </c>
-      <c r="M13" t="s">
+      <c r="N13" t="s">
         <v>79</v>
       </c>
-      <c r="N13" t="s">
-        <v>80</v>
-      </c>
       <c r="O13" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R13" t="s">
+        <v>121</v>
+      </c>
+      <c r="S13" t="s">
         <v>122</v>
       </c>
-      <c r="S13" t="s">
-        <v>123</v>
-      </c>
       <c r="T13" t="s">
+        <v>177</v>
+      </c>
+      <c r="V13" t="s">
+        <v>77</v>
+      </c>
+      <c r="W13" t="s">
+        <v>121</v>
+      </c>
+      <c r="X13" t="s">
+        <v>122</v>
+      </c>
+      <c r="Y13" t="s">
         <v>178</v>
-      </c>
-      <c r="V13" t="s">
-        <v>78</v>
-      </c>
-      <c r="W13" t="s">
-        <v>122</v>
-      </c>
-      <c r="X13" t="s">
-        <v>123</v>
-      </c>
-      <c r="Y13" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="14" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C14" t="s">
+        <v>85</v>
+      </c>
+      <c r="D14" t="s">
         <v>86</v>
       </c>
-      <c r="D14" t="s">
-        <v>87</v>
-      </c>
       <c r="E14" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H14" t="s">
+        <v>89</v>
+      </c>
+      <c r="I14" t="s">
         <v>90</v>
       </c>
-      <c r="I14" t="s">
-        <v>91</v>
-      </c>
       <c r="J14" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M14" t="s">
+        <v>154</v>
+      </c>
+      <c r="N14" t="s">
         <v>155</v>
       </c>
-      <c r="N14" t="s">
-        <v>156</v>
-      </c>
       <c r="O14" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R14" t="s">
+        <v>133</v>
+      </c>
+      <c r="S14" t="s">
         <v>134</v>
       </c>
-      <c r="S14" t="s">
-        <v>135</v>
-      </c>
       <c r="T14" t="s">
+        <v>177</v>
+      </c>
+      <c r="V14" t="s">
+        <v>77</v>
+      </c>
+      <c r="W14" t="s">
+        <v>133</v>
+      </c>
+      <c r="X14" t="s">
+        <v>134</v>
+      </c>
+      <c r="Y14" t="s">
         <v>178</v>
-      </c>
-      <c r="V14" t="s">
-        <v>78</v>
-      </c>
-      <c r="W14" t="s">
-        <v>134</v>
-      </c>
-      <c r="X14" t="s">
-        <v>135</v>
-      </c>
-      <c r="Y14" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="15" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
+        <v>77</v>
+      </c>
+      <c r="C15" t="s">
+        <v>87</v>
+      </c>
+      <c r="D15" t="s">
+        <v>88</v>
+      </c>
+      <c r="E15" t="s">
+        <v>80</v>
+      </c>
+      <c r="G15" t="s">
+        <v>77</v>
+      </c>
+      <c r="H15" t="s">
         <v>78</v>
       </c>
-      <c r="C15" t="s">
-        <v>88</v>
-      </c>
-      <c r="D15" t="s">
-        <v>89</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="I15" t="s">
+        <v>79</v>
+      </c>
+      <c r="J15" t="s">
+        <v>145</v>
+      </c>
+      <c r="L15" t="s">
+        <v>77</v>
+      </c>
+      <c r="M15" t="s">
+        <v>93</v>
+      </c>
+      <c r="N15" t="s">
+        <v>94</v>
+      </c>
+      <c r="O15" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>77</v>
+      </c>
+      <c r="R15" t="s">
         <v>81</v>
       </c>
-      <c r="G15" t="s">
-        <v>78</v>
-      </c>
-      <c r="H15" t="s">
-        <v>79</v>
-      </c>
-      <c r="I15" t="s">
-        <v>80</v>
-      </c>
-      <c r="J15" t="s">
-        <v>146</v>
-      </c>
-      <c r="L15" t="s">
-        <v>78</v>
-      </c>
-      <c r="M15" t="s">
-        <v>94</v>
-      </c>
-      <c r="N15" t="s">
-        <v>95</v>
-      </c>
-      <c r="O15" t="s">
-        <v>161</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>78</v>
-      </c>
-      <c r="R15" t="s">
+      <c r="S15" t="s">
         <v>82</v>
       </c>
-      <c r="S15" t="s">
-        <v>83</v>
-      </c>
       <c r="T15" t="s">
+        <v>177</v>
+      </c>
+      <c r="V15" t="s">
+        <v>77</v>
+      </c>
+      <c r="W15" t="s">
+        <v>81</v>
+      </c>
+      <c r="X15" t="s">
+        <v>82</v>
+      </c>
+      <c r="Y15" t="s">
         <v>178</v>
-      </c>
-      <c r="V15" t="s">
-        <v>78</v>
-      </c>
-      <c r="W15" t="s">
-        <v>82</v>
-      </c>
-      <c r="X15" t="s">
-        <v>83</v>
-      </c>
-      <c r="Y15" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="16" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C16" t="s">
+        <v>89</v>
+      </c>
+      <c r="D16" t="s">
         <v>90</v>
       </c>
-      <c r="D16" t="s">
-        <v>91</v>
-      </c>
       <c r="E16" t="s">
+        <v>80</v>
+      </c>
+      <c r="G16" t="s">
+        <v>77</v>
+      </c>
+      <c r="H16" t="s">
         <v>81</v>
       </c>
-      <c r="G16" t="s">
-        <v>78</v>
-      </c>
-      <c r="H16" t="s">
+      <c r="I16" t="s">
         <v>82</v>
       </c>
-      <c r="I16" t="s">
-        <v>83</v>
-      </c>
       <c r="J16" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M16" t="s">
+        <v>117</v>
+      </c>
+      <c r="N16" t="s">
         <v>118</v>
       </c>
-      <c r="N16" t="s">
-        <v>119</v>
-      </c>
       <c r="O16" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R16" t="s">
+        <v>89</v>
+      </c>
+      <c r="S16" t="s">
         <v>90</v>
       </c>
-      <c r="S16" t="s">
-        <v>91</v>
-      </c>
       <c r="T16" t="s">
+        <v>177</v>
+      </c>
+      <c r="V16" t="s">
+        <v>77</v>
+      </c>
+      <c r="W16" t="s">
+        <v>89</v>
+      </c>
+      <c r="X16" t="s">
+        <v>90</v>
+      </c>
+      <c r="Y16" t="s">
         <v>178</v>
-      </c>
-      <c r="V16" t="s">
-        <v>78</v>
-      </c>
-      <c r="W16" t="s">
-        <v>90</v>
-      </c>
-      <c r="X16" t="s">
-        <v>91</v>
-      </c>
-      <c r="Y16" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="17" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C17" t="s">
+        <v>91</v>
+      </c>
+      <c r="D17" t="s">
         <v>92</v>
       </c>
-      <c r="D17" t="s">
-        <v>93</v>
-      </c>
       <c r="E17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H17" t="s">
+        <v>83</v>
+      </c>
+      <c r="I17" t="s">
         <v>84</v>
       </c>
-      <c r="I17" t="s">
-        <v>85</v>
-      </c>
       <c r="J17" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M17" t="s">
+        <v>125</v>
+      </c>
+      <c r="N17" t="s">
         <v>126</v>
       </c>
-      <c r="N17" t="s">
-        <v>127</v>
-      </c>
       <c r="O17" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R17" t="s">
+        <v>103</v>
+      </c>
+      <c r="S17" t="s">
         <v>104</v>
       </c>
-      <c r="S17" t="s">
-        <v>105</v>
-      </c>
       <c r="T17" t="s">
+        <v>177</v>
+      </c>
+      <c r="V17" t="s">
+        <v>77</v>
+      </c>
+      <c r="W17" t="s">
+        <v>103</v>
+      </c>
+      <c r="X17" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y17" t="s">
         <v>178</v>
-      </c>
-      <c r="V17" t="s">
-        <v>78</v>
-      </c>
-      <c r="W17" t="s">
-        <v>104</v>
-      </c>
-      <c r="X17" t="s">
-        <v>105</v>
-      </c>
-      <c r="Y17" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="18" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C18" t="s">
+        <v>93</v>
+      </c>
+      <c r="D18" t="s">
         <v>94</v>
       </c>
-      <c r="D18" t="s">
-        <v>95</v>
-      </c>
       <c r="E18" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H18" t="s">
+        <v>85</v>
+      </c>
+      <c r="I18" t="s">
         <v>86</v>
       </c>
-      <c r="I18" t="s">
-        <v>87</v>
-      </c>
       <c r="J18" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M18" t="s">
+        <v>111</v>
+      </c>
+      <c r="N18" t="s">
         <v>112</v>
       </c>
-      <c r="N18" t="s">
-        <v>113</v>
-      </c>
       <c r="O18" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R18" t="s">
+        <v>137</v>
+      </c>
+      <c r="S18" t="s">
         <v>138</v>
       </c>
-      <c r="S18" t="s">
-        <v>139</v>
-      </c>
       <c r="T18" t="s">
+        <v>177</v>
+      </c>
+      <c r="V18" t="s">
+        <v>77</v>
+      </c>
+      <c r="W18" t="s">
+        <v>137</v>
+      </c>
+      <c r="X18" t="s">
+        <v>138</v>
+      </c>
+      <c r="Y18" t="s">
         <v>178</v>
-      </c>
-      <c r="V18" t="s">
-        <v>78</v>
-      </c>
-      <c r="W18" t="s">
-        <v>138</v>
-      </c>
-      <c r="X18" t="s">
-        <v>139</v>
-      </c>
-      <c r="Y18" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="19" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C19" t="s">
+        <v>95</v>
+      </c>
+      <c r="D19" t="s">
         <v>96</v>
       </c>
-      <c r="D19" t="s">
-        <v>97</v>
-      </c>
       <c r="E19" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H19" t="s">
+        <v>87</v>
+      </c>
+      <c r="I19" t="s">
         <v>88</v>
       </c>
-      <c r="I19" t="s">
-        <v>89</v>
-      </c>
       <c r="J19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M19" t="s">
+        <v>105</v>
+      </c>
+      <c r="N19" t="s">
         <v>106</v>
       </c>
-      <c r="N19" t="s">
-        <v>107</v>
-      </c>
       <c r="O19" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R19" t="s">
+        <v>95</v>
+      </c>
+      <c r="S19" t="s">
         <v>96</v>
       </c>
-      <c r="S19" t="s">
-        <v>97</v>
-      </c>
       <c r="T19" t="s">
+        <v>177</v>
+      </c>
+      <c r="V19" t="s">
+        <v>77</v>
+      </c>
+      <c r="W19" t="s">
+        <v>95</v>
+      </c>
+      <c r="X19" t="s">
+        <v>96</v>
+      </c>
+      <c r="Y19" t="s">
         <v>178</v>
-      </c>
-      <c r="V19" t="s">
-        <v>78</v>
-      </c>
-      <c r="W19" t="s">
-        <v>96</v>
-      </c>
-      <c r="X19" t="s">
-        <v>97</v>
-      </c>
-      <c r="Y19" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="20" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C20" t="s">
+        <v>97</v>
+      </c>
+      <c r="D20" t="s">
         <v>98</v>
       </c>
-      <c r="D20" t="s">
-        <v>99</v>
-      </c>
       <c r="E20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H20" t="s">
+        <v>91</v>
+      </c>
+      <c r="I20" t="s">
         <v>92</v>
       </c>
-      <c r="I20" t="s">
-        <v>93</v>
-      </c>
       <c r="J20" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M20" t="s">
+        <v>139</v>
+      </c>
+      <c r="N20" t="s">
         <v>140</v>
       </c>
-      <c r="N20" t="s">
-        <v>141</v>
-      </c>
       <c r="O20" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R20" t="s">
+        <v>97</v>
+      </c>
+      <c r="S20" t="s">
         <v>98</v>
       </c>
-      <c r="S20" t="s">
-        <v>99</v>
-      </c>
       <c r="T20" t="s">
+        <v>177</v>
+      </c>
+      <c r="V20" t="s">
+        <v>77</v>
+      </c>
+      <c r="W20" t="s">
+        <v>97</v>
+      </c>
+      <c r="X20" t="s">
+        <v>98</v>
+      </c>
+      <c r="Y20" t="s">
         <v>178</v>
-      </c>
-      <c r="V20" t="s">
-        <v>78</v>
-      </c>
-      <c r="W20" t="s">
-        <v>98</v>
-      </c>
-      <c r="X20" t="s">
-        <v>99</v>
-      </c>
-      <c r="Y20" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="21" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C21" t="s">
+        <v>99</v>
+      </c>
+      <c r="D21" t="s">
         <v>100</v>
       </c>
-      <c r="D21" t="s">
-        <v>101</v>
-      </c>
       <c r="E21" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H21" t="s">
+        <v>93</v>
+      </c>
+      <c r="I21" t="s">
         <v>94</v>
       </c>
-      <c r="I21" t="s">
-        <v>95</v>
-      </c>
       <c r="J21" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M21" t="s">
+        <v>91</v>
+      </c>
+      <c r="N21" t="s">
         <v>92</v>
       </c>
-      <c r="N21" t="s">
-        <v>93</v>
-      </c>
       <c r="O21" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R21" t="s">
+        <v>99</v>
+      </c>
+      <c r="S21" t="s">
         <v>100</v>
       </c>
-      <c r="S21" t="s">
-        <v>101</v>
-      </c>
       <c r="T21" t="s">
+        <v>177</v>
+      </c>
+      <c r="V21" t="s">
+        <v>77</v>
+      </c>
+      <c r="W21" t="s">
+        <v>99</v>
+      </c>
+      <c r="X21" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y21" t="s">
         <v>178</v>
-      </c>
-      <c r="V21" t="s">
-        <v>78</v>
-      </c>
-      <c r="W21" t="s">
-        <v>100</v>
-      </c>
-      <c r="X21" t="s">
-        <v>101</v>
-      </c>
-      <c r="Y21" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="22" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C22" t="s">
+        <v>101</v>
+      </c>
+      <c r="D22" t="s">
         <v>102</v>
       </c>
-      <c r="D22" t="s">
-        <v>103</v>
-      </c>
       <c r="E22" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H22" t="s">
+        <v>137</v>
+      </c>
+      <c r="I22" t="s">
         <v>138</v>
       </c>
-      <c r="I22" t="s">
-        <v>139</v>
-      </c>
       <c r="J22" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M22" t="s">
+        <v>156</v>
+      </c>
+      <c r="N22" t="s">
         <v>157</v>
       </c>
-      <c r="N22" t="s">
-        <v>158</v>
-      </c>
       <c r="O22" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R22" t="s">
+        <v>101</v>
+      </c>
+      <c r="S22" t="s">
         <v>102</v>
       </c>
-      <c r="S22" t="s">
-        <v>103</v>
-      </c>
       <c r="T22" t="s">
+        <v>177</v>
+      </c>
+      <c r="V22" t="s">
+        <v>77</v>
+      </c>
+      <c r="W22" t="s">
+        <v>101</v>
+      </c>
+      <c r="X22" t="s">
+        <v>102</v>
+      </c>
+      <c r="Y22" t="s">
         <v>178</v>
-      </c>
-      <c r="V22" t="s">
-        <v>78</v>
-      </c>
-      <c r="W22" t="s">
-        <v>102</v>
-      </c>
-      <c r="X22" t="s">
-        <v>103</v>
-      </c>
-      <c r="Y22" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="23" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B23" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C23" t="s">
+        <v>103</v>
+      </c>
+      <c r="D23" t="s">
         <v>104</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
+        <v>80</v>
+      </c>
+      <c r="G23" t="s">
+        <v>77</v>
+      </c>
+      <c r="H23" t="s">
+        <v>95</v>
+      </c>
+      <c r="I23" t="s">
+        <v>96</v>
+      </c>
+      <c r="J23" t="s">
+        <v>145</v>
+      </c>
+      <c r="L23" t="s">
+        <v>77</v>
+      </c>
+      <c r="M23" t="s">
+        <v>81</v>
+      </c>
+      <c r="N23" t="s">
+        <v>82</v>
+      </c>
+      <c r="O23" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>77</v>
+      </c>
+      <c r="R23" t="s">
         <v>105</v>
       </c>
-      <c r="E23" t="s">
-        <v>81</v>
-      </c>
-      <c r="G23" t="s">
-        <v>78</v>
-      </c>
-      <c r="H23" t="s">
-        <v>96</v>
-      </c>
-      <c r="I23" t="s">
-        <v>97</v>
-      </c>
-      <c r="J23" t="s">
-        <v>146</v>
-      </c>
-      <c r="L23" t="s">
-        <v>78</v>
-      </c>
-      <c r="M23" t="s">
-        <v>82</v>
-      </c>
-      <c r="N23" t="s">
-        <v>83</v>
-      </c>
-      <c r="O23" t="s">
-        <v>161</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>78</v>
-      </c>
-      <c r="R23" t="s">
+      <c r="S23" t="s">
         <v>106</v>
       </c>
-      <c r="S23" t="s">
-        <v>107</v>
-      </c>
       <c r="T23" t="s">
+        <v>177</v>
+      </c>
+      <c r="V23" t="s">
+        <v>77</v>
+      </c>
+      <c r="W23" t="s">
+        <v>105</v>
+      </c>
+      <c r="X23" t="s">
+        <v>106</v>
+      </c>
+      <c r="Y23" t="s">
         <v>178</v>
-      </c>
-      <c r="V23" t="s">
-        <v>78</v>
-      </c>
-      <c r="W23" t="s">
-        <v>106</v>
-      </c>
-      <c r="X23" t="s">
-        <v>107</v>
-      </c>
-      <c r="Y23" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="24" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C24" t="s">
+        <v>105</v>
+      </c>
+      <c r="D24" t="s">
         <v>106</v>
       </c>
-      <c r="D24" t="s">
-        <v>107</v>
-      </c>
       <c r="E24" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G24" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H24" t="s">
+        <v>97</v>
+      </c>
+      <c r="I24" t="s">
         <v>98</v>
       </c>
-      <c r="I24" t="s">
-        <v>99</v>
-      </c>
       <c r="J24" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L24" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M24" t="s">
+        <v>87</v>
+      </c>
+      <c r="N24" t="s">
         <v>88</v>
       </c>
-      <c r="N24" t="s">
-        <v>89</v>
-      </c>
       <c r="O24" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q24" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R24" t="s">
+        <v>109</v>
+      </c>
+      <c r="S24" t="s">
         <v>110</v>
       </c>
-      <c r="S24" t="s">
-        <v>111</v>
-      </c>
       <c r="T24" t="s">
+        <v>177</v>
+      </c>
+      <c r="V24" t="s">
+        <v>77</v>
+      </c>
+      <c r="W24" t="s">
+        <v>109</v>
+      </c>
+      <c r="X24" t="s">
+        <v>110</v>
+      </c>
+      <c r="Y24" t="s">
         <v>178</v>
-      </c>
-      <c r="V24" t="s">
-        <v>78</v>
-      </c>
-      <c r="W24" t="s">
-        <v>110</v>
-      </c>
-      <c r="X24" t="s">
-        <v>111</v>
-      </c>
-      <c r="Y24" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="25" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B25" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C25" t="s">
+        <v>107</v>
+      </c>
+      <c r="D25" t="s">
         <v>108</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
+        <v>80</v>
+      </c>
+      <c r="G25" t="s">
+        <v>77</v>
+      </c>
+      <c r="H25" t="s">
+        <v>99</v>
+      </c>
+      <c r="I25" t="s">
+        <v>100</v>
+      </c>
+      <c r="J25" t="s">
+        <v>145</v>
+      </c>
+      <c r="L25" t="s">
+        <v>77</v>
+      </c>
+      <c r="M25" t="s">
         <v>109</v>
       </c>
-      <c r="E25" t="s">
-        <v>81</v>
-      </c>
-      <c r="G25" t="s">
-        <v>78</v>
-      </c>
-      <c r="H25" t="s">
-        <v>100</v>
-      </c>
-      <c r="I25" t="s">
-        <v>101</v>
-      </c>
-      <c r="J25" t="s">
-        <v>146</v>
-      </c>
-      <c r="L25" t="s">
-        <v>78</v>
-      </c>
-      <c r="M25" t="s">
+      <c r="N25" t="s">
         <v>110</v>
       </c>
-      <c r="N25" t="s">
+      <c r="O25" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>77</v>
+      </c>
+      <c r="R25" t="s">
         <v>111</v>
       </c>
-      <c r="O25" t="s">
-        <v>161</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>78</v>
-      </c>
-      <c r="R25" t="s">
+      <c r="S25" t="s">
         <v>112</v>
       </c>
-      <c r="S25" t="s">
-        <v>113</v>
-      </c>
       <c r="T25" t="s">
+        <v>177</v>
+      </c>
+      <c r="V25" t="s">
+        <v>77</v>
+      </c>
+      <c r="W25" t="s">
+        <v>111</v>
+      </c>
+      <c r="X25" t="s">
+        <v>112</v>
+      </c>
+      <c r="Y25" t="s">
         <v>178</v>
-      </c>
-      <c r="V25" t="s">
-        <v>78</v>
-      </c>
-      <c r="W25" t="s">
-        <v>112</v>
-      </c>
-      <c r="X25" t="s">
-        <v>113</v>
-      </c>
-      <c r="Y25" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="26" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B26" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C26" t="s">
+        <v>109</v>
+      </c>
+      <c r="D26" t="s">
         <v>110</v>
       </c>
-      <c r="D26" t="s">
-        <v>111</v>
-      </c>
       <c r="E26" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G26" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H26" t="s">
+        <v>101</v>
+      </c>
+      <c r="I26" t="s">
         <v>102</v>
       </c>
-      <c r="I26" t="s">
-        <v>103</v>
-      </c>
       <c r="J26" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L26" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M26" t="s">
+        <v>161</v>
+      </c>
+      <c r="N26" t="s">
         <v>162</v>
       </c>
-      <c r="N26" t="s">
-        <v>163</v>
-      </c>
       <c r="O26" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q26" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R26" t="s">
+        <v>87</v>
+      </c>
+      <c r="S26" t="s">
         <v>88</v>
       </c>
-      <c r="S26" t="s">
-        <v>89</v>
-      </c>
       <c r="T26" t="s">
+        <v>177</v>
+      </c>
+      <c r="V26" t="s">
+        <v>77</v>
+      </c>
+      <c r="W26" t="s">
+        <v>87</v>
+      </c>
+      <c r="X26" t="s">
+        <v>88</v>
+      </c>
+      <c r="Y26" t="s">
         <v>178</v>
-      </c>
-      <c r="V26" t="s">
-        <v>78</v>
-      </c>
-      <c r="W26" t="s">
-        <v>88</v>
-      </c>
-      <c r="X26" t="s">
-        <v>89</v>
-      </c>
-      <c r="Y26" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="27" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B27" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C27" t="s">
+        <v>111</v>
+      </c>
+      <c r="D27" t="s">
         <v>112</v>
       </c>
-      <c r="D27" t="s">
-        <v>113</v>
-      </c>
       <c r="E27" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G27" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H27" t="s">
+        <v>103</v>
+      </c>
+      <c r="I27" t="s">
         <v>104</v>
       </c>
-      <c r="I27" t="s">
-        <v>105</v>
-      </c>
       <c r="J27" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L27" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M27" t="s">
+        <v>115</v>
+      </c>
+      <c r="N27" t="s">
         <v>116</v>
       </c>
-      <c r="N27" t="s">
-        <v>117</v>
-      </c>
       <c r="O27" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q27" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R27" t="s">
+        <v>115</v>
+      </c>
+      <c r="S27" t="s">
         <v>116</v>
       </c>
-      <c r="S27" t="s">
-        <v>117</v>
-      </c>
       <c r="T27" t="s">
+        <v>177</v>
+      </c>
+      <c r="V27" t="s">
+        <v>77</v>
+      </c>
+      <c r="W27" t="s">
+        <v>115</v>
+      </c>
+      <c r="X27" t="s">
+        <v>116</v>
+      </c>
+      <c r="Y27" t="s">
         <v>178</v>
-      </c>
-      <c r="V27" t="s">
-        <v>78</v>
-      </c>
-      <c r="W27" t="s">
-        <v>116</v>
-      </c>
-      <c r="X27" t="s">
-        <v>117</v>
-      </c>
-      <c r="Y27" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="28" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B28" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C28" t="s">
+        <v>113</v>
+      </c>
+      <c r="D28" t="s">
         <v>114</v>
       </c>
-      <c r="D28" t="s">
-        <v>115</v>
-      </c>
       <c r="E28" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G28" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H28" t="s">
+        <v>105</v>
+      </c>
+      <c r="I28" t="s">
         <v>106</v>
       </c>
-      <c r="I28" t="s">
+      <c r="J28" t="s">
+        <v>145</v>
+      </c>
+      <c r="L28" t="s">
+        <v>77</v>
+      </c>
+      <c r="M28" t="s">
         <v>107</v>
       </c>
-      <c r="J28" t="s">
-        <v>146</v>
-      </c>
-      <c r="L28" t="s">
-        <v>78</v>
-      </c>
-      <c r="M28" t="s">
+      <c r="N28" t="s">
         <v>108</v>
       </c>
-      <c r="N28" t="s">
-        <v>109</v>
-      </c>
       <c r="O28" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q28" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R28" t="s">
+        <v>117</v>
+      </c>
+      <c r="S28" t="s">
         <v>118</v>
       </c>
-      <c r="S28" t="s">
-        <v>119</v>
-      </c>
       <c r="T28" t="s">
+        <v>177</v>
+      </c>
+      <c r="V28" t="s">
+        <v>77</v>
+      </c>
+      <c r="W28" t="s">
+        <v>117</v>
+      </c>
+      <c r="X28" t="s">
+        <v>118</v>
+      </c>
+      <c r="Y28" t="s">
         <v>178</v>
-      </c>
-      <c r="V28" t="s">
-        <v>78</v>
-      </c>
-      <c r="W28" t="s">
-        <v>118</v>
-      </c>
-      <c r="X28" t="s">
-        <v>119</v>
-      </c>
-      <c r="Y28" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="29" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B29" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C29" t="s">
+        <v>115</v>
+      </c>
+      <c r="D29" t="s">
         <v>116</v>
       </c>
-      <c r="D29" t="s">
-        <v>117</v>
-      </c>
       <c r="E29" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G29" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H29" t="s">
+        <v>107</v>
+      </c>
+      <c r="I29" t="s">
         <v>108</v>
       </c>
-      <c r="I29" t="s">
-        <v>109</v>
-      </c>
       <c r="J29" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L29" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M29" t="s">
+        <v>143</v>
+      </c>
+      <c r="N29" t="s">
         <v>144</v>
       </c>
-      <c r="N29" t="s">
-        <v>145</v>
-      </c>
       <c r="O29" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q29" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R29" t="s">
+        <v>119</v>
+      </c>
+      <c r="S29" t="s">
         <v>120</v>
       </c>
-      <c r="S29" t="s">
-        <v>121</v>
-      </c>
       <c r="T29" t="s">
+        <v>177</v>
+      </c>
+      <c r="V29" t="s">
+        <v>77</v>
+      </c>
+      <c r="W29" t="s">
+        <v>119</v>
+      </c>
+      <c r="X29" t="s">
+        <v>120</v>
+      </c>
+      <c r="Y29" t="s">
         <v>178</v>
-      </c>
-      <c r="V29" t="s">
-        <v>78</v>
-      </c>
-      <c r="W29" t="s">
-        <v>120</v>
-      </c>
-      <c r="X29" t="s">
-        <v>121</v>
-      </c>
-      <c r="Y29" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="30" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B30" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C30" t="s">
+        <v>117</v>
+      </c>
+      <c r="D30" t="s">
         <v>118</v>
       </c>
-      <c r="D30" t="s">
-        <v>119</v>
-      </c>
       <c r="E30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G30" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H30" t="s">
+        <v>109</v>
+      </c>
+      <c r="I30" t="s">
         <v>110</v>
       </c>
-      <c r="I30" t="s">
-        <v>111</v>
-      </c>
       <c r="J30" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L30" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M30" t="s">
+        <v>83</v>
+      </c>
+      <c r="N30" t="s">
         <v>84</v>
       </c>
-      <c r="N30" t="s">
+      <c r="O30" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>77</v>
+      </c>
+      <c r="R30" t="s">
         <v>85</v>
       </c>
-      <c r="O30" t="s">
-        <v>161</v>
-      </c>
-      <c r="Q30" t="s">
-        <v>78</v>
-      </c>
-      <c r="R30" t="s">
+      <c r="S30" t="s">
         <v>86</v>
       </c>
-      <c r="S30" t="s">
-        <v>87</v>
-      </c>
       <c r="T30" t="s">
+        <v>177</v>
+      </c>
+      <c r="V30" t="s">
+        <v>77</v>
+      </c>
+      <c r="W30" t="s">
+        <v>85</v>
+      </c>
+      <c r="X30" t="s">
+        <v>86</v>
+      </c>
+      <c r="Y30" t="s">
         <v>178</v>
-      </c>
-      <c r="V30" t="s">
-        <v>78</v>
-      </c>
-      <c r="W30" t="s">
-        <v>86</v>
-      </c>
-      <c r="X30" t="s">
-        <v>87</v>
-      </c>
-      <c r="Y30" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="31" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B31" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C31" t="s">
+        <v>119</v>
+      </c>
+      <c r="D31" t="s">
         <v>120</v>
       </c>
-      <c r="D31" t="s">
-        <v>121</v>
-      </c>
       <c r="E31" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G31" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H31" t="s">
+        <v>111</v>
+      </c>
+      <c r="I31" t="s">
         <v>112</v>
       </c>
-      <c r="I31" t="s">
+      <c r="J31" t="s">
+        <v>145</v>
+      </c>
+      <c r="L31" t="s">
+        <v>77</v>
+      </c>
+      <c r="M31" t="s">
         <v>113</v>
       </c>
-      <c r="J31" t="s">
-        <v>146</v>
-      </c>
-      <c r="L31" t="s">
-        <v>78</v>
-      </c>
-      <c r="M31" t="s">
+      <c r="N31" t="s">
         <v>114</v>
       </c>
-      <c r="N31" t="s">
-        <v>115</v>
-      </c>
       <c r="O31" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q31" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R31" t="s">
+        <v>123</v>
+      </c>
+      <c r="S31" t="s">
         <v>124</v>
       </c>
-      <c r="S31" t="s">
-        <v>125</v>
-      </c>
       <c r="T31" t="s">
+        <v>177</v>
+      </c>
+      <c r="V31" t="s">
+        <v>77</v>
+      </c>
+      <c r="W31" t="s">
+        <v>123</v>
+      </c>
+      <c r="X31" t="s">
+        <v>124</v>
+      </c>
+      <c r="Y31" t="s">
         <v>178</v>
-      </c>
-      <c r="V31" t="s">
-        <v>78</v>
-      </c>
-      <c r="W31" t="s">
-        <v>124</v>
-      </c>
-      <c r="X31" t="s">
-        <v>125</v>
-      </c>
-      <c r="Y31" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="32" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B32" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C32" t="s">
+        <v>121</v>
+      </c>
+      <c r="D32" t="s">
         <v>122</v>
       </c>
-      <c r="D32" t="s">
-        <v>123</v>
-      </c>
       <c r="E32" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G32" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H32" t="s">
+        <v>113</v>
+      </c>
+      <c r="I32" t="s">
         <v>114</v>
       </c>
-      <c r="I32" t="s">
-        <v>115</v>
-      </c>
       <c r="J32" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L32" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M32" t="s">
+        <v>163</v>
+      </c>
+      <c r="N32" t="s">
         <v>164</v>
       </c>
-      <c r="N32" t="s">
-        <v>165</v>
-      </c>
       <c r="O32" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q32" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R32" t="s">
+        <v>125</v>
+      </c>
+      <c r="S32" t="s">
         <v>126</v>
       </c>
-      <c r="S32" t="s">
-        <v>127</v>
-      </c>
       <c r="T32" t="s">
+        <v>177</v>
+      </c>
+      <c r="V32" t="s">
+        <v>77</v>
+      </c>
+      <c r="W32" t="s">
+        <v>125</v>
+      </c>
+      <c r="X32" t="s">
+        <v>126</v>
+      </c>
+      <c r="Y32" t="s">
         <v>178</v>
-      </c>
-      <c r="V32" t="s">
-        <v>78</v>
-      </c>
-      <c r="W32" t="s">
-        <v>126</v>
-      </c>
-      <c r="X32" t="s">
-        <v>127</v>
-      </c>
-      <c r="Y32" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="33" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B33" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C33" t="s">
+        <v>123</v>
+      </c>
+      <c r="D33" t="s">
         <v>124</v>
       </c>
-      <c r="D33" t="s">
-        <v>125</v>
-      </c>
       <c r="E33" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G33" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H33" t="s">
+        <v>115</v>
+      </c>
+      <c r="I33" t="s">
         <v>116</v>
       </c>
-      <c r="I33" t="s">
-        <v>117</v>
-      </c>
       <c r="J33" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L33" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M33" t="s">
+        <v>127</v>
+      </c>
+      <c r="N33" t="s">
         <v>128</v>
       </c>
-      <c r="N33" t="s">
-        <v>129</v>
-      </c>
       <c r="O33" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q33" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R33" t="s">
+        <v>113</v>
+      </c>
+      <c r="S33" t="s">
         <v>114</v>
       </c>
-      <c r="S33" t="s">
-        <v>115</v>
-      </c>
       <c r="T33" t="s">
+        <v>177</v>
+      </c>
+      <c r="V33" t="s">
+        <v>77</v>
+      </c>
+      <c r="W33" t="s">
+        <v>113</v>
+      </c>
+      <c r="X33" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y33" t="s">
         <v>178</v>
-      </c>
-      <c r="V33" t="s">
-        <v>78</v>
-      </c>
-      <c r="W33" t="s">
-        <v>114</v>
-      </c>
-      <c r="X33" t="s">
-        <v>115</v>
-      </c>
-      <c r="Y33" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="34" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B34" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C34" t="s">
+        <v>125</v>
+      </c>
+      <c r="D34" t="s">
         <v>126</v>
       </c>
-      <c r="D34" t="s">
+      <c r="E34" t="s">
+        <v>80</v>
+      </c>
+      <c r="G34" t="s">
+        <v>77</v>
+      </c>
+      <c r="H34" t="s">
+        <v>117</v>
+      </c>
+      <c r="I34" t="s">
+        <v>118</v>
+      </c>
+      <c r="J34" t="s">
+        <v>145</v>
+      </c>
+      <c r="L34" t="s">
+        <v>77</v>
+      </c>
+      <c r="M34" t="s">
+        <v>150</v>
+      </c>
+      <c r="N34" t="s">
+        <v>151</v>
+      </c>
+      <c r="O34" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>77</v>
+      </c>
+      <c r="R34" t="s">
         <v>127</v>
       </c>
-      <c r="E34" t="s">
-        <v>81</v>
-      </c>
-      <c r="G34" t="s">
-        <v>78</v>
-      </c>
-      <c r="H34" t="s">
-        <v>118</v>
-      </c>
-      <c r="I34" t="s">
-        <v>119</v>
-      </c>
-      <c r="J34" t="s">
-        <v>146</v>
-      </c>
-      <c r="L34" t="s">
-        <v>78</v>
-      </c>
-      <c r="M34" t="s">
-        <v>151</v>
-      </c>
-      <c r="N34" t="s">
-        <v>152</v>
-      </c>
-      <c r="O34" t="s">
-        <v>161</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>78</v>
-      </c>
-      <c r="R34" t="s">
+      <c r="S34" t="s">
         <v>128</v>
       </c>
-      <c r="S34" t="s">
-        <v>129</v>
-      </c>
       <c r="T34" t="s">
+        <v>177</v>
+      </c>
+      <c r="V34" t="s">
+        <v>77</v>
+      </c>
+      <c r="W34" t="s">
+        <v>127</v>
+      </c>
+      <c r="X34" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y34" t="s">
         <v>178</v>
-      </c>
-      <c r="V34" t="s">
-        <v>78</v>
-      </c>
-      <c r="W34" t="s">
-        <v>128</v>
-      </c>
-      <c r="X34" t="s">
-        <v>129</v>
-      </c>
-      <c r="Y34" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="35" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B35" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C35" t="s">
+        <v>127</v>
+      </c>
+      <c r="D35" t="s">
         <v>128</v>
       </c>
-      <c r="D35" t="s">
-        <v>129</v>
-      </c>
       <c r="E35" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G35" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H35" t="s">
+        <v>119</v>
+      </c>
+      <c r="I35" t="s">
         <v>120</v>
       </c>
-      <c r="I35" t="s">
-        <v>121</v>
-      </c>
       <c r="J35" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L35" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M35" t="s">
+        <v>165</v>
+      </c>
+      <c r="N35" t="s">
         <v>166</v>
       </c>
-      <c r="N35" t="s">
-        <v>167</v>
-      </c>
       <c r="O35" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q35" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R35" t="s">
+        <v>93</v>
+      </c>
+      <c r="S35" t="s">
         <v>94</v>
       </c>
-      <c r="S35" t="s">
-        <v>95</v>
-      </c>
       <c r="T35" t="s">
+        <v>177</v>
+      </c>
+      <c r="V35" t="s">
+        <v>77</v>
+      </c>
+      <c r="W35" t="s">
+        <v>93</v>
+      </c>
+      <c r="X35" t="s">
+        <v>94</v>
+      </c>
+      <c r="Y35" t="s">
         <v>178</v>
-      </c>
-      <c r="V35" t="s">
-        <v>78</v>
-      </c>
-      <c r="W35" t="s">
-        <v>94</v>
-      </c>
-      <c r="X35" t="s">
-        <v>95</v>
-      </c>
-      <c r="Y35" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="36" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B36" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C36" t="s">
+        <v>129</v>
+      </c>
+      <c r="D36" t="s">
         <v>130</v>
       </c>
-      <c r="D36" t="s">
+      <c r="E36" t="s">
+        <v>80</v>
+      </c>
+      <c r="G36" t="s">
+        <v>77</v>
+      </c>
+      <c r="H36" t="s">
+        <v>123</v>
+      </c>
+      <c r="I36" t="s">
+        <v>124</v>
+      </c>
+      <c r="J36" t="s">
+        <v>145</v>
+      </c>
+      <c r="L36" t="s">
+        <v>77</v>
+      </c>
+      <c r="M36" t="s">
+        <v>103</v>
+      </c>
+      <c r="N36" t="s">
+        <v>104</v>
+      </c>
+      <c r="O36" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>77</v>
+      </c>
+      <c r="R36" t="s">
         <v>131</v>
       </c>
-      <c r="E36" t="s">
-        <v>81</v>
-      </c>
-      <c r="G36" t="s">
-        <v>78</v>
-      </c>
-      <c r="H36" t="s">
-        <v>124</v>
-      </c>
-      <c r="I36" t="s">
-        <v>125</v>
-      </c>
-      <c r="J36" t="s">
-        <v>146</v>
-      </c>
-      <c r="L36" t="s">
-        <v>78</v>
-      </c>
-      <c r="M36" t="s">
-        <v>104</v>
-      </c>
-      <c r="N36" t="s">
-        <v>105</v>
-      </c>
-      <c r="O36" t="s">
-        <v>161</v>
-      </c>
-      <c r="Q36" t="s">
-        <v>78</v>
-      </c>
-      <c r="R36" t="s">
+      <c r="S36" t="s">
         <v>132</v>
       </c>
-      <c r="S36" t="s">
-        <v>133</v>
-      </c>
       <c r="T36" t="s">
+        <v>177</v>
+      </c>
+      <c r="V36" t="s">
+        <v>77</v>
+      </c>
+      <c r="W36" t="s">
+        <v>131</v>
+      </c>
+      <c r="X36" t="s">
+        <v>132</v>
+      </c>
+      <c r="Y36" t="s">
         <v>178</v>
-      </c>
-      <c r="V36" t="s">
-        <v>78</v>
-      </c>
-      <c r="W36" t="s">
-        <v>132</v>
-      </c>
-      <c r="X36" t="s">
-        <v>133</v>
-      </c>
-      <c r="Y36" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="37" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B37" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C37" t="s">
+        <v>131</v>
+      </c>
+      <c r="D37" t="s">
         <v>132</v>
       </c>
-      <c r="D37" t="s">
-        <v>133</v>
-      </c>
       <c r="E37" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G37" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H37" t="s">
+        <v>125</v>
+      </c>
+      <c r="I37" t="s">
         <v>126</v>
       </c>
-      <c r="I37" t="s">
-        <v>127</v>
-      </c>
       <c r="J37" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L37" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M37" t="s">
+        <v>131</v>
+      </c>
+      <c r="N37" t="s">
         <v>132</v>
       </c>
-      <c r="N37" t="s">
-        <v>133</v>
-      </c>
       <c r="O37" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q37" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R37" t="s">
+        <v>135</v>
+      </c>
+      <c r="S37" t="s">
         <v>136</v>
       </c>
-      <c r="S37" t="s">
-        <v>137</v>
-      </c>
       <c r="T37" t="s">
+        <v>177</v>
+      </c>
+      <c r="V37" t="s">
+        <v>77</v>
+      </c>
+      <c r="W37" t="s">
+        <v>135</v>
+      </c>
+      <c r="X37" t="s">
+        <v>136</v>
+      </c>
+      <c r="Y37" t="s">
         <v>178</v>
-      </c>
-      <c r="V37" t="s">
-        <v>78</v>
-      </c>
-      <c r="W37" t="s">
-        <v>136</v>
-      </c>
-      <c r="X37" t="s">
-        <v>137</v>
-      </c>
-      <c r="Y37" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="38" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B38" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C38" t="s">
+        <v>133</v>
+      </c>
+      <c r="D38" t="s">
         <v>134</v>
       </c>
-      <c r="D38" t="s">
-        <v>135</v>
-      </c>
       <c r="E38" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G38" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H38" t="s">
+        <v>127</v>
+      </c>
+      <c r="I38" t="s">
         <v>128</v>
       </c>
-      <c r="I38" t="s">
-        <v>129</v>
-      </c>
       <c r="J38" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L38" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M38" t="s">
+        <v>121</v>
+      </c>
+      <c r="N38" t="s">
         <v>122</v>
       </c>
-      <c r="N38" t="s">
-        <v>123</v>
-      </c>
       <c r="O38" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q38" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R38" t="s">
+        <v>139</v>
+      </c>
+      <c r="S38" t="s">
         <v>140</v>
       </c>
-      <c r="S38" t="s">
-        <v>141</v>
-      </c>
       <c r="T38" t="s">
+        <v>177</v>
+      </c>
+      <c r="V38" t="s">
+        <v>77</v>
+      </c>
+      <c r="W38" t="s">
+        <v>139</v>
+      </c>
+      <c r="X38" t="s">
+        <v>140</v>
+      </c>
+      <c r="Y38" t="s">
         <v>178</v>
-      </c>
-      <c r="V38" t="s">
-        <v>78</v>
-      </c>
-      <c r="W38" t="s">
-        <v>140</v>
-      </c>
-      <c r="X38" t="s">
-        <v>141</v>
-      </c>
-      <c r="Y38" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="39" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B39" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C39" t="s">
+        <v>135</v>
+      </c>
+      <c r="D39" t="s">
         <v>136</v>
       </c>
-      <c r="D39" t="s">
-        <v>137</v>
-      </c>
       <c r="E39" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G39" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H39" t="s">
+        <v>131</v>
+      </c>
+      <c r="I39" t="s">
         <v>132</v>
       </c>
-      <c r="I39" t="s">
-        <v>133</v>
-      </c>
       <c r="J39" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L39" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M39" t="s">
+        <v>167</v>
+      </c>
+      <c r="N39" t="s">
         <v>168</v>
       </c>
-      <c r="N39" t="s">
-        <v>169</v>
-      </c>
       <c r="O39" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="Q39" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="R39" t="s">
+        <v>143</v>
+      </c>
+      <c r="S39" t="s">
         <v>144</v>
       </c>
-      <c r="S39" t="s">
-        <v>145</v>
-      </c>
       <c r="T39" t="s">
+        <v>177</v>
+      </c>
+      <c r="V39" t="s">
+        <v>77</v>
+      </c>
+      <c r="W39" t="s">
+        <v>143</v>
+      </c>
+      <c r="X39" t="s">
+        <v>144</v>
+      </c>
+      <c r="Y39" t="s">
         <v>178</v>
-      </c>
-      <c r="V39" t="s">
-        <v>78</v>
-      </c>
-      <c r="W39" t="s">
-        <v>144</v>
-      </c>
-      <c r="X39" t="s">
-        <v>145</v>
-      </c>
-      <c r="Y39" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="40" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B40" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C40" t="s">
+        <v>137</v>
+      </c>
+      <c r="D40" t="s">
         <v>138</v>
       </c>
-      <c r="D40" t="s">
-        <v>139</v>
-      </c>
       <c r="E40" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G40" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H40" t="s">
+        <v>146</v>
+      </c>
+      <c r="I40" t="s">
         <v>147</v>
       </c>
-      <c r="I40" t="s">
-        <v>148</v>
-      </c>
       <c r="J40" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L40" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M40" t="s">
+        <v>97</v>
+      </c>
+      <c r="N40" t="s">
         <v>98</v>
       </c>
-      <c r="N40" t="s">
-        <v>99</v>
-      </c>
       <c r="O40" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="41" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B41" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C41" t="s">
+        <v>139</v>
+      </c>
+      <c r="D41" t="s">
         <v>140</v>
       </c>
-      <c r="D41" t="s">
-        <v>141</v>
-      </c>
       <c r="E41" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G41" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H41" t="s">
+        <v>148</v>
+      </c>
+      <c r="I41" t="s">
         <v>149</v>
       </c>
-      <c r="I41" t="s">
-        <v>150</v>
-      </c>
       <c r="J41" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L41" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M41" t="s">
+        <v>129</v>
+      </c>
+      <c r="N41" t="s">
         <v>130</v>
       </c>
-      <c r="N41" t="s">
-        <v>131</v>
-      </c>
       <c r="O41" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="42" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B42" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C42" t="s">
+        <v>141</v>
+      </c>
+      <c r="D42" t="s">
         <v>142</v>
       </c>
-      <c r="D42" t="s">
-        <v>143</v>
-      </c>
       <c r="E42" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G42" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H42" t="s">
+        <v>150</v>
+      </c>
+      <c r="I42" t="s">
         <v>151</v>
       </c>
-      <c r="I42" t="s">
-        <v>152</v>
-      </c>
       <c r="J42" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L42" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M42" t="s">
+        <v>85</v>
+      </c>
+      <c r="N42" t="s">
         <v>86</v>
       </c>
-      <c r="N42" t="s">
-        <v>87</v>
-      </c>
       <c r="O42" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="43" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B43" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C43" t="s">
+        <v>143</v>
+      </c>
+      <c r="D43" t="s">
         <v>144</v>
       </c>
-      <c r="D43" t="s">
+      <c r="E43" t="s">
+        <v>80</v>
+      </c>
+      <c r="G43" t="s">
+        <v>77</v>
+      </c>
+      <c r="H43" t="s">
+        <v>135</v>
+      </c>
+      <c r="I43" t="s">
+        <v>136</v>
+      </c>
+      <c r="J43" t="s">
         <v>145</v>
       </c>
-      <c r="E43" t="s">
-        <v>81</v>
-      </c>
-      <c r="G43" t="s">
-        <v>78</v>
-      </c>
-      <c r="H43" t="s">
-        <v>136</v>
-      </c>
-      <c r="I43" t="s">
-        <v>137</v>
-      </c>
-      <c r="J43" t="s">
-        <v>146</v>
-      </c>
       <c r="L43" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M43" t="s">
+        <v>123</v>
+      </c>
+      <c r="N43" t="s">
         <v>124</v>
       </c>
-      <c r="N43" t="s">
-        <v>125</v>
-      </c>
       <c r="O43" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="44" spans="2:25" x14ac:dyDescent="0.45">
       <c r="G44" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H44" t="s">
+        <v>139</v>
+      </c>
+      <c r="I44" t="s">
         <v>140</v>
       </c>
-      <c r="I44" t="s">
-        <v>141</v>
-      </c>
       <c r="J44" t="s">
+        <v>145</v>
+      </c>
+      <c r="L44" t="s">
+        <v>77</v>
+      </c>
+      <c r="M44" t="s">
         <v>146</v>
       </c>
-      <c r="L44" t="s">
-        <v>78</v>
-      </c>
-      <c r="M44" t="s">
+      <c r="N44" t="s">
         <v>147</v>
       </c>
-      <c r="N44" t="s">
-        <v>148</v>
-      </c>
       <c r="O44" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.45">
       <c r="G45" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H45" t="s">
+        <v>141</v>
+      </c>
+      <c r="I45" t="s">
         <v>142</v>
       </c>
-      <c r="I45" t="s">
-        <v>143</v>
-      </c>
       <c r="J45" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L45" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M45" t="s">
+        <v>133</v>
+      </c>
+      <c r="N45" t="s">
         <v>134</v>
       </c>
-      <c r="N45" t="s">
-        <v>135</v>
-      </c>
       <c r="O45" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="46" spans="2:25" x14ac:dyDescent="0.45">
       <c r="G46" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H46" t="s">
+        <v>143</v>
+      </c>
+      <c r="I46" t="s">
         <v>144</v>
       </c>
-      <c r="I46" t="s">
+      <c r="J46" t="s">
         <v>145</v>
       </c>
-      <c r="J46" t="s">
-        <v>146</v>
-      </c>
       <c r="L46" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M46" t="s">
+        <v>169</v>
+      </c>
+      <c r="N46" t="s">
         <v>170</v>
       </c>
-      <c r="N46" t="s">
-        <v>171</v>
-      </c>
       <c r="O46" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="47" spans="2:25" x14ac:dyDescent="0.45">
       <c r="G47" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H47" t="s">
+        <v>152</v>
+      </c>
+      <c r="I47" t="s">
         <v>153</v>
       </c>
-      <c r="I47" t="s">
-        <v>154</v>
-      </c>
       <c r="J47" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L47" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M47" t="s">
+        <v>141</v>
+      </c>
+      <c r="N47" t="s">
         <v>142</v>
       </c>
-      <c r="N47" t="s">
-        <v>143</v>
-      </c>
       <c r="O47" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="48" spans="2:25" x14ac:dyDescent="0.45">
       <c r="G48" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H48" t="s">
+        <v>154</v>
+      </c>
+      <c r="I48" t="s">
         <v>155</v>
       </c>
-      <c r="I48" t="s">
-        <v>156</v>
-      </c>
       <c r="J48" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L48" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M48" t="s">
+        <v>101</v>
+      </c>
+      <c r="N48" t="s">
         <v>102</v>
       </c>
-      <c r="N48" t="s">
-        <v>103</v>
-      </c>
       <c r="O48" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="49" spans="7:15" x14ac:dyDescent="0.45">
       <c r="G49" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="H49" t="s">
+        <v>156</v>
+      </c>
+      <c r="I49" t="s">
         <v>157</v>
       </c>
-      <c r="I49" t="s">
-        <v>158</v>
-      </c>
       <c r="J49" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="L49" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M49" t="s">
+        <v>89</v>
+      </c>
+      <c r="N49" t="s">
         <v>90</v>
       </c>
-      <c r="N49" t="s">
-        <v>91</v>
-      </c>
       <c r="O49" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="50" spans="7:15" x14ac:dyDescent="0.45">
       <c r="L50" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M50" t="s">
+        <v>119</v>
+      </c>
+      <c r="N50" t="s">
         <v>120</v>
       </c>
-      <c r="N50" t="s">
-        <v>121</v>
-      </c>
       <c r="O50" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="51" spans="7:15" x14ac:dyDescent="0.45">
       <c r="L51" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M51" t="s">
+        <v>95</v>
+      </c>
+      <c r="N51" t="s">
         <v>96</v>
       </c>
-      <c r="N51" t="s">
-        <v>97</v>
-      </c>
       <c r="O51" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="52" spans="7:15" x14ac:dyDescent="0.45">
       <c r="L52" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M52" t="s">
+        <v>171</v>
+      </c>
+      <c r="N52" t="s">
         <v>172</v>
       </c>
-      <c r="N52" t="s">
-        <v>173</v>
-      </c>
       <c r="O52" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="53" spans="7:15" x14ac:dyDescent="0.45">
       <c r="L53" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M53" t="s">
+        <v>173</v>
+      </c>
+      <c r="N53" t="s">
         <v>174</v>
       </c>
-      <c r="N53" t="s">
-        <v>175</v>
-      </c>
       <c r="O53" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="54" spans="7:15" x14ac:dyDescent="0.45">
       <c r="L54" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M54" t="s">
+        <v>99</v>
+      </c>
+      <c r="N54" t="s">
         <v>100</v>
       </c>
-      <c r="N54" t="s">
-        <v>101</v>
-      </c>
       <c r="O54" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="55" spans="7:15" x14ac:dyDescent="0.45">
       <c r="L55" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M55" t="s">
+        <v>137</v>
+      </c>
+      <c r="N55" t="s">
         <v>138</v>
       </c>
-      <c r="N55" t="s">
-        <v>139</v>
-      </c>
       <c r="O55" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="56" spans="7:15" x14ac:dyDescent="0.45">
       <c r="L56" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M56" t="s">
+        <v>175</v>
+      </c>
+      <c r="N56" t="s">
         <v>176</v>
       </c>
-      <c r="N56" t="s">
-        <v>177</v>
-      </c>
       <c r="O56" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="57" spans="7:15" x14ac:dyDescent="0.45">
       <c r="L57" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M57" t="s">
+        <v>152</v>
+      </c>
+      <c r="N57" t="s">
         <v>153</v>
       </c>
-      <c r="N57" t="s">
-        <v>154</v>
-      </c>
       <c r="O57" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="58" spans="7:15" x14ac:dyDescent="0.45">
       <c r="L58" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M58" t="s">
+        <v>148</v>
+      </c>
+      <c r="N58" t="s">
         <v>149</v>
       </c>
-      <c r="N58" t="s">
-        <v>150</v>
-      </c>
       <c r="O58" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -3822,7 +3822,7 @@
         <v>1.5</v>
       </c>
       <c r="T24" t="str">
-        <f t="shared" ref="T18:T24" si="7">T20</f>
+        <f t="shared" ref="T24" si="7">T20</f>
         <v>E[_]WOF*</v>
       </c>
       <c r="W24" t="str">
@@ -3861,7 +3861,7 @@
     </row>
     <row r="29" spans="3:24" x14ac:dyDescent="0.45">
       <c r="C29" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D29" t="s">
         <v>6</v>
@@ -3881,7 +3881,7 @@
         <v>1</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31" spans="3:24" x14ac:dyDescent="0.45">
@@ -3947,7 +3947,7 @@
         <v>38</v>
       </c>
       <c r="D36" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G36" s="1">
         <v>0.9</v>
@@ -4040,7 +4040,7 @@
         <v>51</v>
       </c>
       <c r="F49" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G49" t="s">
         <v>50</v>
@@ -4057,7 +4057,7 @@
         <v>52</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G50" t="s">
         <v>53</v>
@@ -4085,7 +4085,7 @@
         <v>2100</v>
       </c>
       <c r="F52" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="55" spans="3:13" x14ac:dyDescent="0.45">
@@ -4130,42 +4130,42 @@
     </row>
     <row r="57" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C57" t="s">
+        <v>179</v>
+      </c>
+      <c r="E57" t="s">
         <v>63</v>
       </c>
-      <c r="E57" t="s">
-        <v>64</v>
-      </c>
       <c r="F57" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I57">
         <v>0.95</v>
       </c>
       <c r="L57" t="s">
+        <v>64</v>
+      </c>
+      <c r="M57" t="s">
         <v>65</v>
-      </c>
-      <c r="M57" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="58" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C58" t="s">
-        <v>63</v>
+        <v>179</v>
       </c>
       <c r="E58" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F58" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I58">
         <v>0.85</v>
       </c>
       <c r="L58" t="s">
+        <v>64</v>
+      </c>
+      <c r="M58" t="s">
         <v>65</v>
-      </c>
-      <c r="M58" t="s">
-        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57E899C8-3175-4337-AFC4-0DAA2E4B99E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E52EAD46-2EF1-4954-8DE8-7F3F09DB8F25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -229,6 +229,9 @@
     <t>other_indexes</t>
   </si>
   <si>
+    <t>flo_emis</t>
+  </si>
+  <si>
     <t>gas</t>
   </si>
   <si>
@@ -514,70 +517,67 @@
     <t>at grid node - Krosno_POL</t>
   </si>
   <si>
+    <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
+  </si>
+  <si>
+    <t>Zamosc_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Zamosc_POL</t>
+  </si>
+  <si>
+    <t>Chelm_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Chelm_POL</t>
+  </si>
+  <si>
+    <t>Elk_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Elk_POL</t>
+  </si>
+  <si>
+    <t>OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>at grid node - OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
     <t>Olsztyn_POL</t>
   </si>
   <si>
     <t>at grid node - Olsztyn_POL</t>
   </si>
   <si>
-    <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
-  </si>
-  <si>
-    <t>OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>at grid node - OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>Elk_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Elk_POL</t>
-  </si>
-  <si>
-    <t>Chelm_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Chelm_POL</t>
-  </si>
-  <si>
     <t>Grajewo_POL</t>
   </si>
   <si>
     <t>at grid node - Grajewo_POL</t>
   </si>
   <si>
+    <t>Slupsk_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Slupsk_POL</t>
+  </si>
+  <si>
     <t>Kielce_POL</t>
   </si>
   <si>
     <t>at grid node - Kielce_POL</t>
   </si>
   <si>
-    <t>Slupsk_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Slupsk_POL</t>
-  </si>
-  <si>
     <t>Legnica_POL</t>
   </si>
   <si>
     <t>at grid node - Legnica_POL</t>
   </si>
   <si>
-    <t>Zamosc_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Zamosc_POL</t>
-  </si>
-  <si>
     <t>h_demand</t>
   </si>
   <si>
     <t>en_hop_gas_boiler,en_hop_biomass_chips,en_hop_electric_boiler,en_hp_air_10mw</t>
-  </si>
-  <si>
-    <t>*flo_emis</t>
   </si>
 </sst>
 </file>
@@ -931,19 +931,19 @@
     </row>
     <row r="9" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Q9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="V9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="2:25" x14ac:dyDescent="0.45">
@@ -951,10 +951,10 @@
         <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E10" t="s">
         <v>21</v>
@@ -963,10 +963,10 @@
         <v>32</v>
       </c>
       <c r="H10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="J10" t="s">
         <v>21</v>
@@ -975,10 +975,10 @@
         <v>32</v>
       </c>
       <c r="M10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="N10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="O10" t="s">
         <v>21</v>
@@ -987,10 +987,10 @@
         <v>32</v>
       </c>
       <c r="R10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="S10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="T10" t="s">
         <v>21</v>
@@ -999,10 +999,10 @@
         <v>32</v>
       </c>
       <c r="W10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="X10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="Y10" t="s">
         <v>21</v>
@@ -1010,2234 +1010,2234 @@
     </row>
     <row r="11" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J11" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M11" t="s">
-        <v>158</v>
+        <v>86</v>
       </c>
       <c r="N11" t="s">
-        <v>159</v>
+        <v>87</v>
       </c>
       <c r="O11" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="R11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="S11" t="s">
+        <v>93</v>
+      </c>
+      <c r="T11" t="s">
+        <v>178</v>
+      </c>
+      <c r="V11" t="s">
+        <v>78</v>
+      </c>
+      <c r="W11" t="s">
         <v>92</v>
       </c>
-      <c r="T11" t="s">
-        <v>177</v>
-      </c>
-      <c r="V11" t="s">
-        <v>77</v>
-      </c>
-      <c r="W11" t="s">
-        <v>91</v>
-      </c>
       <c r="X11" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Y11" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C12" t="s">
+        <v>82</v>
+      </c>
+      <c r="D12" t="s">
+        <v>83</v>
+      </c>
+      <c r="E12" t="s">
         <v>81</v>
       </c>
-      <c r="D12" t="s">
-        <v>82</v>
-      </c>
-      <c r="E12" t="s">
-        <v>80</v>
-      </c>
       <c r="G12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="I12" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J12" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M12" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="N12" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="O12" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="R12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="S12" t="s">
+        <v>131</v>
+      </c>
+      <c r="T12" t="s">
+        <v>178</v>
+      </c>
+      <c r="V12" t="s">
+        <v>78</v>
+      </c>
+      <c r="W12" t="s">
         <v>130</v>
       </c>
-      <c r="T12" t="s">
-        <v>177</v>
-      </c>
-      <c r="V12" t="s">
-        <v>77</v>
-      </c>
-      <c r="W12" t="s">
-        <v>129</v>
-      </c>
       <c r="X12" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Y12" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="13" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C13" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H13" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J13" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M13" t="s">
-        <v>78</v>
+        <v>160</v>
       </c>
       <c r="N13" t="s">
-        <v>79</v>
+        <v>161</v>
       </c>
       <c r="O13" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="R13" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="S13" t="s">
+        <v>123</v>
+      </c>
+      <c r="T13" t="s">
+        <v>178</v>
+      </c>
+      <c r="V13" t="s">
+        <v>78</v>
+      </c>
+      <c r="W13" t="s">
         <v>122</v>
       </c>
-      <c r="T13" t="s">
-        <v>177</v>
-      </c>
-      <c r="V13" t="s">
-        <v>77</v>
-      </c>
-      <c r="W13" t="s">
-        <v>121</v>
-      </c>
       <c r="X13" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="Y13" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="14" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J14" t="s">
+        <v>146</v>
+      </c>
+      <c r="L14" t="s">
+        <v>78</v>
+      </c>
+      <c r="M14" t="s">
+        <v>144</v>
+      </c>
+      <c r="N14" t="s">
         <v>145</v>
       </c>
-      <c r="L14" t="s">
-        <v>77</v>
-      </c>
-      <c r="M14" t="s">
-        <v>154</v>
-      </c>
-      <c r="N14" t="s">
-        <v>155</v>
-      </c>
       <c r="O14" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q14" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="R14" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="S14" t="s">
+        <v>135</v>
+      </c>
+      <c r="T14" t="s">
+        <v>178</v>
+      </c>
+      <c r="V14" t="s">
+        <v>78</v>
+      </c>
+      <c r="W14" t="s">
         <v>134</v>
       </c>
-      <c r="T14" t="s">
-        <v>177</v>
-      </c>
-      <c r="V14" t="s">
-        <v>77</v>
-      </c>
-      <c r="W14" t="s">
-        <v>133</v>
-      </c>
       <c r="X14" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="Y14" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="15" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C15" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D15" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E15" t="s">
+        <v>81</v>
+      </c>
+      <c r="G15" t="s">
+        <v>78</v>
+      </c>
+      <c r="H15" t="s">
+        <v>79</v>
+      </c>
+      <c r="I15" t="s">
         <v>80</v>
       </c>
-      <c r="G15" t="s">
-        <v>77</v>
-      </c>
-      <c r="H15" t="s">
-        <v>78</v>
-      </c>
-      <c r="I15" t="s">
-        <v>79</v>
-      </c>
       <c r="J15" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M15" t="s">
-        <v>93</v>
+        <v>122</v>
       </c>
       <c r="N15" t="s">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="O15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="R15" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S15" t="s">
+        <v>83</v>
+      </c>
+      <c r="T15" t="s">
+        <v>178</v>
+      </c>
+      <c r="V15" t="s">
+        <v>78</v>
+      </c>
+      <c r="W15" t="s">
         <v>82</v>
       </c>
-      <c r="T15" t="s">
-        <v>177</v>
-      </c>
-      <c r="V15" t="s">
-        <v>77</v>
-      </c>
-      <c r="W15" t="s">
-        <v>81</v>
-      </c>
       <c r="X15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Y15" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="16" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C16" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D16" t="s">
+        <v>91</v>
+      </c>
+      <c r="E16" t="s">
+        <v>81</v>
+      </c>
+      <c r="G16" t="s">
+        <v>78</v>
+      </c>
+      <c r="H16" t="s">
+        <v>82</v>
+      </c>
+      <c r="I16" t="s">
+        <v>83</v>
+      </c>
+      <c r="J16" t="s">
+        <v>146</v>
+      </c>
+      <c r="L16" t="s">
+        <v>78</v>
+      </c>
+      <c r="M16" t="s">
+        <v>96</v>
+      </c>
+      <c r="N16" t="s">
+        <v>97</v>
+      </c>
+      <c r="O16" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>78</v>
+      </c>
+      <c r="R16" t="s">
         <v>90</v>
       </c>
-      <c r="E16" t="s">
-        <v>80</v>
-      </c>
-      <c r="G16" t="s">
-        <v>77</v>
-      </c>
-      <c r="H16" t="s">
-        <v>81</v>
-      </c>
-      <c r="I16" t="s">
-        <v>82</v>
-      </c>
-      <c r="J16" t="s">
-        <v>145</v>
-      </c>
-      <c r="L16" t="s">
-        <v>77</v>
-      </c>
-      <c r="M16" t="s">
-        <v>117</v>
-      </c>
-      <c r="N16" t="s">
-        <v>118</v>
-      </c>
-      <c r="O16" t="s">
-        <v>160</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>77</v>
-      </c>
-      <c r="R16" t="s">
-        <v>89</v>
-      </c>
       <c r="S16" t="s">
+        <v>91</v>
+      </c>
+      <c r="T16" t="s">
+        <v>178</v>
+      </c>
+      <c r="V16" t="s">
+        <v>78</v>
+      </c>
+      <c r="W16" t="s">
         <v>90</v>
       </c>
-      <c r="T16" t="s">
-        <v>177</v>
-      </c>
-      <c r="V16" t="s">
-        <v>77</v>
-      </c>
-      <c r="W16" t="s">
-        <v>89</v>
-      </c>
       <c r="X16" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Y16" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="17" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C17" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D17" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E17" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H17" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I17" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M17" t="s">
-        <v>125</v>
+        <v>153</v>
       </c>
       <c r="N17" t="s">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="O17" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q17" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="R17" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="S17" t="s">
+        <v>105</v>
+      </c>
+      <c r="T17" t="s">
+        <v>178</v>
+      </c>
+      <c r="V17" t="s">
+        <v>78</v>
+      </c>
+      <c r="W17" t="s">
         <v>104</v>
       </c>
-      <c r="T17" t="s">
-        <v>177</v>
-      </c>
-      <c r="V17" t="s">
-        <v>77</v>
-      </c>
-      <c r="W17" t="s">
-        <v>103</v>
-      </c>
       <c r="X17" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="Y17" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="18" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C18" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D18" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E18" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H18" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J18" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M18" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="N18" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="O18" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q18" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="R18" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="S18" t="s">
+        <v>139</v>
+      </c>
+      <c r="T18" t="s">
+        <v>178</v>
+      </c>
+      <c r="V18" t="s">
+        <v>78</v>
+      </c>
+      <c r="W18" t="s">
         <v>138</v>
       </c>
-      <c r="T18" t="s">
-        <v>177</v>
-      </c>
-      <c r="V18" t="s">
-        <v>77</v>
-      </c>
-      <c r="W18" t="s">
-        <v>137</v>
-      </c>
       <c r="X18" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="Y18" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="19" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B19" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C19" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D19" t="s">
+        <v>97</v>
+      </c>
+      <c r="E19" t="s">
+        <v>81</v>
+      </c>
+      <c r="G19" t="s">
+        <v>78</v>
+      </c>
+      <c r="H19" t="s">
+        <v>88</v>
+      </c>
+      <c r="I19" t="s">
+        <v>89</v>
+      </c>
+      <c r="J19" t="s">
+        <v>146</v>
+      </c>
+      <c r="L19" t="s">
+        <v>78</v>
+      </c>
+      <c r="M19" t="s">
+        <v>162</v>
+      </c>
+      <c r="N19" t="s">
+        <v>163</v>
+      </c>
+      <c r="O19" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>78</v>
+      </c>
+      <c r="R19" t="s">
         <v>96</v>
       </c>
-      <c r="E19" t="s">
-        <v>80</v>
-      </c>
-      <c r="G19" t="s">
-        <v>77</v>
-      </c>
-      <c r="H19" t="s">
-        <v>87</v>
-      </c>
-      <c r="I19" t="s">
-        <v>88</v>
-      </c>
-      <c r="J19" t="s">
-        <v>145</v>
-      </c>
-      <c r="L19" t="s">
-        <v>77</v>
-      </c>
-      <c r="M19" t="s">
-        <v>105</v>
-      </c>
-      <c r="N19" t="s">
-        <v>106</v>
-      </c>
-      <c r="O19" t="s">
-        <v>160</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>77</v>
-      </c>
-      <c r="R19" t="s">
-        <v>95</v>
-      </c>
       <c r="S19" t="s">
+        <v>97</v>
+      </c>
+      <c r="T19" t="s">
+        <v>178</v>
+      </c>
+      <c r="V19" t="s">
+        <v>78</v>
+      </c>
+      <c r="W19" t="s">
         <v>96</v>
       </c>
-      <c r="T19" t="s">
-        <v>177</v>
-      </c>
-      <c r="V19" t="s">
-        <v>77</v>
-      </c>
-      <c r="W19" t="s">
-        <v>95</v>
-      </c>
       <c r="X19" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Y19" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="20" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C20" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D20" t="s">
+        <v>99</v>
+      </c>
+      <c r="E20" t="s">
+        <v>81</v>
+      </c>
+      <c r="G20" t="s">
+        <v>78</v>
+      </c>
+      <c r="H20" t="s">
+        <v>92</v>
+      </c>
+      <c r="I20" t="s">
+        <v>93</v>
+      </c>
+      <c r="J20" t="s">
+        <v>146</v>
+      </c>
+      <c r="L20" t="s">
+        <v>78</v>
+      </c>
+      <c r="M20" t="s">
+        <v>164</v>
+      </c>
+      <c r="N20" t="s">
+        <v>165</v>
+      </c>
+      <c r="O20" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>78</v>
+      </c>
+      <c r="R20" t="s">
         <v>98</v>
       </c>
-      <c r="E20" t="s">
-        <v>80</v>
-      </c>
-      <c r="G20" t="s">
-        <v>77</v>
-      </c>
-      <c r="H20" t="s">
-        <v>91</v>
-      </c>
-      <c r="I20" t="s">
-        <v>92</v>
-      </c>
-      <c r="J20" t="s">
-        <v>145</v>
-      </c>
-      <c r="L20" t="s">
-        <v>77</v>
-      </c>
-      <c r="M20" t="s">
-        <v>139</v>
-      </c>
-      <c r="N20" t="s">
-        <v>140</v>
-      </c>
-      <c r="O20" t="s">
-        <v>160</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>77</v>
-      </c>
-      <c r="R20" t="s">
-        <v>97</v>
-      </c>
       <c r="S20" t="s">
+        <v>99</v>
+      </c>
+      <c r="T20" t="s">
+        <v>178</v>
+      </c>
+      <c r="V20" t="s">
+        <v>78</v>
+      </c>
+      <c r="W20" t="s">
         <v>98</v>
       </c>
-      <c r="T20" t="s">
-        <v>177</v>
-      </c>
-      <c r="V20" t="s">
-        <v>77</v>
-      </c>
-      <c r="W20" t="s">
-        <v>97</v>
-      </c>
       <c r="X20" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Y20" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="21" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B21" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C21" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D21" t="s">
+        <v>101</v>
+      </c>
+      <c r="E21" t="s">
+        <v>81</v>
+      </c>
+      <c r="G21" t="s">
+        <v>78</v>
+      </c>
+      <c r="H21" t="s">
+        <v>94</v>
+      </c>
+      <c r="I21" t="s">
+        <v>95</v>
+      </c>
+      <c r="J21" t="s">
+        <v>146</v>
+      </c>
+      <c r="L21" t="s">
+        <v>78</v>
+      </c>
+      <c r="M21" t="s">
+        <v>166</v>
+      </c>
+      <c r="N21" t="s">
+        <v>167</v>
+      </c>
+      <c r="O21" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>78</v>
+      </c>
+      <c r="R21" t="s">
         <v>100</v>
       </c>
-      <c r="E21" t="s">
-        <v>80</v>
-      </c>
-      <c r="G21" t="s">
-        <v>77</v>
-      </c>
-      <c r="H21" t="s">
-        <v>93</v>
-      </c>
-      <c r="I21" t="s">
-        <v>94</v>
-      </c>
-      <c r="J21" t="s">
-        <v>145</v>
-      </c>
-      <c r="L21" t="s">
-        <v>77</v>
-      </c>
-      <c r="M21" t="s">
-        <v>91</v>
-      </c>
-      <c r="N21" t="s">
-        <v>92</v>
-      </c>
-      <c r="O21" t="s">
-        <v>160</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>77</v>
-      </c>
-      <c r="R21" t="s">
-        <v>99</v>
-      </c>
       <c r="S21" t="s">
+        <v>101</v>
+      </c>
+      <c r="T21" t="s">
+        <v>178</v>
+      </c>
+      <c r="V21" t="s">
+        <v>78</v>
+      </c>
+      <c r="W21" t="s">
         <v>100</v>
       </c>
-      <c r="T21" t="s">
-        <v>177</v>
-      </c>
-      <c r="V21" t="s">
-        <v>77</v>
-      </c>
-      <c r="W21" t="s">
-        <v>99</v>
-      </c>
       <c r="X21" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Y21" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="22" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C22" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D22" t="s">
+        <v>103</v>
+      </c>
+      <c r="E22" t="s">
+        <v>81</v>
+      </c>
+      <c r="G22" t="s">
+        <v>78</v>
+      </c>
+      <c r="H22" t="s">
+        <v>138</v>
+      </c>
+      <c r="I22" t="s">
+        <v>139</v>
+      </c>
+      <c r="J22" t="s">
+        <v>146</v>
+      </c>
+      <c r="L22" t="s">
+        <v>78</v>
+      </c>
+      <c r="M22" t="s">
+        <v>98</v>
+      </c>
+      <c r="N22" t="s">
+        <v>99</v>
+      </c>
+      <c r="O22" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>78</v>
+      </c>
+      <c r="R22" t="s">
         <v>102</v>
       </c>
-      <c r="E22" t="s">
-        <v>80</v>
-      </c>
-      <c r="G22" t="s">
-        <v>77</v>
-      </c>
-      <c r="H22" t="s">
-        <v>137</v>
-      </c>
-      <c r="I22" t="s">
-        <v>138</v>
-      </c>
-      <c r="J22" t="s">
-        <v>145</v>
-      </c>
-      <c r="L22" t="s">
-        <v>77</v>
-      </c>
-      <c r="M22" t="s">
-        <v>156</v>
-      </c>
-      <c r="N22" t="s">
-        <v>157</v>
-      </c>
-      <c r="O22" t="s">
-        <v>160</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>77</v>
-      </c>
-      <c r="R22" t="s">
-        <v>101</v>
-      </c>
       <c r="S22" t="s">
+        <v>103</v>
+      </c>
+      <c r="T22" t="s">
+        <v>178</v>
+      </c>
+      <c r="V22" t="s">
+        <v>78</v>
+      </c>
+      <c r="W22" t="s">
         <v>102</v>
       </c>
-      <c r="T22" t="s">
-        <v>177</v>
-      </c>
-      <c r="V22" t="s">
-        <v>77</v>
-      </c>
-      <c r="W22" t="s">
-        <v>101</v>
-      </c>
       <c r="X22" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="Y22" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="23" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B23" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C23" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D23" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E23" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G23" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H23" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I23" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J23" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L23" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M23" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="N23" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="O23" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q23" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="R23" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="S23" t="s">
+        <v>107</v>
+      </c>
+      <c r="T23" t="s">
+        <v>178</v>
+      </c>
+      <c r="V23" t="s">
+        <v>78</v>
+      </c>
+      <c r="W23" t="s">
         <v>106</v>
       </c>
-      <c r="T23" t="s">
-        <v>177</v>
-      </c>
-      <c r="V23" t="s">
-        <v>77</v>
-      </c>
-      <c r="W23" t="s">
-        <v>105</v>
-      </c>
       <c r="X23" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Y23" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="24" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C24" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D24" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E24" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G24" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H24" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="I24" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J24" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L24" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M24" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="N24" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="O24" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q24" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="R24" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="S24" t="s">
+        <v>111</v>
+      </c>
+      <c r="T24" t="s">
+        <v>178</v>
+      </c>
+      <c r="V24" t="s">
+        <v>78</v>
+      </c>
+      <c r="W24" t="s">
         <v>110</v>
       </c>
-      <c r="T24" t="s">
-        <v>177</v>
-      </c>
-      <c r="V24" t="s">
-        <v>77</v>
-      </c>
-      <c r="W24" t="s">
-        <v>109</v>
-      </c>
       <c r="X24" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y24" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="25" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B25" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C25" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E25" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G25" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H25" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="I25" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J25" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L25" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M25" t="s">
-        <v>109</v>
+        <v>151</v>
       </c>
       <c r="N25" t="s">
-        <v>110</v>
+        <v>152</v>
       </c>
       <c r="O25" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q25" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="R25" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="S25" t="s">
+        <v>113</v>
+      </c>
+      <c r="T25" t="s">
+        <v>178</v>
+      </c>
+      <c r="V25" t="s">
+        <v>78</v>
+      </c>
+      <c r="W25" t="s">
         <v>112</v>
       </c>
-      <c r="T25" t="s">
-        <v>177</v>
-      </c>
-      <c r="V25" t="s">
-        <v>77</v>
-      </c>
-      <c r="W25" t="s">
-        <v>111</v>
-      </c>
       <c r="X25" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Y25" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="26" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B26" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C26" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D26" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E26" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G26" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H26" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I26" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J26" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L26" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M26" t="s">
-        <v>161</v>
+        <v>94</v>
       </c>
       <c r="N26" t="s">
-        <v>162</v>
+        <v>95</v>
       </c>
       <c r="O26" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q26" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="R26" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="S26" t="s">
+        <v>89</v>
+      </c>
+      <c r="T26" t="s">
+        <v>178</v>
+      </c>
+      <c r="V26" t="s">
+        <v>78</v>
+      </c>
+      <c r="W26" t="s">
         <v>88</v>
       </c>
-      <c r="T26" t="s">
-        <v>177</v>
-      </c>
-      <c r="V26" t="s">
-        <v>77</v>
-      </c>
-      <c r="W26" t="s">
-        <v>87</v>
-      </c>
       <c r="X26" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Y26" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="27" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B27" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C27" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D27" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E27" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G27" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I27" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J27" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L27" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M27" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="N27" t="s">
+        <v>129</v>
+      </c>
+      <c r="O27" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>78</v>
+      </c>
+      <c r="R27" t="s">
         <v>116</v>
       </c>
-      <c r="O27" t="s">
-        <v>160</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>77</v>
-      </c>
-      <c r="R27" t="s">
-        <v>115</v>
-      </c>
       <c r="S27" t="s">
+        <v>117</v>
+      </c>
+      <c r="T27" t="s">
+        <v>178</v>
+      </c>
+      <c r="V27" t="s">
+        <v>78</v>
+      </c>
+      <c r="W27" t="s">
         <v>116</v>
       </c>
-      <c r="T27" t="s">
-        <v>177</v>
-      </c>
-      <c r="V27" t="s">
-        <v>77</v>
-      </c>
-      <c r="W27" t="s">
-        <v>115</v>
-      </c>
       <c r="X27" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Y27" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="28" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B28" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C28" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D28" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E28" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G28" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H28" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I28" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J28" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L28" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M28" t="s">
-        <v>107</v>
+        <v>168</v>
       </c>
       <c r="N28" t="s">
-        <v>108</v>
+        <v>169</v>
       </c>
       <c r="O28" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q28" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="R28" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="S28" t="s">
+        <v>119</v>
+      </c>
+      <c r="T28" t="s">
+        <v>178</v>
+      </c>
+      <c r="V28" t="s">
+        <v>78</v>
+      </c>
+      <c r="W28" t="s">
         <v>118</v>
       </c>
-      <c r="T28" t="s">
-        <v>177</v>
-      </c>
-      <c r="V28" t="s">
-        <v>77</v>
-      </c>
-      <c r="W28" t="s">
-        <v>117</v>
-      </c>
       <c r="X28" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Y28" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="29" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B29" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C29" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D29" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E29" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G29" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H29" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I29" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J29" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L29" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M29" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="N29" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="O29" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q29" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="R29" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="S29" t="s">
+        <v>121</v>
+      </c>
+      <c r="T29" t="s">
+        <v>178</v>
+      </c>
+      <c r="V29" t="s">
+        <v>78</v>
+      </c>
+      <c r="W29" t="s">
         <v>120</v>
       </c>
-      <c r="T29" t="s">
-        <v>177</v>
-      </c>
-      <c r="V29" t="s">
-        <v>77</v>
-      </c>
-      <c r="W29" t="s">
-        <v>119</v>
-      </c>
       <c r="X29" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="Y29" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="30" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B30" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C30" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D30" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E30" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G30" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H30" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I30" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J30" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L30" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M30" t="s">
-        <v>83</v>
+        <v>136</v>
       </c>
       <c r="N30" t="s">
-        <v>84</v>
+        <v>137</v>
       </c>
       <c r="O30" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q30" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="R30" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="S30" t="s">
+        <v>87</v>
+      </c>
+      <c r="T30" t="s">
+        <v>178</v>
+      </c>
+      <c r="V30" t="s">
+        <v>78</v>
+      </c>
+      <c r="W30" t="s">
         <v>86</v>
       </c>
-      <c r="T30" t="s">
-        <v>177</v>
-      </c>
-      <c r="V30" t="s">
-        <v>77</v>
-      </c>
-      <c r="W30" t="s">
-        <v>85</v>
-      </c>
       <c r="X30" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="Y30" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="31" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B31" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C31" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D31" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E31" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G31" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H31" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I31" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J31" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L31" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M31" t="s">
-        <v>113</v>
+        <v>157</v>
       </c>
       <c r="N31" t="s">
-        <v>114</v>
+        <v>158</v>
       </c>
       <c r="O31" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q31" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="R31" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="S31" t="s">
+        <v>125</v>
+      </c>
+      <c r="T31" t="s">
+        <v>178</v>
+      </c>
+      <c r="V31" t="s">
+        <v>78</v>
+      </c>
+      <c r="W31" t="s">
         <v>124</v>
       </c>
-      <c r="T31" t="s">
-        <v>177</v>
-      </c>
-      <c r="V31" t="s">
-        <v>77</v>
-      </c>
-      <c r="W31" t="s">
-        <v>123</v>
-      </c>
       <c r="X31" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="Y31" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="32" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B32" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C32" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D32" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E32" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G32" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H32" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I32" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J32" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L32" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M32" t="s">
-        <v>163</v>
+        <v>104</v>
       </c>
       <c r="N32" t="s">
-        <v>164</v>
+        <v>105</v>
       </c>
       <c r="O32" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q32" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="R32" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="S32" t="s">
+        <v>127</v>
+      </c>
+      <c r="T32" t="s">
+        <v>178</v>
+      </c>
+      <c r="V32" t="s">
+        <v>78</v>
+      </c>
+      <c r="W32" t="s">
         <v>126</v>
       </c>
-      <c r="T32" t="s">
-        <v>177</v>
-      </c>
-      <c r="V32" t="s">
-        <v>77</v>
-      </c>
-      <c r="W32" t="s">
-        <v>125</v>
-      </c>
       <c r="X32" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="Y32" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="33" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B33" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C33" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D33" t="s">
+        <v>125</v>
+      </c>
+      <c r="E33" t="s">
+        <v>81</v>
+      </c>
+      <c r="G33" t="s">
+        <v>78</v>
+      </c>
+      <c r="H33" t="s">
+        <v>116</v>
+      </c>
+      <c r="I33" t="s">
+        <v>117</v>
+      </c>
+      <c r="J33" t="s">
+        <v>146</v>
+      </c>
+      <c r="L33" t="s">
+        <v>78</v>
+      </c>
+      <c r="M33" t="s">
         <v>124</v>
       </c>
-      <c r="E33" t="s">
-        <v>80</v>
-      </c>
-      <c r="G33" t="s">
-        <v>77</v>
-      </c>
-      <c r="H33" t="s">
+      <c r="N33" t="s">
+        <v>125</v>
+      </c>
+      <c r="O33" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>78</v>
+      </c>
+      <c r="R33" t="s">
+        <v>114</v>
+      </c>
+      <c r="S33" t="s">
         <v>115</v>
       </c>
-      <c r="I33" t="s">
-        <v>116</v>
-      </c>
-      <c r="J33" t="s">
-        <v>145</v>
-      </c>
-      <c r="L33" t="s">
-        <v>77</v>
-      </c>
-      <c r="M33" t="s">
-        <v>127</v>
-      </c>
-      <c r="N33" t="s">
-        <v>128</v>
-      </c>
-      <c r="O33" t="s">
-        <v>160</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>77</v>
-      </c>
-      <c r="R33" t="s">
-        <v>113</v>
-      </c>
-      <c r="S33" t="s">
+      <c r="T33" t="s">
+        <v>178</v>
+      </c>
+      <c r="V33" t="s">
+        <v>78</v>
+      </c>
+      <c r="W33" t="s">
         <v>114</v>
       </c>
-      <c r="T33" t="s">
-        <v>177</v>
-      </c>
-      <c r="V33" t="s">
-        <v>77</v>
-      </c>
-      <c r="W33" t="s">
-        <v>113</v>
-      </c>
       <c r="X33" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="Y33" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="34" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B34" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C34" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D34" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E34" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G34" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H34" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I34" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J34" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L34" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M34" t="s">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="N34" t="s">
-        <v>151</v>
+        <v>171</v>
       </c>
       <c r="O34" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q34" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="R34" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="S34" t="s">
+        <v>129</v>
+      </c>
+      <c r="T34" t="s">
+        <v>178</v>
+      </c>
+      <c r="V34" t="s">
+        <v>78</v>
+      </c>
+      <c r="W34" t="s">
         <v>128</v>
       </c>
-      <c r="T34" t="s">
-        <v>177</v>
-      </c>
-      <c r="V34" t="s">
-        <v>77</v>
-      </c>
-      <c r="W34" t="s">
-        <v>127</v>
-      </c>
       <c r="X34" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="Y34" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B35" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C35" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D35" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E35" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G35" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H35" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I35" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J35" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L35" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M35" t="s">
-        <v>165</v>
+        <v>88</v>
       </c>
       <c r="N35" t="s">
-        <v>166</v>
+        <v>89</v>
       </c>
       <c r="O35" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q35" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="R35" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="S35" t="s">
+        <v>95</v>
+      </c>
+      <c r="T35" t="s">
+        <v>178</v>
+      </c>
+      <c r="V35" t="s">
+        <v>78</v>
+      </c>
+      <c r="W35" t="s">
         <v>94</v>
       </c>
-      <c r="T35" t="s">
-        <v>177</v>
-      </c>
-      <c r="V35" t="s">
-        <v>77</v>
-      </c>
-      <c r="W35" t="s">
-        <v>93</v>
-      </c>
       <c r="X35" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Y35" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="36" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B36" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C36" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D36" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E36" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G36" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H36" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I36" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J36" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L36" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M36" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="N36" t="s">
-        <v>104</v>
+        <v>83</v>
       </c>
       <c r="O36" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q36" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="R36" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="S36" t="s">
+        <v>133</v>
+      </c>
+      <c r="T36" t="s">
+        <v>178</v>
+      </c>
+      <c r="V36" t="s">
+        <v>78</v>
+      </c>
+      <c r="W36" t="s">
         <v>132</v>
       </c>
-      <c r="T36" t="s">
-        <v>177</v>
-      </c>
-      <c r="V36" t="s">
-        <v>77</v>
-      </c>
-      <c r="W36" t="s">
-        <v>131</v>
-      </c>
       <c r="X36" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="Y36" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="37" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B37" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C37" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D37" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E37" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G37" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H37" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I37" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J37" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L37" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M37" t="s">
-        <v>131</v>
+        <v>110</v>
       </c>
       <c r="N37" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="O37" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q37" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="R37" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="S37" t="s">
+        <v>137</v>
+      </c>
+      <c r="T37" t="s">
+        <v>178</v>
+      </c>
+      <c r="V37" t="s">
+        <v>78</v>
+      </c>
+      <c r="W37" t="s">
         <v>136</v>
       </c>
-      <c r="T37" t="s">
-        <v>177</v>
-      </c>
-      <c r="V37" t="s">
-        <v>77</v>
-      </c>
-      <c r="W37" t="s">
-        <v>135</v>
-      </c>
       <c r="X37" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="Y37" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="38" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B38" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C38" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D38" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E38" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G38" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H38" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I38" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J38" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L38" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M38" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="N38" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="O38" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q38" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="R38" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="S38" t="s">
+        <v>141</v>
+      </c>
+      <c r="T38" t="s">
+        <v>178</v>
+      </c>
+      <c r="V38" t="s">
+        <v>78</v>
+      </c>
+      <c r="W38" t="s">
         <v>140</v>
       </c>
-      <c r="T38" t="s">
-        <v>177</v>
-      </c>
-      <c r="V38" t="s">
-        <v>77</v>
-      </c>
-      <c r="W38" t="s">
-        <v>139</v>
-      </c>
       <c r="X38" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="Y38" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="39" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B39" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C39" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D39" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E39" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G39" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H39" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I39" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J39" t="s">
+        <v>146</v>
+      </c>
+      <c r="L39" t="s">
+        <v>78</v>
+      </c>
+      <c r="M39" t="s">
+        <v>116</v>
+      </c>
+      <c r="N39" t="s">
+        <v>117</v>
+      </c>
+      <c r="O39" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>78</v>
+      </c>
+      <c r="R39" t="s">
+        <v>144</v>
+      </c>
+      <c r="S39" t="s">
         <v>145</v>
       </c>
-      <c r="L39" t="s">
-        <v>77</v>
-      </c>
-      <c r="M39" t="s">
-        <v>167</v>
-      </c>
-      <c r="N39" t="s">
-        <v>168</v>
-      </c>
-      <c r="O39" t="s">
-        <v>160</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>77</v>
-      </c>
-      <c r="R39" t="s">
-        <v>143</v>
-      </c>
-      <c r="S39" t="s">
+      <c r="T39" t="s">
+        <v>178</v>
+      </c>
+      <c r="V39" t="s">
+        <v>78</v>
+      </c>
+      <c r="W39" t="s">
         <v>144</v>
       </c>
-      <c r="T39" t="s">
-        <v>177</v>
-      </c>
-      <c r="V39" t="s">
-        <v>77</v>
-      </c>
-      <c r="W39" t="s">
-        <v>143</v>
-      </c>
       <c r="X39" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Y39" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="40" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B40" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C40" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D40" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E40" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G40" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H40" t="s">
+        <v>147</v>
+      </c>
+      <c r="I40" t="s">
+        <v>148</v>
+      </c>
+      <c r="J40" t="s">
         <v>146</v>
       </c>
-      <c r="I40" t="s">
-        <v>147</v>
-      </c>
-      <c r="J40" t="s">
-        <v>145</v>
-      </c>
       <c r="L40" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M40" t="s">
-        <v>97</v>
+        <v>172</v>
       </c>
       <c r="N40" t="s">
-        <v>98</v>
+        <v>173</v>
       </c>
       <c r="O40" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="41" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B41" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C41" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D41" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E41" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G41" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H41" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I41" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J41" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L41" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M41" t="s">
-        <v>129</v>
+        <v>155</v>
       </c>
       <c r="N41" t="s">
-        <v>130</v>
+        <v>156</v>
       </c>
       <c r="O41" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="42" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B42" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C42" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D42" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E42" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G42" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H42" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="I42" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J42" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L42" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M42" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="N42" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="O42" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="43" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B43" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C43" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D43" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E43" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G43" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H43" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I43" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J43" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L43" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M43" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="N43" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="O43" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="44" spans="2:25" x14ac:dyDescent="0.45">
       <c r="G44" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H44" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I44" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J44" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L44" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M44" t="s">
-        <v>146</v>
+        <v>112</v>
       </c>
       <c r="N44" t="s">
-        <v>147</v>
+        <v>113</v>
       </c>
       <c r="O44" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.45">
       <c r="G45" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H45" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I45" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J45" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L45" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M45" t="s">
+        <v>132</v>
+      </c>
+      <c r="N45" t="s">
         <v>133</v>
       </c>
-      <c r="N45" t="s">
-        <v>134</v>
-      </c>
       <c r="O45" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="46" spans="2:25" x14ac:dyDescent="0.45">
       <c r="G46" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H46" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I46" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J46" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L46" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M46" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="N46" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="O46" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="47" spans="2:25" x14ac:dyDescent="0.45">
       <c r="G47" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H47" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="I47" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J47" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L47" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M47" t="s">
-        <v>141</v>
+        <v>79</v>
       </c>
       <c r="N47" t="s">
-        <v>142</v>
+        <v>80</v>
       </c>
       <c r="O47" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="48" spans="2:25" x14ac:dyDescent="0.45">
       <c r="G48" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H48" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="I48" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J48" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L48" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M48" t="s">
-        <v>101</v>
+        <v>176</v>
       </c>
       <c r="N48" t="s">
-        <v>102</v>
+        <v>177</v>
       </c>
       <c r="O48" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="49" spans="7:15" x14ac:dyDescent="0.45">
       <c r="G49" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H49" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="I49" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J49" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="L49" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M49" t="s">
-        <v>89</v>
+        <v>138</v>
       </c>
       <c r="N49" t="s">
-        <v>90</v>
+        <v>139</v>
       </c>
       <c r="O49" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="50" spans="7:15" x14ac:dyDescent="0.45">
       <c r="L50" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M50" t="s">
-        <v>119</v>
+        <v>84</v>
       </c>
       <c r="N50" t="s">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="O50" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="51" spans="7:15" x14ac:dyDescent="0.45">
       <c r="L51" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M51" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="N51" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="O51" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="52" spans="7:15" x14ac:dyDescent="0.45">
       <c r="L52" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M52" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="N52" t="s">
-        <v>172</v>
+        <v>148</v>
       </c>
       <c r="O52" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="53" spans="7:15" x14ac:dyDescent="0.45">
       <c r="L53" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M53" t="s">
-        <v>173</v>
+        <v>142</v>
       </c>
       <c r="N53" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="O53" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="54" spans="7:15" x14ac:dyDescent="0.45">
       <c r="L54" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M54" t="s">
-        <v>99</v>
+        <v>126</v>
       </c>
       <c r="N54" t="s">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="O54" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="55" spans="7:15" x14ac:dyDescent="0.45">
       <c r="L55" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M55" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="N55" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="O55" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="56" spans="7:15" x14ac:dyDescent="0.45">
       <c r="L56" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M56" t="s">
-        <v>175</v>
+        <v>106</v>
       </c>
       <c r="N56" t="s">
-        <v>176</v>
+        <v>107</v>
       </c>
       <c r="O56" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="57" spans="7:15" x14ac:dyDescent="0.45">
       <c r="L57" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M57" t="s">
-        <v>152</v>
+        <v>108</v>
       </c>
       <c r="N57" t="s">
-        <v>153</v>
+        <v>109</v>
       </c>
       <c r="O57" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="58" spans="7:15" x14ac:dyDescent="0.45">
       <c r="L58" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M58" t="s">
-        <v>148</v>
+        <v>120</v>
       </c>
       <c r="N58" t="s">
-        <v>149</v>
+        <v>121</v>
       </c>
       <c r="O58" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -3822,7 +3822,7 @@
         <v>1.5</v>
       </c>
       <c r="T24" t="str">
-        <f t="shared" ref="T24" si="7">T20</f>
+        <f t="shared" ref="T18:T24" si="7">T20</f>
         <v>E[_]WOF*</v>
       </c>
       <c r="W24" t="str">
@@ -3861,7 +3861,7 @@
     </row>
     <row r="29" spans="3:24" x14ac:dyDescent="0.45">
       <c r="C29" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D29" t="s">
         <v>6</v>
@@ -3881,7 +3881,7 @@
         <v>1</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="31" spans="3:24" x14ac:dyDescent="0.45">
@@ -3947,7 +3947,7 @@
         <v>38</v>
       </c>
       <c r="D36" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G36" s="1">
         <v>0.9</v>
@@ -4040,7 +4040,7 @@
         <v>51</v>
       </c>
       <c r="F49" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G49" t="s">
         <v>50</v>
@@ -4057,7 +4057,7 @@
         <v>52</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G50" t="s">
         <v>53</v>
@@ -4085,7 +4085,7 @@
         <v>2100</v>
       </c>
       <c r="F52" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="55" spans="3:13" x14ac:dyDescent="0.45">
@@ -4130,42 +4130,42 @@
     </row>
     <row r="57" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C57" t="s">
-        <v>179</v>
+        <v>63</v>
       </c>
       <c r="E57" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F57" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I57">
         <v>0.95</v>
       </c>
       <c r="L57" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M57" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="58" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C58" t="s">
-        <v>179</v>
+        <v>63</v>
       </c>
       <c r="E58" t="s">
+        <v>68</v>
+      </c>
+      <c r="F58" t="s">
         <v>67</v>
-      </c>
-      <c r="F58" t="s">
-        <v>66</v>
       </c>
       <c r="I58">
         <v>0.85</v>
       </c>
       <c r="L58" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M58" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E52EAD46-2EF1-4954-8DE8-7F3F09DB8F25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68B39043-E6B2-44CB-9FB3-88A2D2665BEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -520,58 +520,58 @@
     <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
   </si>
   <si>
+    <t>Slupsk_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Slupsk_POL</t>
+  </si>
+  <si>
+    <t>Chelm_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Chelm_POL</t>
+  </si>
+  <si>
+    <t>Legnica_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Legnica_POL</t>
+  </si>
+  <si>
+    <t>Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>Elk_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Elk_POL</t>
+  </si>
+  <si>
+    <t>Grajewo_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Grajewo_POL</t>
+  </si>
+  <si>
     <t>Zamosc_POL</t>
   </si>
   <si>
     <t>at grid node - Zamosc_POL</t>
   </si>
   <si>
-    <t>Chelm_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Chelm_POL</t>
-  </si>
-  <si>
-    <t>Elk_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Elk_POL</t>
+    <t>Kielce_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Kielce_POL</t>
   </si>
   <si>
     <t>OstrowiecSwietokrz_POL</t>
   </si>
   <si>
     <t>at grid node - OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>Grajewo_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Grajewo_POL</t>
-  </si>
-  <si>
-    <t>Slupsk_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Slupsk_POL</t>
-  </si>
-  <si>
-    <t>Kielce_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Kielce_POL</t>
-  </si>
-  <si>
-    <t>Legnica_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Legnica_POL</t>
   </si>
   <si>
     <t>h_demand</t>
@@ -1037,10 +1037,10 @@
         <v>78</v>
       </c>
       <c r="M11" t="s">
-        <v>86</v>
+        <v>151</v>
       </c>
       <c r="N11" t="s">
-        <v>87</v>
+        <v>152</v>
       </c>
       <c r="O11" t="s">
         <v>159</v>
@@ -1099,10 +1099,10 @@
         <v>78</v>
       </c>
       <c r="M12" t="s">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="N12" t="s">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="O12" t="s">
         <v>159</v>
@@ -1161,10 +1161,10 @@
         <v>78</v>
       </c>
       <c r="M13" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="N13" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="O13" t="s">
         <v>159</v>
@@ -1223,10 +1223,10 @@
         <v>78</v>
       </c>
       <c r="M14" t="s">
-        <v>144</v>
+        <v>100</v>
       </c>
       <c r="N14" t="s">
-        <v>145</v>
+        <v>101</v>
       </c>
       <c r="O14" t="s">
         <v>159</v>
@@ -1285,10 +1285,10 @@
         <v>78</v>
       </c>
       <c r="M15" t="s">
-        <v>122</v>
+        <v>162</v>
       </c>
       <c r="N15" t="s">
-        <v>123</v>
+        <v>163</v>
       </c>
       <c r="O15" t="s">
         <v>159</v>
@@ -1347,10 +1347,10 @@
         <v>78</v>
       </c>
       <c r="M16" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="N16" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="O16" t="s">
         <v>159</v>
@@ -1409,10 +1409,10 @@
         <v>78</v>
       </c>
       <c r="M17" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="N17" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="O17" t="s">
         <v>159</v>
@@ -1471,10 +1471,10 @@
         <v>78</v>
       </c>
       <c r="M18" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="N18" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="O18" t="s">
         <v>159</v>
@@ -1533,10 +1533,10 @@
         <v>78</v>
       </c>
       <c r="M19" t="s">
-        <v>162</v>
+        <v>118</v>
       </c>
       <c r="N19" t="s">
-        <v>163</v>
+        <v>119</v>
       </c>
       <c r="O19" t="s">
         <v>159</v>
@@ -1595,10 +1595,10 @@
         <v>78</v>
       </c>
       <c r="M20" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="N20" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="O20" t="s">
         <v>159</v>
@@ -1657,10 +1657,10 @@
         <v>78</v>
       </c>
       <c r="M21" t="s">
-        <v>166</v>
+        <v>82</v>
       </c>
       <c r="N21" t="s">
-        <v>167</v>
+        <v>83</v>
       </c>
       <c r="O21" t="s">
         <v>159</v>
@@ -1719,10 +1719,10 @@
         <v>78</v>
       </c>
       <c r="M22" t="s">
-        <v>98</v>
+        <v>166</v>
       </c>
       <c r="N22" t="s">
-        <v>99</v>
+        <v>167</v>
       </c>
       <c r="O22" t="s">
         <v>159</v>
@@ -1843,10 +1843,10 @@
         <v>78</v>
       </c>
       <c r="M24" t="s">
-        <v>102</v>
+        <v>140</v>
       </c>
       <c r="N24" t="s">
-        <v>103</v>
+        <v>141</v>
       </c>
       <c r="O24" t="s">
         <v>159</v>
@@ -1905,10 +1905,10 @@
         <v>78</v>
       </c>
       <c r="M25" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="N25" t="s">
-        <v>152</v>
+        <v>133</v>
       </c>
       <c r="O25" t="s">
         <v>159</v>
@@ -1967,10 +1967,10 @@
         <v>78</v>
       </c>
       <c r="M26" t="s">
-        <v>94</v>
+        <v>147</v>
       </c>
       <c r="N26" t="s">
-        <v>95</v>
+        <v>148</v>
       </c>
       <c r="O26" t="s">
         <v>159</v>
@@ -2029,10 +2029,10 @@
         <v>78</v>
       </c>
       <c r="M27" t="s">
-        <v>128</v>
+        <v>90</v>
       </c>
       <c r="N27" t="s">
-        <v>129</v>
+        <v>91</v>
       </c>
       <c r="O27" t="s">
         <v>159</v>
@@ -2091,10 +2091,10 @@
         <v>78</v>
       </c>
       <c r="M28" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="N28" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="O28" t="s">
         <v>159</v>
@@ -2153,10 +2153,10 @@
         <v>78</v>
       </c>
       <c r="M29" t="s">
-        <v>149</v>
+        <v>112</v>
       </c>
       <c r="N29" t="s">
-        <v>150</v>
+        <v>113</v>
       </c>
       <c r="O29" t="s">
         <v>159</v>
@@ -2215,10 +2215,10 @@
         <v>78</v>
       </c>
       <c r="M30" t="s">
-        <v>136</v>
+        <v>108</v>
       </c>
       <c r="N30" t="s">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="O30" t="s">
         <v>159</v>
@@ -2277,10 +2277,10 @@
         <v>78</v>
       </c>
       <c r="M31" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="N31" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="O31" t="s">
         <v>159</v>
@@ -2339,10 +2339,10 @@
         <v>78</v>
       </c>
       <c r="M32" t="s">
-        <v>104</v>
+        <v>138</v>
       </c>
       <c r="N32" t="s">
-        <v>105</v>
+        <v>139</v>
       </c>
       <c r="O32" t="s">
         <v>159</v>
@@ -2401,10 +2401,10 @@
         <v>78</v>
       </c>
       <c r="M33" t="s">
-        <v>124</v>
+        <v>86</v>
       </c>
       <c r="N33" t="s">
-        <v>125</v>
+        <v>87</v>
       </c>
       <c r="O33" t="s">
         <v>159</v>
@@ -2463,10 +2463,10 @@
         <v>78</v>
       </c>
       <c r="M34" t="s">
-        <v>170</v>
+        <v>110</v>
       </c>
       <c r="N34" t="s">
-        <v>171</v>
+        <v>111</v>
       </c>
       <c r="O34" t="s">
         <v>159</v>
@@ -2525,10 +2525,10 @@
         <v>78</v>
       </c>
       <c r="M35" t="s">
-        <v>88</v>
+        <v>170</v>
       </c>
       <c r="N35" t="s">
-        <v>89</v>
+        <v>171</v>
       </c>
       <c r="O35" t="s">
         <v>159</v>
@@ -2587,10 +2587,10 @@
         <v>78</v>
       </c>
       <c r="M36" t="s">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="N36" t="s">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="O36" t="s">
         <v>159</v>
@@ -2649,10 +2649,10 @@
         <v>78</v>
       </c>
       <c r="M37" t="s">
-        <v>110</v>
+        <v>172</v>
       </c>
       <c r="N37" t="s">
-        <v>111</v>
+        <v>173</v>
       </c>
       <c r="O37" t="s">
         <v>159</v>
@@ -2773,10 +2773,10 @@
         <v>78</v>
       </c>
       <c r="M39" t="s">
-        <v>116</v>
+        <v>88</v>
       </c>
       <c r="N39" t="s">
-        <v>117</v>
+        <v>89</v>
       </c>
       <c r="O39" t="s">
         <v>159</v>
@@ -2835,10 +2835,10 @@
         <v>78</v>
       </c>
       <c r="M40" t="s">
-        <v>172</v>
+        <v>130</v>
       </c>
       <c r="N40" t="s">
-        <v>173</v>
+        <v>131</v>
       </c>
       <c r="O40" t="s">
         <v>159</v>
@@ -2873,10 +2873,10 @@
         <v>78</v>
       </c>
       <c r="M41" t="s">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="N41" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="O41" t="s">
         <v>159</v>
@@ -2911,10 +2911,10 @@
         <v>78</v>
       </c>
       <c r="M42" t="s">
-        <v>100</v>
+        <v>174</v>
       </c>
       <c r="N42" t="s">
-        <v>101</v>
+        <v>175</v>
       </c>
       <c r="O42" t="s">
         <v>159</v>
@@ -2949,10 +2949,10 @@
         <v>78</v>
       </c>
       <c r="M43" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="N43" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="O43" t="s">
         <v>159</v>
@@ -2975,10 +2975,10 @@
         <v>78</v>
       </c>
       <c r="M44" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="N44" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="O44" t="s">
         <v>159</v>
@@ -3001,10 +3001,10 @@
         <v>78</v>
       </c>
       <c r="M45" t="s">
-        <v>132</v>
+        <v>102</v>
       </c>
       <c r="N45" t="s">
-        <v>133</v>
+        <v>103</v>
       </c>
       <c r="O45" t="s">
         <v>159</v>
@@ -3027,10 +3027,10 @@
         <v>78</v>
       </c>
       <c r="M46" t="s">
-        <v>174</v>
+        <v>104</v>
       </c>
       <c r="N46" t="s">
-        <v>175</v>
+        <v>105</v>
       </c>
       <c r="O46" t="s">
         <v>159</v>
@@ -3053,10 +3053,10 @@
         <v>78</v>
       </c>
       <c r="M47" t="s">
-        <v>79</v>
+        <v>120</v>
       </c>
       <c r="N47" t="s">
-        <v>80</v>
+        <v>121</v>
       </c>
       <c r="O47" t="s">
         <v>159</v>
@@ -3079,10 +3079,10 @@
         <v>78</v>
       </c>
       <c r="M48" t="s">
-        <v>176</v>
+        <v>153</v>
       </c>
       <c r="N48" t="s">
-        <v>177</v>
+        <v>154</v>
       </c>
       <c r="O48" t="s">
         <v>159</v>
@@ -3105,10 +3105,10 @@
         <v>78</v>
       </c>
       <c r="M49" t="s">
-        <v>138</v>
+        <v>176</v>
       </c>
       <c r="N49" t="s">
-        <v>139</v>
+        <v>177</v>
       </c>
       <c r="O49" t="s">
         <v>159</v>
@@ -3119,10 +3119,10 @@
         <v>78</v>
       </c>
       <c r="M50" t="s">
-        <v>84</v>
+        <v>124</v>
       </c>
       <c r="N50" t="s">
-        <v>85</v>
+        <v>125</v>
       </c>
       <c r="O50" t="s">
         <v>159</v>
@@ -3133,10 +3133,10 @@
         <v>78</v>
       </c>
       <c r="M51" t="s">
-        <v>90</v>
+        <v>122</v>
       </c>
       <c r="N51" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="O51" t="s">
         <v>159</v>
@@ -3147,10 +3147,10 @@
         <v>78</v>
       </c>
       <c r="M52" t="s">
-        <v>147</v>
+        <v>106</v>
       </c>
       <c r="N52" t="s">
-        <v>148</v>
+        <v>107</v>
       </c>
       <c r="O52" t="s">
         <v>159</v>
@@ -3161,10 +3161,10 @@
         <v>78</v>
       </c>
       <c r="M53" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="N53" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="O53" t="s">
         <v>159</v>
@@ -3175,10 +3175,10 @@
         <v>78</v>
       </c>
       <c r="M54" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="N54" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="O54" t="s">
         <v>159</v>
@@ -3189,10 +3189,10 @@
         <v>78</v>
       </c>
       <c r="M55" t="s">
-        <v>134</v>
+        <v>94</v>
       </c>
       <c r="N55" t="s">
-        <v>135</v>
+        <v>95</v>
       </c>
       <c r="O55" t="s">
         <v>159</v>
@@ -3203,10 +3203,10 @@
         <v>78</v>
       </c>
       <c r="M56" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="N56" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="O56" t="s">
         <v>159</v>
@@ -3217,10 +3217,10 @@
         <v>78</v>
       </c>
       <c r="M57" t="s">
-        <v>108</v>
+        <v>136</v>
       </c>
       <c r="N57" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="O57" t="s">
         <v>159</v>
@@ -3231,10 +3231,10 @@
         <v>78</v>
       </c>
       <c r="M58" t="s">
-        <v>120</v>
+        <v>79</v>
       </c>
       <c r="N58" t="s">
-        <v>121</v>
+        <v>80</v>
       </c>
       <c r="O58" t="s">
         <v>159</v>

--- a/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68B39043-E6B2-44CB-9FB3-88A2D2665BEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C87B6AD-AD16-4B2A-A794-27EFAFCD6E4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -478,7 +478,7 @@
     <t>at grid node - Boleslawiec_POL</t>
   </si>
   <si>
-    <t>EN_STG8hbNREL,EN_STG4hbNREL</t>
+    <t>en_battery_4h,en_battery_8h</t>
   </si>
   <si>
     <t>Ustka_POL</t>
@@ -520,58 +520,58 @@
     <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
   </si>
   <si>
+    <t>Zamosc_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Zamosc_POL</t>
+  </si>
+  <si>
+    <t>Elk_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Elk_POL</t>
+  </si>
+  <si>
+    <t>Grajewo_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Grajewo_POL</t>
+  </si>
+  <si>
     <t>Slupsk_POL</t>
   </si>
   <si>
     <t>at grid node - Slupsk_POL</t>
   </si>
   <si>
+    <t>Legnica_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Legnica_POL</t>
+  </si>
+  <si>
+    <t>Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>at grid node - OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
     <t>Chelm_POL</t>
   </si>
   <si>
     <t>at grid node - Chelm_POL</t>
   </si>
   <si>
-    <t>Legnica_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Legnica_POL</t>
-  </si>
-  <si>
-    <t>Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>Elk_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Elk_POL</t>
-  </si>
-  <si>
-    <t>Grajewo_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Grajewo_POL</t>
-  </si>
-  <si>
-    <t>Zamosc_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Zamosc_POL</t>
-  </si>
-  <si>
     <t>Kielce_POL</t>
   </si>
   <si>
     <t>at grid node - Kielce_POL</t>
-  </si>
-  <si>
-    <t>OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>at grid node - OstrowiecSwietokrz_POL</t>
   </si>
   <si>
     <t>h_demand</t>
@@ -1037,10 +1037,10 @@
         <v>78</v>
       </c>
       <c r="M11" t="s">
-        <v>151</v>
+        <v>108</v>
       </c>
       <c r="N11" t="s">
-        <v>152</v>
+        <v>109</v>
       </c>
       <c r="O11" t="s">
         <v>159</v>
@@ -1099,10 +1099,10 @@
         <v>78</v>
       </c>
       <c r="M12" t="s">
-        <v>160</v>
+        <v>132</v>
       </c>
       <c r="N12" t="s">
-        <v>161</v>
+        <v>133</v>
       </c>
       <c r="O12" t="s">
         <v>159</v>
@@ -1161,10 +1161,10 @@
         <v>78</v>
       </c>
       <c r="M13" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="N13" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="O13" t="s">
         <v>159</v>
@@ -1223,10 +1223,10 @@
         <v>78</v>
       </c>
       <c r="M14" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N14" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="O14" t="s">
         <v>159</v>
@@ -1285,10 +1285,10 @@
         <v>78</v>
       </c>
       <c r="M15" t="s">
-        <v>162</v>
+        <v>114</v>
       </c>
       <c r="N15" t="s">
-        <v>163</v>
+        <v>115</v>
       </c>
       <c r="O15" t="s">
         <v>159</v>
@@ -1347,10 +1347,10 @@
         <v>78</v>
       </c>
       <c r="M16" t="s">
-        <v>84</v>
+        <v>110</v>
       </c>
       <c r="N16" t="s">
-        <v>85</v>
+        <v>111</v>
       </c>
       <c r="O16" t="s">
         <v>159</v>
@@ -1409,10 +1409,10 @@
         <v>78</v>
       </c>
       <c r="M17" t="s">
-        <v>164</v>
+        <v>140</v>
       </c>
       <c r="N17" t="s">
-        <v>165</v>
+        <v>141</v>
       </c>
       <c r="O17" t="s">
         <v>159</v>
@@ -1471,10 +1471,10 @@
         <v>78</v>
       </c>
       <c r="M18" t="s">
-        <v>128</v>
+        <v>162</v>
       </c>
       <c r="N18" t="s">
-        <v>129</v>
+        <v>163</v>
       </c>
       <c r="O18" t="s">
         <v>159</v>
@@ -1533,10 +1533,10 @@
         <v>78</v>
       </c>
       <c r="M19" t="s">
-        <v>118</v>
+        <v>147</v>
       </c>
       <c r="N19" t="s">
-        <v>119</v>
+        <v>148</v>
       </c>
       <c r="O19" t="s">
         <v>159</v>
@@ -1595,10 +1595,10 @@
         <v>78</v>
       </c>
       <c r="M20" t="s">
-        <v>157</v>
+        <v>130</v>
       </c>
       <c r="N20" t="s">
-        <v>158</v>
+        <v>131</v>
       </c>
       <c r="O20" t="s">
         <v>159</v>
@@ -1657,10 +1657,10 @@
         <v>78</v>
       </c>
       <c r="M21" t="s">
-        <v>82</v>
+        <v>164</v>
       </c>
       <c r="N21" t="s">
-        <v>83</v>
+        <v>165</v>
       </c>
       <c r="O21" t="s">
         <v>159</v>
@@ -1781,10 +1781,10 @@
         <v>78</v>
       </c>
       <c r="M23" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="N23" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="O23" t="s">
         <v>159</v>
@@ -1843,10 +1843,10 @@
         <v>78</v>
       </c>
       <c r="M24" t="s">
-        <v>140</v>
+        <v>168</v>
       </c>
       <c r="N24" t="s">
-        <v>141</v>
+        <v>169</v>
       </c>
       <c r="O24" t="s">
         <v>159</v>
@@ -1905,10 +1905,10 @@
         <v>78</v>
       </c>
       <c r="M25" t="s">
-        <v>132</v>
+        <v>79</v>
       </c>
       <c r="N25" t="s">
-        <v>133</v>
+        <v>80</v>
       </c>
       <c r="O25" t="s">
         <v>159</v>
@@ -1967,10 +1967,10 @@
         <v>78</v>
       </c>
       <c r="M26" t="s">
-        <v>147</v>
+        <v>88</v>
       </c>
       <c r="N26" t="s">
-        <v>148</v>
+        <v>89</v>
       </c>
       <c r="O26" t="s">
         <v>159</v>
@@ -2029,10 +2029,10 @@
         <v>78</v>
       </c>
       <c r="M27" t="s">
-        <v>90</v>
+        <v>128</v>
       </c>
       <c r="N27" t="s">
-        <v>91</v>
+        <v>129</v>
       </c>
       <c r="O27" t="s">
         <v>159</v>
@@ -2091,10 +2091,10 @@
         <v>78</v>
       </c>
       <c r="M28" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
       <c r="N28" t="s">
-        <v>156</v>
+        <v>139</v>
       </c>
       <c r="O28" t="s">
         <v>159</v>
@@ -2153,10 +2153,10 @@
         <v>78</v>
       </c>
       <c r="M29" t="s">
-        <v>112</v>
+        <v>142</v>
       </c>
       <c r="N29" t="s">
-        <v>113</v>
+        <v>143</v>
       </c>
       <c r="O29" t="s">
         <v>159</v>
@@ -2215,10 +2215,10 @@
         <v>78</v>
       </c>
       <c r="M30" t="s">
-        <v>108</v>
+        <v>136</v>
       </c>
       <c r="N30" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="O30" t="s">
         <v>159</v>
@@ -2277,10 +2277,10 @@
         <v>78</v>
       </c>
       <c r="M31" t="s">
-        <v>168</v>
+        <v>120</v>
       </c>
       <c r="N31" t="s">
-        <v>169</v>
+        <v>121</v>
       </c>
       <c r="O31" t="s">
         <v>159</v>
@@ -2339,10 +2339,10 @@
         <v>78</v>
       </c>
       <c r="M32" t="s">
-        <v>138</v>
+        <v>155</v>
       </c>
       <c r="N32" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="O32" t="s">
         <v>159</v>
@@ -2401,10 +2401,10 @@
         <v>78</v>
       </c>
       <c r="M33" t="s">
-        <v>86</v>
+        <v>116</v>
       </c>
       <c r="N33" t="s">
-        <v>87</v>
+        <v>117</v>
       </c>
       <c r="O33" t="s">
         <v>159</v>
@@ -2463,10 +2463,10 @@
         <v>78</v>
       </c>
       <c r="M34" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="N34" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="O34" t="s">
         <v>159</v>
@@ -2587,10 +2587,10 @@
         <v>78</v>
       </c>
       <c r="M36" t="s">
-        <v>142</v>
+        <v>96</v>
       </c>
       <c r="N36" t="s">
-        <v>143</v>
+        <v>97</v>
       </c>
       <c r="O36" t="s">
         <v>159</v>
@@ -2711,10 +2711,10 @@
         <v>78</v>
       </c>
       <c r="M38" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="N38" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="O38" t="s">
         <v>159</v>
@@ -2773,10 +2773,10 @@
         <v>78</v>
       </c>
       <c r="M39" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="N39" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="O39" t="s">
         <v>159</v>
@@ -2835,10 +2835,10 @@
         <v>78</v>
       </c>
       <c r="M40" t="s">
-        <v>130</v>
+        <v>86</v>
       </c>
       <c r="N40" t="s">
-        <v>131</v>
+        <v>87</v>
       </c>
       <c r="O40" t="s">
         <v>159</v>
@@ -2873,10 +2873,10 @@
         <v>78</v>
       </c>
       <c r="M41" t="s">
-        <v>134</v>
+        <v>174</v>
       </c>
       <c r="N41" t="s">
-        <v>135</v>
+        <v>175</v>
       </c>
       <c r="O41" t="s">
         <v>159</v>
@@ -2911,10 +2911,10 @@
         <v>78</v>
       </c>
       <c r="M42" t="s">
-        <v>174</v>
+        <v>151</v>
       </c>
       <c r="N42" t="s">
-        <v>175</v>
+        <v>152</v>
       </c>
       <c r="O42" t="s">
         <v>159</v>
@@ -2949,10 +2949,10 @@
         <v>78</v>
       </c>
       <c r="M43" t="s">
-        <v>126</v>
+        <v>100</v>
       </c>
       <c r="N43" t="s">
-        <v>127</v>
+        <v>101</v>
       </c>
       <c r="O43" t="s">
         <v>159</v>
@@ -2975,10 +2975,10 @@
         <v>78</v>
       </c>
       <c r="M44" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="N44" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="O44" t="s">
         <v>159</v>
@@ -3001,10 +3001,10 @@
         <v>78</v>
       </c>
       <c r="M45" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="N45" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="O45" t="s">
         <v>159</v>
@@ -3027,10 +3027,10 @@
         <v>78</v>
       </c>
       <c r="M46" t="s">
-        <v>104</v>
+        <v>134</v>
       </c>
       <c r="N46" t="s">
-        <v>105</v>
+        <v>135</v>
       </c>
       <c r="O46" t="s">
         <v>159</v>
@@ -3053,10 +3053,10 @@
         <v>78</v>
       </c>
       <c r="M47" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="N47" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="O47" t="s">
         <v>159</v>
@@ -3079,10 +3079,10 @@
         <v>78</v>
       </c>
       <c r="M48" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="N48" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="O48" t="s">
         <v>159</v>
@@ -3105,10 +3105,10 @@
         <v>78</v>
       </c>
       <c r="M49" t="s">
-        <v>176</v>
+        <v>126</v>
       </c>
       <c r="N49" t="s">
-        <v>177</v>
+        <v>127</v>
       </c>
       <c r="O49" t="s">
         <v>159</v>
@@ -3119,10 +3119,10 @@
         <v>78</v>
       </c>
       <c r="M50" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="N50" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="O50" t="s">
         <v>159</v>
@@ -3133,10 +3133,10 @@
         <v>78</v>
       </c>
       <c r="M51" t="s">
-        <v>122</v>
+        <v>94</v>
       </c>
       <c r="N51" t="s">
-        <v>123</v>
+        <v>95</v>
       </c>
       <c r="O51" t="s">
         <v>159</v>
@@ -3147,10 +3147,10 @@
         <v>78</v>
       </c>
       <c r="M52" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="N52" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="O52" t="s">
         <v>159</v>
@@ -3161,10 +3161,10 @@
         <v>78</v>
       </c>
       <c r="M53" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="N53" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="O53" t="s">
         <v>159</v>
@@ -3175,10 +3175,10 @@
         <v>78</v>
       </c>
       <c r="M54" t="s">
-        <v>116</v>
+        <v>144</v>
       </c>
       <c r="N54" t="s">
-        <v>117</v>
+        <v>145</v>
       </c>
       <c r="O54" t="s">
         <v>159</v>
@@ -3189,10 +3189,10 @@
         <v>78</v>
       </c>
       <c r="M55" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="N55" t="s">
-        <v>95</v>
+        <v>125</v>
       </c>
       <c r="O55" t="s">
         <v>159</v>
@@ -3203,10 +3203,10 @@
         <v>78</v>
       </c>
       <c r="M56" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="N56" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="O56" t="s">
         <v>159</v>
@@ -3217,10 +3217,10 @@
         <v>78</v>
       </c>
       <c r="M57" t="s">
-        <v>136</v>
+        <v>176</v>
       </c>
       <c r="N57" t="s">
-        <v>137</v>
+        <v>177</v>
       </c>
       <c r="O57" t="s">
         <v>159</v>
@@ -3231,10 +3231,10 @@
         <v>78</v>
       </c>
       <c r="M58" t="s">
-        <v>79</v>
+        <v>149</v>
       </c>
       <c r="N58" t="s">
-        <v>80</v>
+        <v>150</v>
       </c>
       <c r="O58" t="s">
         <v>159</v>

--- a/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C87B6AD-AD16-4B2A-A794-27EFAFCD6E4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2EA9739-DF74-49F2-A51B-3B5FEC2E4205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="907" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="930" uniqueCount="188">
   <si>
     <t>PSET_PN</t>
   </si>
@@ -274,6 +274,30 @@
     <t>ELE,CHP,HPL</t>
   </si>
   <si>
+    <t>top_check</t>
+  </si>
+  <si>
+    <t>FLO_FUNC</t>
+  </si>
+  <si>
+    <t>AuxStoOUT</t>
+  </si>
+  <si>
+    <t>STG</t>
+  </si>
+  <si>
+    <t>en[_]*?h*</t>
+  </si>
+  <si>
+    <t>ELC,e[_]*</t>
+  </si>
+  <si>
+    <t>OUT</t>
+  </si>
+  <si>
+    <t>~TFM_TOPINS-A</t>
+  </si>
+  <si>
     <t>POL</t>
   </si>
   <si>
@@ -520,58 +544,58 @@
     <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
   </si>
   <si>
+    <t>Legnica_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Legnica_POL</t>
+  </si>
+  <si>
+    <t>Slupsk_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Slupsk_POL</t>
+  </si>
+  <si>
+    <t>Chelm_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Chelm_POL</t>
+  </si>
+  <si>
+    <t>Elk_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Elk_POL</t>
+  </si>
+  <si>
+    <t>Grajewo_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Grajewo_POL</t>
+  </si>
+  <si>
+    <t>Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>Kielce_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Kielce_POL</t>
+  </si>
+  <si>
+    <t>OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>at grid node - OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
     <t>Zamosc_POL</t>
   </si>
   <si>
     <t>at grid node - Zamosc_POL</t>
-  </si>
-  <si>
-    <t>Elk_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Elk_POL</t>
-  </si>
-  <si>
-    <t>Grajewo_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Grajewo_POL</t>
-  </si>
-  <si>
-    <t>Slupsk_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Slupsk_POL</t>
-  </si>
-  <si>
-    <t>Legnica_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Legnica_POL</t>
-  </si>
-  <si>
-    <t>Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>at grid node - OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>Chelm_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Chelm_POL</t>
-  </si>
-  <si>
-    <t>Kielce_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Kielce_POL</t>
   </si>
   <si>
     <t>h_demand</t>
@@ -584,7 +608,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -599,6 +623,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -608,7 +648,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -616,17 +656,42 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="2"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="Heading 2" xfId="1" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="2" builtinId="18"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1010,2234 +1075,2234 @@
     </row>
     <row r="11" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C11" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D11" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="E11" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="G11" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H11" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="I11" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="J11" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="L11" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="M11" t="s">
-        <v>108</v>
+        <v>132</v>
       </c>
       <c r="N11" t="s">
-        <v>109</v>
+        <v>133</v>
       </c>
       <c r="O11" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="Q11" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="R11" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="S11" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="T11" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="V11" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="W11" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="X11" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="Y11" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C12" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="D12" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="E12" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="G12" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H12" t="s">
+        <v>130</v>
+      </c>
+      <c r="I12" t="s">
+        <v>131</v>
+      </c>
+      <c r="J12" t="s">
+        <v>154</v>
+      </c>
+      <c r="L12" t="s">
+        <v>86</v>
+      </c>
+      <c r="M12" t="s">
         <v>122</v>
       </c>
-      <c r="I12" t="s">
+      <c r="N12" t="s">
         <v>123</v>
       </c>
-      <c r="J12" t="s">
-        <v>146</v>
-      </c>
-      <c r="L12" t="s">
-        <v>78</v>
-      </c>
-      <c r="M12" t="s">
-        <v>132</v>
-      </c>
-      <c r="N12" t="s">
-        <v>133</v>
-      </c>
       <c r="O12" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="Q12" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="R12" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="S12" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="T12" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="V12" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="W12" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="X12" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="Y12" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C13" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="D13" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="E13" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="G13" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H13" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="I13" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="J13" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="L13" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="M13" t="s">
-        <v>160</v>
+        <v>138</v>
       </c>
       <c r="N13" t="s">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="O13" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="Q13" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="R13" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="S13" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="T13" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="V13" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="W13" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="X13" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="Y13" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
     </row>
     <row r="14" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C14" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="D14" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="E14" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="G14" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H14" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="I14" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="J14" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="L14" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="M14" t="s">
-        <v>102</v>
+        <v>152</v>
       </c>
       <c r="N14" t="s">
-        <v>103</v>
+        <v>153</v>
       </c>
       <c r="O14" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="Q14" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="R14" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="S14" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="T14" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="V14" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="W14" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="X14" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="Y14" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
     </row>
     <row r="15" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C15" t="s">
+        <v>96</v>
+      </c>
+      <c r="D15" t="s">
+        <v>97</v>
+      </c>
+      <c r="E15" t="s">
+        <v>89</v>
+      </c>
+      <c r="G15" t="s">
+        <v>86</v>
+      </c>
+      <c r="H15" t="s">
+        <v>87</v>
+      </c>
+      <c r="I15" t="s">
         <v>88</v>
       </c>
-      <c r="D15" t="s">
-        <v>89</v>
-      </c>
-      <c r="E15" t="s">
-        <v>81</v>
-      </c>
-      <c r="G15" t="s">
-        <v>78</v>
-      </c>
-      <c r="H15" t="s">
-        <v>79</v>
-      </c>
-      <c r="I15" t="s">
-        <v>80</v>
-      </c>
       <c r="J15" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="L15" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="M15" t="s">
-        <v>114</v>
+        <v>148</v>
       </c>
       <c r="N15" t="s">
-        <v>115</v>
+        <v>149</v>
       </c>
       <c r="O15" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="Q15" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="R15" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="S15" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="T15" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="V15" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="W15" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="X15" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="Y15" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
     </row>
     <row r="16" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C16" t="s">
+        <v>98</v>
+      </c>
+      <c r="D16" t="s">
+        <v>99</v>
+      </c>
+      <c r="E16" t="s">
+        <v>89</v>
+      </c>
+      <c r="G16" t="s">
+        <v>86</v>
+      </c>
+      <c r="H16" t="s">
         <v>90</v>
       </c>
-      <c r="D16" t="s">
+      <c r="I16" t="s">
         <v>91</v>
       </c>
-      <c r="E16" t="s">
-        <v>81</v>
-      </c>
-      <c r="G16" t="s">
-        <v>78</v>
-      </c>
-      <c r="H16" t="s">
-        <v>82</v>
-      </c>
-      <c r="I16" t="s">
-        <v>83</v>
-      </c>
       <c r="J16" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="L16" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="M16" t="s">
-        <v>110</v>
+        <v>163</v>
       </c>
       <c r="N16" t="s">
-        <v>111</v>
+        <v>164</v>
       </c>
       <c r="O16" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="Q16" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="R16" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="S16" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="T16" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="V16" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="W16" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="X16" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="Y16" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
     </row>
     <row r="17" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C17" t="s">
+        <v>100</v>
+      </c>
+      <c r="D17" t="s">
+        <v>101</v>
+      </c>
+      <c r="E17" t="s">
+        <v>89</v>
+      </c>
+      <c r="G17" t="s">
+        <v>86</v>
+      </c>
+      <c r="H17" t="s">
         <v>92</v>
       </c>
-      <c r="D17" t="s">
+      <c r="I17" t="s">
         <v>93</v>
       </c>
-      <c r="E17" t="s">
-        <v>81</v>
-      </c>
-      <c r="G17" t="s">
-        <v>78</v>
-      </c>
-      <c r="H17" t="s">
-        <v>84</v>
-      </c>
-      <c r="I17" t="s">
-        <v>85</v>
-      </c>
       <c r="J17" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="L17" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="M17" t="s">
-        <v>140</v>
+        <v>168</v>
       </c>
       <c r="N17" t="s">
-        <v>141</v>
+        <v>169</v>
       </c>
       <c r="O17" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="Q17" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="R17" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="S17" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="T17" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="V17" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="W17" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="X17" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="Y17" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
     </row>
     <row r="18" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C18" t="s">
+        <v>102</v>
+      </c>
+      <c r="D18" t="s">
+        <v>103</v>
+      </c>
+      <c r="E18" t="s">
+        <v>89</v>
+      </c>
+      <c r="G18" t="s">
+        <v>86</v>
+      </c>
+      <c r="H18" t="s">
         <v>94</v>
       </c>
-      <c r="D18" t="s">
+      <c r="I18" t="s">
         <v>95</v>
       </c>
-      <c r="E18" t="s">
-        <v>81</v>
-      </c>
-      <c r="G18" t="s">
-        <v>78</v>
-      </c>
-      <c r="H18" t="s">
-        <v>86</v>
-      </c>
-      <c r="I18" t="s">
-        <v>87</v>
-      </c>
       <c r="J18" t="s">
+        <v>154</v>
+      </c>
+      <c r="L18" t="s">
+        <v>86</v>
+      </c>
+      <c r="M18" t="s">
+        <v>159</v>
+      </c>
+      <c r="N18" t="s">
+        <v>160</v>
+      </c>
+      <c r="O18" t="s">
+        <v>167</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>86</v>
+      </c>
+      <c r="R18" t="s">
         <v>146</v>
       </c>
-      <c r="L18" t="s">
-        <v>78</v>
-      </c>
-      <c r="M18" t="s">
-        <v>162</v>
-      </c>
-      <c r="N18" t="s">
-        <v>163</v>
-      </c>
-      <c r="O18" t="s">
-        <v>159</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>78</v>
-      </c>
-      <c r="R18" t="s">
-        <v>138</v>
-      </c>
       <c r="S18" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="T18" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="V18" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="W18" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="X18" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="Y18" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
     </row>
     <row r="19" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B19" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C19" t="s">
+        <v>104</v>
+      </c>
+      <c r="D19" t="s">
+        <v>105</v>
+      </c>
+      <c r="E19" t="s">
+        <v>89</v>
+      </c>
+      <c r="G19" t="s">
+        <v>86</v>
+      </c>
+      <c r="H19" t="s">
         <v>96</v>
       </c>
-      <c r="D19" t="s">
+      <c r="I19" t="s">
         <v>97</v>
       </c>
-      <c r="E19" t="s">
-        <v>81</v>
-      </c>
-      <c r="G19" t="s">
-        <v>78</v>
-      </c>
-      <c r="H19" t="s">
-        <v>88</v>
-      </c>
-      <c r="I19" t="s">
-        <v>89</v>
-      </c>
       <c r="J19" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="L19" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="M19" t="s">
-        <v>147</v>
+        <v>170</v>
       </c>
       <c r="N19" t="s">
-        <v>148</v>
+        <v>171</v>
       </c>
       <c r="O19" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="Q19" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="R19" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="S19" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="T19" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="V19" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="W19" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="X19" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="Y19" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
     </row>
     <row r="20" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B20" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C20" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="D20" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="E20" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="G20" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H20" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="I20" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="J20" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="L20" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="M20" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="N20" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="O20" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="Q20" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="R20" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="S20" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="T20" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="V20" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="W20" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="X20" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="Y20" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
     </row>
     <row r="21" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B21" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C21" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="D21" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="E21" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="G21" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H21" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="I21" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="J21" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="L21" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="M21" t="s">
-        <v>164</v>
+        <v>102</v>
       </c>
       <c r="N21" t="s">
-        <v>165</v>
+        <v>103</v>
       </c>
       <c r="O21" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="Q21" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="R21" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="S21" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="T21" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="V21" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="W21" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="X21" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="Y21" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
     </row>
     <row r="22" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B22" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C22" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="D22" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="E22" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="G22" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H22" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="I22" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="J22" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="L22" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="M22" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N22" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="O22" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="Q22" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="R22" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="S22" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="T22" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="V22" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="W22" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="X22" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="Y22" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
     </row>
     <row r="23" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B23" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C23" t="s">
+        <v>112</v>
+      </c>
+      <c r="D23" t="s">
+        <v>113</v>
+      </c>
+      <c r="E23" t="s">
+        <v>89</v>
+      </c>
+      <c r="G23" t="s">
+        <v>86</v>
+      </c>
+      <c r="H23" t="s">
         <v>104</v>
       </c>
-      <c r="D23" t="s">
+      <c r="I23" t="s">
         <v>105</v>
       </c>
-      <c r="E23" t="s">
-        <v>81</v>
-      </c>
-      <c r="G23" t="s">
-        <v>78</v>
-      </c>
-      <c r="H23" t="s">
-        <v>96</v>
-      </c>
-      <c r="I23" t="s">
-        <v>97</v>
-      </c>
       <c r="J23" t="s">
+        <v>154</v>
+      </c>
+      <c r="L23" t="s">
+        <v>86</v>
+      </c>
+      <c r="M23" t="s">
         <v>146</v>
       </c>
-      <c r="L23" t="s">
-        <v>78</v>
-      </c>
-      <c r="M23" t="s">
-        <v>98</v>
-      </c>
       <c r="N23" t="s">
-        <v>99</v>
+        <v>147</v>
       </c>
       <c r="O23" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="Q23" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="R23" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="S23" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="T23" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="V23" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="W23" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="X23" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="Y23" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
     </row>
     <row r="24" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B24" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C24" t="s">
+        <v>114</v>
+      </c>
+      <c r="D24" t="s">
+        <v>115</v>
+      </c>
+      <c r="E24" t="s">
+        <v>89</v>
+      </c>
+      <c r="G24" t="s">
+        <v>86</v>
+      </c>
+      <c r="H24" t="s">
         <v>106</v>
       </c>
-      <c r="D24" t="s">
+      <c r="I24" t="s">
         <v>107</v>
       </c>
-      <c r="E24" t="s">
-        <v>81</v>
-      </c>
-      <c r="G24" t="s">
-        <v>78</v>
-      </c>
-      <c r="H24" t="s">
-        <v>98</v>
-      </c>
-      <c r="I24" t="s">
-        <v>99</v>
-      </c>
       <c r="J24" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="L24" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="M24" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="N24" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="O24" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="Q24" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="R24" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="S24" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="T24" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="V24" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="W24" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="X24" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="Y24" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
     </row>
     <row r="25" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B25" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C25" t="s">
+        <v>116</v>
+      </c>
+      <c r="D25" t="s">
+        <v>117</v>
+      </c>
+      <c r="E25" t="s">
+        <v>89</v>
+      </c>
+      <c r="G25" t="s">
+        <v>86</v>
+      </c>
+      <c r="H25" t="s">
         <v>108</v>
       </c>
-      <c r="D25" t="s">
+      <c r="I25" t="s">
         <v>109</v>
       </c>
-      <c r="E25" t="s">
-        <v>81</v>
-      </c>
-      <c r="G25" t="s">
-        <v>78</v>
-      </c>
-      <c r="H25" t="s">
-        <v>100</v>
-      </c>
-      <c r="I25" t="s">
-        <v>101</v>
-      </c>
       <c r="J25" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="L25" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="M25" t="s">
-        <v>79</v>
+        <v>176</v>
       </c>
       <c r="N25" t="s">
-        <v>80</v>
+        <v>177</v>
       </c>
       <c r="O25" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="Q25" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="R25" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="S25" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="T25" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="V25" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="W25" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="X25" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="Y25" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
     </row>
     <row r="26" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B26" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C26" t="s">
+        <v>118</v>
+      </c>
+      <c r="D26" t="s">
+        <v>119</v>
+      </c>
+      <c r="E26" t="s">
+        <v>89</v>
+      </c>
+      <c r="G26" t="s">
+        <v>86</v>
+      </c>
+      <c r="H26" t="s">
         <v>110</v>
       </c>
-      <c r="D26" t="s">
+      <c r="I26" t="s">
         <v>111</v>
       </c>
-      <c r="E26" t="s">
-        <v>81</v>
-      </c>
-      <c r="G26" t="s">
-        <v>78</v>
-      </c>
-      <c r="H26" t="s">
-        <v>102</v>
-      </c>
-      <c r="I26" t="s">
-        <v>103</v>
-      </c>
       <c r="J26" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="L26" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="M26" t="s">
-        <v>88</v>
+        <v>114</v>
       </c>
       <c r="N26" t="s">
-        <v>89</v>
+        <v>115</v>
       </c>
       <c r="O26" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="Q26" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="R26" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="S26" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="T26" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="V26" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="W26" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="X26" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="Y26" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
     </row>
     <row r="27" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B27" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C27" t="s">
+        <v>120</v>
+      </c>
+      <c r="D27" t="s">
+        <v>121</v>
+      </c>
+      <c r="E27" t="s">
+        <v>89</v>
+      </c>
+      <c r="G27" t="s">
+        <v>86</v>
+      </c>
+      <c r="H27" t="s">
         <v>112</v>
       </c>
-      <c r="D27" t="s">
+      <c r="I27" t="s">
         <v>113</v>
       </c>
-      <c r="E27" t="s">
-        <v>81</v>
-      </c>
-      <c r="G27" t="s">
-        <v>78</v>
-      </c>
-      <c r="H27" t="s">
-        <v>104</v>
-      </c>
-      <c r="I27" t="s">
-        <v>105</v>
-      </c>
       <c r="J27" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="L27" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="M27" t="s">
-        <v>128</v>
+        <v>157</v>
       </c>
       <c r="N27" t="s">
-        <v>129</v>
+        <v>158</v>
       </c>
       <c r="O27" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="Q27" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="R27" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="S27" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="T27" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="V27" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="W27" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="X27" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="Y27" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
     </row>
     <row r="28" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B28" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C28" t="s">
+        <v>122</v>
+      </c>
+      <c r="D28" t="s">
+        <v>123</v>
+      </c>
+      <c r="E28" t="s">
+        <v>89</v>
+      </c>
+      <c r="G28" t="s">
+        <v>86</v>
+      </c>
+      <c r="H28" t="s">
         <v>114</v>
       </c>
-      <c r="D28" t="s">
+      <c r="I28" t="s">
         <v>115</v>
       </c>
-      <c r="E28" t="s">
-        <v>81</v>
-      </c>
-      <c r="G28" t="s">
-        <v>78</v>
-      </c>
-      <c r="H28" t="s">
-        <v>106</v>
-      </c>
-      <c r="I28" t="s">
-        <v>107</v>
-      </c>
       <c r="J28" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="L28" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="M28" t="s">
-        <v>138</v>
+        <v>161</v>
       </c>
       <c r="N28" t="s">
-        <v>139</v>
+        <v>162</v>
       </c>
       <c r="O28" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="Q28" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="R28" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="S28" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="T28" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="V28" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="W28" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="X28" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="Y28" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
     </row>
     <row r="29" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B29" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C29" t="s">
+        <v>124</v>
+      </c>
+      <c r="D29" t="s">
+        <v>125</v>
+      </c>
+      <c r="E29" t="s">
+        <v>89</v>
+      </c>
+      <c r="G29" t="s">
+        <v>86</v>
+      </c>
+      <c r="H29" t="s">
         <v>116</v>
       </c>
-      <c r="D29" t="s">
+      <c r="I29" t="s">
         <v>117</v>
       </c>
-      <c r="E29" t="s">
-        <v>81</v>
-      </c>
-      <c r="G29" t="s">
-        <v>78</v>
-      </c>
-      <c r="H29" t="s">
-        <v>108</v>
-      </c>
-      <c r="I29" t="s">
-        <v>109</v>
-      </c>
       <c r="J29" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="L29" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="M29" t="s">
-        <v>142</v>
+        <v>96</v>
       </c>
       <c r="N29" t="s">
-        <v>143</v>
+        <v>97</v>
       </c>
       <c r="O29" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="Q29" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="R29" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="S29" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="T29" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="V29" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="W29" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="X29" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="Y29" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
     </row>
     <row r="30" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B30" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C30" t="s">
+        <v>126</v>
+      </c>
+      <c r="D30" t="s">
+        <v>127</v>
+      </c>
+      <c r="E30" t="s">
+        <v>89</v>
+      </c>
+      <c r="G30" t="s">
+        <v>86</v>
+      </c>
+      <c r="H30" t="s">
         <v>118</v>
       </c>
-      <c r="D30" t="s">
+      <c r="I30" t="s">
         <v>119</v>
       </c>
-      <c r="E30" t="s">
-        <v>81</v>
-      </c>
-      <c r="G30" t="s">
-        <v>78</v>
-      </c>
-      <c r="H30" t="s">
-        <v>110</v>
-      </c>
-      <c r="I30" t="s">
-        <v>111</v>
-      </c>
       <c r="J30" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="L30" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="M30" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="N30" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="O30" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="Q30" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="R30" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="S30" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="T30" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="V30" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="W30" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="X30" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="Y30" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
     </row>
     <row r="31" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B31" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C31" t="s">
+        <v>128</v>
+      </c>
+      <c r="D31" t="s">
+        <v>129</v>
+      </c>
+      <c r="E31" t="s">
+        <v>89</v>
+      </c>
+      <c r="G31" t="s">
+        <v>86</v>
+      </c>
+      <c r="H31" t="s">
         <v>120</v>
       </c>
-      <c r="D31" t="s">
+      <c r="I31" t="s">
         <v>121</v>
       </c>
-      <c r="E31" t="s">
-        <v>81</v>
-      </c>
-      <c r="G31" t="s">
-        <v>78</v>
-      </c>
-      <c r="H31" t="s">
-        <v>112</v>
-      </c>
-      <c r="I31" t="s">
-        <v>113</v>
-      </c>
       <c r="J31" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="L31" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="M31" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="N31" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="O31" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="Q31" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="R31" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="S31" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="T31" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="V31" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="W31" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="X31" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="Y31" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
     </row>
     <row r="32" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B32" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C32" t="s">
+        <v>130</v>
+      </c>
+      <c r="D32" t="s">
+        <v>131</v>
+      </c>
+      <c r="E32" t="s">
+        <v>89</v>
+      </c>
+      <c r="G32" t="s">
+        <v>86</v>
+      </c>
+      <c r="H32" t="s">
         <v>122</v>
       </c>
-      <c r="D32" t="s">
+      <c r="I32" t="s">
         <v>123</v>
       </c>
-      <c r="E32" t="s">
-        <v>81</v>
-      </c>
-      <c r="G32" t="s">
-        <v>78</v>
-      </c>
-      <c r="H32" t="s">
-        <v>114</v>
-      </c>
-      <c r="I32" t="s">
-        <v>115</v>
-      </c>
       <c r="J32" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="L32" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="M32" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="N32" t="s">
-        <v>156</v>
+        <v>179</v>
       </c>
       <c r="O32" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="Q32" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="R32" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="S32" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="T32" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="V32" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="W32" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="X32" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="Y32" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
     </row>
     <row r="33" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B33" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C33" t="s">
+        <v>132</v>
+      </c>
+      <c r="D33" t="s">
+        <v>133</v>
+      </c>
+      <c r="E33" t="s">
+        <v>89</v>
+      </c>
+      <c r="G33" t="s">
+        <v>86</v>
+      </c>
+      <c r="H33" t="s">
         <v>124</v>
       </c>
-      <c r="D33" t="s">
+      <c r="I33" t="s">
         <v>125</v>
       </c>
-      <c r="E33" t="s">
-        <v>81</v>
-      </c>
-      <c r="G33" t="s">
-        <v>78</v>
-      </c>
-      <c r="H33" t="s">
-        <v>116</v>
-      </c>
-      <c r="I33" t="s">
-        <v>117</v>
-      </c>
       <c r="J33" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="L33" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="M33" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="N33" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="O33" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="Q33" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="R33" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="S33" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="T33" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="V33" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="W33" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="X33" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="Y33" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
     </row>
     <row r="34" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B34" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C34" t="s">
+        <v>134</v>
+      </c>
+      <c r="D34" t="s">
+        <v>135</v>
+      </c>
+      <c r="E34" t="s">
+        <v>89</v>
+      </c>
+      <c r="G34" t="s">
+        <v>86</v>
+      </c>
+      <c r="H34" t="s">
         <v>126</v>
       </c>
-      <c r="D34" t="s">
+      <c r="I34" t="s">
         <v>127</v>
       </c>
-      <c r="E34" t="s">
-        <v>81</v>
-      </c>
-      <c r="G34" t="s">
-        <v>78</v>
-      </c>
-      <c r="H34" t="s">
-        <v>118</v>
-      </c>
-      <c r="I34" t="s">
-        <v>119</v>
-      </c>
       <c r="J34" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="L34" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="M34" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="N34" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="O34" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="Q34" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="R34" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="S34" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="T34" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="V34" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="W34" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="X34" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="Y34" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
     </row>
     <row r="35" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B35" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C35" t="s">
+        <v>136</v>
+      </c>
+      <c r="D35" t="s">
+        <v>137</v>
+      </c>
+      <c r="E35" t="s">
+        <v>89</v>
+      </c>
+      <c r="G35" t="s">
+        <v>86</v>
+      </c>
+      <c r="H35" t="s">
         <v>128</v>
       </c>
-      <c r="D35" t="s">
+      <c r="I35" t="s">
         <v>129</v>
       </c>
-      <c r="E35" t="s">
-        <v>81</v>
-      </c>
-      <c r="G35" t="s">
-        <v>78</v>
-      </c>
-      <c r="H35" t="s">
-        <v>120</v>
-      </c>
-      <c r="I35" t="s">
-        <v>121</v>
-      </c>
       <c r="J35" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="L35" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="M35" t="s">
-        <v>170</v>
+        <v>128</v>
       </c>
       <c r="N35" t="s">
-        <v>171</v>
+        <v>129</v>
       </c>
       <c r="O35" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="Q35" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="R35" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="S35" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="T35" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="V35" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="W35" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="X35" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="Y35" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
     </row>
     <row r="36" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B36" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C36" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="D36" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E36" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="G36" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H36" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="I36" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="J36" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="L36" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="M36" t="s">
-        <v>96</v>
+        <v>180</v>
       </c>
       <c r="N36" t="s">
-        <v>97</v>
+        <v>181</v>
       </c>
       <c r="O36" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="Q36" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="R36" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="S36" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="T36" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="V36" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="W36" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="X36" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="Y36" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
     </row>
     <row r="37" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B37" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C37" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="D37" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="E37" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="G37" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H37" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="I37" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="J37" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="L37" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="M37" t="s">
-        <v>172</v>
+        <v>98</v>
       </c>
       <c r="N37" t="s">
-        <v>173</v>
+        <v>99</v>
       </c>
       <c r="O37" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="Q37" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="R37" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="S37" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="T37" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="V37" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="W37" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="X37" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="Y37" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
     </row>
     <row r="38" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B38" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C38" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="D38" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
       <c r="E38" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="G38" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H38" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="I38" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="J38" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="L38" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="M38" t="s">
-        <v>122</v>
+        <v>90</v>
       </c>
       <c r="N38" t="s">
-        <v>123</v>
+        <v>91</v>
       </c>
       <c r="O38" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="Q38" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="R38" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="S38" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="T38" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="V38" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="W38" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="X38" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="Y38" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
     </row>
     <row r="39" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B39" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C39" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="D39" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="E39" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="G39" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H39" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="I39" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="J39" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="L39" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="M39" t="s">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="N39" t="s">
-        <v>83</v>
+        <v>117</v>
       </c>
       <c r="O39" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="Q39" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="R39" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="S39" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="T39" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="V39" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="W39" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="X39" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="Y39" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
     </row>
     <row r="40" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B40" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C40" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="D40" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="E40" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="G40" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H40" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="I40" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="J40" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="L40" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="M40" t="s">
-        <v>86</v>
+        <v>134</v>
       </c>
       <c r="N40" t="s">
-        <v>87</v>
+        <v>135</v>
       </c>
       <c r="O40" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
     </row>
     <row r="41" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B41" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C41" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="D41" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="E41" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="G41" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H41" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="I41" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="J41" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="L41" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="M41" t="s">
-        <v>174</v>
+        <v>144</v>
       </c>
       <c r="N41" t="s">
-        <v>175</v>
+        <v>145</v>
       </c>
       <c r="O41" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
     </row>
     <row r="42" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B42" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C42" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="D42" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="E42" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="G42" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H42" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="I42" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="J42" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="L42" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="M42" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="N42" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="O42" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
     </row>
     <row r="43" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B43" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C43" t="s">
+        <v>152</v>
+      </c>
+      <c r="D43" t="s">
+        <v>153</v>
+      </c>
+      <c r="E43" t="s">
+        <v>89</v>
+      </c>
+      <c r="G43" t="s">
+        <v>86</v>
+      </c>
+      <c r="H43" t="s">
         <v>144</v>
       </c>
-      <c r="D43" t="s">
+      <c r="I43" t="s">
         <v>145</v>
       </c>
-      <c r="E43" t="s">
-        <v>81</v>
-      </c>
-      <c r="G43" t="s">
-        <v>78</v>
-      </c>
-      <c r="H43" t="s">
-        <v>136</v>
-      </c>
-      <c r="I43" t="s">
-        <v>137</v>
-      </c>
       <c r="J43" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="L43" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="M43" t="s">
-        <v>100</v>
+        <v>142</v>
       </c>
       <c r="N43" t="s">
-        <v>101</v>
+        <v>143</v>
       </c>
       <c r="O43" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
     </row>
     <row r="44" spans="2:25" x14ac:dyDescent="0.45">
       <c r="G44" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H44" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="I44" t="s">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="J44" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="L44" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="M44" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="N44" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="O44" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.45">
       <c r="G45" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H45" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="I45" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="J45" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="L45" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="M45" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="N45" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="O45" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
     </row>
     <row r="46" spans="2:25" x14ac:dyDescent="0.45">
       <c r="G46" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H46" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="I46" t="s">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="J46" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="L46" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="M46" t="s">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="N46" t="s">
-        <v>135</v>
+        <v>156</v>
       </c>
       <c r="O46" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
     </row>
     <row r="47" spans="2:25" x14ac:dyDescent="0.45">
       <c r="G47" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H47" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="I47" t="s">
+        <v>162</v>
+      </c>
+      <c r="J47" t="s">
         <v>154</v>
       </c>
-      <c r="J47" t="s">
-        <v>146</v>
-      </c>
       <c r="L47" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="M47" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="N47" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="O47" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
     </row>
     <row r="48" spans="2:25" x14ac:dyDescent="0.45">
       <c r="G48" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H48" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="I48" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="J48" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="L48" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="M48" t="s">
-        <v>157</v>
+        <v>118</v>
       </c>
       <c r="N48" t="s">
-        <v>158</v>
+        <v>119</v>
       </c>
       <c r="O48" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
     </row>
     <row r="49" spans="7:15" x14ac:dyDescent="0.45">
       <c r="G49" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="H49" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="I49" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="J49" t="s">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="L49" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="M49" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="N49" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="O49" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
     </row>
     <row r="50" spans="7:15" x14ac:dyDescent="0.45">
       <c r="L50" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="M50" t="s">
-        <v>106</v>
+        <v>182</v>
       </c>
       <c r="N50" t="s">
-        <v>107</v>
+        <v>183</v>
       </c>
       <c r="O50" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
     </row>
     <row r="51" spans="7:15" x14ac:dyDescent="0.45">
       <c r="L51" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="M51" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="N51" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="O51" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
     </row>
     <row r="52" spans="7:15" x14ac:dyDescent="0.45">
       <c r="L52" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="M52" t="s">
-        <v>92</v>
+        <v>165</v>
       </c>
       <c r="N52" t="s">
-        <v>93</v>
+        <v>166</v>
       </c>
       <c r="O52" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
     </row>
     <row r="53" spans="7:15" x14ac:dyDescent="0.45">
       <c r="L53" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="M53" t="s">
-        <v>153</v>
+        <v>87</v>
       </c>
       <c r="N53" t="s">
-        <v>154</v>
+        <v>88</v>
       </c>
       <c r="O53" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
     </row>
     <row r="54" spans="7:15" x14ac:dyDescent="0.45">
       <c r="L54" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="M54" t="s">
-        <v>144</v>
+        <v>184</v>
       </c>
       <c r="N54" t="s">
-        <v>145</v>
+        <v>185</v>
       </c>
       <c r="O54" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
     </row>
     <row r="55" spans="7:15" x14ac:dyDescent="0.45">
       <c r="L55" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="M55" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="N55" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="O55" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
     </row>
     <row r="56" spans="7:15" x14ac:dyDescent="0.45">
       <c r="L56" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="M56" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="N56" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="O56" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
     </row>
     <row r="57" spans="7:15" x14ac:dyDescent="0.45">
       <c r="L57" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="M57" t="s">
-        <v>176</v>
+        <v>124</v>
       </c>
       <c r="N57" t="s">
-        <v>177</v>
+        <v>125</v>
       </c>
       <c r="O57" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
     </row>
     <row r="58" spans="7:15" x14ac:dyDescent="0.45">
       <c r="L58" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="M58" t="s">
-        <v>149</v>
+        <v>92</v>
       </c>
       <c r="N58" t="s">
-        <v>150</v>
+        <v>93</v>
       </c>
       <c r="O58" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>
@@ -3284,6 +3349,13 @@
     <col min="11" max="11" width="5" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="6.265625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="4.265625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.86328125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="8.59765625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.06640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="4" spans="3:24" x14ac:dyDescent="0.45">
@@ -3906,7 +3978,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="33" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="33" spans="3:22" x14ac:dyDescent="0.45">
       <c r="D33" t="s">
         <v>10</v>
       </c>
@@ -3917,7 +3989,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="34" spans="3:22" x14ac:dyDescent="0.45">
       <c r="D34" t="s">
         <v>9</v>
       </c>
@@ -3928,7 +4000,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="35" spans="3:22" x14ac:dyDescent="0.45">
       <c r="C35" t="s">
         <v>17</v>
       </c>
@@ -3942,7 +4014,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="36" spans="3:22" x14ac:dyDescent="0.45">
       <c r="C36" t="s">
         <v>38</v>
       </c>
@@ -3953,12 +4025,15 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="39" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="39" spans="3:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C39" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="40" spans="3:7" x14ac:dyDescent="0.45">
+      <c r="P39" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="3:22" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="C40" t="s">
         <v>21</v>
       </c>
@@ -3968,8 +4043,29 @@
       <c r="E40" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="41" spans="3:7" x14ac:dyDescent="0.45">
+      <c r="P40" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q40" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="R40" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="S40" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="T40" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="U40" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="V40" s="6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="41" spans="3:22" x14ac:dyDescent="0.45">
       <c r="C41" t="s">
         <v>14</v>
       </c>
@@ -3979,8 +4075,29 @@
       <c r="E41" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="42" spans="3:7" x14ac:dyDescent="0.45">
+      <c r="P41" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>80</v>
+      </c>
+      <c r="R41" t="s">
+        <v>81</v>
+      </c>
+      <c r="S41">
+        <v>1</v>
+      </c>
+      <c r="T41" t="s">
+        <v>82</v>
+      </c>
+      <c r="U41" t="s">
+        <v>83</v>
+      </c>
+      <c r="V41" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="42" spans="3:22" x14ac:dyDescent="0.45">
       <c r="C42" t="s">
         <v>15</v>
       </c>
@@ -3991,7 +4108,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="43" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="43" spans="3:22" x14ac:dyDescent="0.45">
       <c r="C43" t="s">
         <v>42</v>
       </c>
@@ -4002,7 +4119,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="44" spans="3:7" x14ac:dyDescent="0.45">
+    <row r="44" spans="3:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C44" t="s">
         <v>40</v>
       </c>
@@ -4012,8 +4129,11 @@
       <c r="E44" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="45" spans="3:7" x14ac:dyDescent="0.45">
+      <c r="P44" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="45" spans="3:22" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="C45" t="s">
         <v>41</v>
       </c>
@@ -4023,8 +4143,34 @@
       <c r="E45" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="48" spans="3:7" x14ac:dyDescent="0.45">
+      <c r="P45" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q45" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="R45" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="S45" s="6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="46" spans="3:22" x14ac:dyDescent="0.45">
+      <c r="P46" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>80</v>
+      </c>
+      <c r="R46" t="s">
+        <v>84</v>
+      </c>
+      <c r="S46" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="48" spans="3:22" x14ac:dyDescent="0.45">
       <c r="C48" t="s">
         <v>4</v>
       </c>

--- a/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2EA9739-DF74-49F2-A51B-3B5FEC2E4205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{340379A5-E493-49E8-84D6-A9AA9665F5AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -541,6 +541,12 @@
     <t>at grid node - Krosno_POL</t>
   </si>
   <si>
+    <t>Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Olsztyn_POL</t>
+  </si>
+  <si>
     <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
   </si>
   <si>
@@ -556,46 +562,40 @@
     <t>at grid node - Slupsk_POL</t>
   </si>
   <si>
+    <t>Zamosc_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Zamosc_POL</t>
+  </si>
+  <si>
+    <t>Kielce_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Kielce_POL</t>
+  </si>
+  <si>
+    <t>Elk_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Elk_POL</t>
+  </si>
+  <si>
+    <t>OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>at grid node - OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>Grajewo_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Grajewo_POL</t>
+  </si>
+  <si>
     <t>Chelm_POL</t>
   </si>
   <si>
     <t>at grid node - Chelm_POL</t>
-  </si>
-  <si>
-    <t>Elk_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Elk_POL</t>
-  </si>
-  <si>
-    <t>Grajewo_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Grajewo_POL</t>
-  </si>
-  <si>
-    <t>Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>Kielce_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Kielce_POL</t>
-  </si>
-  <si>
-    <t>OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>at grid node - OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>Zamosc_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Zamosc_POL</t>
   </si>
   <si>
     <t>h_demand</t>
@@ -1102,13 +1102,13 @@
         <v>86</v>
       </c>
       <c r="M11" t="s">
-        <v>132</v>
+        <v>167</v>
       </c>
       <c r="N11" t="s">
-        <v>133</v>
+        <v>168</v>
       </c>
       <c r="O11" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q11" t="s">
         <v>86</v>
@@ -1164,13 +1164,13 @@
         <v>86</v>
       </c>
       <c r="M12" t="s">
-        <v>122</v>
+        <v>157</v>
       </c>
       <c r="N12" t="s">
-        <v>123</v>
+        <v>158</v>
       </c>
       <c r="O12" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q12" t="s">
         <v>86</v>
@@ -1226,13 +1226,13 @@
         <v>86</v>
       </c>
       <c r="M13" t="s">
-        <v>138</v>
+        <v>159</v>
       </c>
       <c r="N13" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="O13" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q13" t="s">
         <v>86</v>
@@ -1288,13 +1288,13 @@
         <v>86</v>
       </c>
       <c r="M14" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="N14" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="O14" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q14" t="s">
         <v>86</v>
@@ -1356,7 +1356,7 @@
         <v>149</v>
       </c>
       <c r="O15" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q15" t="s">
         <v>86</v>
@@ -1412,13 +1412,13 @@
         <v>86</v>
       </c>
       <c r="M16" t="s">
-        <v>163</v>
+        <v>124</v>
       </c>
       <c r="N16" t="s">
-        <v>164</v>
+        <v>125</v>
       </c>
       <c r="O16" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q16" t="s">
         <v>86</v>
@@ -1474,13 +1474,13 @@
         <v>86</v>
       </c>
       <c r="M17" t="s">
-        <v>168</v>
+        <v>126</v>
       </c>
       <c r="N17" t="s">
-        <v>169</v>
+        <v>127</v>
       </c>
       <c r="O17" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q17" t="s">
         <v>86</v>
@@ -1536,13 +1536,13 @@
         <v>86</v>
       </c>
       <c r="M18" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="N18" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="O18" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q18" t="s">
         <v>86</v>
@@ -1598,13 +1598,13 @@
         <v>86</v>
       </c>
       <c r="M19" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="N19" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="O19" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q19" t="s">
         <v>86</v>
@@ -1660,13 +1660,13 @@
         <v>86</v>
       </c>
       <c r="M20" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="N20" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="O20" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q20" t="s">
         <v>86</v>
@@ -1722,13 +1722,13 @@
         <v>86</v>
       </c>
       <c r="M21" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="N21" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="O21" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q21" t="s">
         <v>86</v>
@@ -1784,13 +1784,13 @@
         <v>86</v>
       </c>
       <c r="M22" t="s">
-        <v>172</v>
+        <v>122</v>
       </c>
       <c r="N22" t="s">
-        <v>173</v>
+        <v>123</v>
       </c>
       <c r="O22" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q22" t="s">
         <v>86</v>
@@ -1846,13 +1846,13 @@
         <v>86</v>
       </c>
       <c r="M23" t="s">
-        <v>146</v>
+        <v>176</v>
       </c>
       <c r="N23" t="s">
-        <v>147</v>
+        <v>177</v>
       </c>
       <c r="O23" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q23" t="s">
         <v>86</v>
@@ -1908,13 +1908,13 @@
         <v>86</v>
       </c>
       <c r="M24" t="s">
-        <v>174</v>
+        <v>90</v>
       </c>
       <c r="N24" t="s">
-        <v>175</v>
+        <v>91</v>
       </c>
       <c r="O24" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q24" t="s">
         <v>86</v>
@@ -1970,13 +1970,13 @@
         <v>86</v>
       </c>
       <c r="M25" t="s">
-        <v>176</v>
+        <v>87</v>
       </c>
       <c r="N25" t="s">
-        <v>177</v>
+        <v>88</v>
       </c>
       <c r="O25" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q25" t="s">
         <v>86</v>
@@ -2032,13 +2032,13 @@
         <v>86</v>
       </c>
       <c r="M26" t="s">
-        <v>114</v>
+        <v>165</v>
       </c>
       <c r="N26" t="s">
-        <v>115</v>
+        <v>166</v>
       </c>
       <c r="O26" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q26" t="s">
         <v>86</v>
@@ -2094,13 +2094,13 @@
         <v>86</v>
       </c>
       <c r="M27" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="N27" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="O27" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q27" t="s">
         <v>86</v>
@@ -2156,13 +2156,13 @@
         <v>86</v>
       </c>
       <c r="M28" t="s">
-        <v>161</v>
+        <v>106</v>
       </c>
       <c r="N28" t="s">
-        <v>162</v>
+        <v>107</v>
       </c>
       <c r="O28" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q28" t="s">
         <v>86</v>
@@ -2218,13 +2218,13 @@
         <v>86</v>
       </c>
       <c r="M29" t="s">
-        <v>96</v>
+        <v>146</v>
       </c>
       <c r="N29" t="s">
-        <v>97</v>
+        <v>147</v>
       </c>
       <c r="O29" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q29" t="s">
         <v>86</v>
@@ -2280,13 +2280,13 @@
         <v>86</v>
       </c>
       <c r="M30" t="s">
-        <v>150</v>
+        <v>178</v>
       </c>
       <c r="N30" t="s">
-        <v>151</v>
+        <v>179</v>
       </c>
       <c r="O30" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q30" t="s">
         <v>86</v>
@@ -2342,13 +2342,13 @@
         <v>86</v>
       </c>
       <c r="M31" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="N31" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="O31" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q31" t="s">
         <v>86</v>
@@ -2404,13 +2404,13 @@
         <v>86</v>
       </c>
       <c r="M32" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="N32" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="O32" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q32" t="s">
         <v>86</v>
@@ -2466,13 +2466,13 @@
         <v>86</v>
       </c>
       <c r="M33" t="s">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="N33" t="s">
-        <v>111</v>
+        <v>151</v>
       </c>
       <c r="O33" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q33" t="s">
         <v>86</v>
@@ -2528,13 +2528,13 @@
         <v>86</v>
       </c>
       <c r="M34" t="s">
-        <v>126</v>
+        <v>180</v>
       </c>
       <c r="N34" t="s">
-        <v>127</v>
+        <v>181</v>
       </c>
       <c r="O34" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q34" t="s">
         <v>86</v>
@@ -2590,13 +2590,13 @@
         <v>86</v>
       </c>
       <c r="M35" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="N35" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="O35" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q35" t="s">
         <v>86</v>
@@ -2652,13 +2652,13 @@
         <v>86</v>
       </c>
       <c r="M36" t="s">
-        <v>180</v>
+        <v>161</v>
       </c>
       <c r="N36" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="O36" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q36" t="s">
         <v>86</v>
@@ -2714,13 +2714,13 @@
         <v>86</v>
       </c>
       <c r="M37" t="s">
-        <v>98</v>
+        <v>182</v>
       </c>
       <c r="N37" t="s">
-        <v>99</v>
+        <v>183</v>
       </c>
       <c r="O37" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q37" t="s">
         <v>86</v>
@@ -2776,13 +2776,13 @@
         <v>86</v>
       </c>
       <c r="M38" t="s">
-        <v>90</v>
+        <v>128</v>
       </c>
       <c r="N38" t="s">
-        <v>91</v>
+        <v>129</v>
       </c>
       <c r="O38" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q38" t="s">
         <v>86</v>
@@ -2838,13 +2838,13 @@
         <v>86</v>
       </c>
       <c r="M39" t="s">
-        <v>116</v>
+        <v>152</v>
       </c>
       <c r="N39" t="s">
-        <v>117</v>
+        <v>153</v>
       </c>
       <c r="O39" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q39" t="s">
         <v>86</v>
@@ -2900,13 +2900,13 @@
         <v>86</v>
       </c>
       <c r="M40" t="s">
-        <v>134</v>
+        <v>102</v>
       </c>
       <c r="N40" t="s">
-        <v>135</v>
+        <v>103</v>
       </c>
       <c r="O40" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="41" spans="2:25" x14ac:dyDescent="0.45">
@@ -2938,13 +2938,13 @@
         <v>86</v>
       </c>
       <c r="M41" t="s">
-        <v>144</v>
+        <v>100</v>
       </c>
       <c r="N41" t="s">
-        <v>145</v>
+        <v>101</v>
       </c>
       <c r="O41" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="42" spans="2:25" x14ac:dyDescent="0.45">
@@ -2976,13 +2976,13 @@
         <v>86</v>
       </c>
       <c r="M42" t="s">
-        <v>140</v>
+        <v>96</v>
       </c>
       <c r="N42" t="s">
-        <v>141</v>
+        <v>97</v>
       </c>
       <c r="O42" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="43" spans="2:25" x14ac:dyDescent="0.45">
@@ -3014,13 +3014,13 @@
         <v>86</v>
       </c>
       <c r="M43" t="s">
-        <v>142</v>
+        <v>98</v>
       </c>
       <c r="N43" t="s">
-        <v>143</v>
+        <v>99</v>
       </c>
       <c r="O43" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="44" spans="2:25" x14ac:dyDescent="0.45">
@@ -3040,13 +3040,13 @@
         <v>86</v>
       </c>
       <c r="M44" t="s">
-        <v>94</v>
+        <v>142</v>
       </c>
       <c r="N44" t="s">
-        <v>95</v>
+        <v>143</v>
       </c>
       <c r="O44" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.45">
@@ -3066,13 +3066,13 @@
         <v>86</v>
       </c>
       <c r="M45" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="N45" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="O45" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="46" spans="2:25" x14ac:dyDescent="0.45">
@@ -3092,13 +3092,13 @@
         <v>86</v>
       </c>
       <c r="M46" t="s">
-        <v>155</v>
+        <v>112</v>
       </c>
       <c r="N46" t="s">
-        <v>156</v>
+        <v>113</v>
       </c>
       <c r="O46" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="47" spans="2:25" x14ac:dyDescent="0.45">
@@ -3118,13 +3118,13 @@
         <v>86</v>
       </c>
       <c r="M47" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="N47" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="O47" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="48" spans="2:25" x14ac:dyDescent="0.45">
@@ -3144,13 +3144,13 @@
         <v>86</v>
       </c>
       <c r="M48" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
       <c r="N48" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="O48" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="49" spans="7:15" x14ac:dyDescent="0.45">
@@ -3170,13 +3170,13 @@
         <v>86</v>
       </c>
       <c r="M49" t="s">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="N49" t="s">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="O49" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="50" spans="7:15" x14ac:dyDescent="0.45">
@@ -3184,13 +3184,13 @@
         <v>86</v>
       </c>
       <c r="M50" t="s">
-        <v>182</v>
+        <v>136</v>
       </c>
       <c r="N50" t="s">
-        <v>183</v>
+        <v>137</v>
       </c>
       <c r="O50" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="51" spans="7:15" x14ac:dyDescent="0.45">
@@ -3198,13 +3198,13 @@
         <v>86</v>
       </c>
       <c r="M51" t="s">
-        <v>100</v>
+        <v>134</v>
       </c>
       <c r="N51" t="s">
-        <v>101</v>
+        <v>135</v>
       </c>
       <c r="O51" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="52" spans="7:15" x14ac:dyDescent="0.45">
@@ -3212,13 +3212,13 @@
         <v>86</v>
       </c>
       <c r="M52" t="s">
-        <v>165</v>
+        <v>120</v>
       </c>
       <c r="N52" t="s">
-        <v>166</v>
+        <v>121</v>
       </c>
       <c r="O52" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="53" spans="7:15" x14ac:dyDescent="0.45">
@@ -3226,13 +3226,13 @@
         <v>86</v>
       </c>
       <c r="M53" t="s">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="N53" t="s">
-        <v>88</v>
+        <v>117</v>
       </c>
       <c r="O53" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="54" spans="7:15" x14ac:dyDescent="0.45">
@@ -3240,13 +3240,13 @@
         <v>86</v>
       </c>
       <c r="M54" t="s">
-        <v>184</v>
+        <v>108</v>
       </c>
       <c r="N54" t="s">
-        <v>185</v>
+        <v>109</v>
       </c>
       <c r="O54" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="55" spans="7:15" x14ac:dyDescent="0.45">
@@ -3254,13 +3254,13 @@
         <v>86</v>
       </c>
       <c r="M55" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="N55" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="O55" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="56" spans="7:15" x14ac:dyDescent="0.45">
@@ -3268,13 +3268,13 @@
         <v>86</v>
       </c>
       <c r="M56" t="s">
-        <v>104</v>
+        <v>144</v>
       </c>
       <c r="N56" t="s">
-        <v>105</v>
+        <v>145</v>
       </c>
       <c r="O56" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="57" spans="7:15" x14ac:dyDescent="0.45">
@@ -3282,13 +3282,13 @@
         <v>86</v>
       </c>
       <c r="M57" t="s">
-        <v>124</v>
+        <v>184</v>
       </c>
       <c r="N57" t="s">
-        <v>125</v>
+        <v>185</v>
       </c>
       <c r="O57" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="58" spans="7:15" x14ac:dyDescent="0.45">
@@ -3296,13 +3296,13 @@
         <v>86</v>
       </c>
       <c r="M58" t="s">
-        <v>92</v>
+        <v>138</v>
       </c>
       <c r="N58" t="s">
-        <v>93</v>
+        <v>139</v>
       </c>
       <c r="O58" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{340379A5-E493-49E8-84D6-A9AA9665F5AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13964169-BCB8-4254-A000-ECC0F3306E14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -541,61 +541,61 @@
     <t>at grid node - Krosno_POL</t>
   </si>
   <si>
+    <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
+  </si>
+  <si>
+    <t>Kielce_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Kielce_POL</t>
+  </si>
+  <si>
+    <t>Elk_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Elk_POL</t>
+  </si>
+  <si>
+    <t>Slupsk_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Slupsk_POL</t>
+  </si>
+  <si>
+    <t>Legnica_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Legnica_POL</t>
+  </si>
+  <si>
+    <t>OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>at grid node - OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
     <t>Olsztyn_POL</t>
   </si>
   <si>
     <t>at grid node - Olsztyn_POL</t>
   </si>
   <si>
-    <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
-  </si>
-  <si>
-    <t>Legnica_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Legnica_POL</t>
-  </si>
-  <si>
-    <t>Slupsk_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Slupsk_POL</t>
-  </si>
-  <si>
     <t>Zamosc_POL</t>
   </si>
   <si>
     <t>at grid node - Zamosc_POL</t>
   </si>
   <si>
-    <t>Kielce_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Kielce_POL</t>
-  </si>
-  <si>
-    <t>Elk_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Elk_POL</t>
-  </si>
-  <si>
-    <t>OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>at grid node - OstrowiecSwietokrz_POL</t>
+    <t>Chelm_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Chelm_POL</t>
   </si>
   <si>
     <t>Grajewo_POL</t>
   </si>
   <si>
     <t>at grid node - Grajewo_POL</t>
-  </si>
-  <si>
-    <t>Chelm_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Chelm_POL</t>
   </si>
   <si>
     <t>h_demand</t>
@@ -1102,13 +1102,13 @@
         <v>86</v>
       </c>
       <c r="M11" t="s">
-        <v>167</v>
+        <v>102</v>
       </c>
       <c r="N11" t="s">
-        <v>168</v>
+        <v>103</v>
       </c>
       <c r="O11" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q11" t="s">
         <v>86</v>
@@ -1164,13 +1164,13 @@
         <v>86</v>
       </c>
       <c r="M12" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="N12" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="O12" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q12" t="s">
         <v>86</v>
@@ -1226,13 +1226,13 @@
         <v>86</v>
       </c>
       <c r="M13" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="N13" t="s">
-        <v>160</v>
+        <v>143</v>
       </c>
       <c r="O13" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q13" t="s">
         <v>86</v>
@@ -1288,13 +1288,13 @@
         <v>86</v>
       </c>
       <c r="M14" t="s">
-        <v>170</v>
+        <v>118</v>
       </c>
       <c r="N14" t="s">
-        <v>171</v>
+        <v>119</v>
       </c>
       <c r="O14" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q14" t="s">
         <v>86</v>
@@ -1350,13 +1350,13 @@
         <v>86</v>
       </c>
       <c r="M15" t="s">
-        <v>148</v>
+        <v>116</v>
       </c>
       <c r="N15" t="s">
-        <v>149</v>
+        <v>117</v>
       </c>
       <c r="O15" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q15" t="s">
         <v>86</v>
@@ -1412,13 +1412,13 @@
         <v>86</v>
       </c>
       <c r="M16" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="N16" t="s">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="O16" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q16" t="s">
         <v>86</v>
@@ -1474,13 +1474,13 @@
         <v>86</v>
       </c>
       <c r="M17" t="s">
-        <v>126</v>
+        <v>168</v>
       </c>
       <c r="N17" t="s">
-        <v>127</v>
+        <v>169</v>
       </c>
       <c r="O17" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q17" t="s">
         <v>86</v>
@@ -1536,13 +1536,13 @@
         <v>86</v>
       </c>
       <c r="M18" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="N18" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="O18" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q18" t="s">
         <v>86</v>
@@ -1598,13 +1598,13 @@
         <v>86</v>
       </c>
       <c r="M19" t="s">
-        <v>174</v>
+        <v>87</v>
       </c>
       <c r="N19" t="s">
-        <v>175</v>
+        <v>88</v>
       </c>
       <c r="O19" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q19" t="s">
         <v>86</v>
@@ -1660,13 +1660,13 @@
         <v>86</v>
       </c>
       <c r="M20" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="N20" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="O20" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q20" t="s">
         <v>86</v>
@@ -1722,13 +1722,13 @@
         <v>86</v>
       </c>
       <c r="M21" t="s">
-        <v>114</v>
+        <v>161</v>
       </c>
       <c r="N21" t="s">
-        <v>115</v>
+        <v>162</v>
       </c>
       <c r="O21" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q21" t="s">
         <v>86</v>
@@ -1784,13 +1784,13 @@
         <v>86</v>
       </c>
       <c r="M22" t="s">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="N22" t="s">
-        <v>123</v>
+        <v>145</v>
       </c>
       <c r="O22" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q22" t="s">
         <v>86</v>
@@ -1846,13 +1846,13 @@
         <v>86</v>
       </c>
       <c r="M23" t="s">
-        <v>176</v>
+        <v>132</v>
       </c>
       <c r="N23" t="s">
-        <v>177</v>
+        <v>133</v>
       </c>
       <c r="O23" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q23" t="s">
         <v>86</v>
@@ -1908,13 +1908,13 @@
         <v>86</v>
       </c>
       <c r="M24" t="s">
-        <v>90</v>
+        <v>155</v>
       </c>
       <c r="N24" t="s">
-        <v>91</v>
+        <v>156</v>
       </c>
       <c r="O24" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q24" t="s">
         <v>86</v>
@@ -1970,13 +1970,13 @@
         <v>86</v>
       </c>
       <c r="M25" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="N25" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="O25" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q25" t="s">
         <v>86</v>
@@ -2032,13 +2032,13 @@
         <v>86</v>
       </c>
       <c r="M26" t="s">
-        <v>165</v>
+        <v>108</v>
       </c>
       <c r="N26" t="s">
-        <v>166</v>
+        <v>109</v>
       </c>
       <c r="O26" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q26" t="s">
         <v>86</v>
@@ -2094,13 +2094,13 @@
         <v>86</v>
       </c>
       <c r="M27" t="s">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="N27" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="O27" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q27" t="s">
         <v>86</v>
@@ -2156,13 +2156,13 @@
         <v>86</v>
       </c>
       <c r="M28" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="N28" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="O28" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q28" t="s">
         <v>86</v>
@@ -2218,13 +2218,13 @@
         <v>86</v>
       </c>
       <c r="M29" t="s">
-        <v>146</v>
+        <v>98</v>
       </c>
       <c r="N29" t="s">
-        <v>147</v>
+        <v>99</v>
       </c>
       <c r="O29" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q29" t="s">
         <v>86</v>
@@ -2280,13 +2280,13 @@
         <v>86</v>
       </c>
       <c r="M30" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="N30" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="O30" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q30" t="s">
         <v>86</v>
@@ -2342,13 +2342,13 @@
         <v>86</v>
       </c>
       <c r="M31" t="s">
-        <v>140</v>
+        <v>163</v>
       </c>
       <c r="N31" t="s">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="O31" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q31" t="s">
         <v>86</v>
@@ -2404,13 +2404,13 @@
         <v>86</v>
       </c>
       <c r="M32" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="N32" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="O32" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q32" t="s">
         <v>86</v>
@@ -2466,13 +2466,13 @@
         <v>86</v>
       </c>
       <c r="M33" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="N33" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="O33" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q33" t="s">
         <v>86</v>
@@ -2528,13 +2528,13 @@
         <v>86</v>
       </c>
       <c r="M34" t="s">
-        <v>180</v>
+        <v>136</v>
       </c>
       <c r="N34" t="s">
-        <v>181</v>
+        <v>137</v>
       </c>
       <c r="O34" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q34" t="s">
         <v>86</v>
@@ -2590,13 +2590,13 @@
         <v>86</v>
       </c>
       <c r="M35" t="s">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="N35" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="O35" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q35" t="s">
         <v>86</v>
@@ -2652,13 +2652,13 @@
         <v>86</v>
       </c>
       <c r="M36" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="N36" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="O36" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q36" t="s">
         <v>86</v>
@@ -2714,13 +2714,13 @@
         <v>86</v>
       </c>
       <c r="M37" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="N37" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="O37" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q37" t="s">
         <v>86</v>
@@ -2776,13 +2776,13 @@
         <v>86</v>
       </c>
       <c r="M38" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="N38" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="O38" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q38" t="s">
         <v>86</v>
@@ -2838,13 +2838,13 @@
         <v>86</v>
       </c>
       <c r="M39" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="N39" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="O39" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q39" t="s">
         <v>86</v>
@@ -2900,13 +2900,13 @@
         <v>86</v>
       </c>
       <c r="M40" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="N40" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="O40" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="41" spans="2:25" x14ac:dyDescent="0.45">
@@ -2938,13 +2938,13 @@
         <v>86</v>
       </c>
       <c r="M41" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="N41" t="s">
-        <v>101</v>
+        <v>125</v>
       </c>
       <c r="O41" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="42" spans="2:25" x14ac:dyDescent="0.45">
@@ -2976,13 +2976,13 @@
         <v>86</v>
       </c>
       <c r="M42" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N42" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="O42" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="43" spans="2:25" x14ac:dyDescent="0.45">
@@ -3014,13 +3014,13 @@
         <v>86</v>
       </c>
       <c r="M43" t="s">
-        <v>98</v>
+        <v>128</v>
       </c>
       <c r="N43" t="s">
-        <v>99</v>
+        <v>129</v>
       </c>
       <c r="O43" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="44" spans="2:25" x14ac:dyDescent="0.45">
@@ -3040,13 +3040,13 @@
         <v>86</v>
       </c>
       <c r="M44" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="N44" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="O44" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.45">
@@ -3072,7 +3072,7 @@
         <v>105</v>
       </c>
       <c r="O45" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="46" spans="2:25" x14ac:dyDescent="0.45">
@@ -3092,13 +3092,13 @@
         <v>86</v>
       </c>
       <c r="M46" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="N46" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="O46" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="47" spans="2:25" x14ac:dyDescent="0.45">
@@ -3118,13 +3118,13 @@
         <v>86</v>
       </c>
       <c r="M47" t="s">
-        <v>118</v>
+        <v>159</v>
       </c>
       <c r="N47" t="s">
-        <v>119</v>
+        <v>160</v>
       </c>
       <c r="O47" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="48" spans="2:25" x14ac:dyDescent="0.45">
@@ -3144,13 +3144,13 @@
         <v>86</v>
       </c>
       <c r="M48" t="s">
-        <v>132</v>
+        <v>180</v>
       </c>
       <c r="N48" t="s">
-        <v>133</v>
+        <v>181</v>
       </c>
       <c r="O48" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="49" spans="7:15" x14ac:dyDescent="0.45">
@@ -3170,13 +3170,13 @@
         <v>86</v>
       </c>
       <c r="M49" t="s">
-        <v>110</v>
+        <v>182</v>
       </c>
       <c r="N49" t="s">
-        <v>111</v>
+        <v>183</v>
       </c>
       <c r="O49" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="50" spans="7:15" x14ac:dyDescent="0.45">
@@ -3184,13 +3184,13 @@
         <v>86</v>
       </c>
       <c r="M50" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="N50" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="O50" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="51" spans="7:15" x14ac:dyDescent="0.45">
@@ -3198,13 +3198,13 @@
         <v>86</v>
       </c>
       <c r="M51" t="s">
-        <v>134</v>
+        <v>184</v>
       </c>
       <c r="N51" t="s">
-        <v>135</v>
+        <v>185</v>
       </c>
       <c r="O51" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="52" spans="7:15" x14ac:dyDescent="0.45">
@@ -3212,13 +3212,13 @@
         <v>86</v>
       </c>
       <c r="M52" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="N52" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="O52" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="53" spans="7:15" x14ac:dyDescent="0.45">
@@ -3226,13 +3226,13 @@
         <v>86</v>
       </c>
       <c r="M53" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="N53" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="O53" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="54" spans="7:15" x14ac:dyDescent="0.45">
@@ -3240,13 +3240,13 @@
         <v>86</v>
       </c>
       <c r="M54" t="s">
-        <v>108</v>
+        <v>157</v>
       </c>
       <c r="N54" t="s">
-        <v>109</v>
+        <v>158</v>
       </c>
       <c r="O54" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="55" spans="7:15" x14ac:dyDescent="0.45">
@@ -3254,13 +3254,13 @@
         <v>86</v>
       </c>
       <c r="M55" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="N55" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="O55" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="56" spans="7:15" x14ac:dyDescent="0.45">
@@ -3268,13 +3268,13 @@
         <v>86</v>
       </c>
       <c r="M56" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="N56" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="O56" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="57" spans="7:15" x14ac:dyDescent="0.45">
@@ -3282,13 +3282,13 @@
         <v>86</v>
       </c>
       <c r="M57" t="s">
-        <v>184</v>
+        <v>126</v>
       </c>
       <c r="N57" t="s">
-        <v>185</v>
+        <v>127</v>
       </c>
       <c r="O57" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="58" spans="7:15" x14ac:dyDescent="0.45">
@@ -3296,13 +3296,13 @@
         <v>86</v>
       </c>
       <c r="M58" t="s">
-        <v>138</v>
+        <v>106</v>
       </c>
       <c r="N58" t="s">
-        <v>139</v>
+        <v>107</v>
       </c>
       <c r="O58" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13964169-BCB8-4254-A000-ECC0F3306E14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D6510B1-14B4-479B-9ED5-B56F14EEF0AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -544,52 +544,52 @@
     <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
   </si>
   <si>
+    <t>OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>at grid node - OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
     <t>Kielce_POL</t>
   </si>
   <si>
     <t>at grid node - Kielce_POL</t>
   </si>
   <si>
+    <t>Zamosc_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Zamosc_POL</t>
+  </si>
+  <si>
     <t>Elk_POL</t>
   </si>
   <si>
     <t>at grid node - Elk_POL</t>
   </si>
   <si>
+    <t>Legnica_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Legnica_POL</t>
+  </si>
+  <si>
+    <t>Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>Chelm_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Chelm_POL</t>
+  </si>
+  <si>
     <t>Slupsk_POL</t>
   </si>
   <si>
     <t>at grid node - Slupsk_POL</t>
-  </si>
-  <si>
-    <t>Legnica_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Legnica_POL</t>
-  </si>
-  <si>
-    <t>OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>at grid node - OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>Zamosc_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Zamosc_POL</t>
-  </si>
-  <si>
-    <t>Chelm_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Chelm_POL</t>
   </si>
   <si>
     <t>Grajewo_POL</t>
@@ -1102,10 +1102,10 @@
         <v>86</v>
       </c>
       <c r="M11" t="s">
-        <v>102</v>
+        <v>159</v>
       </c>
       <c r="N11" t="s">
-        <v>103</v>
+        <v>160</v>
       </c>
       <c r="O11" t="s">
         <v>167</v>
@@ -1164,10 +1164,10 @@
         <v>86</v>
       </c>
       <c r="M12" t="s">
-        <v>165</v>
+        <v>118</v>
       </c>
       <c r="N12" t="s">
-        <v>166</v>
+        <v>119</v>
       </c>
       <c r="O12" t="s">
         <v>167</v>
@@ -1226,10 +1226,10 @@
         <v>86</v>
       </c>
       <c r="M13" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="N13" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="O13" t="s">
         <v>167</v>
@@ -1288,10 +1288,10 @@
         <v>86</v>
       </c>
       <c r="M14" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="N14" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
       <c r="O14" t="s">
         <v>167</v>
@@ -1350,10 +1350,10 @@
         <v>86</v>
       </c>
       <c r="M15" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="N15" t="s">
-        <v>117</v>
+        <v>139</v>
       </c>
       <c r="O15" t="s">
         <v>167</v>
@@ -1412,10 +1412,10 @@
         <v>86</v>
       </c>
       <c r="M16" t="s">
-        <v>140</v>
+        <v>94</v>
       </c>
       <c r="N16" t="s">
-        <v>141</v>
+        <v>95</v>
       </c>
       <c r="O16" t="s">
         <v>167</v>
@@ -1474,10 +1474,10 @@
         <v>86</v>
       </c>
       <c r="M17" t="s">
-        <v>168</v>
+        <v>132</v>
       </c>
       <c r="N17" t="s">
-        <v>169</v>
+        <v>133</v>
       </c>
       <c r="O17" t="s">
         <v>167</v>
@@ -1536,10 +1536,10 @@
         <v>86</v>
       </c>
       <c r="M18" t="s">
-        <v>170</v>
+        <v>112</v>
       </c>
       <c r="N18" t="s">
-        <v>171</v>
+        <v>113</v>
       </c>
       <c r="O18" t="s">
         <v>167</v>
@@ -1598,10 +1598,10 @@
         <v>86</v>
       </c>
       <c r="M19" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="N19" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="O19" t="s">
         <v>167</v>
@@ -1660,10 +1660,10 @@
         <v>86</v>
       </c>
       <c r="M20" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="N20" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="O20" t="s">
         <v>167</v>
@@ -1722,10 +1722,10 @@
         <v>86</v>
       </c>
       <c r="M21" t="s">
-        <v>161</v>
+        <v>120</v>
       </c>
       <c r="N21" t="s">
-        <v>162</v>
+        <v>121</v>
       </c>
       <c r="O21" t="s">
         <v>167</v>
@@ -1784,10 +1784,10 @@
         <v>86</v>
       </c>
       <c r="M22" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="N22" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="O22" t="s">
         <v>167</v>
@@ -1846,10 +1846,10 @@
         <v>86</v>
       </c>
       <c r="M23" t="s">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="N23" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="O23" t="s">
         <v>167</v>
@@ -1908,10 +1908,10 @@
         <v>86</v>
       </c>
       <c r="M24" t="s">
-        <v>155</v>
+        <v>106</v>
       </c>
       <c r="N24" t="s">
-        <v>156</v>
+        <v>107</v>
       </c>
       <c r="O24" t="s">
         <v>167</v>
@@ -1970,10 +1970,10 @@
         <v>86</v>
       </c>
       <c r="M25" t="s">
-        <v>90</v>
+        <v>146</v>
       </c>
       <c r="N25" t="s">
-        <v>91</v>
+        <v>147</v>
       </c>
       <c r="O25" t="s">
         <v>167</v>
@@ -2032,10 +2032,10 @@
         <v>86</v>
       </c>
       <c r="M26" t="s">
-        <v>108</v>
+        <v>170</v>
       </c>
       <c r="N26" t="s">
-        <v>109</v>
+        <v>171</v>
       </c>
       <c r="O26" t="s">
         <v>167</v>
@@ -2094,10 +2094,10 @@
         <v>86</v>
       </c>
       <c r="M27" t="s">
-        <v>134</v>
+        <v>104</v>
       </c>
       <c r="N27" t="s">
-        <v>135</v>
+        <v>105</v>
       </c>
       <c r="O27" t="s">
         <v>167</v>
@@ -2156,10 +2156,10 @@
         <v>86</v>
       </c>
       <c r="M28" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="N28" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="O28" t="s">
         <v>167</v>
@@ -2218,10 +2218,10 @@
         <v>86</v>
       </c>
       <c r="M29" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="N29" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="O29" t="s">
         <v>167</v>
@@ -2280,10 +2280,10 @@
         <v>86</v>
       </c>
       <c r="M30" t="s">
-        <v>172</v>
+        <v>116</v>
       </c>
       <c r="N30" t="s">
-        <v>173</v>
+        <v>117</v>
       </c>
       <c r="O30" t="s">
         <v>167</v>
@@ -2342,10 +2342,10 @@
         <v>86</v>
       </c>
       <c r="M31" t="s">
-        <v>163</v>
+        <v>142</v>
       </c>
       <c r="N31" t="s">
-        <v>164</v>
+        <v>143</v>
       </c>
       <c r="O31" t="s">
         <v>167</v>
@@ -2404,10 +2404,10 @@
         <v>86</v>
       </c>
       <c r="M32" t="s">
-        <v>174</v>
+        <v>130</v>
       </c>
       <c r="N32" t="s">
-        <v>175</v>
+        <v>131</v>
       </c>
       <c r="O32" t="s">
         <v>167</v>
@@ -2466,10 +2466,10 @@
         <v>86</v>
       </c>
       <c r="M33" t="s">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="N33" t="s">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="O33" t="s">
         <v>167</v>
@@ -2528,10 +2528,10 @@
         <v>86</v>
       </c>
       <c r="M34" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="N34" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="O34" t="s">
         <v>167</v>
@@ -2590,10 +2590,10 @@
         <v>86</v>
       </c>
       <c r="M35" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="N35" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="O35" t="s">
         <v>167</v>
@@ -2652,10 +2652,10 @@
         <v>86</v>
       </c>
       <c r="M36" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="N36" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="O36" t="s">
         <v>167</v>
@@ -2714,10 +2714,10 @@
         <v>86</v>
       </c>
       <c r="M37" t="s">
-        <v>178</v>
+        <v>161</v>
       </c>
       <c r="N37" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="O37" t="s">
         <v>167</v>
@@ -2776,10 +2776,10 @@
         <v>86</v>
       </c>
       <c r="M38" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="N38" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="O38" t="s">
         <v>167</v>
@@ -2838,10 +2838,10 @@
         <v>86</v>
       </c>
       <c r="M39" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="N39" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="O39" t="s">
         <v>167</v>
@@ -2900,10 +2900,10 @@
         <v>86</v>
       </c>
       <c r="M40" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="N40" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="O40" t="s">
         <v>167</v>
@@ -2938,10 +2938,10 @@
         <v>86</v>
       </c>
       <c r="M41" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="N41" t="s">
-        <v>125</v>
+        <v>97</v>
       </c>
       <c r="O41" t="s">
         <v>167</v>
@@ -2976,10 +2976,10 @@
         <v>86</v>
       </c>
       <c r="M42" t="s">
-        <v>94</v>
+        <v>124</v>
       </c>
       <c r="N42" t="s">
-        <v>95</v>
+        <v>125</v>
       </c>
       <c r="O42" t="s">
         <v>167</v>
@@ -3014,10 +3014,10 @@
         <v>86</v>
       </c>
       <c r="M43" t="s">
-        <v>128</v>
+        <v>174</v>
       </c>
       <c r="N43" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="O43" t="s">
         <v>167</v>
@@ -3040,10 +3040,10 @@
         <v>86</v>
       </c>
       <c r="M44" t="s">
-        <v>148</v>
+        <v>126</v>
       </c>
       <c r="N44" t="s">
-        <v>149</v>
+        <v>127</v>
       </c>
       <c r="O44" t="s">
         <v>167</v>
@@ -3066,10 +3066,10 @@
         <v>86</v>
       </c>
       <c r="M45" t="s">
-        <v>104</v>
+        <v>176</v>
       </c>
       <c r="N45" t="s">
-        <v>105</v>
+        <v>177</v>
       </c>
       <c r="O45" t="s">
         <v>167</v>
@@ -3092,10 +3092,10 @@
         <v>86</v>
       </c>
       <c r="M46" t="s">
-        <v>122</v>
+        <v>87</v>
       </c>
       <c r="N46" t="s">
-        <v>123</v>
+        <v>88</v>
       </c>
       <c r="O46" t="s">
         <v>167</v>
@@ -3118,10 +3118,10 @@
         <v>86</v>
       </c>
       <c r="M47" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="N47" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="O47" t="s">
         <v>167</v>
@@ -3144,10 +3144,10 @@
         <v>86</v>
       </c>
       <c r="M48" t="s">
-        <v>180</v>
+        <v>110</v>
       </c>
       <c r="N48" t="s">
-        <v>181</v>
+        <v>111</v>
       </c>
       <c r="O48" t="s">
         <v>167</v>
@@ -3170,10 +3170,10 @@
         <v>86</v>
       </c>
       <c r="M49" t="s">
-        <v>182</v>
+        <v>102</v>
       </c>
       <c r="N49" t="s">
-        <v>183</v>
+        <v>103</v>
       </c>
       <c r="O49" t="s">
         <v>167</v>
@@ -3184,10 +3184,10 @@
         <v>86</v>
       </c>
       <c r="M50" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="N50" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="O50" t="s">
         <v>167</v>
@@ -3198,10 +3198,10 @@
         <v>86</v>
       </c>
       <c r="M51" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="N51" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="O51" t="s">
         <v>167</v>
@@ -3212,10 +3212,10 @@
         <v>86</v>
       </c>
       <c r="M52" t="s">
-        <v>114</v>
+        <v>150</v>
       </c>
       <c r="N52" t="s">
-        <v>115</v>
+        <v>151</v>
       </c>
       <c r="O52" t="s">
         <v>167</v>
@@ -3226,10 +3226,10 @@
         <v>86</v>
       </c>
       <c r="M53" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="N53" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="O53" t="s">
         <v>167</v>
@@ -3240,10 +3240,10 @@
         <v>86</v>
       </c>
       <c r="M54" t="s">
-        <v>157</v>
+        <v>180</v>
       </c>
       <c r="N54" t="s">
-        <v>158</v>
+        <v>181</v>
       </c>
       <c r="O54" t="s">
         <v>167</v>
@@ -3254,10 +3254,10 @@
         <v>86</v>
       </c>
       <c r="M55" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="N55" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="O55" t="s">
         <v>167</v>
@@ -3268,10 +3268,10 @@
         <v>86</v>
       </c>
       <c r="M56" t="s">
-        <v>130</v>
+        <v>155</v>
       </c>
       <c r="N56" t="s">
-        <v>131</v>
+        <v>156</v>
       </c>
       <c r="O56" t="s">
         <v>167</v>
@@ -3282,10 +3282,10 @@
         <v>86</v>
       </c>
       <c r="M57" t="s">
-        <v>126</v>
+        <v>182</v>
       </c>
       <c r="N57" t="s">
-        <v>127</v>
+        <v>183</v>
       </c>
       <c r="O57" t="s">
         <v>167</v>
@@ -3296,10 +3296,10 @@
         <v>86</v>
       </c>
       <c r="M58" t="s">
-        <v>106</v>
+        <v>184</v>
       </c>
       <c r="N58" t="s">
-        <v>107</v>
+        <v>185</v>
       </c>
       <c r="O58" t="s">
         <v>167</v>

--- a/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D6510B1-14B4-479B-9ED5-B56F14EEF0AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{975EE90F-44D2-436B-A527-0C504E7A01D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="930" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="189">
   <si>
     <t>PSET_PN</t>
   </si>
@@ -602,6 +602,9 @@
   </si>
   <si>
     <t>en_hop_gas_boiler,en_hop_biomass_chips,en_hop_electric_boiler,en_hp_air_10mw</t>
+  </si>
+  <si>
+    <t>ELE,CHP,-STG</t>
   </si>
 </sst>
 </file>
@@ -3336,7 +3339,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="C4:X58"/>
+  <dimension ref="C4:X57"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="3" max="3" width="13.3984375" bestFit="1" customWidth="1"/>
@@ -3894,7 +3897,7 @@
         <v>1.5</v>
       </c>
       <c r="T24" t="str">
-        <f t="shared" ref="T18:T24" si="7">T20</f>
+        <f t="shared" ref="T24" si="7">T20</f>
         <v>E[_]WOF*</v>
       </c>
       <c r="W24" t="str">
@@ -4002,276 +4005,282 @@
     </row>
     <row r="35" spans="3:22" x14ac:dyDescent="0.45">
       <c r="C35" t="s">
-        <v>17</v>
+        <v>188</v>
       </c>
       <c r="D35" t="s">
-        <v>12</v>
-      </c>
-      <c r="F35">
-        <v>0</v>
-      </c>
-      <c r="G35">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="36" spans="3:22" x14ac:dyDescent="0.45">
-      <c r="C36" t="s">
-        <v>38</v>
-      </c>
-      <c r="D36" t="s">
         <v>69</v>
       </c>
-      <c r="G36" s="1">
+      <c r="G35" s="1">
         <v>0.9</v>
       </c>
     </row>
-    <row r="39" spans="3:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="3:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="C38" t="s">
+        <v>20</v>
+      </c>
+      <c r="P38" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="3:22" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="C39" t="s">
-        <v>20</v>
-      </c>
-      <c r="P39" s="4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="40" spans="3:22" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
+        <v>21</v>
+      </c>
+      <c r="D39" t="s">
+        <v>22</v>
+      </c>
+      <c r="E39" t="s">
+        <v>23</v>
+      </c>
+      <c r="P39" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="Q39" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="R39" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="S39" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="T39" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="U39" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="V39" s="6" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="40" spans="3:22" x14ac:dyDescent="0.45">
       <c r="C40" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D40" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="E40" t="s">
-        <v>23</v>
-      </c>
-      <c r="P40" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q40" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="R40" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="S40" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="T40" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="U40" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="V40" s="6" t="s">
-        <v>78</v>
+        <v>24</v>
+      </c>
+      <c r="P40" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>80</v>
+      </c>
+      <c r="R40" t="s">
+        <v>81</v>
+      </c>
+      <c r="S40">
+        <v>1</v>
+      </c>
+      <c r="T40" t="s">
+        <v>82</v>
+      </c>
+      <c r="U40" t="s">
+        <v>83</v>
+      </c>
+      <c r="V40" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="41" spans="3:22" x14ac:dyDescent="0.45">
       <c r="C41" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D41" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="E41" t="s">
         <v>24</v>
       </c>
-      <c r="P41" t="s">
-        <v>79</v>
-      </c>
-      <c r="Q41" t="s">
-        <v>80</v>
-      </c>
-      <c r="R41" t="s">
-        <v>81</v>
-      </c>
-      <c r="S41">
-        <v>1</v>
-      </c>
-      <c r="T41" t="s">
-        <v>82</v>
-      </c>
-      <c r="U41" t="s">
-        <v>83</v>
-      </c>
-      <c r="V41" t="s">
-        <v>84</v>
-      </c>
     </row>
     <row r="42" spans="3:22" x14ac:dyDescent="0.45">
       <c r="C42" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="D42" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="E42" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="43" spans="3:22" x14ac:dyDescent="0.45">
+    <row r="43" spans="3:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C43" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D43" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="E43" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="44" spans="3:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="P43" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="44" spans="3:22" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="C44" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D44" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E44" t="s">
         <v>24</v>
       </c>
-      <c r="P44" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="45" spans="3:22" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="C45" t="s">
-        <v>41</v>
-      </c>
-      <c r="D45" t="s">
-        <v>58</v>
-      </c>
-      <c r="E45" t="s">
-        <v>24</v>
-      </c>
-      <c r="P45" s="5" t="s">
+      <c r="P44" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="Q45" s="5" t="s">
+      <c r="Q44" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="R45" s="5" t="s">
+      <c r="R44" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="S45" s="6" t="s">
+      <c r="S44" s="6" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="46" spans="3:22" x14ac:dyDescent="0.45">
-      <c r="P46" t="s">
+    <row r="45" spans="3:22" x14ac:dyDescent="0.45">
+      <c r="P45" t="s">
         <v>82</v>
       </c>
-      <c r="Q46" t="s">
+      <c r="Q45" t="s">
         <v>80</v>
       </c>
-      <c r="R46" t="s">
+      <c r="R45" t="s">
         <v>84</v>
       </c>
-      <c r="S46" t="s">
+      <c r="S45" t="s">
         <v>81</v>
+      </c>
+    </row>
+    <row r="47" spans="3:22" x14ac:dyDescent="0.45">
+      <c r="C47" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="48" spans="3:22" x14ac:dyDescent="0.45">
       <c r="C48" t="s">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="D48" t="s">
+        <v>26</v>
+      </c>
+      <c r="E48" t="s">
+        <v>51</v>
+      </c>
+      <c r="F48" t="s">
+        <v>73</v>
+      </c>
+      <c r="G48" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="49" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C49" t="s">
-        <v>1</v>
-      </c>
-      <c r="D49" t="s">
-        <v>26</v>
-      </c>
-      <c r="E49" t="s">
-        <v>51</v>
-      </c>
-      <c r="F49" t="s">
-        <v>73</v>
+        <v>49</v>
+      </c>
+      <c r="D49">
+        <v>2025</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>74</v>
       </c>
       <c r="G49" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
     <row r="50" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C50" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D50">
-        <v>2025</v>
+        <v>40</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="G50" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="51" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C51" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D51">
-        <v>40</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="G51" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.45">
-      <c r="C52" t="s">
-        <v>49</v>
-      </c>
-      <c r="D52">
         <v>2100</v>
       </c>
-      <c r="F52" t="s">
+      <c r="F51" t="s">
         <v>76</v>
+      </c>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.45">
+      <c r="C54" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="55" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C55" t="s">
-        <v>37</v>
+        <v>25</v>
+      </c>
+      <c r="D55" t="s">
+        <v>60</v>
+      </c>
+      <c r="E55" t="s">
+        <v>50</v>
+      </c>
+      <c r="F55" t="s">
+        <v>21</v>
+      </c>
+      <c r="G55" t="s">
+        <v>51</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55">
+        <v>2022</v>
+      </c>
+      <c r="J55">
+        <v>2030</v>
+      </c>
+      <c r="K55" t="s">
+        <v>61</v>
+      </c>
+      <c r="L55" t="s">
+        <v>62</v>
+      </c>
+      <c r="M55" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="56" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C56" t="s">
-        <v>25</v>
-      </c>
-      <c r="D56" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E56" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="F56" t="s">
-        <v>21</v>
-      </c>
-      <c r="G56" t="s">
-        <v>51</v>
-      </c>
-      <c r="H56">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="I56">
-        <v>2022</v>
-      </c>
-      <c r="J56">
-        <v>2030</v>
-      </c>
-      <c r="K56" t="s">
-        <v>61</v>
+        <v>0.95</v>
       </c>
       <c r="L56" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="M56" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
     </row>
     <row r="57" spans="3:13" x14ac:dyDescent="0.45">
@@ -4279,38 +4288,18 @@
         <v>63</v>
       </c>
       <c r="E57" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F57" t="s">
         <v>67</v>
       </c>
       <c r="I57">
-        <v>0.95</v>
+        <v>0.85</v>
       </c>
       <c r="L57" t="s">
         <v>65</v>
       </c>
       <c r="M57" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.45">
-      <c r="C58" t="s">
-        <v>63</v>
-      </c>
-      <c r="E58" t="s">
-        <v>68</v>
-      </c>
-      <c r="F58" t="s">
-        <v>67</v>
-      </c>
-      <c r="I58">
-        <v>0.85</v>
-      </c>
-      <c r="L58" t="s">
-        <v>65</v>
-      </c>
-      <c r="M58" t="s">
         <v>66</v>
       </c>
     </row>

--- a/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{975EE90F-44D2-436B-A527-0C504E7A01D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCF81AE6-557B-43AC-9296-A007A1246212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="928" uniqueCount="188">
   <si>
     <t>PSET_PN</t>
   </si>
@@ -94,9 +94,6 @@
     <t>ELE</t>
   </si>
   <si>
-    <t>NCAP_DRATE</t>
-  </si>
-  <si>
     <t>EN[_]Hydro*</t>
   </si>
   <si>
@@ -298,6 +295,9 @@
     <t>~TFM_TOPINS-A</t>
   </si>
   <si>
+    <t>ELE,CHP,-STG</t>
+  </si>
+  <si>
     <t>POL</t>
   </si>
   <si>
@@ -541,19 +541,55 @@
     <t>at grid node - Krosno_POL</t>
   </si>
   <si>
+    <t>Kielce_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Kielce_POL</t>
+  </si>
+  <si>
     <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
   </si>
   <si>
+    <t>Legnica_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Legnica_POL</t>
+  </si>
+  <si>
+    <t>Elk_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Elk_POL</t>
+  </si>
+  <si>
     <t>OstrowiecSwietokrz_POL</t>
   </si>
   <si>
     <t>at grid node - OstrowiecSwietokrz_POL</t>
   </si>
   <si>
-    <t>Kielce_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Kielce_POL</t>
+    <t>Slupsk_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Slupsk_POL</t>
+  </si>
+  <si>
+    <t>Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>Grajewo_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Grajewo_POL</t>
+  </si>
+  <si>
+    <t>Chelm_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Chelm_POL</t>
   </si>
   <si>
     <t>Zamosc_POL</t>
@@ -562,49 +598,10 @@
     <t>at grid node - Zamosc_POL</t>
   </si>
   <si>
-    <t>Elk_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Elk_POL</t>
-  </si>
-  <si>
-    <t>Legnica_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Legnica_POL</t>
-  </si>
-  <si>
-    <t>Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>Chelm_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Chelm_POL</t>
-  </si>
-  <si>
-    <t>Slupsk_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Slupsk_POL</t>
-  </si>
-  <si>
-    <t>Grajewo_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Grajewo_POL</t>
-  </si>
-  <si>
     <t>h_demand</t>
   </si>
   <si>
     <t>en_hop_gas_boiler,en_hop_biomass_chips,en_hop_electric_boiler,en_hp_air_10mw</t>
-  </si>
-  <si>
-    <t>ELE,CHP,-STG</t>
   </si>
 </sst>
 </file>
@@ -978,20 +975,20 @@
   <sheetData>
     <row r="3" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -999,81 +996,81 @@
     </row>
     <row r="9" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="V9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" spans="2:25" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C10" t="s">
+        <v>70</v>
+      </c>
+      <c r="D10" t="s">
         <v>71</v>
       </c>
-      <c r="D10" t="s">
-        <v>72</v>
-      </c>
       <c r="E10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H10" t="s">
+        <v>70</v>
+      </c>
+      <c r="I10" t="s">
         <v>71</v>
       </c>
-      <c r="I10" t="s">
-        <v>72</v>
-      </c>
       <c r="J10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M10" t="s">
+        <v>70</v>
+      </c>
+      <c r="N10" t="s">
         <v>71</v>
       </c>
-      <c r="N10" t="s">
-        <v>72</v>
-      </c>
       <c r="O10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Q10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R10" t="s">
+        <v>70</v>
+      </c>
+      <c r="S10" t="s">
         <v>71</v>
       </c>
-      <c r="S10" t="s">
-        <v>72</v>
-      </c>
       <c r="T10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="V10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="W10" t="s">
+        <v>70</v>
+      </c>
+      <c r="X10" t="s">
         <v>71</v>
       </c>
-      <c r="X10" t="s">
-        <v>72</v>
-      </c>
       <c r="Y10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="2:25" x14ac:dyDescent="0.45">
@@ -1105,13 +1102,13 @@
         <v>86</v>
       </c>
       <c r="M11" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="N11" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="O11" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q11" t="s">
         <v>86</v>
@@ -1167,13 +1164,13 @@
         <v>86</v>
       </c>
       <c r="M12" t="s">
-        <v>118</v>
+        <v>170</v>
       </c>
       <c r="N12" t="s">
-        <v>119</v>
+        <v>171</v>
       </c>
       <c r="O12" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q12" t="s">
         <v>86</v>
@@ -1229,13 +1226,13 @@
         <v>86</v>
       </c>
       <c r="M13" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="N13" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="O13" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q13" t="s">
         <v>86</v>
@@ -1291,13 +1288,13 @@
         <v>86</v>
       </c>
       <c r="M14" t="s">
-        <v>140</v>
+        <v>112</v>
       </c>
       <c r="N14" t="s">
-        <v>141</v>
+        <v>113</v>
       </c>
       <c r="O14" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q14" t="s">
         <v>86</v>
@@ -1353,13 +1350,13 @@
         <v>86</v>
       </c>
       <c r="M15" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="N15" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="O15" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q15" t="s">
         <v>86</v>
@@ -1415,13 +1412,13 @@
         <v>86</v>
       </c>
       <c r="M16" t="s">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="N16" t="s">
-        <v>95</v>
+        <v>123</v>
       </c>
       <c r="O16" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q16" t="s">
         <v>86</v>
@@ -1477,13 +1474,13 @@
         <v>86</v>
       </c>
       <c r="M17" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="N17" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="O17" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q17" t="s">
         <v>86</v>
@@ -1539,13 +1536,13 @@
         <v>86</v>
       </c>
       <c r="M18" t="s">
-        <v>112</v>
+        <v>174</v>
       </c>
       <c r="N18" t="s">
-        <v>113</v>
+        <v>175</v>
       </c>
       <c r="O18" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q18" t="s">
         <v>86</v>
@@ -1601,13 +1598,13 @@
         <v>86</v>
       </c>
       <c r="M19" t="s">
-        <v>90</v>
+        <v>159</v>
       </c>
       <c r="N19" t="s">
-        <v>91</v>
+        <v>160</v>
       </c>
       <c r="O19" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q19" t="s">
         <v>86</v>
@@ -1669,7 +1666,7 @@
         <v>101</v>
       </c>
       <c r="O20" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q20" t="s">
         <v>86</v>
@@ -1725,13 +1722,13 @@
         <v>86</v>
       </c>
       <c r="M21" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="N21" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="O21" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q21" t="s">
         <v>86</v>
@@ -1787,13 +1784,13 @@
         <v>86</v>
       </c>
       <c r="M22" t="s">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="N22" t="s">
-        <v>135</v>
+        <v>147</v>
       </c>
       <c r="O22" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q22" t="s">
         <v>86</v>
@@ -1849,13 +1846,13 @@
         <v>86</v>
       </c>
       <c r="M23" t="s">
-        <v>152</v>
+        <v>87</v>
       </c>
       <c r="N23" t="s">
-        <v>153</v>
+        <v>88</v>
       </c>
       <c r="O23" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q23" t="s">
         <v>86</v>
@@ -1911,13 +1908,13 @@
         <v>86</v>
       </c>
       <c r="M24" t="s">
-        <v>106</v>
+        <v>165</v>
       </c>
       <c r="N24" t="s">
-        <v>107</v>
+        <v>166</v>
       </c>
       <c r="O24" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q24" t="s">
         <v>86</v>
@@ -1973,13 +1970,13 @@
         <v>86</v>
       </c>
       <c r="M25" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="N25" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="O25" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q25" t="s">
         <v>86</v>
@@ -2035,13 +2032,13 @@
         <v>86</v>
       </c>
       <c r="M26" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="N26" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="O26" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q26" t="s">
         <v>86</v>
@@ -2097,13 +2094,13 @@
         <v>86</v>
       </c>
       <c r="M27" t="s">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="N27" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="O27" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q27" t="s">
         <v>86</v>
@@ -2159,13 +2156,13 @@
         <v>86</v>
       </c>
       <c r="M28" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="N28" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="O28" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q28" t="s">
         <v>86</v>
@@ -2221,13 +2218,13 @@
         <v>86</v>
       </c>
       <c r="M29" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="N29" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="O29" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q29" t="s">
         <v>86</v>
@@ -2283,13 +2280,13 @@
         <v>86</v>
       </c>
       <c r="M30" t="s">
-        <v>116</v>
+        <v>163</v>
       </c>
       <c r="N30" t="s">
-        <v>117</v>
+        <v>164</v>
       </c>
       <c r="O30" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q30" t="s">
         <v>86</v>
@@ -2345,13 +2342,13 @@
         <v>86</v>
       </c>
       <c r="M31" t="s">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="N31" t="s">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="O31" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q31" t="s">
         <v>86</v>
@@ -2407,13 +2404,13 @@
         <v>86</v>
       </c>
       <c r="M32" t="s">
-        <v>130</v>
+        <v>92</v>
       </c>
       <c r="N32" t="s">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="O32" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q32" t="s">
         <v>86</v>
@@ -2469,13 +2466,13 @@
         <v>86</v>
       </c>
       <c r="M33" t="s">
-        <v>172</v>
+        <v>126</v>
       </c>
       <c r="N33" t="s">
-        <v>173</v>
+        <v>127</v>
       </c>
       <c r="O33" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q33" t="s">
         <v>86</v>
@@ -2531,13 +2528,13 @@
         <v>86</v>
       </c>
       <c r="M34" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="N34" t="s">
-        <v>123</v>
+        <v>99</v>
       </c>
       <c r="O34" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q34" t="s">
         <v>86</v>
@@ -2593,13 +2590,13 @@
         <v>86</v>
       </c>
       <c r="M35" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="N35" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="O35" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q35" t="s">
         <v>86</v>
@@ -2655,13 +2652,13 @@
         <v>86</v>
       </c>
       <c r="M36" t="s">
-        <v>165</v>
+        <v>120</v>
       </c>
       <c r="N36" t="s">
-        <v>166</v>
+        <v>121</v>
       </c>
       <c r="O36" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q36" t="s">
         <v>86</v>
@@ -2717,13 +2714,13 @@
         <v>86</v>
       </c>
       <c r="M37" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="N37" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="O37" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q37" t="s">
         <v>86</v>
@@ -2779,13 +2776,13 @@
         <v>86</v>
       </c>
       <c r="M38" t="s">
-        <v>108</v>
+        <v>178</v>
       </c>
       <c r="N38" t="s">
-        <v>109</v>
+        <v>179</v>
       </c>
       <c r="O38" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q38" t="s">
         <v>86</v>
@@ -2841,13 +2838,13 @@
         <v>86</v>
       </c>
       <c r="M39" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="N39" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="O39" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q39" t="s">
         <v>86</v>
@@ -2903,13 +2900,13 @@
         <v>86</v>
       </c>
       <c r="M40" t="s">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="N40" t="s">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="O40" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="41" spans="2:25" x14ac:dyDescent="0.45">
@@ -2941,13 +2938,13 @@
         <v>86</v>
       </c>
       <c r="M41" t="s">
-        <v>96</v>
+        <v>180</v>
       </c>
       <c r="N41" t="s">
-        <v>97</v>
+        <v>181</v>
       </c>
       <c r="O41" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="42" spans="2:25" x14ac:dyDescent="0.45">
@@ -2979,13 +2976,13 @@
         <v>86</v>
       </c>
       <c r="M42" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="N42" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="O42" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="43" spans="2:25" x14ac:dyDescent="0.45">
@@ -3017,13 +3014,13 @@
         <v>86</v>
       </c>
       <c r="M43" t="s">
-        <v>174</v>
+        <v>124</v>
       </c>
       <c r="N43" t="s">
-        <v>175</v>
+        <v>125</v>
       </c>
       <c r="O43" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="44" spans="2:25" x14ac:dyDescent="0.45">
@@ -3043,13 +3040,13 @@
         <v>86</v>
       </c>
       <c r="M44" t="s">
-        <v>126</v>
+        <v>96</v>
       </c>
       <c r="N44" t="s">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="O44" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.45">
@@ -3069,13 +3066,13 @@
         <v>86</v>
       </c>
       <c r="M45" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="N45" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="O45" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="46" spans="2:25" x14ac:dyDescent="0.45">
@@ -3095,13 +3092,13 @@
         <v>86</v>
       </c>
       <c r="M46" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="N46" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="O46" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="47" spans="2:25" x14ac:dyDescent="0.45">
@@ -3121,13 +3118,13 @@
         <v>86</v>
       </c>
       <c r="M47" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="N47" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="O47" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="48" spans="2:25" x14ac:dyDescent="0.45">
@@ -3147,13 +3144,13 @@
         <v>86</v>
       </c>
       <c r="M48" t="s">
-        <v>110</v>
+        <v>155</v>
       </c>
       <c r="N48" t="s">
-        <v>111</v>
+        <v>156</v>
       </c>
       <c r="O48" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="49" spans="7:15" x14ac:dyDescent="0.45">
@@ -3173,13 +3170,13 @@
         <v>86</v>
       </c>
       <c r="M49" t="s">
-        <v>102</v>
+        <v>148</v>
       </c>
       <c r="N49" t="s">
-        <v>103</v>
+        <v>149</v>
       </c>
       <c r="O49" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="50" spans="7:15" x14ac:dyDescent="0.45">
@@ -3187,13 +3184,13 @@
         <v>86</v>
       </c>
       <c r="M50" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="N50" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="O50" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="51" spans="7:15" x14ac:dyDescent="0.45">
@@ -3201,13 +3198,13 @@
         <v>86</v>
       </c>
       <c r="M51" t="s">
-        <v>178</v>
+        <v>136</v>
       </c>
       <c r="N51" t="s">
-        <v>179</v>
+        <v>137</v>
       </c>
       <c r="O51" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="52" spans="7:15" x14ac:dyDescent="0.45">
@@ -3215,13 +3212,13 @@
         <v>86</v>
       </c>
       <c r="M52" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="N52" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="O52" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="53" spans="7:15" x14ac:dyDescent="0.45">
@@ -3229,13 +3226,13 @@
         <v>86</v>
       </c>
       <c r="M53" t="s">
-        <v>136</v>
+        <v>90</v>
       </c>
       <c r="N53" t="s">
-        <v>137</v>
+        <v>91</v>
       </c>
       <c r="O53" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="54" spans="7:15" x14ac:dyDescent="0.45">
@@ -3243,13 +3240,13 @@
         <v>86</v>
       </c>
       <c r="M54" t="s">
-        <v>180</v>
+        <v>108</v>
       </c>
       <c r="N54" t="s">
-        <v>181</v>
+        <v>109</v>
       </c>
       <c r="O54" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="55" spans="7:15" x14ac:dyDescent="0.45">
@@ -3257,13 +3254,13 @@
         <v>86</v>
       </c>
       <c r="M55" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="N55" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="O55" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="56" spans="7:15" x14ac:dyDescent="0.45">
@@ -3271,13 +3268,13 @@
         <v>86</v>
       </c>
       <c r="M56" t="s">
-        <v>155</v>
+        <v>184</v>
       </c>
       <c r="N56" t="s">
-        <v>156</v>
+        <v>185</v>
       </c>
       <c r="O56" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="57" spans="7:15" x14ac:dyDescent="0.45">
@@ -3285,13 +3282,13 @@
         <v>86</v>
       </c>
       <c r="M57" t="s">
-        <v>182</v>
+        <v>102</v>
       </c>
       <c r="N57" t="s">
-        <v>183</v>
+        <v>103</v>
       </c>
       <c r="O57" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="58" spans="7:15" x14ac:dyDescent="0.45">
@@ -3299,13 +3296,13 @@
         <v>86</v>
       </c>
       <c r="M58" t="s">
-        <v>184</v>
+        <v>144</v>
       </c>
       <c r="N58" t="s">
-        <v>185</v>
+        <v>145</v>
       </c>
       <c r="O58" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -3366,13 +3363,13 @@
         <v>4</v>
       </c>
       <c r="L4" t="s">
+        <v>24</v>
+      </c>
+      <c r="M4" t="s">
         <v>25</v>
       </c>
-      <c r="M4" t="s">
-        <v>26</v>
-      </c>
       <c r="N4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="3:24" x14ac:dyDescent="0.45">
@@ -3392,13 +3389,13 @@
         <v>5</v>
       </c>
       <c r="L5" t="s">
+        <v>26</v>
+      </c>
+      <c r="M5" t="s">
         <v>27</v>
       </c>
-      <c r="M5" t="s">
+      <c r="N5" t="s">
         <v>28</v>
-      </c>
-      <c r="N5" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="6" spans="3:24" x14ac:dyDescent="0.45">
@@ -3406,19 +3403,19 @@
         <v>6</v>
       </c>
       <c r="E6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G6" s="1">
         <v>8.76</v>
       </c>
       <c r="L6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M6" t="s">
+        <v>27</v>
+      </c>
+      <c r="N6" t="s">
         <v>28</v>
-      </c>
-      <c r="N6" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="7" spans="3:24" x14ac:dyDescent="0.45">
@@ -3426,19 +3423,19 @@
         <v>7</v>
       </c>
       <c r="E7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G7">
         <v>25</v>
       </c>
       <c r="L7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M7" t="s">
+        <v>27</v>
+      </c>
+      <c r="N7" t="s">
         <v>28</v>
-      </c>
-      <c r="N7" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="8" spans="3:24" x14ac:dyDescent="0.45">
@@ -3446,7 +3443,7 @@
         <v>8</v>
       </c>
       <c r="E8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G8" s="1">
         <v>1</v>
@@ -3468,13 +3465,13 @@
         <v>10</v>
       </c>
       <c r="E10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G10">
         <v>20</v>
       </c>
       <c r="P10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="3:24" x14ac:dyDescent="0.45">
@@ -3482,13 +3479,13 @@
         <v>6</v>
       </c>
       <c r="E11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G11" s="1">
         <v>8.76</v>
       </c>
       <c r="P11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q11">
         <v>2023</v>
@@ -3500,12 +3497,12 @@
         <v>2050</v>
       </c>
       <c r="T11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="3:24" x14ac:dyDescent="0.45">
       <c r="P12" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q12" s="2">
         <v>2494</v>
@@ -3517,7 +3514,7 @@
         <v>2494</v>
       </c>
       <c r="T12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="3:24" x14ac:dyDescent="0.45">
@@ -3525,7 +3522,7 @@
         <v>4</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q13" s="2">
         <v>61</v>
@@ -3537,13 +3534,13 @@
         <v>61</v>
       </c>
       <c r="T13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="W13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="X13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="3:24" x14ac:dyDescent="0.45">
@@ -3563,7 +3560,7 @@
         <v>5</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q14" s="2">
         <v>4</v>
@@ -3575,13 +3572,13 @@
         <v>4</v>
       </c>
       <c r="T14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="W14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="X14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="3:24" x14ac:dyDescent="0.45">
@@ -3592,7 +3589,7 @@
         <v>12</v>
       </c>
       <c r="E15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F15">
         <v>0</v>
@@ -3601,7 +3598,7 @@
         <v>3</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q15" s="2">
         <v>715</v>
@@ -3613,13 +3610,13 @@
         <v>367</v>
       </c>
       <c r="T15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="W15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="X15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="3:24" x14ac:dyDescent="0.45">
@@ -3627,13 +3624,13 @@
         <v>6</v>
       </c>
       <c r="E16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G16" s="1">
         <v>8.76</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q16" s="2">
         <v>11</v>
@@ -3645,13 +3642,13 @@
         <v>9</v>
       </c>
       <c r="T16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="W16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="X16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" spans="3:24" x14ac:dyDescent="0.45">
@@ -3659,13 +3656,13 @@
         <v>13</v>
       </c>
       <c r="E17" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G17">
         <v>4</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q17" s="2">
         <v>1.5</v>
@@ -3677,7 +3674,7 @@
         <v>1.5</v>
       </c>
       <c r="T17" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="W17" t="str">
         <f>W13</f>
@@ -3693,13 +3690,13 @@
         <v>13</v>
       </c>
       <c r="E18" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G18">
         <v>2</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q18" s="2">
         <v>3256</v>
@@ -3711,7 +3708,7 @@
         <v>1863</v>
       </c>
       <c r="T18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="W18" t="str">
         <f t="shared" ref="W18" si="1">W14</f>
@@ -3727,13 +3724,13 @@
         <v>7</v>
       </c>
       <c r="E19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G19">
         <v>30</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q19" s="2">
         <v>66</v>
@@ -3745,7 +3742,7 @@
         <v>42</v>
       </c>
       <c r="T19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="W19" t="str">
         <f t="shared" ref="W19" si="2">W15</f>
@@ -3761,13 +3758,13 @@
         <v>8</v>
       </c>
       <c r="E20" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G20">
         <v>1</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q20" s="2">
         <v>3</v>
@@ -3779,7 +3776,7 @@
         <v>3</v>
       </c>
       <c r="T20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="W20" t="str">
         <f t="shared" ref="W20" si="3">W16</f>
@@ -3801,7 +3798,7 @@
         <v>0.25</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q21" s="2">
         <v>1524</v>
@@ -3813,7 +3810,7 @@
         <v>1421</v>
       </c>
       <c r="T21" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W21" t="str">
         <f t="shared" ref="W21" si="4">W17</f>
@@ -3829,13 +3826,13 @@
         <v>10</v>
       </c>
       <c r="E22" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G22">
         <v>20</v>
       </c>
       <c r="P22" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Q22" s="2">
         <v>38</v>
@@ -3847,7 +3844,7 @@
         <v>36</v>
       </c>
       <c r="T22" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W22" t="str">
         <f t="shared" ref="W22" si="5">W18</f>
@@ -3860,7 +3857,7 @@
     </row>
     <row r="23" spans="3:24" x14ac:dyDescent="0.45">
       <c r="P23" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q23" s="2">
         <v>1.5</v>
@@ -3872,7 +3869,7 @@
         <v>1.5</v>
       </c>
       <c r="T23" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="W23" t="str">
         <f t="shared" ref="W23" si="6">W19</f>
@@ -3885,7 +3882,7 @@
     </row>
     <row r="24" spans="3:24" x14ac:dyDescent="0.45">
       <c r="P24" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="Q24" s="2">
         <v>1.5</v>
@@ -3897,7 +3894,7 @@
         <v>1.5</v>
       </c>
       <c r="T24" t="str">
-        <f t="shared" ref="T24" si="7">T20</f>
+        <f t="shared" ref="T18:T24" si="7">T20</f>
         <v>E[_]WOF*</v>
       </c>
       <c r="W24" t="str">
@@ -3931,12 +3928,12 @@
         <v>5</v>
       </c>
       <c r="H28" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="29" spans="3:24" x14ac:dyDescent="0.45">
       <c r="C29" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D29" t="s">
         <v>6</v>
@@ -3947,7 +3944,7 @@
     </row>
     <row r="30" spans="3:24" x14ac:dyDescent="0.45">
       <c r="C30" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D30" t="s">
         <v>8</v>
@@ -3956,59 +3953,62 @@
         <v>1</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31" spans="3:24" x14ac:dyDescent="0.45">
-      <c r="C31" t="s">
-        <v>17</v>
-      </c>
       <c r="D31" t="s">
+        <v>7</v>
+      </c>
+      <c r="E31" t="s">
         <v>18</v>
       </c>
-      <c r="G31" s="1">
-        <v>0.1</v>
+      <c r="G31">
+        <v>200</v>
       </c>
     </row>
     <row r="32" spans="3:24" x14ac:dyDescent="0.45">
       <c r="D32" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E32" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G32">
-        <v>200</v>
+        <v>30</v>
       </c>
     </row>
     <row r="33" spans="3:22" x14ac:dyDescent="0.45">
       <c r="D33" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E33" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G33">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="3:22" x14ac:dyDescent="0.45">
+      <c r="C34" t="s">
+        <v>17</v>
+      </c>
       <c r="D34" t="s">
-        <v>9</v>
-      </c>
-      <c r="E34" t="s">
-        <v>19</v>
+        <v>12</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
       </c>
       <c r="G34">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35" spans="3:22" x14ac:dyDescent="0.45">
       <c r="C35" t="s">
-        <v>188</v>
+        <v>85</v>
       </c>
       <c r="D35" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G35" s="1">
         <v>0.9</v>
@@ -4016,7 +4016,7 @@
     </row>
     <row r="38" spans="3:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C38" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P38" s="4" t="s">
         <v>4</v>
@@ -4024,34 +4024,34 @@
     </row>
     <row r="39" spans="3:22" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="C39" t="s">
+        <v>20</v>
+      </c>
+      <c r="D39" t="s">
         <v>21</v>
       </c>
-      <c r="D39" t="s">
+      <c r="E39" t="s">
         <v>22</v>
       </c>
-      <c r="E39" t="s">
-        <v>23</v>
-      </c>
       <c r="P39" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Q39" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="R39" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="S39" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="T39" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="U39" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="U39" s="5" t="s">
-        <v>22</v>
-      </c>
       <c r="V39" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="40" spans="3:22" x14ac:dyDescent="0.45">
@@ -4059,31 +4059,31 @@
         <v>14</v>
       </c>
       <c r="D40" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E40" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P40" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q40" t="s">
         <v>79</v>
       </c>
-      <c r="Q40" t="s">
+      <c r="R40" t="s">
         <v>80</v>
-      </c>
-      <c r="R40" t="s">
-        <v>81</v>
       </c>
       <c r="S40">
         <v>1</v>
       </c>
       <c r="T40" t="s">
+        <v>81</v>
+      </c>
+      <c r="U40" t="s">
         <v>82</v>
       </c>
-      <c r="U40" t="s">
+      <c r="V40" t="s">
         <v>83</v>
-      </c>
-      <c r="V40" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="41" spans="3:22" x14ac:dyDescent="0.45">
@@ -4091,72 +4091,72 @@
         <v>15</v>
       </c>
       <c r="D41" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E41" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="42" spans="3:22" x14ac:dyDescent="0.45">
       <c r="C42" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D42" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E42" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="43" spans="3:22" ht="17.25" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C43" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D43" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E43" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P43" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="44" spans="3:22" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="C44" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D44" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E44" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P44" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q44" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="Q44" s="5" t="s">
-        <v>22</v>
-      </c>
       <c r="R44" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="S44" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="45" spans="3:22" x14ac:dyDescent="0.45">
       <c r="P45" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Q45" t="s">
+        <v>79</v>
+      </c>
+      <c r="R45" t="s">
+        <v>83</v>
+      </c>
+      <c r="S45" t="s">
         <v>80</v>
-      </c>
-      <c r="R45" t="s">
-        <v>84</v>
-      </c>
-      <c r="S45" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="47" spans="3:22" x14ac:dyDescent="0.45">
@@ -4169,80 +4169,80 @@
         <v>1</v>
       </c>
       <c r="D48" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E48" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F48" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G48" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="49" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C49" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D49">
         <v>2025</v>
       </c>
       <c r="E49" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G49" t="s">
         <v>52</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="G49" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="50" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C50" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D50">
         <v>40</v>
       </c>
       <c r="E50" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G50" t="s">
         <v>55</v>
-      </c>
-      <c r="G50" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="51" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C51" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D51">
         <v>2100</v>
       </c>
       <c r="F51" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="54" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C54" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="55" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C55" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D55" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E55" t="s">
+        <v>49</v>
+      </c>
+      <c r="F55" t="s">
+        <v>20</v>
+      </c>
+      <c r="G55" t="s">
         <v>50</v>
-      </c>
-      <c r="F55" t="s">
-        <v>21</v>
-      </c>
-      <c r="G55" t="s">
-        <v>51</v>
       </c>
       <c r="H55">
         <v>0</v>
@@ -4254,53 +4254,53 @@
         <v>2030</v>
       </c>
       <c r="K55" t="s">
+        <v>60</v>
+      </c>
+      <c r="L55" t="s">
         <v>61</v>
       </c>
-      <c r="L55" t="s">
-        <v>62</v>
-      </c>
       <c r="M55" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="56" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C56" t="s">
+        <v>62</v>
+      </c>
+      <c r="E56" t="s">
         <v>63</v>
       </c>
-      <c r="E56" t="s">
-        <v>64</v>
-      </c>
       <c r="F56" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I56">
         <v>0.95</v>
       </c>
       <c r="L56" t="s">
+        <v>64</v>
+      </c>
+      <c r="M56" t="s">
         <v>65</v>
-      </c>
-      <c r="M56" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="57" spans="3:13" x14ac:dyDescent="0.45">
       <c r="C57" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E57" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F57" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="I57">
         <v>0.85</v>
       </c>
       <c r="L57" t="s">
+        <v>64</v>
+      </c>
+      <c r="M57" t="s">
         <v>65</v>
-      </c>
-      <c r="M57" t="s">
-        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25928"/>
   <workbookPr updateLinks="never"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCF81AE6-557B-43AC-9296-A007A1246212}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73BBC569-B211-4141-9EE2-2A9AAD8643B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2573" yWindow="2573" windowWidth="21600" windowHeight="11422" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AVA" sheetId="6" r:id="rId1"/>
@@ -541,13 +541,49 @@
     <t>at grid node - Krosno_POL</t>
   </si>
   <si>
+    <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
+  </si>
+  <si>
+    <t>Elk_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Elk_POL</t>
+  </si>
+  <si>
+    <t>Grajewo_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Grajewo_POL</t>
+  </si>
+  <si>
     <t>Kielce_POL</t>
   </si>
   <si>
     <t>at grid node - Kielce_POL</t>
   </si>
   <si>
-    <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
+    <t>Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>Slupsk_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Slupsk_POL</t>
+  </si>
+  <si>
+    <t>OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>at grid node - OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>Zamosc_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Zamosc_POL</t>
   </si>
   <si>
     <t>Legnica_POL</t>
@@ -556,46 +592,10 @@
     <t>at grid node - Legnica_POL</t>
   </si>
   <si>
-    <t>Elk_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Elk_POL</t>
-  </si>
-  <si>
-    <t>OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>at grid node - OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>Slupsk_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Slupsk_POL</t>
-  </si>
-  <si>
-    <t>Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>Grajewo_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Grajewo_POL</t>
-  </si>
-  <si>
     <t>Chelm_POL</t>
   </si>
   <si>
     <t>at grid node - Chelm_POL</t>
-  </si>
-  <si>
-    <t>Zamosc_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Zamosc_POL</t>
   </si>
   <si>
     <t>h_demand</t>
@@ -1102,13 +1102,13 @@
         <v>86</v>
       </c>
       <c r="M11" t="s">
-        <v>167</v>
+        <v>116</v>
       </c>
       <c r="N11" t="s">
-        <v>168</v>
+        <v>117</v>
       </c>
       <c r="O11" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q11" t="s">
         <v>86</v>
@@ -1164,13 +1164,13 @@
         <v>86</v>
       </c>
       <c r="M12" t="s">
-        <v>170</v>
+        <v>146</v>
       </c>
       <c r="N12" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="O12" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q12" t="s">
         <v>86</v>
@@ -1226,13 +1226,13 @@
         <v>86</v>
       </c>
       <c r="M13" t="s">
-        <v>172</v>
+        <v>104</v>
       </c>
       <c r="N13" t="s">
-        <v>173</v>
+        <v>105</v>
       </c>
       <c r="O13" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q13" t="s">
         <v>86</v>
@@ -1288,13 +1288,13 @@
         <v>86</v>
       </c>
       <c r="M14" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="N14" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="O14" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q14" t="s">
         <v>86</v>
@@ -1350,13 +1350,13 @@
         <v>86</v>
       </c>
       <c r="M15" t="s">
-        <v>140</v>
+        <v>168</v>
       </c>
       <c r="N15" t="s">
-        <v>141</v>
+        <v>169</v>
       </c>
       <c r="O15" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q15" t="s">
         <v>86</v>
@@ -1412,13 +1412,13 @@
         <v>86</v>
       </c>
       <c r="M16" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="N16" t="s">
-        <v>123</v>
+        <v>99</v>
       </c>
       <c r="O16" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q16" t="s">
         <v>86</v>
@@ -1474,13 +1474,13 @@
         <v>86</v>
       </c>
       <c r="M17" t="s">
-        <v>118</v>
+        <v>87</v>
       </c>
       <c r="N17" t="s">
-        <v>119</v>
+        <v>88</v>
       </c>
       <c r="O17" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q17" t="s">
         <v>86</v>
@@ -1536,13 +1536,13 @@
         <v>86</v>
       </c>
       <c r="M18" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="N18" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="O18" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q18" t="s">
         <v>86</v>
@@ -1598,13 +1598,13 @@
         <v>86</v>
       </c>
       <c r="M19" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="N19" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="O19" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q19" t="s">
         <v>86</v>
@@ -1666,7 +1666,7 @@
         <v>101</v>
       </c>
       <c r="O20" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q20" t="s">
         <v>86</v>
@@ -1722,13 +1722,13 @@
         <v>86</v>
       </c>
       <c r="M21" t="s">
-        <v>130</v>
+        <v>172</v>
       </c>
       <c r="N21" t="s">
-        <v>131</v>
+        <v>173</v>
       </c>
       <c r="O21" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q21" t="s">
         <v>86</v>
@@ -1784,13 +1784,13 @@
         <v>86</v>
       </c>
       <c r="M22" t="s">
-        <v>146</v>
+        <v>96</v>
       </c>
       <c r="N22" t="s">
-        <v>147</v>
+        <v>97</v>
       </c>
       <c r="O22" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q22" t="s">
         <v>86</v>
@@ -1846,13 +1846,13 @@
         <v>86</v>
       </c>
       <c r="M23" t="s">
-        <v>87</v>
+        <v>110</v>
       </c>
       <c r="N23" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="O23" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q23" t="s">
         <v>86</v>
@@ -1908,13 +1908,13 @@
         <v>86</v>
       </c>
       <c r="M24" t="s">
-        <v>165</v>
+        <v>114</v>
       </c>
       <c r="N24" t="s">
-        <v>166</v>
+        <v>115</v>
       </c>
       <c r="O24" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q24" t="s">
         <v>86</v>
@@ -1970,13 +1970,13 @@
         <v>86</v>
       </c>
       <c r="M25" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="N25" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="O25" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q25" t="s">
         <v>86</v>
@@ -2032,13 +2032,13 @@
         <v>86</v>
       </c>
       <c r="M26" t="s">
-        <v>157</v>
+        <v>120</v>
       </c>
       <c r="N26" t="s">
-        <v>158</v>
+        <v>121</v>
       </c>
       <c r="O26" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q26" t="s">
         <v>86</v>
@@ -2094,13 +2094,13 @@
         <v>86</v>
       </c>
       <c r="M27" t="s">
-        <v>116</v>
+        <v>174</v>
       </c>
       <c r="N27" t="s">
-        <v>117</v>
+        <v>175</v>
       </c>
       <c r="O27" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q27" t="s">
         <v>86</v>
@@ -2156,13 +2156,13 @@
         <v>86</v>
       </c>
       <c r="M28" t="s">
-        <v>110</v>
+        <v>152</v>
       </c>
       <c r="N28" t="s">
-        <v>111</v>
+        <v>153</v>
       </c>
       <c r="O28" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q28" t="s">
         <v>86</v>
@@ -2218,13 +2218,13 @@
         <v>86</v>
       </c>
       <c r="M29" t="s">
-        <v>94</v>
+        <v>176</v>
       </c>
       <c r="N29" t="s">
-        <v>95</v>
+        <v>177</v>
       </c>
       <c r="O29" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q29" t="s">
         <v>86</v>
@@ -2280,13 +2280,13 @@
         <v>86</v>
       </c>
       <c r="M30" t="s">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="N30" t="s">
-        <v>164</v>
+        <v>137</v>
       </c>
       <c r="O30" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q30" t="s">
         <v>86</v>
@@ -2342,13 +2342,13 @@
         <v>86</v>
       </c>
       <c r="M31" t="s">
-        <v>150</v>
+        <v>108</v>
       </c>
       <c r="N31" t="s">
-        <v>151</v>
+        <v>109</v>
       </c>
       <c r="O31" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q31" t="s">
         <v>86</v>
@@ -2404,13 +2404,13 @@
         <v>86</v>
       </c>
       <c r="M32" t="s">
-        <v>92</v>
+        <v>155</v>
       </c>
       <c r="N32" t="s">
-        <v>93</v>
+        <v>156</v>
       </c>
       <c r="O32" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q32" t="s">
         <v>86</v>
@@ -2466,13 +2466,13 @@
         <v>86</v>
       </c>
       <c r="M33" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="N33" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="O33" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q33" t="s">
         <v>86</v>
@@ -2528,13 +2528,13 @@
         <v>86</v>
       </c>
       <c r="M34" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="N34" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="O34" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q34" t="s">
         <v>86</v>
@@ -2590,13 +2590,13 @@
         <v>86</v>
       </c>
       <c r="M35" t="s">
-        <v>161</v>
+        <v>112</v>
       </c>
       <c r="N35" t="s">
-        <v>162</v>
+        <v>113</v>
       </c>
       <c r="O35" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q35" t="s">
         <v>86</v>
@@ -2652,13 +2652,13 @@
         <v>86</v>
       </c>
       <c r="M36" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="N36" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="O36" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q36" t="s">
         <v>86</v>
@@ -2714,13 +2714,13 @@
         <v>86</v>
       </c>
       <c r="M37" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="N37" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="O37" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q37" t="s">
         <v>86</v>
@@ -2776,13 +2776,13 @@
         <v>86</v>
       </c>
       <c r="M38" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="N38" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="O38" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q38" t="s">
         <v>86</v>
@@ -2838,13 +2838,13 @@
         <v>86</v>
       </c>
       <c r="M39" t="s">
-        <v>152</v>
+        <v>102</v>
       </c>
       <c r="N39" t="s">
-        <v>153</v>
+        <v>103</v>
       </c>
       <c r="O39" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="Q39" t="s">
         <v>86</v>
@@ -2900,13 +2900,13 @@
         <v>86</v>
       </c>
       <c r="M40" t="s">
-        <v>106</v>
+        <v>182</v>
       </c>
       <c r="N40" t="s">
-        <v>107</v>
+        <v>183</v>
       </c>
       <c r="O40" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="41" spans="2:25" x14ac:dyDescent="0.45">
@@ -2938,13 +2938,13 @@
         <v>86</v>
       </c>
       <c r="M41" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="N41" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="O41" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="42" spans="2:25" x14ac:dyDescent="0.45">
@@ -2976,13 +2976,13 @@
         <v>86</v>
       </c>
       <c r="M42" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="N42" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="O42" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="43" spans="2:25" x14ac:dyDescent="0.45">
@@ -3014,13 +3014,13 @@
         <v>86</v>
       </c>
       <c r="M43" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="N43" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="O43" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="44" spans="2:25" x14ac:dyDescent="0.45">
@@ -3040,13 +3040,13 @@
         <v>86</v>
       </c>
       <c r="M44" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="N44" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="O44" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.45">
@@ -3066,13 +3066,13 @@
         <v>86</v>
       </c>
       <c r="M45" t="s">
-        <v>182</v>
+        <v>126</v>
       </c>
       <c r="N45" t="s">
-        <v>183</v>
+        <v>127</v>
       </c>
       <c r="O45" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="46" spans="2:25" x14ac:dyDescent="0.45">
@@ -3092,13 +3092,13 @@
         <v>86</v>
       </c>
       <c r="M46" t="s">
-        <v>104</v>
+        <v>150</v>
       </c>
       <c r="N46" t="s">
-        <v>105</v>
+        <v>151</v>
       </c>
       <c r="O46" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="47" spans="2:25" x14ac:dyDescent="0.45">
@@ -3118,13 +3118,13 @@
         <v>86</v>
       </c>
       <c r="M47" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="N47" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="O47" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="48" spans="2:25" x14ac:dyDescent="0.45">
@@ -3144,13 +3144,13 @@
         <v>86</v>
       </c>
       <c r="M48" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="N48" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="O48" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="49" spans="7:15" x14ac:dyDescent="0.45">
@@ -3170,13 +3170,13 @@
         <v>86</v>
       </c>
       <c r="M49" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="N49" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="O49" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="50" spans="7:15" x14ac:dyDescent="0.45">
@@ -3184,13 +3184,13 @@
         <v>86</v>
       </c>
       <c r="M50" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="N50" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="O50" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="51" spans="7:15" x14ac:dyDescent="0.45">
@@ -3198,13 +3198,13 @@
         <v>86</v>
       </c>
       <c r="M51" t="s">
-        <v>136</v>
+        <v>184</v>
       </c>
       <c r="N51" t="s">
-        <v>137</v>
+        <v>185</v>
       </c>
       <c r="O51" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="52" spans="7:15" x14ac:dyDescent="0.45">
@@ -3212,13 +3212,13 @@
         <v>86</v>
       </c>
       <c r="M52" t="s">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="N52" t="s">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="O52" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="53" spans="7:15" x14ac:dyDescent="0.45">
@@ -3226,13 +3226,13 @@
         <v>86</v>
       </c>
       <c r="M53" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="N53" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="O53" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="54" spans="7:15" x14ac:dyDescent="0.45">
@@ -3240,13 +3240,13 @@
         <v>86</v>
       </c>
       <c r="M54" t="s">
-        <v>108</v>
+        <v>138</v>
       </c>
       <c r="N54" t="s">
-        <v>109</v>
+        <v>139</v>
       </c>
       <c r="O54" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="55" spans="7:15" x14ac:dyDescent="0.45">
@@ -3254,13 +3254,13 @@
         <v>86</v>
       </c>
       <c r="M55" t="s">
-        <v>114</v>
+        <v>161</v>
       </c>
       <c r="N55" t="s">
-        <v>115</v>
+        <v>162</v>
       </c>
       <c r="O55" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="56" spans="7:15" x14ac:dyDescent="0.45">
@@ -3268,13 +3268,13 @@
         <v>86</v>
       </c>
       <c r="M56" t="s">
-        <v>184</v>
+        <v>140</v>
       </c>
       <c r="N56" t="s">
-        <v>185</v>
+        <v>141</v>
       </c>
       <c r="O56" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="57" spans="7:15" x14ac:dyDescent="0.45">
@@ -3282,13 +3282,13 @@
         <v>86</v>
       </c>
       <c r="M57" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="N57" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="O57" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="58" spans="7:15" x14ac:dyDescent="0.45">
@@ -3296,13 +3296,13 @@
         <v>86</v>
       </c>
       <c r="M58" t="s">
-        <v>144</v>
+        <v>163</v>
       </c>
       <c r="N58" t="s">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="O58" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr updateLinks="never"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73BBC569-B211-4141-9EE2-2A9AAD8643B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9394C322-DC6D-4CF9-8CB5-22BDB0960AAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2573" yWindow="2573" windowWidth="21600" windowHeight="11422" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28702" yWindow="-98" windowWidth="28995" windowHeight="15675" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AVA" sheetId="6" r:id="rId1"/>
@@ -544,58 +544,58 @@
     <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
   </si>
   <si>
+    <t>Grajewo_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Grajewo_POL</t>
+  </si>
+  <si>
+    <t>Slupsk_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Slupsk_POL</t>
+  </si>
+  <si>
+    <t>Chelm_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Chelm_POL</t>
+  </si>
+  <si>
+    <t>Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>Legnica_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Legnica_POL</t>
+  </si>
+  <si>
+    <t>Kielce_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Kielce_POL</t>
+  </si>
+  <si>
     <t>Elk_POL</t>
   </si>
   <si>
     <t>at grid node - Elk_POL</t>
   </si>
   <si>
-    <t>Grajewo_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Grajewo_POL</t>
-  </si>
-  <si>
-    <t>Kielce_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Kielce_POL</t>
-  </si>
-  <si>
-    <t>Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>Slupsk_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Slupsk_POL</t>
+    <t>Zamosc_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Zamosc_POL</t>
   </si>
   <si>
     <t>OstrowiecSwietokrz_POL</t>
   </si>
   <si>
     <t>at grid node - OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>Zamosc_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Zamosc_POL</t>
-  </si>
-  <si>
-    <t>Legnica_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Legnica_POL</t>
-  </si>
-  <si>
-    <t>Chelm_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Chelm_POL</t>
   </si>
   <si>
     <t>h_demand</t>
@@ -1102,10 +1102,10 @@
         <v>86</v>
       </c>
       <c r="M11" t="s">
-        <v>116</v>
+        <v>148</v>
       </c>
       <c r="N11" t="s">
-        <v>117</v>
+        <v>149</v>
       </c>
       <c r="O11" t="s">
         <v>167</v>
@@ -1164,10 +1164,10 @@
         <v>86</v>
       </c>
       <c r="M12" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="N12" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="O12" t="s">
         <v>167</v>
@@ -1226,10 +1226,10 @@
         <v>86</v>
       </c>
       <c r="M13" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="N13" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="O13" t="s">
         <v>167</v>
@@ -1288,10 +1288,10 @@
         <v>86</v>
       </c>
       <c r="M14" t="s">
-        <v>94</v>
+        <v>165</v>
       </c>
       <c r="N14" t="s">
-        <v>95</v>
+        <v>166</v>
       </c>
       <c r="O14" t="s">
         <v>167</v>
@@ -1350,10 +1350,10 @@
         <v>86</v>
       </c>
       <c r="M15" t="s">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="N15" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="O15" t="s">
         <v>167</v>
@@ -1412,10 +1412,10 @@
         <v>86</v>
       </c>
       <c r="M16" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="N16" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="O16" t="s">
         <v>167</v>
@@ -1474,10 +1474,10 @@
         <v>86</v>
       </c>
       <c r="M17" t="s">
-        <v>87</v>
+        <v>155</v>
       </c>
       <c r="N17" t="s">
-        <v>88</v>
+        <v>156</v>
       </c>
       <c r="O17" t="s">
         <v>167</v>
@@ -1536,10 +1536,10 @@
         <v>86</v>
       </c>
       <c r="M18" t="s">
-        <v>170</v>
+        <v>132</v>
       </c>
       <c r="N18" t="s">
-        <v>171</v>
+        <v>133</v>
       </c>
       <c r="O18" t="s">
         <v>167</v>
@@ -1598,10 +1598,10 @@
         <v>86</v>
       </c>
       <c r="M19" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="N19" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="O19" t="s">
         <v>167</v>
@@ -1660,10 +1660,10 @@
         <v>86</v>
       </c>
       <c r="M20" t="s">
-        <v>100</v>
+        <v>138</v>
       </c>
       <c r="N20" t="s">
-        <v>101</v>
+        <v>139</v>
       </c>
       <c r="O20" t="s">
         <v>167</v>
@@ -1722,10 +1722,10 @@
         <v>86</v>
       </c>
       <c r="M21" t="s">
-        <v>172</v>
+        <v>122</v>
       </c>
       <c r="N21" t="s">
-        <v>173</v>
+        <v>123</v>
       </c>
       <c r="O21" t="s">
         <v>167</v>
@@ -1784,10 +1784,10 @@
         <v>86</v>
       </c>
       <c r="M22" t="s">
-        <v>96</v>
+        <v>152</v>
       </c>
       <c r="N22" t="s">
-        <v>97</v>
+        <v>153</v>
       </c>
       <c r="O22" t="s">
         <v>167</v>
@@ -1846,10 +1846,10 @@
         <v>86</v>
       </c>
       <c r="M23" t="s">
-        <v>110</v>
+        <v>170</v>
       </c>
       <c r="N23" t="s">
-        <v>111</v>
+        <v>171</v>
       </c>
       <c r="O23" t="s">
         <v>167</v>
@@ -1908,10 +1908,10 @@
         <v>86</v>
       </c>
       <c r="M24" t="s">
-        <v>114</v>
+        <v>161</v>
       </c>
       <c r="N24" t="s">
-        <v>115</v>
+        <v>162</v>
       </c>
       <c r="O24" t="s">
         <v>167</v>
@@ -1970,10 +1970,10 @@
         <v>86</v>
       </c>
       <c r="M25" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="N25" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="O25" t="s">
         <v>167</v>
@@ -2032,10 +2032,10 @@
         <v>86</v>
       </c>
       <c r="M26" t="s">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="N26" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="O26" t="s">
         <v>167</v>
@@ -2094,10 +2094,10 @@
         <v>86</v>
       </c>
       <c r="M27" t="s">
-        <v>174</v>
+        <v>114</v>
       </c>
       <c r="N27" t="s">
-        <v>175</v>
+        <v>115</v>
       </c>
       <c r="O27" t="s">
         <v>167</v>
@@ -2156,10 +2156,10 @@
         <v>86</v>
       </c>
       <c r="M28" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="N28" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="O28" t="s">
         <v>167</v>
@@ -2218,10 +2218,10 @@
         <v>86</v>
       </c>
       <c r="M29" t="s">
-        <v>176</v>
+        <v>108</v>
       </c>
       <c r="N29" t="s">
-        <v>177</v>
+        <v>109</v>
       </c>
       <c r="O29" t="s">
         <v>167</v>
@@ -2280,10 +2280,10 @@
         <v>86</v>
       </c>
       <c r="M30" t="s">
-        <v>136</v>
+        <v>172</v>
       </c>
       <c r="N30" t="s">
-        <v>137</v>
+        <v>173</v>
       </c>
       <c r="O30" t="s">
         <v>167</v>
@@ -2342,10 +2342,10 @@
         <v>86</v>
       </c>
       <c r="M31" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="N31" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="O31" t="s">
         <v>167</v>
@@ -2404,10 +2404,10 @@
         <v>86</v>
       </c>
       <c r="M32" t="s">
-        <v>155</v>
+        <v>174</v>
       </c>
       <c r="N32" t="s">
-        <v>156</v>
+        <v>175</v>
       </c>
       <c r="O32" t="s">
         <v>167</v>
@@ -2466,10 +2466,10 @@
         <v>86</v>
       </c>
       <c r="M33" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="N33" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="O33" t="s">
         <v>167</v>
@@ -2528,10 +2528,10 @@
         <v>86</v>
       </c>
       <c r="M34" t="s">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="N34" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="O34" t="s">
         <v>167</v>
@@ -2590,10 +2590,10 @@
         <v>86</v>
       </c>
       <c r="M35" t="s">
-        <v>112</v>
+        <v>176</v>
       </c>
       <c r="N35" t="s">
-        <v>113</v>
+        <v>177</v>
       </c>
       <c r="O35" t="s">
         <v>167</v>
@@ -2652,10 +2652,10 @@
         <v>86</v>
       </c>
       <c r="M36" t="s">
-        <v>128</v>
+        <v>92</v>
       </c>
       <c r="N36" t="s">
-        <v>129</v>
+        <v>93</v>
       </c>
       <c r="O36" t="s">
         <v>167</v>
@@ -2714,10 +2714,10 @@
         <v>86</v>
       </c>
       <c r="M37" t="s">
-        <v>178</v>
+        <v>128</v>
       </c>
       <c r="N37" t="s">
-        <v>179</v>
+        <v>129</v>
       </c>
       <c r="O37" t="s">
         <v>167</v>
@@ -2776,10 +2776,10 @@
         <v>86</v>
       </c>
       <c r="M38" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="N38" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="O38" t="s">
         <v>167</v>
@@ -2838,10 +2838,10 @@
         <v>86</v>
       </c>
       <c r="M39" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="N39" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="O39" t="s">
         <v>167</v>
@@ -2900,10 +2900,10 @@
         <v>86</v>
       </c>
       <c r="M40" t="s">
-        <v>182</v>
+        <v>118</v>
       </c>
       <c r="N40" t="s">
-        <v>183</v>
+        <v>119</v>
       </c>
       <c r="O40" t="s">
         <v>167</v>
@@ -2938,10 +2938,10 @@
         <v>86</v>
       </c>
       <c r="M41" t="s">
-        <v>165</v>
+        <v>142</v>
       </c>
       <c r="N41" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
       <c r="O41" t="s">
         <v>167</v>
@@ -2976,10 +2976,10 @@
         <v>86</v>
       </c>
       <c r="M42" t="s">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="N42" t="s">
-        <v>131</v>
+        <v>91</v>
       </c>
       <c r="O42" t="s">
         <v>167</v>
@@ -3014,10 +3014,10 @@
         <v>86</v>
       </c>
       <c r="M43" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="N43" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="O43" t="s">
         <v>167</v>
@@ -3040,10 +3040,10 @@
         <v>86</v>
       </c>
       <c r="M44" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="N44" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="O44" t="s">
         <v>167</v>
@@ -3066,10 +3066,10 @@
         <v>86</v>
       </c>
       <c r="M45" t="s">
-        <v>126</v>
+        <v>163</v>
       </c>
       <c r="N45" t="s">
-        <v>127</v>
+        <v>164</v>
       </c>
       <c r="O45" t="s">
         <v>167</v>
@@ -3092,10 +3092,10 @@
         <v>86</v>
       </c>
       <c r="M46" t="s">
-        <v>150</v>
+        <v>94</v>
       </c>
       <c r="N46" t="s">
-        <v>151</v>
+        <v>95</v>
       </c>
       <c r="O46" t="s">
         <v>167</v>
@@ -3118,10 +3118,10 @@
         <v>86</v>
       </c>
       <c r="M47" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="N47" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="O47" t="s">
         <v>167</v>
@@ -3144,10 +3144,10 @@
         <v>86</v>
       </c>
       <c r="M48" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="N48" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="O48" t="s">
         <v>167</v>
@@ -3170,10 +3170,10 @@
         <v>86</v>
       </c>
       <c r="M49" t="s">
-        <v>159</v>
+        <v>130</v>
       </c>
       <c r="N49" t="s">
-        <v>160</v>
+        <v>131</v>
       </c>
       <c r="O49" t="s">
         <v>167</v>
@@ -3184,10 +3184,10 @@
         <v>86</v>
       </c>
       <c r="M50" t="s">
-        <v>132</v>
+        <v>87</v>
       </c>
       <c r="N50" t="s">
-        <v>133</v>
+        <v>88</v>
       </c>
       <c r="O50" t="s">
         <v>167</v>
@@ -3198,10 +3198,10 @@
         <v>86</v>
       </c>
       <c r="M51" t="s">
-        <v>184</v>
+        <v>106</v>
       </c>
       <c r="N51" t="s">
-        <v>185</v>
+        <v>107</v>
       </c>
       <c r="O51" t="s">
         <v>167</v>
@@ -3212,10 +3212,10 @@
         <v>86</v>
       </c>
       <c r="M52" t="s">
-        <v>106</v>
+        <v>180</v>
       </c>
       <c r="N52" t="s">
-        <v>107</v>
+        <v>181</v>
       </c>
       <c r="O52" t="s">
         <v>167</v>
@@ -3226,10 +3226,10 @@
         <v>86</v>
       </c>
       <c r="M53" t="s">
-        <v>92</v>
+        <v>182</v>
       </c>
       <c r="N53" t="s">
-        <v>93</v>
+        <v>183</v>
       </c>
       <c r="O53" t="s">
         <v>167</v>
@@ -3240,10 +3240,10 @@
         <v>86</v>
       </c>
       <c r="M54" t="s">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="N54" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="O54" t="s">
         <v>167</v>
@@ -3254,10 +3254,10 @@
         <v>86</v>
       </c>
       <c r="M55" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="N55" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="O55" t="s">
         <v>167</v>
@@ -3268,10 +3268,10 @@
         <v>86</v>
       </c>
       <c r="M56" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="N56" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="O56" t="s">
         <v>167</v>
@@ -3282,10 +3282,10 @@
         <v>86</v>
       </c>
       <c r="M57" t="s">
-        <v>124</v>
+        <v>157</v>
       </c>
       <c r="N57" t="s">
-        <v>125</v>
+        <v>158</v>
       </c>
       <c r="O57" t="s">
         <v>167</v>
@@ -3296,10 +3296,10 @@
         <v>86</v>
       </c>
       <c r="M58" t="s">
-        <v>163</v>
+        <v>184</v>
       </c>
       <c r="N58" t="s">
-        <v>164</v>
+        <v>185</v>
       </c>
       <c r="O58" t="s">
         <v>167</v>

--- a/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25928"/>
   <workbookPr updateLinks="never"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9394C322-DC6D-4CF9-8CB5-22BDB0960AAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1417676E-2F8C-4C79-95EF-C51211EFDB10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28702" yWindow="-98" windowWidth="28995" windowHeight="15675" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2573" yWindow="2573" windowWidth="21600" windowHeight="11422" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AVA" sheetId="6" r:id="rId1"/>
@@ -544,58 +544,58 @@
     <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
   </si>
   <si>
+    <t>Chelm_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Chelm_POL</t>
+  </si>
+  <si>
+    <t>Slupsk_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Slupsk_POL</t>
+  </si>
+  <si>
+    <t>Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>Kielce_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Kielce_POL</t>
+  </si>
+  <si>
     <t>Grajewo_POL</t>
   </si>
   <si>
     <t>at grid node - Grajewo_POL</t>
   </si>
   <si>
-    <t>Slupsk_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Slupsk_POL</t>
-  </si>
-  <si>
-    <t>Chelm_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Chelm_POL</t>
-  </si>
-  <si>
-    <t>Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Olsztyn_POL</t>
+    <t>Elk_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Elk_POL</t>
+  </si>
+  <si>
+    <t>Zamosc_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Zamosc_POL</t>
+  </si>
+  <si>
+    <t>OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>at grid node - OstrowiecSwietokrz_POL</t>
   </si>
   <si>
     <t>Legnica_POL</t>
   </si>
   <si>
     <t>at grid node - Legnica_POL</t>
-  </si>
-  <si>
-    <t>Kielce_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Kielce_POL</t>
-  </si>
-  <si>
-    <t>Elk_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Elk_POL</t>
-  </si>
-  <si>
-    <t>Zamosc_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Zamosc_POL</t>
-  </si>
-  <si>
-    <t>OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>at grid node - OstrowiecSwietokrz_POL</t>
   </si>
   <si>
     <t>h_demand</t>
@@ -1102,10 +1102,10 @@
         <v>86</v>
       </c>
       <c r="M11" t="s">
-        <v>148</v>
+        <v>92</v>
       </c>
       <c r="N11" t="s">
-        <v>149</v>
+        <v>93</v>
       </c>
       <c r="O11" t="s">
         <v>167</v>
@@ -1164,10 +1164,10 @@
         <v>86</v>
       </c>
       <c r="M12" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="N12" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="O12" t="s">
         <v>167</v>
@@ -1226,10 +1226,10 @@
         <v>86</v>
       </c>
       <c r="M13" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="N13" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="O13" t="s">
         <v>167</v>
@@ -1288,10 +1288,10 @@
         <v>86</v>
       </c>
       <c r="M14" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="N14" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="O14" t="s">
         <v>167</v>
@@ -1350,10 +1350,10 @@
         <v>86</v>
       </c>
       <c r="M15" t="s">
-        <v>150</v>
+        <v>104</v>
       </c>
       <c r="N15" t="s">
-        <v>151</v>
+        <v>105</v>
       </c>
       <c r="O15" t="s">
         <v>167</v>
@@ -1412,10 +1412,10 @@
         <v>86</v>
       </c>
       <c r="M16" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="N16" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="O16" t="s">
         <v>167</v>
@@ -1474,10 +1474,10 @@
         <v>86</v>
       </c>
       <c r="M17" t="s">
-        <v>155</v>
+        <v>136</v>
       </c>
       <c r="N17" t="s">
-        <v>156</v>
+        <v>137</v>
       </c>
       <c r="O17" t="s">
         <v>167</v>
@@ -1536,10 +1536,10 @@
         <v>86</v>
       </c>
       <c r="M18" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="N18" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="O18" t="s">
         <v>167</v>
@@ -1598,10 +1598,10 @@
         <v>86</v>
       </c>
       <c r="M19" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="N19" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="O19" t="s">
         <v>167</v>
@@ -1660,10 +1660,10 @@
         <v>86</v>
       </c>
       <c r="M20" t="s">
-        <v>138</v>
+        <v>102</v>
       </c>
       <c r="N20" t="s">
-        <v>139</v>
+        <v>103</v>
       </c>
       <c r="O20" t="s">
         <v>167</v>
@@ -1722,10 +1722,10 @@
         <v>86</v>
       </c>
       <c r="M21" t="s">
-        <v>122</v>
+        <v>134</v>
       </c>
       <c r="N21" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="O21" t="s">
         <v>167</v>
@@ -1784,10 +1784,10 @@
         <v>86</v>
       </c>
       <c r="M22" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="N22" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="O22" t="s">
         <v>167</v>
@@ -1846,10 +1846,10 @@
         <v>86</v>
       </c>
       <c r="M23" t="s">
-        <v>170</v>
+        <v>106</v>
       </c>
       <c r="N23" t="s">
-        <v>171</v>
+        <v>107</v>
       </c>
       <c r="O23" t="s">
         <v>167</v>
@@ -1908,10 +1908,10 @@
         <v>86</v>
       </c>
       <c r="M24" t="s">
-        <v>161</v>
+        <v>132</v>
       </c>
       <c r="N24" t="s">
-        <v>162</v>
+        <v>133</v>
       </c>
       <c r="O24" t="s">
         <v>167</v>
@@ -1970,10 +1970,10 @@
         <v>86</v>
       </c>
       <c r="M25" t="s">
-        <v>120</v>
+        <v>172</v>
       </c>
       <c r="N25" t="s">
-        <v>121</v>
+        <v>173</v>
       </c>
       <c r="O25" t="s">
         <v>167</v>
@@ -2032,10 +2032,10 @@
         <v>86</v>
       </c>
       <c r="M26" t="s">
-        <v>98</v>
+        <v>174</v>
       </c>
       <c r="N26" t="s">
-        <v>99</v>
+        <v>175</v>
       </c>
       <c r="O26" t="s">
         <v>167</v>
@@ -2094,10 +2094,10 @@
         <v>86</v>
       </c>
       <c r="M27" t="s">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="N27" t="s">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="O27" t="s">
         <v>167</v>
@@ -2156,10 +2156,10 @@
         <v>86</v>
       </c>
       <c r="M28" t="s">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="N28" t="s">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="O28" t="s">
         <v>167</v>
@@ -2218,10 +2218,10 @@
         <v>86</v>
       </c>
       <c r="M29" t="s">
-        <v>108</v>
+        <v>161</v>
       </c>
       <c r="N29" t="s">
-        <v>109</v>
+        <v>162</v>
       </c>
       <c r="O29" t="s">
         <v>167</v>
@@ -2280,10 +2280,10 @@
         <v>86</v>
       </c>
       <c r="M30" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="N30" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="O30" t="s">
         <v>167</v>
@@ -2342,10 +2342,10 @@
         <v>86</v>
       </c>
       <c r="M31" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="N31" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="O31" t="s">
         <v>167</v>
@@ -2404,10 +2404,10 @@
         <v>86</v>
       </c>
       <c r="M32" t="s">
-        <v>174</v>
+        <v>110</v>
       </c>
       <c r="N32" t="s">
-        <v>175</v>
+        <v>111</v>
       </c>
       <c r="O32" t="s">
         <v>167</v>
@@ -2466,10 +2466,10 @@
         <v>86</v>
       </c>
       <c r="M33" t="s">
-        <v>140</v>
+        <v>90</v>
       </c>
       <c r="N33" t="s">
-        <v>141</v>
+        <v>91</v>
       </c>
       <c r="O33" t="s">
         <v>167</v>
@@ -2528,10 +2528,10 @@
         <v>86</v>
       </c>
       <c r="M34" t="s">
-        <v>104</v>
+        <v>138</v>
       </c>
       <c r="N34" t="s">
-        <v>105</v>
+        <v>139</v>
       </c>
       <c r="O34" t="s">
         <v>167</v>
@@ -2590,10 +2590,10 @@
         <v>86</v>
       </c>
       <c r="M35" t="s">
-        <v>176</v>
+        <v>130</v>
       </c>
       <c r="N35" t="s">
-        <v>177</v>
+        <v>131</v>
       </c>
       <c r="O35" t="s">
         <v>167</v>
@@ -2652,10 +2652,10 @@
         <v>86</v>
       </c>
       <c r="M36" t="s">
-        <v>92</v>
+        <v>140</v>
       </c>
       <c r="N36" t="s">
-        <v>93</v>
+        <v>141</v>
       </c>
       <c r="O36" t="s">
         <v>167</v>
@@ -2714,10 +2714,10 @@
         <v>86</v>
       </c>
       <c r="M37" t="s">
-        <v>128</v>
+        <v>180</v>
       </c>
       <c r="N37" t="s">
-        <v>129</v>
+        <v>181</v>
       </c>
       <c r="O37" t="s">
         <v>167</v>
@@ -2776,10 +2776,10 @@
         <v>86</v>
       </c>
       <c r="M38" t="s">
-        <v>178</v>
+        <v>142</v>
       </c>
       <c r="N38" t="s">
-        <v>179</v>
+        <v>143</v>
       </c>
       <c r="O38" t="s">
         <v>167</v>
@@ -2838,10 +2838,10 @@
         <v>86</v>
       </c>
       <c r="M39" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="N39" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="O39" t="s">
         <v>167</v>
@@ -2900,10 +2900,10 @@
         <v>86</v>
       </c>
       <c r="M40" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="N40" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="O40" t="s">
         <v>167</v>
@@ -2938,10 +2938,10 @@
         <v>86</v>
       </c>
       <c r="M41" t="s">
-        <v>142</v>
+        <v>108</v>
       </c>
       <c r="N41" t="s">
-        <v>143</v>
+        <v>109</v>
       </c>
       <c r="O41" t="s">
         <v>167</v>
@@ -2976,10 +2976,10 @@
         <v>86</v>
       </c>
       <c r="M42" t="s">
-        <v>90</v>
+        <v>159</v>
       </c>
       <c r="N42" t="s">
-        <v>91</v>
+        <v>160</v>
       </c>
       <c r="O42" t="s">
         <v>167</v>
@@ -3014,10 +3014,10 @@
         <v>86</v>
       </c>
       <c r="M43" t="s">
-        <v>110</v>
+        <v>182</v>
       </c>
       <c r="N43" t="s">
-        <v>111</v>
+        <v>183</v>
       </c>
       <c r="O43" t="s">
         <v>167</v>
@@ -3040,10 +3040,10 @@
         <v>86</v>
       </c>
       <c r="M44" t="s">
-        <v>102</v>
+        <v>152</v>
       </c>
       <c r="N44" t="s">
-        <v>103</v>
+        <v>153</v>
       </c>
       <c r="O44" t="s">
         <v>167</v>
@@ -3066,10 +3066,10 @@
         <v>86</v>
       </c>
       <c r="M45" t="s">
-        <v>163</v>
+        <v>144</v>
       </c>
       <c r="N45" t="s">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="O45" t="s">
         <v>167</v>
@@ -3092,10 +3092,10 @@
         <v>86</v>
       </c>
       <c r="M46" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="N46" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="O46" t="s">
         <v>167</v>
@@ -3118,10 +3118,10 @@
         <v>86</v>
       </c>
       <c r="M47" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="N47" t="s">
-        <v>137</v>
+        <v>117</v>
       </c>
       <c r="O47" t="s">
         <v>167</v>
@@ -3144,10 +3144,10 @@
         <v>86</v>
       </c>
       <c r="M48" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="N48" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="O48" t="s">
         <v>167</v>
@@ -3170,10 +3170,10 @@
         <v>86</v>
       </c>
       <c r="M49" t="s">
-        <v>130</v>
+        <v>112</v>
       </c>
       <c r="N49" t="s">
-        <v>131</v>
+        <v>113</v>
       </c>
       <c r="O49" t="s">
         <v>167</v>
@@ -3184,10 +3184,10 @@
         <v>86</v>
       </c>
       <c r="M50" t="s">
-        <v>87</v>
+        <v>165</v>
       </c>
       <c r="N50" t="s">
-        <v>88</v>
+        <v>166</v>
       </c>
       <c r="O50" t="s">
         <v>167</v>
@@ -3198,10 +3198,10 @@
         <v>86</v>
       </c>
       <c r="M51" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="N51" t="s">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="O51" t="s">
         <v>167</v>
@@ -3212,10 +3212,10 @@
         <v>86</v>
       </c>
       <c r="M52" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="N52" t="s">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="O52" t="s">
         <v>167</v>
@@ -3226,10 +3226,10 @@
         <v>86</v>
       </c>
       <c r="M53" t="s">
-        <v>182</v>
+        <v>148</v>
       </c>
       <c r="N53" t="s">
-        <v>183</v>
+        <v>149</v>
       </c>
       <c r="O53" t="s">
         <v>167</v>
@@ -3240,10 +3240,10 @@
         <v>86</v>
       </c>
       <c r="M54" t="s">
-        <v>116</v>
+        <v>146</v>
       </c>
       <c r="N54" t="s">
-        <v>117</v>
+        <v>147</v>
       </c>
       <c r="O54" t="s">
         <v>167</v>
@@ -3254,10 +3254,10 @@
         <v>86</v>
       </c>
       <c r="M55" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="N55" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="O55" t="s">
         <v>167</v>
@@ -3268,10 +3268,10 @@
         <v>86</v>
       </c>
       <c r="M56" t="s">
-        <v>134</v>
+        <v>184</v>
       </c>
       <c r="N56" t="s">
-        <v>135</v>
+        <v>185</v>
       </c>
       <c r="O56" t="s">
         <v>167</v>
@@ -3282,10 +3282,10 @@
         <v>86</v>
       </c>
       <c r="M57" t="s">
-        <v>157</v>
+        <v>96</v>
       </c>
       <c r="N57" t="s">
-        <v>158</v>
+        <v>97</v>
       </c>
       <c r="O57" t="s">
         <v>167</v>
@@ -3296,10 +3296,10 @@
         <v>86</v>
       </c>
       <c r="M58" t="s">
-        <v>184</v>
+        <v>118</v>
       </c>
       <c r="N58" t="s">
-        <v>185</v>
+        <v>119</v>
       </c>
       <c r="O58" t="s">
         <v>167</v>

--- a/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1417676E-2F8C-4C79-95EF-C51211EFDB10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32D136AD-76BB-432D-8FF5-B539730FAD58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2573" yWindow="2573" windowWidth="21600" windowHeight="11422" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="368" yWindow="368" windowWidth="21599" windowHeight="12772" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AVA" sheetId="6" r:id="rId1"/>
@@ -541,13 +541,19 @@
     <t>at grid node - Krosno_POL</t>
   </si>
   <si>
+    <t>Chelm_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Chelm_POL</t>
+  </si>
+  <si>
     <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
   </si>
   <si>
-    <t>Chelm_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Chelm_POL</t>
+    <t>Elk_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Elk_POL</t>
   </si>
   <si>
     <t>Slupsk_POL</t>
@@ -556,46 +562,40 @@
     <t>at grid node - Slupsk_POL</t>
   </si>
   <si>
+    <t>Kielce_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Kielce_POL</t>
+  </si>
+  <si>
+    <t>Zamosc_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Zamosc_POL</t>
+  </si>
+  <si>
     <t>Olsztyn_POL</t>
   </si>
   <si>
     <t>at grid node - Olsztyn_POL</t>
   </si>
   <si>
-    <t>Kielce_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Kielce_POL</t>
+    <t>Legnica_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Legnica_POL</t>
+  </si>
+  <si>
+    <t>OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>at grid node - OstrowiecSwietokrz_POL</t>
   </si>
   <si>
     <t>Grajewo_POL</t>
   </si>
   <si>
     <t>at grid node - Grajewo_POL</t>
-  </si>
-  <si>
-    <t>Elk_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Elk_POL</t>
-  </si>
-  <si>
-    <t>Zamosc_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Zamosc_POL</t>
-  </si>
-  <si>
-    <t>OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>at grid node - OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>Legnica_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Legnica_POL</t>
   </si>
   <si>
     <t>h_demand</t>
@@ -1102,13 +1102,13 @@
         <v>86</v>
       </c>
       <c r="M11" t="s">
-        <v>92</v>
+        <v>167</v>
       </c>
       <c r="N11" t="s">
-        <v>93</v>
+        <v>168</v>
       </c>
       <c r="O11" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q11" t="s">
         <v>86</v>
@@ -1164,13 +1164,13 @@
         <v>86</v>
       </c>
       <c r="M12" t="s">
-        <v>150</v>
+        <v>104</v>
       </c>
       <c r="N12" t="s">
-        <v>151</v>
+        <v>105</v>
       </c>
       <c r="O12" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q12" t="s">
         <v>86</v>
@@ -1226,13 +1226,13 @@
         <v>86</v>
       </c>
       <c r="M13" t="s">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="N13" t="s">
-        <v>95</v>
+        <v>123</v>
       </c>
       <c r="O13" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q13" t="s">
         <v>86</v>
@@ -1288,13 +1288,13 @@
         <v>86</v>
       </c>
       <c r="M14" t="s">
-        <v>168</v>
+        <v>144</v>
       </c>
       <c r="N14" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="O14" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q14" t="s">
         <v>86</v>
@@ -1350,13 +1350,13 @@
         <v>86</v>
       </c>
       <c r="M15" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="N15" t="s">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="O15" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q15" t="s">
         <v>86</v>
@@ -1412,13 +1412,13 @@
         <v>86</v>
       </c>
       <c r="M16" t="s">
-        <v>114</v>
+        <v>150</v>
       </c>
       <c r="N16" t="s">
-        <v>115</v>
+        <v>151</v>
       </c>
       <c r="O16" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q16" t="s">
         <v>86</v>
@@ -1474,13 +1474,13 @@
         <v>86</v>
       </c>
       <c r="M17" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="N17" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="O17" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q17" t="s">
         <v>86</v>
@@ -1536,13 +1536,13 @@
         <v>86</v>
       </c>
       <c r="M18" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="N18" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="O18" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q18" t="s">
         <v>86</v>
@@ -1604,7 +1604,7 @@
         <v>171</v>
       </c>
       <c r="O19" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q19" t="s">
         <v>86</v>
@@ -1660,13 +1660,13 @@
         <v>86</v>
       </c>
       <c r="M20" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="N20" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="O20" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q20" t="s">
         <v>86</v>
@@ -1722,13 +1722,13 @@
         <v>86</v>
       </c>
       <c r="M21" t="s">
-        <v>134</v>
+        <v>98</v>
       </c>
       <c r="N21" t="s">
-        <v>135</v>
+        <v>99</v>
       </c>
       <c r="O21" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q21" t="s">
         <v>86</v>
@@ -1784,13 +1784,13 @@
         <v>86</v>
       </c>
       <c r="M22" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="N22" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="O22" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q22" t="s">
         <v>86</v>
@@ -1846,13 +1846,13 @@
         <v>86</v>
       </c>
       <c r="M23" t="s">
-        <v>106</v>
+        <v>161</v>
       </c>
       <c r="N23" t="s">
-        <v>107</v>
+        <v>162</v>
       </c>
       <c r="O23" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q23" t="s">
         <v>86</v>
@@ -1908,13 +1908,13 @@
         <v>86</v>
       </c>
       <c r="M24" t="s">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="N24" t="s">
-        <v>133</v>
+        <v>160</v>
       </c>
       <c r="O24" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q24" t="s">
         <v>86</v>
@@ -1970,13 +1970,13 @@
         <v>86</v>
       </c>
       <c r="M25" t="s">
-        <v>172</v>
+        <v>120</v>
       </c>
       <c r="N25" t="s">
-        <v>173</v>
+        <v>121</v>
       </c>
       <c r="O25" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q25" t="s">
         <v>86</v>
@@ -2032,13 +2032,13 @@
         <v>86</v>
       </c>
       <c r="M26" t="s">
-        <v>174</v>
+        <v>132</v>
       </c>
       <c r="N26" t="s">
-        <v>175</v>
+        <v>133</v>
       </c>
       <c r="O26" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q26" t="s">
         <v>86</v>
@@ -2094,13 +2094,13 @@
         <v>86</v>
       </c>
       <c r="M27" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="N27" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="O27" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q27" t="s">
         <v>86</v>
@@ -2156,13 +2156,13 @@
         <v>86</v>
       </c>
       <c r="M28" t="s">
-        <v>176</v>
+        <v>148</v>
       </c>
       <c r="N28" t="s">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="O28" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q28" t="s">
         <v>86</v>
@@ -2218,13 +2218,13 @@
         <v>86</v>
       </c>
       <c r="M29" t="s">
-        <v>161</v>
+        <v>100</v>
       </c>
       <c r="N29" t="s">
-        <v>162</v>
+        <v>101</v>
       </c>
       <c r="O29" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q29" t="s">
         <v>86</v>
@@ -2280,13 +2280,13 @@
         <v>86</v>
       </c>
       <c r="M30" t="s">
-        <v>178</v>
+        <v>152</v>
       </c>
       <c r="N30" t="s">
-        <v>179</v>
+        <v>153</v>
       </c>
       <c r="O30" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q30" t="s">
         <v>86</v>
@@ -2342,13 +2342,13 @@
         <v>86</v>
       </c>
       <c r="M31" t="s">
-        <v>126</v>
+        <v>92</v>
       </c>
       <c r="N31" t="s">
-        <v>127</v>
+        <v>93</v>
       </c>
       <c r="O31" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q31" t="s">
         <v>86</v>
@@ -2404,13 +2404,13 @@
         <v>86</v>
       </c>
       <c r="M32" t="s">
-        <v>110</v>
+        <v>155</v>
       </c>
       <c r="N32" t="s">
-        <v>111</v>
+        <v>156</v>
       </c>
       <c r="O32" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q32" t="s">
         <v>86</v>
@@ -2466,13 +2466,13 @@
         <v>86</v>
       </c>
       <c r="M33" t="s">
-        <v>90</v>
+        <v>174</v>
       </c>
       <c r="N33" t="s">
-        <v>91</v>
+        <v>175</v>
       </c>
       <c r="O33" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q33" t="s">
         <v>86</v>
@@ -2528,13 +2528,13 @@
         <v>86</v>
       </c>
       <c r="M34" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="N34" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="O34" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q34" t="s">
         <v>86</v>
@@ -2590,13 +2590,13 @@
         <v>86</v>
       </c>
       <c r="M35" t="s">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="N35" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="O35" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q35" t="s">
         <v>86</v>
@@ -2652,13 +2652,13 @@
         <v>86</v>
       </c>
       <c r="M36" t="s">
-        <v>140</v>
+        <v>176</v>
       </c>
       <c r="N36" t="s">
-        <v>141</v>
+        <v>177</v>
       </c>
       <c r="O36" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q36" t="s">
         <v>86</v>
@@ -2714,13 +2714,13 @@
         <v>86</v>
       </c>
       <c r="M37" t="s">
-        <v>180</v>
+        <v>108</v>
       </c>
       <c r="N37" t="s">
-        <v>181</v>
+        <v>109</v>
       </c>
       <c r="O37" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q37" t="s">
         <v>86</v>
@@ -2776,13 +2776,13 @@
         <v>86</v>
       </c>
       <c r="M38" t="s">
-        <v>142</v>
+        <v>94</v>
       </c>
       <c r="N38" t="s">
-        <v>143</v>
+        <v>95</v>
       </c>
       <c r="O38" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q38" t="s">
         <v>86</v>
@@ -2838,13 +2838,13 @@
         <v>86</v>
       </c>
       <c r="M39" t="s">
-        <v>100</v>
+        <v>138</v>
       </c>
       <c r="N39" t="s">
-        <v>101</v>
+        <v>139</v>
       </c>
       <c r="O39" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="Q39" t="s">
         <v>86</v>
@@ -2900,13 +2900,13 @@
         <v>86</v>
       </c>
       <c r="M40" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="N40" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="O40" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="41" spans="2:25" x14ac:dyDescent="0.45">
@@ -2938,13 +2938,13 @@
         <v>86</v>
       </c>
       <c r="M41" t="s">
-        <v>108</v>
+        <v>157</v>
       </c>
       <c r="N41" t="s">
-        <v>109</v>
+        <v>158</v>
       </c>
       <c r="O41" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="42" spans="2:25" x14ac:dyDescent="0.45">
@@ -2976,13 +2976,13 @@
         <v>86</v>
       </c>
       <c r="M42" t="s">
-        <v>159</v>
+        <v>114</v>
       </c>
       <c r="N42" t="s">
-        <v>160</v>
+        <v>115</v>
       </c>
       <c r="O42" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="43" spans="2:25" x14ac:dyDescent="0.45">
@@ -3014,13 +3014,13 @@
         <v>86</v>
       </c>
       <c r="M43" t="s">
-        <v>182</v>
+        <v>140</v>
       </c>
       <c r="N43" t="s">
-        <v>183</v>
+        <v>141</v>
       </c>
       <c r="O43" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="44" spans="2:25" x14ac:dyDescent="0.45">
@@ -3040,13 +3040,13 @@
         <v>86</v>
       </c>
       <c r="M44" t="s">
-        <v>152</v>
+        <v>178</v>
       </c>
       <c r="N44" t="s">
-        <v>153</v>
+        <v>179</v>
       </c>
       <c r="O44" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.45">
@@ -3066,13 +3066,13 @@
         <v>86</v>
       </c>
       <c r="M45" t="s">
-        <v>144</v>
+        <v>90</v>
       </c>
       <c r="N45" t="s">
-        <v>145</v>
+        <v>91</v>
       </c>
       <c r="O45" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="46" spans="2:25" x14ac:dyDescent="0.45">
@@ -3092,13 +3092,13 @@
         <v>86</v>
       </c>
       <c r="M46" t="s">
-        <v>98</v>
+        <v>180</v>
       </c>
       <c r="N46" t="s">
-        <v>99</v>
+        <v>181</v>
       </c>
       <c r="O46" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="47" spans="2:25" x14ac:dyDescent="0.45">
@@ -3118,13 +3118,13 @@
         <v>86</v>
       </c>
       <c r="M47" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="N47" t="s">
-        <v>117</v>
+        <v>131</v>
       </c>
       <c r="O47" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="48" spans="2:25" x14ac:dyDescent="0.45">
@@ -3144,13 +3144,13 @@
         <v>86</v>
       </c>
       <c r="M48" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="N48" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="O48" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="49" spans="7:15" x14ac:dyDescent="0.45">
@@ -3170,13 +3170,13 @@
         <v>86</v>
       </c>
       <c r="M49" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="N49" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="O49" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="50" spans="7:15" x14ac:dyDescent="0.45">
@@ -3184,13 +3184,13 @@
         <v>86</v>
       </c>
       <c r="M50" t="s">
-        <v>165</v>
+        <v>126</v>
       </c>
       <c r="N50" t="s">
-        <v>166</v>
+        <v>127</v>
       </c>
       <c r="O50" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="51" spans="7:15" x14ac:dyDescent="0.45">
@@ -3198,13 +3198,13 @@
         <v>86</v>
       </c>
       <c r="M51" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="N51" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="O51" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="52" spans="7:15" x14ac:dyDescent="0.45">
@@ -3212,13 +3212,13 @@
         <v>86</v>
       </c>
       <c r="M52" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="N52" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O52" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="53" spans="7:15" x14ac:dyDescent="0.45">
@@ -3226,13 +3226,13 @@
         <v>86</v>
       </c>
       <c r="M53" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="N53" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="O53" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="54" spans="7:15" x14ac:dyDescent="0.45">
@@ -3240,13 +3240,13 @@
         <v>86</v>
       </c>
       <c r="M54" t="s">
-        <v>146</v>
+        <v>87</v>
       </c>
       <c r="N54" t="s">
-        <v>147</v>
+        <v>88</v>
       </c>
       <c r="O54" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="55" spans="7:15" x14ac:dyDescent="0.45">
@@ -3254,13 +3254,13 @@
         <v>86</v>
       </c>
       <c r="M55" t="s">
-        <v>155</v>
+        <v>102</v>
       </c>
       <c r="N55" t="s">
-        <v>156</v>
+        <v>103</v>
       </c>
       <c r="O55" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="56" spans="7:15" x14ac:dyDescent="0.45">
@@ -3268,13 +3268,13 @@
         <v>86</v>
       </c>
       <c r="M56" t="s">
-        <v>184</v>
+        <v>163</v>
       </c>
       <c r="N56" t="s">
-        <v>185</v>
+        <v>164</v>
       </c>
       <c r="O56" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="57" spans="7:15" x14ac:dyDescent="0.45">
@@ -3282,13 +3282,13 @@
         <v>86</v>
       </c>
       <c r="M57" t="s">
-        <v>96</v>
+        <v>182</v>
       </c>
       <c r="N57" t="s">
-        <v>97</v>
+        <v>183</v>
       </c>
       <c r="O57" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="58" spans="7:15" x14ac:dyDescent="0.45">
@@ -3296,13 +3296,13 @@
         <v>86</v>
       </c>
       <c r="M58" t="s">
-        <v>118</v>
+        <v>184</v>
       </c>
       <c r="N58" t="s">
-        <v>119</v>
+        <v>185</v>
       </c>
       <c r="O58" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>

--- a/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
+++ b/VerveStacks_POL_grids_kan50/SubRES_Tmpl/SubRES_New_RE_and_Conventional_Trans.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan50\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32D136AD-76BB-432D-8FF5-B539730FAD58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06207D76-FEBF-44F4-BE86-8127EF830D95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="368" yWindow="368" windowWidth="21599" windowHeight="12772" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -541,61 +541,61 @@
     <t>at grid node - Krosno_POL</t>
   </si>
   <si>
+    <t>Legnica_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Legnica_POL</t>
+  </si>
+  <si>
+    <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
+  </si>
+  <si>
+    <t>Grajewo_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Grajewo_POL</t>
+  </si>
+  <si>
+    <t>Kielce_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Kielce_POL</t>
+  </si>
+  <si>
+    <t>Slupsk_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Slupsk_POL</t>
+  </si>
+  <si>
+    <t>OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>at grid node - OstrowiecSwietokrz_POL</t>
+  </si>
+  <si>
+    <t>Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Olsztyn_POL</t>
+  </si>
+  <si>
+    <t>Elk_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Elk_POL</t>
+  </si>
+  <si>
+    <t>Zamosc_POL</t>
+  </si>
+  <si>
+    <t>at grid node - Zamosc_POL</t>
+  </si>
+  <si>
     <t>Chelm_POL</t>
   </si>
   <si>
     <t>at grid node - Chelm_POL</t>
-  </si>
-  <si>
-    <t>e_demand,ev_battery,H2prd_Elc_PEM,H2prd_Elc_ALK</t>
-  </si>
-  <si>
-    <t>Elk_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Elk_POL</t>
-  </si>
-  <si>
-    <t>Slupsk_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Slupsk_POL</t>
-  </si>
-  <si>
-    <t>Kielce_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Kielce_POL</t>
-  </si>
-  <si>
-    <t>Zamosc_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Zamosc_POL</t>
-  </si>
-  <si>
-    <t>Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Olsztyn_POL</t>
-  </si>
-  <si>
-    <t>Legnica_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Legnica_POL</t>
-  </si>
-  <si>
-    <t>OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>at grid node - OstrowiecSwietokrz_POL</t>
-  </si>
-  <si>
-    <t>Grajewo_POL</t>
-  </si>
-  <si>
-    <t>at grid node - Grajewo_POL</t>
   </si>
   <si>
     <t>h_demand</t>
@@ -1164,10 +1164,10 @@
         <v>86</v>
       </c>
       <c r="M12" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="N12" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="O12" t="s">
         <v>169</v>
@@ -1226,10 +1226,10 @@
         <v>86</v>
       </c>
       <c r="M13" t="s">
-        <v>122</v>
+        <v>170</v>
       </c>
       <c r="N13" t="s">
-        <v>123</v>
+        <v>171</v>
       </c>
       <c r="O13" t="s">
         <v>169</v>
@@ -1288,10 +1288,10 @@
         <v>86</v>
       </c>
       <c r="M14" t="s">
-        <v>144</v>
+        <v>172</v>
       </c>
       <c r="N14" t="s">
-        <v>145</v>
+        <v>173</v>
       </c>
       <c r="O14" t="s">
         <v>169</v>
@@ -1350,10 +1350,10 @@
         <v>86</v>
       </c>
       <c r="M15" t="s">
-        <v>128</v>
+        <v>94</v>
       </c>
       <c r="N15" t="s">
-        <v>129</v>
+        <v>95</v>
       </c>
       <c r="O15" t="s">
         <v>169</v>
@@ -1412,10 +1412,10 @@
         <v>86</v>
       </c>
       <c r="M16" t="s">
-        <v>150</v>
+        <v>116</v>
       </c>
       <c r="N16" t="s">
-        <v>151</v>
+        <v>117</v>
       </c>
       <c r="O16" t="s">
         <v>169</v>
@@ -1474,10 +1474,10 @@
         <v>86</v>
       </c>
       <c r="M17" t="s">
-        <v>124</v>
+        <v>174</v>
       </c>
       <c r="N17" t="s">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="O17" t="s">
         <v>169</v>
@@ -1536,10 +1536,10 @@
         <v>86</v>
       </c>
       <c r="M18" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="N18" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="O18" t="s">
         <v>169</v>
@@ -1598,10 +1598,10 @@
         <v>86</v>
       </c>
       <c r="M19" t="s">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="N19" t="s">
-        <v>171</v>
+        <v>141</v>
       </c>
       <c r="O19" t="s">
         <v>169</v>
@@ -1660,10 +1660,10 @@
         <v>86</v>
       </c>
       <c r="M20" t="s">
-        <v>116</v>
+        <v>144</v>
       </c>
       <c r="N20" t="s">
-        <v>117</v>
+        <v>145</v>
       </c>
       <c r="O20" t="s">
         <v>169</v>
@@ -1722,10 +1722,10 @@
         <v>86</v>
       </c>
       <c r="M21" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="N21" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="O21" t="s">
         <v>169</v>
@@ -1784,10 +1784,10 @@
         <v>86</v>
       </c>
       <c r="M22" t="s">
-        <v>172</v>
+        <v>124</v>
       </c>
       <c r="N22" t="s">
-        <v>173</v>
+        <v>125</v>
       </c>
       <c r="O22" t="s">
         <v>169</v>
@@ -1846,10 +1846,10 @@
         <v>86</v>
       </c>
       <c r="M23" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="N23" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="O23" t="s">
         <v>169</v>
@@ -1908,10 +1908,10 @@
         <v>86</v>
       </c>
       <c r="M24" t="s">
-        <v>159</v>
+        <v>92</v>
       </c>
       <c r="N24" t="s">
-        <v>160</v>
+        <v>93</v>
       </c>
       <c r="O24" t="s">
         <v>169</v>
@@ -1970,10 +1970,10 @@
         <v>86</v>
       </c>
       <c r="M25" t="s">
-        <v>120</v>
+        <v>176</v>
       </c>
       <c r="N25" t="s">
-        <v>121</v>
+        <v>177</v>
       </c>
       <c r="O25" t="s">
         <v>169</v>
@@ -2032,10 +2032,10 @@
         <v>86</v>
       </c>
       <c r="M26" t="s">
-        <v>132</v>
+        <v>157</v>
       </c>
       <c r="N26" t="s">
-        <v>133</v>
+        <v>158</v>
       </c>
       <c r="O26" t="s">
         <v>169</v>
@@ -2094,10 +2094,10 @@
         <v>86</v>
       </c>
       <c r="M27" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="N27" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="O27" t="s">
         <v>169</v>
@@ -2156,10 +2156,10 @@
         <v>86</v>
       </c>
       <c r="M28" t="s">
-        <v>148</v>
+        <v>114</v>
       </c>
       <c r="N28" t="s">
-        <v>149</v>
+        <v>115</v>
       </c>
       <c r="O28" t="s">
         <v>169</v>
@@ -2218,10 +2218,10 @@
         <v>86</v>
       </c>
       <c r="M29" t="s">
-        <v>100</v>
+        <v>138</v>
       </c>
       <c r="N29" t="s">
-        <v>101</v>
+        <v>139</v>
       </c>
       <c r="O29" t="s">
         <v>169</v>
@@ -2280,10 +2280,10 @@
         <v>86</v>
       </c>
       <c r="M30" t="s">
-        <v>152</v>
+        <v>178</v>
       </c>
       <c r="N30" t="s">
-        <v>153</v>
+        <v>179</v>
       </c>
       <c r="O30" t="s">
         <v>169</v>
@@ -2342,10 +2342,10 @@
         <v>86</v>
       </c>
       <c r="M31" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="N31" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="O31" t="s">
         <v>169</v>
@@ -2404,10 +2404,10 @@
         <v>86</v>
       </c>
       <c r="M32" t="s">
-        <v>155</v>
+        <v>130</v>
       </c>
       <c r="N32" t="s">
-        <v>156</v>
+        <v>131</v>
       </c>
       <c r="O32" t="s">
         <v>169</v>
@@ -2466,10 +2466,10 @@
         <v>86</v>
       </c>
       <c r="M33" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="N33" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="O33" t="s">
         <v>169</v>
@@ -2528,10 +2528,10 @@
         <v>86</v>
       </c>
       <c r="M34" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="N34" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="O34" t="s">
         <v>169</v>
@@ -2590,10 +2590,10 @@
         <v>86</v>
       </c>
       <c r="M35" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
       <c r="N35" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="O35" t="s">
         <v>169</v>
@@ -2652,10 +2652,10 @@
         <v>86</v>
       </c>
       <c r="M36" t="s">
-        <v>176</v>
+        <v>98</v>
       </c>
       <c r="N36" t="s">
-        <v>177</v>
+        <v>99</v>
       </c>
       <c r="O36" t="s">
         <v>169</v>
@@ -2714,10 +2714,10 @@
         <v>86</v>
       </c>
       <c r="M37" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="N37" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="O37" t="s">
         <v>169</v>
@@ -2776,10 +2776,10 @@
         <v>86</v>
       </c>
       <c r="M38" t="s">
-        <v>94</v>
+        <v>136</v>
       </c>
       <c r="N38" t="s">
-        <v>95</v>
+        <v>137</v>
       </c>
       <c r="O38" t="s">
         <v>169</v>
@@ -2838,10 +2838,10 @@
         <v>86</v>
       </c>
       <c r="M39" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="N39" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="O39" t="s">
         <v>169</v>
@@ -2900,10 +2900,10 @@
         <v>86</v>
       </c>
       <c r="M40" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="N40" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="O40" t="s">
         <v>169</v>
@@ -2938,10 +2938,10 @@
         <v>86</v>
       </c>
       <c r="M41" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="N41" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="O41" t="s">
         <v>169</v>
@@ -2976,10 +2976,10 @@
         <v>86</v>
       </c>
       <c r="M42" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="N42" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="O42" t="s">
         <v>169</v>
@@ -3014,10 +3014,10 @@
         <v>86</v>
       </c>
       <c r="M43" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="N43" t="s">
-        <v>141</v>
+        <v>101</v>
       </c>
       <c r="O43" t="s">
         <v>169</v>
@@ -3040,10 +3040,10 @@
         <v>86</v>
       </c>
       <c r="M44" t="s">
-        <v>178</v>
+        <v>122</v>
       </c>
       <c r="N44" t="s">
-        <v>179</v>
+        <v>123</v>
       </c>
       <c r="O44" t="s">
         <v>169</v>
@@ -3066,10 +3066,10 @@
         <v>86</v>
       </c>
       <c r="M45" t="s">
-        <v>90</v>
+        <v>146</v>
       </c>
       <c r="N45" t="s">
-        <v>91</v>
+        <v>147</v>
       </c>
       <c r="O45" t="s">
         <v>169</v>
@@ -3092,10 +3092,10 @@
         <v>86</v>
       </c>
       <c r="M46" t="s">
-        <v>180</v>
+        <v>112</v>
       </c>
       <c r="N46" t="s">
-        <v>181</v>
+        <v>113</v>
       </c>
       <c r="O46" t="s">
         <v>169</v>
@@ -3118,10 +3118,10 @@
         <v>86</v>
       </c>
       <c r="M47" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="N47" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="O47" t="s">
         <v>169</v>
@@ -3144,10 +3144,10 @@
         <v>86</v>
       </c>
       <c r="M48" t="s">
-        <v>112</v>
+        <v>180</v>
       </c>
       <c r="N48" t="s">
-        <v>113</v>
+        <v>181</v>
       </c>
       <c r="O48" t="s">
         <v>169</v>
@@ -3170,10 +3170,10 @@
         <v>86</v>
       </c>
       <c r="M49" t="s">
-        <v>118</v>
+        <v>148</v>
       </c>
       <c r="N49" t="s">
-        <v>119</v>
+        <v>149</v>
       </c>
       <c r="O49" t="s">
         <v>169</v>
@@ -3184,10 +3184,10 @@
         <v>86</v>
       </c>
       <c r="M50" t="s">
-        <v>126</v>
+        <v>159</v>
       </c>
       <c r="N50" t="s">
-        <v>127</v>
+        <v>160</v>
       </c>
       <c r="O50" t="s">
         <v>169</v>
@@ -3198,10 +3198,10 @@
         <v>86</v>
       </c>
       <c r="M51" t="s">
-        <v>142</v>
+        <v>182</v>
       </c>
       <c r="N51" t="s">
-        <v>143</v>
+        <v>183</v>
       </c>
       <c r="O51" t="s">
         <v>169</v>
@@ -3212,10 +3212,10 @@
         <v>86</v>
       </c>
       <c r="M52" t="s">
-        <v>165</v>
+        <v>134</v>
       </c>
       <c r="N52" t="s">
-        <v>166</v>
+        <v>135</v>
       </c>
       <c r="O52" t="s">
         <v>169</v>
@@ -3226,10 +3226,10 @@
         <v>86</v>
       </c>
       <c r="M53" t="s">
-        <v>134</v>
+        <v>87</v>
       </c>
       <c r="N53" t="s">
-        <v>135</v>
+        <v>88</v>
       </c>
       <c r="O53" t="s">
         <v>169</v>
@@ -3240,10 +3240,10 @@
         <v>86</v>
       </c>
       <c r="M54" t="s">
-        <v>87</v>
+        <v>184</v>
       </c>
       <c r="N54" t="s">
-        <v>88</v>
+        <v>185</v>
       </c>
       <c r="O54" t="s">
         <v>169</v>
@@ -3268,10 +3268,10 @@
         <v>86</v>
       </c>
       <c r="M56" t="s">
-        <v>163</v>
+        <v>126</v>
       </c>
       <c r="N56" t="s">
-        <v>164</v>
+        <v>127</v>
       </c>
       <c r="O56" t="s">
         <v>169</v>
@@ -3282,10 +3282,10 @@
         <v>86</v>
       </c>
       <c r="M57" t="s">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="N57" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="O57" t="s">
         <v>169</v>
@@ -3296,10 +3296,10 @@
         <v>86</v>
       </c>
       <c r="M58" t="s">
-        <v>184</v>
+        <v>155</v>
       </c>
       <c r="N58" t="s">
-        <v>185</v>
+        <v>156</v>
       </c>
       <c r="O58" t="s">
         <v>169</v>
